--- a/ai-player/goal-table/小麦家族工作分解-填写版.xlsx
+++ b/ai-player/goal-table/小麦家族工作分解-填写版.xlsx
@@ -50,7 +50,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -72,6 +72,11 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -85,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -104,6 +109,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -668,7 +676,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
@@ -896,12 +904,12 @@
     <row r="19">
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>M3-1</t>
+          <t>M1-3</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>小麦替新家找一块地：离出生点 300~600 格；附近 64 格没有别人放的方块、没有领地；32 格内没有村庄或别人的建筑；地面平、没有树挡着；紧挨着没有水（否则安不了家）；24 格内有水，留着以后种田。</t>
+          <t>「收麦子 → 做面包 → 多出来的面包放进粮箱」这条路完整走通一圈：粮箱里至少有 3 个面包。</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
@@ -912,45 +920,49 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>J-M3-1</t>
+          <t>J-M1-4, wife_bread, wife_craft_chest, wife_get_crop_chest, wife_store_crop</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr"/>
+          <t>麦娘</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>M1-2</t>
+        </is>
+      </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>新家址已选定 = 1 并且 新家址离出生点 ≥ 300 并且 新家址离出生点 ≤ 600 并且 新家址64格内别人放的方块数 = 0 并且 新家址64格内领地数 = 0 并且 新家址32格内人造方块数 = 0 并且 新家址地面高低差 ≤ 1 并且 新家址地基上方障碍格数 = 0 并且 新家址3格内有水 = 0 并且 新家址24格内水源格数 ≥ 1 并且 新家址地面高度 ≥ 64 并且 新家址在主世界 = 1</t>
+          <t>有粮箱 ≥ 1 并且 粮箱里的面包 ≥ 3</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>300 格约是 10 区块视距（160 格）的两倍，从出生点完全看不到。出生点在 (8,15)；孩子们的住宅区在 (85,219) 一带，也在出生点南边。初稿「沿出生点→旧家方向延长、再偏 ±45°」一路朝南，偏东那一步几乎正对孩子们那片，所以方向要按足迹数据挑。孩子的远方基地可能在很远的地方（例如 -5300,-4300），「离别人远」以足迹为准，不以离出生点多远为准。重生顺序是「床 → 家 → 出生点」，小麦现在的重生点是村庄那张床 (-73,72,106)，路上死了会在那里醒。</t>
+          <t>面包 = 3 小麦横排、箱子 = 8 木板，都要工作台；田离家远的话，做面包的地方 32 格内要有工作台，或者她身上带一张（4 木板）。store_crop 会让她身上留 3 个面包、9 个小麦、16 颗种子，多的才进粮箱；9 格田一茬只出 9 个小麦 = 3 个面包，正好被她自己留下，所以粮箱要到第 2~3 茬才见得到面包——湿地约 1.5~2.5 小时，干地约 3.5~5 小时，这是正常的，不是卡住。收割用 J-M1-4（收完当场补种），wife_harvest 关掉或降成备用。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>M3-2</t>
+          <t>M1-4</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>麦娘按选定的木头样式，把盖房的结构材料备齐、放进共用箱子：木板 163 块（墙 82 + 屋顶 81）、做柱子的原木 12 根、木半砖 49 块、门 1 扇。</t>
+          <t>收完的地不空着：最近一小时里，每一格收完或被踩坏的地都在 3 分钟内重新种上，身上常备够补一整块田的种子。</t>
         </is>
       </c>
       <c r="D20" s="7" t="n">
@@ -961,12 +973,12 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>J-G3-0a, J-M3-2</t>
+          <t>J-M1-2, J-M1-4, wife_find_seeds, wife_gather_seeds, wife_harvest, wife_plant</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
@@ -974,32 +986,36 @@
           <t>麦娘</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr"/>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>M1-2</t>
+        </is>
+      </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>新房木板缺口 = 0 并且 新房原木缺口 = 0 并且 新房半砖缺口 = 0 并且 新房门缺口 = 0</t>
+          <t>补种最长等待秒数_新口径 ≤ 180 并且 有种子 ≥ 9</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
-          <t>1 根原木 = 4 块木板；半砖是 3 块木板出 6 块，门是 6 块同种木板出 3 扇，两样都要工作台（3 格宽的配方），craft 要能在旧家附近找到或摆出工作台。同一扇门、同一批半砖都必须用同一种木板。结构总共 196 木板（49 根原木）加 12 根柱子原木。地基补平的用料要等选完地才知道，不算在这里，由 J-M3-3 现拿现做。库存：橡木 232 根，什么组合都够；樱花 83 根 = 332 木板，墙 + 屋顶（163）一起都够；桦木 28 根 = 112 木板，够墙或屋顶其中一样。旧判据「房子还要料」「盖房的材料够吗」保持原来的意思，不改成新计划（改了会让旧脚本乱开工）。</t>
+          <t>熟麦每格掉 1 个小麦 + 1~4 颗种子（平均约 2.7），种回去 1 颗还净多约 1.7，种子越收越多。干地的空耕地平均约 68 秒就退回泥土，补种要快；湿地不会退，但空着也不长。M1-3 和 M1-4 同级、都是麦娘的，同时有两件以上能开工、而且组合是新的时，由 T1 让模型挑一次。🔴 零候选审计：原来的「补种最长等待秒数」在 60 分钟内一格都没空过时返回 9999——这时田是满的、根本没活，这条却一直算「没完成」，挂在它下面的 J-M1-2 会走到田里什么也不做就算完，来回空转。完成标准换成新口径（C-FRM-23）：60 分钟内没空过 → 0（没有要等的）；麦娘不在线或田没加载 → 沿用上一次的值。另外 M1-1（种子 ≥ 9）是 M1-2 的前置、M1-2 又是这条的前置：9 颗种子一种下去 M1-1 就变回没完成，收割（正是补种子的路）反而被卡住，所以前置按「完成过」算（C-ENG-22）。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>M4-1</t>
+          <t>M1-8</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>找到至少 1 处合格的新家址(Owner 也可以在后台直接填坐标)</t>
+          <t>田里熟了的麦子不放着：熟了就收，收完当场种回去，小麦和种子存进粮箱；麦豆在妈妈忙别的时帮她收。</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
@@ -1010,23 +1026,27 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>J-M4-1</t>
+          <t>J-M1-4, J-M1-8, J-M1-8c, J-M1-8d, wife_harvest, wife_plant</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>G4</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr"/>
+          <t>麦娘, 麦豆</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>M1-2</t>
+        </is>
+      </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>合格候选家址数 ≥ 1</t>
+          <t>该收割了 = 0</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
@@ -1034,17 +1054,21 @@
           <t>判据动作都缺</t>
         </is>
       </c>
-      <c r="L21" s="7" t="inlineStr"/>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>🔴 零候选审计补的：原来没有任何小目标管「熟了就收」——M1-2 管种满，M1-4 管收完补种，M1-3 只管粮箱第一次有 3 个面包，麦子熟了不会让任何一条变回没完成。完成标准和两条脚本的开工都调同一个「该收割了」（门槛按田的大小自动在 3~16 之间），不再是原稿的「≤ 2 / ≥ 3 / ≥ 6」三个数——那样熟了 3~15 格时这条算没完成，却谁也开不了工。🔴 两人不会同时收：谁先动手谁拿「田里收割锁」，另一个人这一步跳过、不算失败。所以麦豆是在妈妈忙别的（做面包、存东西、扩田）时帮她收，不会跟她抢同一块田。麦豆存进粮箱的小麦由麦娘的 J-M1-9 拿去做面包。64 格湿地平均不到 1 分钟就熟一格，这条经常重开，是麦娘和麦豆的常驻活。harvest_crop 只动登记簿里的格子；不踩田的护栏 09-18 已经上线。</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>M5-1</t>
+          <t>M3-1</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>每个会打架的在线家人手上都有一把剑(麦豆只跑不打,不算)</t>
+          <t>小麦替新家找一块地：离出生点 300~600 格；附近 64 格没有别人放的方块、没有领地；32 格内没有村庄或别人的建筑；地面平、没有树挡着；紧挨着没有水（否则安不了家）；24 格内有水，留着以后种田。</t>
         </is>
       </c>
       <c r="D22" s="7" t="n">
@@ -1055,45 +1079,45 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>make_sword</t>
+          <t>J-M3-1</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>G5</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>任意</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr"/>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>在线会打架的家人里没剑的人数 = 0</t>
+          <t>新家址已选定 = 1 并且 新家址离出生点 ≥ 300 并且 新家址离出生点 ≤ 600 并且 新家址64格内别人放的方块数 = 0 并且 新家址64格内领地数 = 0 并且 新家址32格内人造方块数 = 0 并且 新家址地面高低差 ≤ 1 并且 新家址地基上方障碍格数 = 0 并且 新家址3格内有水 = 0 并且 新家址24格内水源格数 ≥ 1 并且 新家址地面高度 ≥ 64 并且 新家址在主世界 = 1</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>「在线家人里没剑的人数」只数 roles.json 能做的动作里有 fight 的在线家人(现在只有小麦;麦娘等 C-PRM-6 放行后自动算进来)。麦豆只跑不打,给他剑没用,也不能让这条因为他永远完不成。剑数读家族状态板(C-FAM-1),C-DAT-5 的 held_&lt;角色&gt; 并进状态板,口径同 C-FAM-12(剑种当参数,M5-4、M5-6 用同一个函数)。家里谁手上有用不上的剑(比如麦娘做的、麦豆捡的),由 A23 直接送到缺剑的人手上;make_sword 只在全家都没有多余的剑时才需要开工。</t>
+          <t>300 格约是 10 区块视距（160 格）的两倍，从出生点完全看不到。出生点在 (8,15)；孩子们的住宅区在 (85,219) 一带，也在出生点南边。初稿「沿出生点→旧家方向延长、再偏 ±45°」一路朝南，偏东那一步几乎正对孩子们那片，所以方向要按足迹数据挑。孩子的远方基地可能在很远的地方（例如 -5300,-4300），「离别人远」以足迹为准，不以离出生点多远为准。重生顺序是「床 → 家 → 出生点」，小麦现在的重生点是村庄那张床 (-73,72,106)，路上死了会在那里醒。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>M6-1</t>
+          <t>M4-1</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>共用箱子里一直留着至少 9 个空格</t>
+          <t>找到至少 1 处合格的新家址(Owner 也可以在后台直接填坐标)</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
@@ -1104,45 +1128,41 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>wife_craft_chest</t>
+          <t>J-M4-1</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>G6</t>
+          <t>G4</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>麦娘</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr"/>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>共用箱子空格 ≥ 9</t>
+          <t>合格候选家址数 ≥ 1</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
-        </is>
-      </c>
-      <c r="L23" s="7" t="inlineStr">
-        <is>
-          <t>箱子 = 8 木板。搬家前只在现有箱子旁边拼成大箱,不在出生点旁另开地方</t>
-        </is>
-      </c>
+          <t>判据动作都缺</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>M7-1</t>
+          <t>M5-1</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>近 1 小时麦豆离家最远不超过 64 格</t>
+          <t>每个会打架的在线家人手上都有一把剑(麦豆只跑不打,不算)</t>
         </is>
       </c>
       <c r="D24" s="7" t="n">
@@ -1153,23 +1173,23 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>child_home, child_watch_dad</t>
+          <t>guard_home, make_sword</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>麦豆</t>
+          <t>任意</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr"/>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>近1小时麦豆离家最远距离 ≤ 64</t>
+          <t>在线会打架的家人里没剑的人数 = 0</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr">
@@ -1177,17 +1197,21 @@
           <t>缺判据</t>
         </is>
       </c>
-      <c r="L24" s="7" t="inlineStr"/>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>⏳ 过渡:guard_home(家门口赶怪)本属状态维持 A18,2a 只按小目标派活,先挂这里保证不丢;2b 状态维持能派活后从这里摘掉。 「在线家人里没剑的人数」只数 roles.json 能做的动作里有 fight 的在线家人(现在只有小麦;麦娘等 C-PRM-6 放行后自动算进来)。麦豆只跑不打,给他剑没用,也不能让这条因为他永远完不成。剑数读家族状态板(C-FAM-1),C-DAT-5 的 held_&lt;角色&gt; 并进状态板,口径同 C-FAM-12(剑种当参数,M5-4、M5-6 用同一个函数)。家里谁手上有用不上的剑(比如麦娘做的、麦豆捡的),由 A23 直接送到缺剑的人手上;make_sword 只在全家都没有多余的剑时才需要开工。</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>M7-2</t>
+          <t>M6-1</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>麦豆近 24 小时一次没死</t>
+          <t>共用箱子里一直留着至少 9 个空格</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
@@ -1198,23 +1222,23 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>child_home, child_play</t>
+          <t>make_base, wife_craft_chest, wife_store</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>G6</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>麦豆</t>
+          <t>麦娘, 小麦</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr"/>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>近24小时麦豆死亡次数 = 0</t>
+          <t>共用箱子空格 ≥ 9</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr">
@@ -1222,17 +1246,21 @@
           <t>缺判据</t>
         </is>
       </c>
-      <c r="L25" s="7" t="inlineStr"/>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>箱子 = 8 木板。搬家前只在现有箱子旁边拼成大箱,不在出生点旁另开地方</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>M7-4</t>
+          <t>M7-1</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>麦豆没被点名时,离真人玩家至少 16 格</t>
+          <t>近 1 小时麦豆离家最远不超过 64 格</t>
         </is>
       </c>
       <c r="D26" s="7" t="n">
@@ -1243,7 +1271,7 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>J-M7-4</t>
+          <t>child_home</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
@@ -1259,7 +1287,7 @@
       <c r="I26" s="7" t="inlineStr"/>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>近1小时未被点名时离真人玩家最近距离 ≥ 16</t>
+          <t>近1小时麦豆离家最远距离 ≤ 64</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr">
@@ -1375,7 +1403,7 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>麦娘手上有一把锄头、身上有至少 9 颗小麦种子，开第一块田的家伙齐了。</t>
+          <t>麦娘手上有一把锄头、身上有至少 3 颗小麦种子，开第一块田的家伙齐了。</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
@@ -1402,7 +1430,7 @@
       <c r="I29" s="7" t="inlineStr"/>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>有锄头 ≥ 1 并且 有种子 ≥ 9</t>
+          <t>有锄头 ≥ 1 并且 有种子 ≥ 3</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
@@ -1419,12 +1447,12 @@
     <row r="30">
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>M2-1</t>
+          <t>M1-2</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>做出 3 张床（小麦、麦娘、麦豆各一张）：先用箱子里现成的线合成白羊毛来做，线不够时再由小麦打羊兜底</t>
+          <t>在选好的田址上开出第一块 9 格麦田：9 格都锄好、都种上麦子，一格不空。</t>
         </is>
       </c>
       <c r="D30" s="7" t="n">
@@ -1435,23 +1463,27 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>J-M2-1-1, J-M2-1-2</t>
+          <t>J-M1-2, wife_plant, wife_till</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>G2</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>麦娘（主）/ 小麦（兜底）</t>
-        </is>
-      </c>
-      <c r="I30" s="7" t="inlineStr"/>
+          <t>麦娘</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>M1-0, M1-1</t>
+        </is>
+      </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>全家床数 ≥ 3</t>
+          <t>耕好的地 ≥ 9 并且 空着的耕地 = 0</t>
         </is>
       </c>
       <c r="K30" s="7" t="inlineStr">
@@ -1461,19 +1493,19 @@
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
-          <t>1.21.4 配方：4 根线在 2×2 格里合 1 块白羊毛（white_wool_from_string，背包里就能合，这条没实测过）。48 根线 = 12 块白羊毛 = 4 张床，3 张床用掉 36 根。床 = 3 块同色羊毛 + 3 块木板，3 格宽，必须用工作台。游戏本身允许混种木板，但机器人用的合成库要 3 块同种，所以按同种准备。没有剪毛动作，打死一只羊掉 1 块羊毛，颜色随羊：白约 82%，黑/灰/淡灰各 5%，棕 3%，粉 0.16%；凑 3 块同色平均要打 3~4 只。没有繁殖动作，羊越打越少；09-17 查过，家 48 格内没有羊。做好的床在 STORE_NEVER（永远不存进箱子）名单里，会一直在做床的人身上，直到摆下去。</t>
+          <t>水边田址上刚锄好的湿耕地不会退回泥土，所以「锄一批再种」没问题；只有 Owner 选了家门口干地时，才会碰到「锄好约 1 分钟就变回泥土」，那时由 J-M1-2 下一轮把退回的格子重锄重种，慢慢凑满。wife_till 关掉（开 = false），它要先锄满 9 格才轮到播种。作物要亮度 ≥ 9 才长、≥ 8 或头顶见天才种得活；露天的田夜里也照长。从高处跳下落到耕地上（下落超过半格）会把它踩回泥土、麦子掉出来——孩子们和寻路时的机器人都可能踩，被踩的格子由登记簿记成「空」，交给 J-M1-2 补。完成状态每次重算：哪格空了，M1-2 自动回到没完成，J-M1-2 再开工补上。🔴 前置 M1-0 标成「必须现在成立」（C-ENG-22 的例外）：家搬走、田址失效时，不能继续在 300 格外的旧田上干（旁边没人，庄稼也不长），要等新田址定下来；M1-1 仍按「完成过」算（种子一种下去就少于 9 颗，按现在算会把自己卡死）。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>M2-2</t>
+          <t>M2-1</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>新房子里要空出能放 3 张床、还留一条走道的地方（现在的 4×4 泥土房屋里只有 2×2 共 4 格，放 2 张床就没地方站）。活归 G3 的盖新房子，这里只负责验收</t>
+          <t>做出 3 张床（小麦、麦娘、麦豆各一张）：先用箱子里现成的线合成白羊毛来做，线不够时再由小麦打羊兜底</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
@@ -1482,7 +1514,11 @@
       <c r="E31" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F31" s="7" t="inlineStr"/>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>J-M2-1-1, J-M2-1-2</t>
+        </is>
+      </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
           <t>G2</t>
@@ -1490,17 +1526,13 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
-        </is>
-      </c>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>M3-1</t>
-        </is>
-      </c>
+          <t>麦娘（主）/ 小麦（兜底）</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr"/>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>房子盖好了 = 1 并且 屋里床位总数 ≥ 3</t>
+          <t>全家床数 ≥ 3</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr">
@@ -1510,19 +1542,19 @@
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>M3-1 指 G3 里「新房子盖好」那一条，编号以 G3 定稿为准。加「房子盖好了=1」是因为墙和屋顶没完成的框架里，空格也会被数成床位。床占 2 格（床头加床尾）。3 张床要 6 格，再加一排走道，所以屋内至少 3×3。床只能放在主世界，下界和末地一放就爆。现在不圈地，别人可以拆掉我们的床，所以「家里摆着的床」每次都要实地扫，不能只信记录。屋外一律不摆床。新房子要离出生点和孩子们的建筑远一些（Owner 已经说过现在太近），这一条归 G3。</t>
+          <t>1.21.4 配方：4 根线在 2×2 格里合 1 块白羊毛（white_wool_from_string，背包里就能合，这条没实测过）。48 根线 = 12 块白羊毛 = 4 张床，3 张床用掉 36 根。床 = 3 块同色羊毛 + 3 块木板，3 格宽，必须用工作台。游戏本身允许混种木板，但机器人用的合成库要 3 块同种，所以按同种准备。没有剪毛动作，打死一只羊掉 1 块羊毛，颜色随羊：白约 82%，黑/灰/淡灰各 5%，棕 3%，粉 0.16%；凑 3 块同色平均要打 3~4 只。没有繁殖动作，羊越打越少；09-17 查过，家 48 格内没有羊。做好的床在 STORE_NEVER（永远不存进箱子）名单里，会一直在做床的人身上，直到摆下去。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>M3-3</t>
+          <t>M2-2</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>小麦在选好的地上，先把低的地面补平，再砌 9×9、3 格高的外墙（四个角用竖着的原木当柱子，其余用木板），最后装一扇门。</t>
+          <t>新房子里要空出能放 3 张床、还留一条走道的地方（现在的 4×4 泥土房屋里只有 2×2 共 4 格，放 2 张床就没地方站）。活归 G3 的盖新房子，这里只负责验收</t>
         </is>
       </c>
       <c r="D32" s="7" t="n">
@@ -1531,14 +1563,10 @@
       <c r="E32" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>J-M3-3</t>
-        </is>
-      </c>
+      <c r="F32" s="7" t="inlineStr"/>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>G2</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
@@ -1548,12 +1576,12 @@
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>M3-1, M3-2</t>
+          <t>M3-1</t>
         </is>
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>地基补平缺口 = 0 并且 新房墙缺口数 = 0 并且 新房有门 = 1</t>
+          <t>房子盖好了 = 1 并且 屋里床位总数 ≥ 3</t>
         </is>
       </c>
       <c r="K32" s="7" t="inlineStr">
@@ -1563,19 +1591,19 @@
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
-          <t>门是 2 格高的物品，要点门洞下面那块地面的顶面放，朝向跟人的朝向走。墙的判定只看实心不实心，不看方块名（泥土长成草那次的教训）。站位必须站在墙格以外的格子上，不能用「离中心多远」来判断。僵尸自己开不了木门。</t>
+          <t>M3-1 指 G3 里「新房子盖好」那一条，编号以 G3 定稿为准。加「房子盖好了=1」是因为墙和屋顶没完成的框架里，空格也会被数成床位。床占 2 格（床头加床尾）。3 张床要 6 格，再加一排走道，所以屋内至少 3×3。床只能放在主世界，下界和末地一放就爆。现在不圈地，别人可以拆掉我们的床，所以「家里摆着的床」每次都要实地扫，不能只信记录。屋外一律不摆床。新房子要离出生点和孩子们的建筑远一些（Owner 已经说过现在太近），这一条归 G3。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>M3-5</t>
+          <t>M3-3</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>麦娘把新家的家具先做好、带在身上：3 张白床、6 个箱子、1 个工作台。这一步不用等房子，可以和小麦砌墙同时做。</t>
+          <t>小麦在选好的地上，先把低的地面补平，再砌 9×9、3 格高的外墙（四个角用竖着的原木当柱子，其余用木板），最后装一扇门。</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
@@ -1586,7 +1614,7 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>J-M3-5a, J-M3-5b</t>
+          <t>J-M3-3, build_house, get_build_mats, son_take_mats</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
@@ -1596,13 +1624,17 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>麦娘</t>
-        </is>
-      </c>
-      <c r="I33" s="7" t="inlineStr"/>
+          <t>小麦</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>M3-1, M3-2</t>
+        </is>
+      </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>麦家的床数 ≥ 3 并且 麦家的箱子数 ≥ 6 并且 麦家的工作台数 ≥ 1</t>
+          <t>地基补平缺口 = 0 并且 新房墙缺口数 = 0 并且 新房有门 = 1</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr">
@@ -1612,19 +1644,19 @@
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>床 = 3 块同色羊毛 + 3 块木板（木板可以混种）；白羊毛 = 4 根线，背包里的 2×2 格就能合成。箱子里约 48 根线，够做 12 块羊毛 = 4 张床，只有 1 张的余量，所以床绝不能被旧家的睡觉规则消耗掉。线不够时也可以打羊：每只掉 1 块羊毛，颜色随羊，同一张床要同色。床、箱子、工作台的配方都要工作台。家具用非设计木种的木板（比如桦木），别吃掉盖房的料。多人睡觉跳夜：默认要在线玩家全部睡着才跳，有真人孩子醒着时，麦家睡下也不会跳夜；床的价值是安全躺着 + 重生点。这 3 张床就是 G2 的床，两边不要重复做。</t>
+          <t>⏳ 过渡:搬家(拍板第 1 件)定之前,挂在这里的 build_house / get_build_mats / son_take_mats 仍在现在的家把房子盖完(线上老行为,不倒退);定了搬以后改成在新家址盖。 门是 2 格高的物品，要点门洞下面那块地面的顶面放，朝向跟人的朝向走。墙的判定只看实心不实心，不看方块名（泥土长成草那次的教训）。站位必须站在墙格以外的格子上，不能用「离中心多远」来判断。僵尸自己开不了木门。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>M4-2</t>
+          <t>M3-5</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>在选定的新家址落户</t>
+          <t>麦娘把新家的家具先做好、带在身上：3 张白床、6 个箱子、1 个工作台。这一步不用等房子，可以和小麦砌墙同时做。</t>
         </is>
       </c>
       <c r="D34" s="7" t="n">
@@ -1635,49 +1667,45 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>J-M4-2, think_home_site</t>
+          <t>J-M3-5a, J-M3-5b</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>G4</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
-        </is>
-      </c>
-      <c r="I34" s="7" t="inlineStr">
-        <is>
-          <t>M4-1</t>
-        </is>
-      </c>
+          <t>麦娘</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr"/>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>家离出生点 ≥ 300 并且 Essentials家已挪到新址 = 1</t>
+          <t>麦家的床数 ≥ 3 并且 麦家的箱子数 ≥ 6 并且 麦家的工作台数 ≥ 1</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
-          <t>机器人读不到 Essentials 的家,要 Owner 在游戏里打 /sethome XiaoMai:base;不挪的话,respawn-at-home 会一直把人重生在旧家</t>
+          <t>床 = 3 块同色羊毛 + 3 块木板（木板可以混种）；白羊毛 = 4 根线，背包里的 2×2 格就能合成。箱子里约 48 根线，够做 12 块羊毛 = 4 张床，只有 1 张的余量，所以床绝不能被旧家的睡觉规则消耗掉。线不够时也可以打羊：每只掉 1 块羊毛，颜色随羊，同一张床要同色。床、箱子、工作台的配方都要工作台。家具用非设计木种的木板（比如桦木），别吃掉盖房的料。多人睡觉跳夜：默认要在线玩家全部睡着才跳，有真人孩子醒着时，麦家睡下也不会跳夜；床的价值是安全躺着 + 重生点。这 3 张床就是 G2 的床，两边不要重复做。</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>M5-5</t>
+          <t>M4-2</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>箱子里常备 3 把木剑</t>
+          <t>在选定的新家址落户</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
@@ -1688,12 +1716,12 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>J-M5-5</t>
+          <t>J-M4-2, think_home_site</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>G5</t>
+          <t>G4</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
@@ -1701,10 +1729,14 @@
           <t>小麦</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr"/>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>M4-1</t>
+        </is>
+      </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>箱子里剑数 ≥ 3</t>
+          <t>家离出生点 ≥ 300 并且 Essentials家已挪到新址 = 1</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr">
@@ -1714,30 +1746,30 @@
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>木剑 = 2 木板 + 1 木棍;剑断了回家拿一把就行,不用临时去合成</t>
+          <t>机器人读不到 Essentials 的家,要 Owner 在游戏里打 /sethome XiaoMai:base;不挪的话,respawn-at-home 会一直把人重生在旧家</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>M5-6</t>
+          <t>M5-5</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>用箱子里的钻石给会打架的家人每人做一把钻石剑(麦豆不算;等 Owner 批准)</t>
+          <t>箱子里常备 3 把木剑</t>
         </is>
       </c>
       <c r="D36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>make_sword</t>
+          <t>J-M5-5</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
@@ -1753,7 +1785,7 @@
       <c r="I36" s="7" t="inlineStr"/>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>在线家人里没钻石剑的人数 = 0</t>
+          <t>箱子里剑数 ≥ 3</t>
         </is>
       </c>
       <c r="K36" s="7" t="inlineStr">
@@ -1763,35 +1795,31 @@
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
-          <t>钻石剑 = 2 钻石 + 1 木棍;现在只数会打架的人(小麦,麦娘放行 fight 后再加一把),2 把用 4 颗,箱子里有 27 颗。「在线家人里没钻石剑的人数」和 M5-1 同一个函数(C-FAM-12,剑种当参数)。钻石按物品分类表算贵重;换下来的旧剑存进箱子当备用,不扔。</t>
+          <t>木剑 = 2 木板 + 1 木棍;剑断了回家拿一把就行,不用临时去合成</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>M6-3</t>
+          <t>M5-6</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>箱子里原木不少于 64 根(掉下去才补)</t>
+          <t>用箱子里的钻石给会打架的家人每人做一把钻石剑(麦豆不算;等 Owner 批准)</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>chop_wood, find_forest, store_wood</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="F37" s="7" t="inlineStr"/>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>G6</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
@@ -1802,7 +1830,7 @@
       <c r="I37" s="7" t="inlineStr"/>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>箱子里原木 ≥ 64</t>
+          <t>在线家人里没钻石剑的人数 = 0</t>
         </is>
       </c>
       <c r="K37" s="7" t="inlineStr">
@@ -1812,19 +1840,19 @@
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>一棵树砍干净再走,不留半截;有树叶、周围没有人造方块才砍的护栏已经在了。现在有 343 根,已经达成</t>
+          <t>钻石剑 = 2 钻石 + 1 木棍;现在只数会打架的人(小麦,麦娘放行 fight 后再加一把),2 把用 4 颗,箱子里有 27 颗。「在线家人里没钻石剑的人数」和 M5-1 同一个函数(C-FAM-12,剑种当参数)。钻石按物品分类表算贵重;换下来的旧剑存进箱子当备用,不扔。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>M7-3</t>
+          <t>M6-3</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>麦豆跟着爸爸,自己成功砍过 3 次树</t>
+          <t>箱子里原木不少于 64 根(掉下去才补)</t>
         </is>
       </c>
       <c r="D38" s="7" t="n">
@@ -1835,41 +1863,45 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>J-M7-3, child_watch_dad</t>
+          <t>chop_wood, find_forest, store_wood</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>G6</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>麦豆</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr"/>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>麦豆砍树成功次数 ≥ 3</t>
+          <t>箱子里原木 ≥ 64</t>
         </is>
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
-        </is>
-      </c>
-      <c r="L38" s="7" t="inlineStr"/>
+          <t>缺判据</t>
+        </is>
+      </c>
+      <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>一棵树砍干净再走,不留半截;有树叶、周围没有人造方块才砍的护栏已经在了。现在有 343 根,已经达成</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>M8-2</t>
+          <t>M7-2</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>小麦去资源世界挖铁矿、就地烧成铁锭，直到家里的铁够把还缺的铁装备（铁剑、四件铁甲、盾、水桶、打火石）全部做出来。</t>
+          <t>麦豆近 24 小时一次没死</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
@@ -1880,133 +1912,117 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>J-M8-2</t>
+          <t>child_home, child_play</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>G8</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
-        </is>
-      </c>
-      <c r="I39" s="7" t="inlineStr">
-        <is>
-          <t>M8-1</t>
-        </is>
-      </c>
+          <t>麦豆</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr"/>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>铁装备还差的铁锭 = 0</t>
+          <t>近24小时麦豆死亡次数 = 0</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
-        </is>
-      </c>
-      <c r="L39" s="7" t="inlineStr">
-        <is>
-          <t>全套一共 34 个铁锭：镐 3（M8-1 已做）+ 剑 2 + 头盔 5 + 胸甲 8 + 护腿 7 + 靴子 4 + 盾 1 + 桶 3 + 打火石 1。🔴 完成标准不用「铁的家底 ≥ 34」：钻石镐做出来以后铁镐一用坏、或者桶被田里用掉，家底就掉到 34 以下，小麦会为一件已经不需要的东西再跑一趟资源世界；也不能按「箱子里有几个铁锭」算，铁锭做成铁甲以后箱子里就少了，会一直挖。按「还差几个」算：只有缺的件真用坏了才重开，而那正是该去补的时候。粗铁按 1 锭算（一趟被打断时带回来的粗铁不会被当成不存在），下一趟带去资源世界一起烧。1.18 以后铁矿在 y≈16 附近最多，石镐就能挖；y&lt;0 挖出来的是深板岩圆石，照样能做熔炉。熔炉 = 8 圆石，烧一个 10 秒；1 块煤烧 8 个，1 根原木烧 1.5 个。每趟最多 25 分钟，背包只剩 2 格就回。只有小麦去。🔴 出发前必须「资源世界死亡不掉东西 = 1」：server/04-resource-worlds.md 明写这条没核实，死在回不去的资源世界，铁装备就永久没了。离 05:00（东京时间）重启不到 40 分钟就不出发，不到 15 分钟就当场回主世界。「在资源世界下线再上线会卡全服」这个说法没有出处，但避开重启本来就该做，护栏保留。「只在中心 ±900 格里挖」删掉：落点是插件随机给的，机器人控制不了。</t>
-        </is>
-      </c>
+          <t>缺判据</t>
+        </is>
+      </c>
+      <c r="L39" s="7" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>M1-2</t>
+          <t>M7-4</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>在选好的田址上开出第一块 9 格麦田：9 格都锄好、都种上麦子，一格不空。</t>
+          <t>麦豆没被点名时,离真人玩家至少 16 格</t>
         </is>
       </c>
       <c r="D40" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>J-M1-2, wife_plant</t>
+          <t>J-M7-4</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>G1</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>麦娘</t>
-        </is>
-      </c>
-      <c r="I40" s="7" t="inlineStr">
-        <is>
-          <t>M1-0, M1-1</t>
-        </is>
-      </c>
+          <t>麦豆</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr"/>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>耕好的地 ≥ 9 并且 空着的耕地 = 0</t>
+          <t>近1小时未被点名时离真人玩家最近距离 ≥ 16</t>
         </is>
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
-        </is>
-      </c>
-      <c r="L40" s="7" t="inlineStr">
-        <is>
-          <t>水边田址上刚锄好的湿耕地不会退回泥土，所以「锄一批再种」没问题；只有 Owner 选了家门口干地时，才会碰到「锄好约 1 分钟就变回泥土」，那时由 J-M1-2 下一轮把退回的格子重锄重种，慢慢凑满。wife_till 关掉（开 = false），它要先锄满 9 格才轮到播种。作物要亮度 ≥ 9 才长、≥ 8 或头顶见天才种得活；露天的田夜里也照长。从高处跳下落到耕地上（下落超过半格）会把它踩回泥土、麦子掉出来——孩子们和寻路时的机器人都可能踩，被踩的格子由登记簿记成「空」，交给 J-M1-2 补。完成状态每次重算：哪格空了，M1-2 自动回到没完成，J-M1-2 再开工补上。🔴 前置 M1-0 标成「必须现在成立」（C-ENG-22 的例外）：家搬走、田址失效时，不能继续在 300 格外的旧田上干（旁边没人，庄稼也不长），要等新田址定下来；M1-1 仍按「完成过」算（种子一种下去就少于 9 颗，按现在算会把自己卡死）。</t>
-        </is>
-      </c>
+          <t>缺判据</t>
+        </is>
+      </c>
+      <c r="L40" s="7" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>M2-3</t>
+          <t>M8-2</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>把做好的床摆进屋里，每张记在一个家人名下；麦豆那张由身上有床的人替他摆</t>
+          <t>小麦去资源世界挖铁矿、就地烧成铁锭，直到家里的铁够把还缺的铁装备（铁剑、四件铁甲、盾、水桶、打火石）全部做出来。</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>J-M2-3-1</t>
+          <t>J-M8-2</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>G2</t>
+          <t>G8</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>麦娘 / 小麦（谁身上有床谁摆）</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>M2-1, M2-2</t>
+          <t>M8-1</t>
         </is>
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>没床的家人数 = 0 并且 家里摆着的床 ≥ 3</t>
+          <t>铁装备还差的铁锭 = 0</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr">
@@ -2016,19 +2032,19 @@
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>游戏里任何人都能睡任何一张没人占的床，「这是谁的床」只是我们自己记的账。重生点跟着最后睡过的那张床走；两个人不能同时睡一张床（会提示床已被占用）。现在的 sleep 只在 24 格内一张床都没有时才自己摆床，所以结构上只摆得出第一张，第二、第三张只能靠 place_bed。麦豆没有合成动作，也没有把东西交给别人的动作，所以他的床只能由做床的人直接摆进屋。</t>
+          <t>全套一共 34 个铁锭：镐 3（M8-1 已做）+ 剑 2 + 头盔 5 + 胸甲 8 + 护腿 7 + 靴子 4 + 盾 1 + 桶 3 + 打火石 1。🔴 完成标准不用「铁的家底 ≥ 34」：钻石镐做出来以后铁镐一用坏、或者桶被田里用掉，家底就掉到 34 以下，小麦会为一件已经不需要的东西再跑一趟资源世界；也不能按「箱子里有几个铁锭」算，铁锭做成铁甲以后箱子里就少了，会一直挖。按「还差几个」算：只有缺的件真用坏了才重开，而那正是该去补的时候。粗铁按 1 锭算（一趟被打断时带回来的粗铁不会被当成不存在），下一趟带去资源世界一起烧。1.18 以后铁矿在 y≈16 附近最多，石镐就能挖；y&lt;0 挖出来的是深板岩圆石，照样能做熔炉。熔炉 = 8 圆石，烧一个 10 秒；1 块煤烧 8 个，1 根原木烧 1.5 个。每趟最多 25 分钟，背包只剩 2 格就回。只有小麦去。🔴 出发前必须「资源世界死亡不掉东西 = 1」：server/04-resource-worlds.md 明写这条没核实，死在回不去的资源世界，铁装备就永久没了。离 05:00（东京时间）重启不到 40 分钟就不出发，不到 15 分钟就当场回主世界。「在资源世界下线再上线会卡全服」这个说法没有出处，但避开重启本来就该做，护栏保留。「只在中心 ±900 格里挖」删掉：落点是插件随机给的，机器人控制不了。</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>M3-4</t>
+          <t>M1-7</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>小麦先把屋里 49 格地面铺满木半砖，再封上 9×9 的平屋顶。铺了半砖的地面怪物刷不出来，所以屋顶封上的那一刻，屋里就已经不刷怪了。</t>
+          <t>在田址里、水浇得到的地方把麦田扩到 64 格以上，全是湿地、几乎全种上：按估算这么大的田刚好够全家三口天天吃面包。</t>
         </is>
       </c>
       <c r="D42" s="7" t="n">
@@ -2039,27 +2055,27 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>J-M3-4</t>
+          <t>J-M1-4, J-M1-7, J-M1-7b, wife_find_seeds, wife_gather_seeds</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>麦娘</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>M3-3</t>
+          <t>M1-4, M1-6</t>
         </is>
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>新房地面裸露格数 = 0 并且 新房屋顶缺口数 = 0</t>
+          <t>田格余量 ≥ 0 并且 空着的耕地 ≤ 4</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr">
@@ -2069,19 +2085,19 @@
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
-          <t>1.18 起，敌对怪只在方块光照为 0 的地方刷，而且刷不到底半砖上（顶半砖和双层半砖上能刷）。人站在半砖上眼睛高出 0.5 格；放方块的伸手距离是 3.6 时，屋顶格在水平约 3.3 格内都够得着。对着同种底半砖的顶面再放一块，会合成双层半砖（完整方块，能刷怪），所以 placeAt「放之前先看目标格是不是空的」这条不能绕过。</t>
+          <t>算账：64 格湿地整块种满，每格约 48 分钟出 1 个小麦 → 每游戏日约 27 个小麦 = 9 个面包 = 3 人 × 3 个；没水的话要约 140 格。一格水最多浇 80 格，靠边、靠角的格子邻居少，比中间长得慢一点。64 格要 64 颗种子：9 格田一茬净多约 15 颗，大约要 3~4 茬才攒够。木锄 59 次耐久，锄 64 格外加重锄，至少还要再做一把。🔴 零候选审计：原来固定 64 格。G1 的「面包盈余 ≥ 0」不成立（全家吃得比田里产的多，小麦远征路上吃的也算在内）时，G1 变回没完成，可 64 格早就达成了，没有任何小目标去扩田。改成「田格余量 ≥ 0」（C-FRM-22）：田格余量 = 有水的自家田 − 该有的田格数；该有的田格数 = 64 和按实测吃掉的面包算出的格数里取大的，再以田址实际能开的格数封顶。超了就按封顶算完成，并在后台写「田址不够大，面包仍然不够」，不让它变成永远做不完、又没人能推的死目标。</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>M4-3</t>
+          <t>M1-9</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>旧家箱子里的东西全部搬到新家</t>
+          <t>粮箱里的面包补到 18 个（够全家吃两天），被家人拿走就接着补。</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
@@ -2092,12 +2108,12 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>J-M4-3, wife_craft_chest</t>
+          <t>J-M1-4, J-M1-9, wife_bread, wife_store_crop</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>G4</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
@@ -2107,34 +2123,34 @@
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>M4-2</t>
+          <t>M1-3</t>
         </is>
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>旧家箱子非空格数 = 0 并且 有箱子 = 1</t>
+          <t>粮箱里的面包 ≥ 18</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>keepInventory 开着,路上死了也不掉东西;大约两趟搬完</t>
+          <t>🔴 零候选审计补的。G1 要求粮箱常备 18 个面包，但下面只有 M1-3「第一次走通、有 3 个」：粮箱到 3 个以后，3 到 18 之间没有任何小目标管，麦娘会零候选，G1 却一直没完成。家人一拿面包（A14 口粮、小麦远征），这条就重开，是麦娘的常驻活。优先级 5：原稿的 4 和 M1-7（扩田）同档，每次都会触发 T1 去问模型「先补面包还是先扩田」，这件事代码能定——日常口粮有 A14/A4 保底，扩田本身就是在提高面包产量，所以扩田在前。G8 的 M8-7 在这个基础上再加到 34。</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>M7-5</t>
+          <t>M2-3</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>麦豆白天陪在正在干活的家人旁边（比如看妈妈种地），不跑远、不乱逛。</t>
+          <t>把做好的床摆进屋里，每张记在一个家人名下；麦豆那张由身上有床的人替他摆</t>
         </is>
       </c>
       <c r="D44" s="7" t="n">
@@ -2145,23 +2161,27 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>J-M7-5</t>
+          <t>J-M2-3-1</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>G2</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>麦豆</t>
-        </is>
-      </c>
-      <c r="I44" s="7" t="inlineStr"/>
+          <t>麦娘 / 小麦（谁身上有床谁摆）</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>M2-1, M2-2</t>
+        </is>
+      </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>离最近在干活的家人距离 ≤ 16</t>
+          <t>没床的家人数 = 0 并且 家里摆着的床 ≥ 3</t>
         </is>
       </c>
       <c r="K44" s="7" t="inlineStr">
@@ -2171,19 +2191,19 @@
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
-          <t>🔴 零候选修正：原设计靠 M1-8（帮妈妈收麦子）解决麦豆的零候选，但那要先等您放行；放行之前，麦豆的小目标要么是「不走丢、不死、不打扰孩子」这种做到了就没活的，要么是要放行才能做的砍树，他会一直零候选、一直标红。这一条只用他现在就有的 goto_place 和 idle，符合他「爱跟着大人跑」的人设，也不去打扰真人小孩。只陪在主世界、离家 64 格内、干的不是远征活的家人；停在 4~8 格外，不进田、不挡路。家人一走开，这条就重开，是麦豆的常驻活；没人在家附近干活时算完成，缺口记录记成「在等」。晚上交给 A11。</t>
+          <t>游戏里任何人都能睡任何一张没人占的床，「这是谁的床」只是我们自己记的账。重生点跟着最后睡过的那张床走；两个人不能同时睡一张床（会提示床已被占用）。现在的 sleep 只在 24 格内一张床都没有时才自己摆床，所以结构上只摆得出第一张，第二、第三张只能靠 place_bed。麦豆没有合成动作，也没有把东西交给别人的动作，所以他的床只能由做床的人直接摆进屋。</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>M8-3</t>
+          <t>M3-4</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>小麦有一身能保命的铁装备：四件铁甲（头盔、胸甲、护腿、靴子）、铁剑、盾，外加一桶水和一个打火石（点下界传送门用）。</t>
+          <t>小麦先把屋里 49 格地面铺满木半砖，再封上 9×9 的平屋顶。铺了半砖的地面怪物刷不出来，所以屋顶封上的那一刻，屋里就已经不刷怪了。</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
@@ -2194,12 +2214,12 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>J-M8-3a, J-M8-3b, J-M8-3c</t>
+          <t>J-M3-4</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>G8</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
@@ -2209,12 +2229,12 @@
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>M8-2</t>
+          <t>M3-3</t>
         </is>
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>拥有的铁或更好护甲件数 ≥ 4 并且 最好的剑等级 ≥ 3 并且 有盾牌 ≥ 1 并且 身上装水的桶 ≥ 1 并且 有打火石 ≥ 1</t>
+          <t>新房地面裸露格数 = 0 并且 新房屋顶缺口数 = 0</t>
         </is>
       </c>
       <c r="K45" s="7" t="inlineStr">
@@ -2224,35 +2244,35 @@
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>护甲、剑、盾看「拥有的」＝身上穿的 + 背包 + 箱子里（上次开箱看到的）。🔴 只看身上和背包不够：去下界要换金头盔，铁头盔放进背包，常驻层 A12/A19 会把它存进箱子，件数变成 3，这条就重开，又花 5 个铁做一顶。所以一是箱子里的也算，二是 C-ITM-26 规定小麦自己的护甲、剑、镐、盾、桶、打火石不算「可存的东西」。🔴 机器人现有代码 wearBestArmor（bot.real.js 约 2344 行）每 30 秒把背包里「更好」的护甲穿上，铁排在金前面，进下界时会把金头盔换回铁头盔，所以下界脚本期间由 C-ITM-23 让它跳过头盔。耐久：铁甲各件 165~240 次，铁剑 250 次，盾 336 次；用坏了这条自动重开，铁不够时 M8-2 也跟着重开。钻石或更好的也算。盾 = 6 木板 + 1 铁锭；打火石 = 1 铁锭 + 1 燧石，背包里的小格子就能做；沙砾挖一块有 10% 掉燧石。水桶只算身上装着水的；倒掉（浇黑曜石）以后收回来就还算有。</t>
+          <t>1.18 起，敌对怪只在方块光照为 0 的地方刷，而且刷不到底半砖上（顶半砖和双层半砖上能刷）。人站在半砖上眼睛高出 0.5 格；放方块的伸手距离是 3.6 时，屋顶格在水平约 3.3 格内都够得着。对着同种底半砖的顶面再放一块，会合成双层半砖（完整方块，能刷怪），所以 placeAt「放之前先看目标格是不是空的」这条不能绕过。</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>M1-3</t>
+          <t>M4-3</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>「收麦子 → 做面包 → 多出来的面包放进粮箱」这条路完整走通一圈：粮箱里至少有 3 个面包。</t>
+          <t>旧家箱子里的东西全部搬到新家</t>
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E46" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>J-M1-4, wife_bread, wife_craft_chest, wife_get_crop_chest, wife_store_crop</t>
+          <t>J-M4-3, wife_craft_chest</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>G1</t>
+          <t>G4</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
@@ -2262,103 +2282,95 @@
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>M1-2</t>
+          <t>M4-2</t>
         </is>
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>有粮箱 ≥ 1 并且 粮箱里的面包 ≥ 3</t>
+          <t>旧家箱子非空格数 = 0 并且 有箱子 = 1</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
-          <t>面包 = 3 小麦横排、箱子 = 8 木板，都要工作台；田离家远的话，做面包的地方 32 格内要有工作台，或者她身上带一张（4 木板）。store_crop 会让她身上留 3 个面包、9 个小麦、16 颗种子，多的才进粮箱；9 格田一茬只出 9 个小麦 = 3 个面包，正好被她自己留下，所以粮箱要到第 2~3 茬才见得到面包——湿地约 1.5~2.5 小时，干地约 3.5~5 小时，这是正常的，不是卡住。收割用 J-M1-4（收完当场补种），wife_harvest 关掉或降成备用。</t>
+          <t>keepInventory 开着,路上死了也不掉东西;大约两趟搬完</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>M1-4</t>
+          <t>M7-3</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>收完的地不空着：最近一小时里，每一格收完或被踩坏的地都在 3 分钟内重新种上，身上常备够补一整块田的种子。</t>
+          <t>麦豆跟着爸爸,自己成功砍过 3 次树</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E47" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>J-M1-2, J-M1-4, wife_find_seeds, wife_gather_seeds</t>
+          <t>J-M7-3, J-M7-3c, J-M7-3d, child_watch_dad</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>G1</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>麦娘</t>
-        </is>
-      </c>
-      <c r="I47" s="7" t="inlineStr">
-        <is>
-          <t>M1-2</t>
-        </is>
-      </c>
+          <t>麦豆</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr"/>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>补种最长等待秒数_新口径 ≤ 180 并且 有种子 ≥ 9</t>
+          <t>麦豆砍树成功次数 ≥ 3</t>
         </is>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
-        </is>
-      </c>
-      <c r="L47" s="7" t="inlineStr">
-        <is>
-          <t>熟麦每格掉 1 个小麦 + 1~4 颗种子（平均约 2.7），种回去 1 颗还净多约 1.7，种子越收越多。干地的空耕地平均约 68 秒就退回泥土，补种要快；湿地不会退，但空着也不长。M1-3 和 M1-4 同级、都是麦娘的，同时有两件以上能开工、而且组合是新的时，由 T1 让模型挑一次。🔴 零候选审计：原来的「补种最长等待秒数」在 60 分钟内一格都没空过时返回 9999——这时田是满的、根本没活，这条却一直算「没完成」，挂在它下面的 J-M1-2 会走到田里什么也不做就算完，来回空转。完成标准换成新口径（C-FRM-23）：60 分钟内没空过 → 0（没有要等的）；麦娘不在线或田没加载 → 沿用上一次的值。另外 M1-1（种子 ≥ 9）是 M1-2 的前置、M1-2 又是这条的前置：9 颗种子一种下去 M1-1 就变回没完成，收割（正是补种子的路）反而被卡住，所以前置按「完成过」算（C-ENG-22）。</t>
-        </is>
-      </c>
+          <t>判据动作都缺</t>
+        </is>
+      </c>
+      <c r="L47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>M1-6</t>
+          <t>M8-3</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>麦田的 9 格全都有水浇着：挨着河选的田天生就有；实在没有，才由小麦做个铁桶，在田边挖一格坑倒水（要 Owner 先点头）。</t>
+          <t>小麦有一身能保命的铁装备：四件铁甲（头盔、胸甲、护腿、靴子）、铁剑、盾，外加一桶水和一个打火石（点下界传送门用）。</t>
         </is>
       </c>
       <c r="D48" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E48" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>J-M1-6</t>
+          <t>J-M8-3a, J-M8-3b, J-M8-3c</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>G1</t>
+          <t>G8</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
@@ -2368,12 +2380,12 @@
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>M1-2</t>
+          <t>M8-2</t>
         </is>
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>有水的自家田 ≥ 9</t>
+          <t>拥有的铁或更好护甲件数 ≥ 4 并且 最好的剑等级 ≥ 3 并且 有盾牌 ≥ 1 并且 身上装水的桶 ≥ 1 并且 有打火石 ≥ 1</t>
         </is>
       </c>
       <c r="K48" s="7" t="inlineStr">
@@ -2383,19 +2395,19 @@
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
-          <t>水边田址上这条一开始就成立，J-M1-6 不会开工；只有 Owner 选了家门口、或附近找不到水边空地时才走铁桶这条路。坑挖在田边（紧挨 9 格田中间那一格的外侧），不挖在田里：挖在正中会让 9 格变 8 格，M1-2 立刻变回没完成，两个小目标互相拆台。田边那格水离 9 格里最远的只有 3 格，全都浇得到；以后扩田也以它为中心，一格水最多浇湿周围 9×9 = 80 格。水放在四面都是实心方块的一格坑里不会流出去。</t>
+          <t>护甲、剑、盾看「拥有的」＝身上穿的 + 背包 + 箱子里（上次开箱看到的）。🔴 只看身上和背包不够：去下界要换金头盔，铁头盔放进背包，常驻层 A12/A19 会把它存进箱子，件数变成 3，这条就重开，又花 5 个铁做一顶。所以一是箱子里的也算，二是 C-ITM-26 规定小麦自己的护甲、剑、镐、盾、桶、打火石不算「可存的东西」。🔴 机器人现有代码 wearBestArmor（bot.real.js 约 2344 行）每 30 秒把背包里「更好」的护甲穿上，铁排在金前面，进下界时会把金头盔换回铁头盔，所以下界脚本期间由 C-ITM-23 让它跳过头盔。耐久：铁甲各件 165~240 次，铁剑 250 次，盾 336 次；用坏了这条自动重开，铁不够时 M8-2 也跟着重开。钻石或更好的也算。盾 = 6 木板 + 1 铁锭；打火石 = 1 铁锭 + 1 燧石，背包里的小格子就能做；沙砾挖一块有 10% 掉燧石。水桶只算身上装着水的；倒掉（浇黑曜石）以后收回来就还算有。</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>M1-8</t>
+          <t>M1-6</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>田里熟了的麦子不放着：熟了就收，收完当场种回去，小麦和种子存进粮箱；麦豆在妈妈忙别的时帮她收。</t>
+          <t>麦田的 9 格全都有水浇着：挨着河选的田天生就有；实在没有，才由小麦做个铁桶，在田边挖一格坑倒水（要 Owner 先点头）。</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
@@ -2406,7 +2418,7 @@
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>J-M1-4, J-M1-8</t>
+          <t>J-M1-6</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
@@ -2416,7 +2428,7 @@
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>麦娘 / 麦豆（麦豆要等您放行收麦子）</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
@@ -2426,7 +2438,7 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>该收割了 = 0</t>
+          <t>有水的自家田 ≥ 9</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr">
@@ -2436,7 +2448,7 @@
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>🔴 零候选审计补的：原来没有任何小目标管「熟了就收」——M1-2 管种满，M1-4 管收完补种，M1-3 只管粮箱第一次有 3 个面包，麦子熟了不会让任何一条变回没完成。完成标准和两条脚本的开工都调同一个「该收割了」（门槛按田的大小自动在 3~16 之间），不再是原稿的「≤ 2 / ≥ 3 / ≥ 6」三个数——那样熟了 3~15 格时这条算没完成，却谁也开不了工。🔴 两人不会同时收：谁先动手谁拿「田里收割锁」，另一个人这一步跳过、不算失败。所以麦豆是在妈妈忙别的（做面包、存东西、扩田）时帮她收，不会跟她抢同一块田。麦豆存进粮箱的小麦由麦娘的 J-M1-9 拿去做面包。64 格湿地平均不到 1 分钟就熟一格，这条经常重开，是麦娘和麦豆的常驻活。harvest_crop 只动登记簿里的格子；不踩田的护栏 09-18 已经上线。</t>
+          <t>水边田址上这条一开始就成立，J-M1-6 不会开工；只有 Owner 选了家门口、或附近找不到水边空地时才走铁桶这条路。坑挖在田边（紧挨 9 格田中间那一格的外侧），不挖在田里：挖在正中会让 9 格变 8 格，M1-2 立刻变回没完成，两个小目标互相拆台。田边那格水离 9 格里最远的只有 3 格，全都浇得到；以后扩田也以它为中心，一格水最多浇湿周围 9×9 = 80 格。水放在四面都是实心方块的一格坑里不会流出去。</t>
         </is>
       </c>
     </row>
@@ -2496,12 +2508,12 @@
     <row r="51">
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>M3-6</t>
+          <t>M3-2</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>房子盖好以后，麦娘把 3 张床、6 个箱子（两两拼成 3 个大箱子）和工作台摆进新房：床靠一面墙并排，箱子靠另一面墙，工作台垫在半砖上、放在墙角。</t>
+          <t>麦娘按选定的木头样式，把盖房的结构材料备齐、放进共用箱子：木板 163 块（墙 82 + 屋顶 81）、做柱子的原木 12 根、木半砖 49 块、门 1 扇。</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
@@ -2512,7 +2524,7 @@
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>J-G3-0b, J-M3-6</t>
+          <t>J-G3-0a, J-M3-2, wife_planks</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
@@ -2525,14 +2537,10 @@
           <t>麦娘</t>
         </is>
       </c>
-      <c r="I51" s="7" t="inlineStr">
-        <is>
-          <t>M3-4, M3-5</t>
-        </is>
-      </c>
+      <c r="I51" s="7" t="inlineStr"/>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>新房里的床 ≥ 3 并且 新房里的箱子格数 ≥ 6 并且 新房里的工作台 ≥ 1 并且 屋内能刷怪的格数 = 0 并且 麦家名下领地数 = 0</t>
+          <t>新房木板缺口 = 0 并且 新房原木缺口 = 0 并且 新房半砖缺口 = 0 并且 新房门缺口 = 0</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
@@ -2542,19 +2550,19 @@
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>GP 在本服的设定是「新玩家放第一个箱子，自动圈一块半径 4 的地」。2026-09-18 已把两个 AI 账号的 griefprevention.createclaims 设成 false，按设计能挡住这条路，但没在游戏里实测过，麦豆的账号也不一定在那两个里面，所以只让麦娘放箱子，并且放完第一个就核对。箱子正上方要留空才能打开（放在半砖上的箱子，头顶还有 1 格空，够用）。Java 版里床和箱子都能放在半砖上，下面会空出半格，这是正常的。工作台顶面是完整方块，放在墙角、垫在半砖上以后，头顶只剩 1 格：僵尸、骷髅、苦力怕都太高；蜘蛛宽 1.4 格，被两面墙挡住，所以不会刷怪。</t>
+          <t>1 根原木 = 4 块木板；半砖是 3 块木板出 6 块，门是 6 块同种木板出 3 扇，两样都要工作台（3 格宽的配方），craft 要能在旧家附近找到或摆出工作台。同一扇门、同一批半砖都必须用同一种木板。结构总共 196 木板（49 根原木）加 12 根柱子原木。地基补平的用料要等选完地才知道，不算在这里，由 J-M3-3 现拿现做。库存：橡木 232 根，什么组合都够；樱花 83 根 = 332 木板，墙 + 屋顶（163）一起都够；桦木 28 根 = 112 木板，够墙或屋顶其中一样。旧判据「房子还要料」「盖房的材料够吗」保持原来的意思，不改成新计划（改了会让旧脚本乱开工）。</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>M4-4</t>
+          <t>M3-6</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>出生点旁机器人自己放下的方块全部清掉(泥土房、箱子、地上的木头)</t>
+          <t>房子盖好以后，麦娘把 3 张床、6 个箱子（两两拼成 3 个大箱子）和工作台摆进新房：床靠一面墙并排，箱子靠另一面墙，工作台垫在半砖上、放在墙角。</t>
         </is>
       </c>
       <c r="D52" s="7" t="n">
@@ -2565,27 +2573,27 @@
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>J-M4-4</t>
+          <t>J-G3-0b, J-M3-6</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>G4</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>麦娘</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
         <is>
-          <t>M4-3</t>
+          <t>M3-4, M3-5</t>
         </is>
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>出生点旁机器人放下且还在的方块数 = 0</t>
+          <t>新房里的床 ≥ 3 并且 新房里的箱子格数 ≥ 6 并且 新房里的工作台 ≥ 1 并且 屋内能刷怪的格数 = 0 并且 麦家名下领地数 = 0</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr">
@@ -2595,19 +2603,19 @@
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
-          <t>Owner 收到过「地上的木头太丑」的抱怨。清单以外的一格都不碰</t>
+          <t>GP 在本服的设定是「新玩家放第一个箱子，自动圈一块半径 4 的地」。2026-09-18 已把两个 AI 账号的 griefprevention.createclaims 设成 false，按设计能挡住这条路，但没在游戏里实测过，麦豆的账号也不一定在那两个里面，所以只让麦娘放箱子，并且放完第一个就核对。箱子正上方要留空才能打开（放在半砖上的箱子，头顶还有 1 格空，够用）。Java 版里床和箱子都能放在半砖上，下面会空出半格，这是正常的。工作台顶面是完整方块，放在墙角、垫在半砖上以后，头顶只剩 1 格：僵尸、骷髅、苦力怕都太高；蜘蛛宽 1.4 格，被两面墙挡住，所以不会刷怪。</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>M5-2</t>
+          <t>M4-4</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>小麦有一把镐（木镐或更好的都算，放在箱子里的也算）</t>
+          <t>出生点旁机器人自己放下的方块全部清掉(泥土房、箱子、地上的木头)</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
@@ -2618,12 +2626,12 @@
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>J-M5-2</t>
+          <t>J-M4-4</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>G5</t>
+          <t>G4</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr">
@@ -2631,10 +2639,14 @@
           <t>小麦</t>
         </is>
       </c>
-      <c r="I53" s="7" t="inlineStr"/>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>M4-3</t>
+        </is>
+      </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>最好的镐等级 ≥ 1</t>
+          <t>出生点旁机器人放下且还在的方块数 = 0</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr">
@@ -2644,19 +2656,19 @@
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>木镐 = 3 木板 + 2 木棍,耐久 59;挖 64 块圆石要 2 把</t>
+          <t>Owner 收到过「地上的木头太丑」的抱怨。清单以外的一格都不碰</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>M8-4</t>
+          <t>M5-2</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>小麦有一把钻石镐（黑曜石只有钻石镐才挖得动）。</t>
+          <t>小麦有一把镐（木镐或更好的都算，放在箱子里的也算）</t>
         </is>
       </c>
       <c r="D54" s="7" t="n">
@@ -2667,12 +2679,12 @@
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>J-M8-4a, J-M8-4b</t>
+          <t>J-M5-2</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>G8</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr">
@@ -2680,14 +2692,10 @@
           <t>小麦</t>
         </is>
       </c>
-      <c r="I54" s="7" t="inlineStr">
-        <is>
-          <t>M8-1</t>
-        </is>
-      </c>
+      <c r="I54" s="7" t="inlineStr"/>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>最好的镐等级 ≥ 4</t>
+          <t>最好的镐等级 ≥ 1</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr">
@@ -2697,50 +2705,46 @@
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
-          <t>钻石镐 = 3 钻石 + 2 木棍，要工作台。有两条路：箱子里有 27 颗钻石，您同意就直接拿 3 颗做（J-M8-4a，几秒钟）；不同意就去资源世界 y≈−58 挖（J-M8-4b，要铁镐、穿铁甲、带水桶；那一层岩浆最多，是整条链里最容易死的一次挖矿，所以出发前必须核实资源世界死了不掉东西）。这和钻石剑（M5-6）是同一个问题，一起问您。钻石镐耐久 1561，基本用不坏。</t>
+          <t>木镐 = 3 木板 + 2 木棍,耐久 59;挖 64 块圆石要 2 把</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>M1-7</t>
+          <t>M7-5</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>在田址里、水浇得到的地方把麦田扩到 64 格以上，全是湿地、几乎全种上：按估算这么大的田刚好够全家三口天天吃面包。</t>
+          <t>麦豆白天陪在正在干活的家人旁边（比如看妈妈种地），不跑远、不乱逛。</t>
         </is>
       </c>
       <c r="D55" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E55" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>J-M1-4, J-M1-7, J-M1-7b, wife_find_seeds, wife_gather_seeds</t>
+          <t>J-M7-5</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>G1</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>麦娘</t>
-        </is>
-      </c>
-      <c r="I55" s="7" t="inlineStr">
-        <is>
-          <t>M1-4, M1-6</t>
-        </is>
-      </c>
+          <t>麦豆</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr"/>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>田格余量 ≥ 0 并且 空着的耕地 ≤ 4</t>
+          <t>离最近在干活的家人距离 ≤ 16</t>
         </is>
       </c>
       <c r="K55" s="7" t="inlineStr">
@@ -2750,50 +2754,50 @@
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>算账：64 格湿地整块种满，每格约 48 分钟出 1 个小麦 → 每游戏日约 27 个小麦 = 9 个面包 = 3 人 × 3 个；没水的话要约 140 格。一格水最多浇 80 格，靠边、靠角的格子邻居少，比中间长得慢一点。64 格要 64 颗种子：9 格田一茬净多约 15 颗，大约要 3~4 茬才攒够。木锄 59 次耐久，锄 64 格外加重锄，至少还要再做一把。🔴 零候选审计：原来固定 64 格。G1 的「面包盈余 ≥ 0」不成立（全家吃得比田里产的多，小麦远征路上吃的也算在内）时，G1 变回没完成，可 64 格早就达成了，没有任何小目标去扩田。改成「田格余量 ≥ 0」（C-FRM-22）：田格余量 = 有水的自家田 − 该有的田格数；该有的田格数 = 64 和按实测吃掉的面包算出的格数里取大的，再以田址实际能开的格数封顶。超了就按封顶算完成，并在后台写「田址不够大，面包仍然不够」，不让它变成永远做不完、又没人能推的死目标。</t>
+          <t>🔴 零候选修正：原设计靠 M1-8（帮妈妈收麦子）解决麦豆的零候选，但那要先等您放行；放行之前，麦豆的小目标要么是「不走丢、不死、不打扰孩子」这种做到了就没活的，要么是要放行才能做的砍树，他会一直零候选、一直标红。这一条只用他现在就有的 goto_place 和 idle，符合他「爱跟着大人跑」的人设，也不去打扰真人小孩。只陪在主世界、离家 64 格内、干的不是远征活的家人；停在 4~8 格外，不进田、不挡路。家人一走开，这条就重开，是麦豆的常驻活；没人在家附近干活时算完成，缺口记录记成「在等」。晚上交给 A11。</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>M3-7</t>
+          <t>M8-4</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>全家搬进新房：先把旧箱子里的东西全部搬进新房的箱子，再让每个人把「家」设在新房里，并在新房里自己那张床上点一下，这样以后谁死了都在新房里醒来。现在的家是你亲手定的，要你同意才搬。</t>
+          <t>小麦有一把钻石镐（黑曜石只有钻石镐才挖得动）。</t>
         </is>
       </c>
       <c r="D56" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E56" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>J-M3-7a, J-M3-7b, J-M3-7c</t>
+          <t>J-M8-4a, J-M8-4b</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>G8</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>全家</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr">
         <is>
-          <t>M3-6</t>
+          <t>M8-1</t>
         </is>
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>旧箱子剩余物品数 = 0 并且 共用箱子在新房里 = 1 并且 没搬进新房的家人数 = 0</t>
+          <t>最好的镐等级 ≥ 4</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
@@ -2803,19 +2807,19 @@
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>🔴 本服 Essentials 设的是 respawn-at-home: true + respawn-at-home-bed: true，重生顺序是「床 → 家 → 出生点」。小麦 09-17 已经在村庄那张床 (-73,72,106) 设过重生点，所以现在死了是在村庄醒，不是在旧家；光 set_home 搬不走重生点，必须在新床上点一下。set_home 还要求：脚下是实地、y ≥ 62、离出生点 ≥ 80、旁边 3 格没有水；M3-1 的选址条件已经保证这些。库存约 343 根原木（6 组）、67 根木棍、27 颗钻石，加一些零碎，一两趟就能搬完。</t>
+          <t>钻石镐 = 3 钻石 + 2 木棍，要工作台。有两条路：箱子里有 27 颗钻石，您同意就直接拿 3 颗做（J-M8-4a，几秒钟）；不同意就去资源世界 y≈−58 挖（J-M8-4b，要铁镐、穿铁甲、带水桶；那一层岩浆最多，是整条链里最容易死的一次挖矿，所以出发前必须核实资源世界死了不掉东西）。这和钻石剑（M5-6）是同一个问题，一起问您。钻石镐耐久 1561，基本用不坏。</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>M5-3</t>
+          <t>M3-7</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>从资源世界挖回 64 块圆石,放进家里箱子</t>
+          <t>全家搬进新房：先把旧箱子里的东西全部搬进新房的箱子，再让每个人把「家」设在新房里，并在新房里自己那张床上点一下，这样以后谁死了都在新房里醒来。现在的家是你亲手定的，要你同意才搬。</t>
         </is>
       </c>
       <c r="D57" s="7" t="n">
@@ -2826,27 +2830,27 @@
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>J-M5-3, J-M5-3b</t>
+          <t>J-M3-7a, J-M3-7b, J-M3-7c</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>G5</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="I57" s="7" t="inlineStr">
         <is>
-          <t>M5-2</t>
+          <t>M3-6</t>
         </is>
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>箱子里圆石 ≥ 64</t>
+          <t>旧箱子剩余物品数 = 0 并且 共用箱子在新房里 = 1 并且 没搬进新房的家人数 = 0</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr">
@@ -2856,19 +2860,19 @@
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>原来挂的 J-M5-3 只有「去资源世界入口 → 回家 → 存箱子」三步，中间没有挖，改挂 J-M5-3b（带挖石头这一步，回主世界用 /home base）。前置 M5-2（有镐）按「完成过」算；镐用坏了，由 J-M5-3b 的「还要满足：最好的镐等级 ≥ 1」挡住，不会空手去。圆石是打龙路线的底料（熔炉、石镐、下界搭桥和挡火球），小麦出远门从箱子拿走 64 块后，这条会重开去补，这是对的。y &lt; 0 挖出来的深板岩圆石也算。出发前要求资源世界死了不掉东西（C-END-18）。</t>
+          <t>🔴 本服 Essentials 设的是 respawn-at-home: true + respawn-at-home-bed: true，重生顺序是「床 → 家 → 出生点」。小麦 09-17 已经在村庄那张床 (-73,72,106) 设过重生点，所以现在死了是在村庄醒，不是在旧家；光 set_home 搬不走重生点，必须在新床上点一下。set_home 还要求：脚下是实地、y ≥ 62、离出生点 ≥ 80、旁边 3 格没有水；M3-1 的选址条件已经保证这些。库存约 343 根原木（6 组）、67 根木棍、27 颗钻石，加一些零碎，一两趟就能搬完。</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>M8-5</t>
+          <t>M5-3</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>麦家攒够 10 块黑曜石（搭一个下界传送门框的量）：小麦在资源世界找到岩浆，浇上水变成黑曜石，再用钻石镐挖回来。</t>
+          <t>从资源世界挖回 64 块圆石,放进家里箱子</t>
         </is>
       </c>
       <c r="D58" s="7" t="n">
@@ -2879,12 +2883,12 @@
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>J-M8-5</t>
+          <t>J-M5-3, J-M5-3b</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>G8</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr">
@@ -2894,12 +2898,12 @@
       </c>
       <c r="I58" s="7" t="inlineStr">
         <is>
-          <t>M8-3, M8-4</t>
+          <t>M5-2</t>
         </is>
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>黑曜石的家底 ≥ 10</t>
+          <t>箱子里圆石 ≥ 64</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
@@ -2909,60 +2913,60 @@
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
-          <t>传送门框最少 4 宽 5 高，四个角可以不放，要 10 块。流水流过岩浆源，会把它变成黑曜石；钻石镐挖一块约 9.4 秒，别的镐挖不下来。家底把已经砌进自家门框的也算上，所以门搭好以后这条不会重开；门被人拆了、黑曜石掉了，才重开。只在资源世界做：主世界的岩浆湖可能在别人家旁边。地表岩浆湖在 1.18 以后不多，找不到就去 y≈−54 以下的洞穴（那一层岩浆最多）。掉进岩浆是最快的死法（每 0.5 秒 4 点血），出事交给常驻层 A8 直接传送走。</t>
+          <t>原来挂的 J-M5-3 只有「去资源世界入口 → 回家 → 存箱子」三步，中间没有挖，改挂 J-M5-3b（带挖石头这一步，回主世界用 /home base）。前置 M5-2（有镐）按「完成过」算；镐用坏了，由 J-M5-3b 的「还要满足：最好的镐等级 ≥ 1」挡住，不会空手去。圆石是打龙路线的底料（熔炉、石镐、下界搭桥和挡火球），小麦出远门从箱子拿走 64 块后，这条会重开去补，这是对的。y &lt; 0 挖出来的深板岩圆石也算。出发前要求资源世界死了不掉东西（C-END-18）。</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>M1-9</t>
+          <t>M8-5</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>粮箱里的面包补到 18 个（够全家吃两天），被家人拿走就接着补。</t>
+          <t>麦家攒够 10 块黑曜石（搭一个下界传送门框的量）：小麦在资源世界找到岩浆，浇上水变成黑曜石，再用钻石镐挖回来。</t>
         </is>
       </c>
       <c r="D59" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E59" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>J-M1-4, J-M1-9, wife_bread, wife_store_crop</t>
+          <t>J-M8-5</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>G1</t>
+          <t>G8</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>麦娘</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr">
         <is>
-          <t>M1-3</t>
+          <t>M8-3, M8-4</t>
         </is>
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>粮箱里的面包 ≥ 18</t>
+          <t>黑曜石的家底 ≥ 10</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>🔴 零候选审计补的。G1 要求粮箱常备 18 个面包，但下面只有 M1-3「第一次走通、有 3 个」：粮箱到 3 个以后，3 到 18 之间没有任何小目标管，麦娘会零候选，G1 却一直没完成。家人一拿面包（A14 口粮、小麦远征），这条就重开，是麦娘的常驻活。优先级 5：原稿的 4 和 M1-7（扩田）同档，每次都会触发 T1 去问模型「先补面包还是先扩田」，这件事代码能定——日常口粮有 A14/A4 保底，扩田本身就是在提高面包产量，所以扩田在前。G8 的 M8-7 在这个基础上再加到 34。</t>
+          <t>传送门框最少 4 宽 5 高，四个角可以不放，要 10 块。流水流过岩浆源，会把它变成黑曜石；钻石镐挖一块约 9.4 秒，别的镐挖不下来。家底把已经砌进自家门框的也算上，所以门搭好以后这条不会重开；门被人拆了、黑曜石掉了，才重开。只在资源世界做：主世界的岩浆湖可能在别人家旁边。地表岩浆湖在 1.18 以后不多，找不到就去 y≈−54 以下的洞穴（那一层岩浆最多）。掉进岩浆是最快的死法（每 0.5 秒 4 点血），出事交给常驻层 A8 直接传送走。</t>
         </is>
       </c>
     </row>
@@ -2983,11 +2987,7 @@
       <c r="E60" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>make_sword</t>
-        </is>
-      </c>
+      <c r="F60" s="7" t="inlineStr"/>
       <c r="G60" s="7" t="inlineStr">
         <is>
           <t>G5</t>
@@ -5463,7 +5463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G150"/>
+  <dimension ref="A1:G157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>M3-3, T4</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr"/>
@@ -5624,7 +5624,7 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>M7-1, M7-3</t>
+          <t>M7-3</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr"/>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>M3-3, T4</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>A18, T8</t>
+          <t>A18, M5-1, T8</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr"/>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>M6-1, T5</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>M5-1, M5-4, M5-6, T8</t>
+          <t>M5-1, T8</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr"/>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>M3-3, T4</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr"/>
@@ -6109,17 +6109,17 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>wife_make_hoe</t>
+          <t>wife_harvest</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>自己做一把锄头</t>
+          <t>收割熟了的庄稼</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>M1-1</t>
+          <t>M1-4, M1-8</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr"/>
@@ -6142,17 +6142,17 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>wife_plant</t>
+          <t>wife_make_hoe</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>把种子种下去</t>
+          <t>自己做一把锄头</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>M1-2</t>
+          <t>M1-1</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr"/>
@@ -6175,17 +6175,17 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>wife_store</t>
+          <t>wife_planks</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>把家当收进箱子</t>
+          <t>把原木做成木板</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>A12, A19, J-A12-2</t>
+          <t>M3-2</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
@@ -6208,17 +6208,17 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>wife_store_crop</t>
+          <t>wife_plant</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>把粮食收进粮箱</t>
+          <t>把种子种下去</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>A14, M1-3, M1-9, M8-7</t>
+          <t>M1-2, M1-4, M1-8</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr"/>
@@ -6241,17 +6241,17 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>wife_take_planks</t>
+          <t>wife_store</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>从箱子里拿木板</t>
+          <t>把家当收进箱子</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>M1-1</t>
+          <t>A12, A19, J-A12-2, M6-1</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr"/>
@@ -6274,138 +6274,126 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>J-A1-1</t>
+          <t>wife_store_crop</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>残血(≤6)又有危险:立刻传送脱险(人在家门口就去出生点)</t>
+          <t>把粮食收进粮箱</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>全家</t>
-        </is>
-      </c>
+          <t>A14, M1-3, M1-9, M8-7</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr"/>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>escape_tp</t>
+          <t>(已写好,在 scripts.json 里)</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>新写</t>
+          <t>现有</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>现在就能做</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>J-A1-2</t>
+          <t>wife_take_planks</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>血不到一半、还有危险(或传送在冷却):先跑开</t>
+          <t>从箱子里拿木板</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>全家</t>
-        </is>
-      </c>
+          <t>M1-1</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr"/>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>flee</t>
+          <t>(已写好,在 scripts.json 里)</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>新写</t>
+          <t>现有</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>现在就能做</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>J-A1-3</t>
+          <t>wife_till</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>没危险了:吃到能回血,原地歇着,血涨回14点</t>
+          <t>在家门口耕一块地</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>全家</t>
-        </is>
-      </c>
+          <t>M1-2</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr"/>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>eat(跳过条件: 饱食度 ≥ 18) → idle(秒=8; 跳过条件: 饱食度 ≤ 17)</t>
+          <t>(已写好,在 scripts.json 里)</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>新写</t>
+          <t>现有</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>现在就能做</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>J-A2-1</t>
+          <t>J-A1-1</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>小麦把贴脸的普通近战怪打掉(怪不多、不在水里、不是刚复活、怪没着火)</t>
+          <t>残血(≤6)又有危险:立刻传送脱险(人在家门口就去出生点)</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>fight</t>
+          <t>escape_tp</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -6415,34 +6403,34 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>J-A2-2</t>
+          <t>J-A1-2</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>麦娘手里有剑时才还手,其余条件同小麦</t>
+          <t>血不到一半、还有危险(或传送在冷却):先跑开</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>麦娘</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>fight</t>
+          <t>flee</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -6452,24 +6440,24 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>J-A2-3</t>
+          <t>J-A1-3</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>还在挨打,或刚复活就被怪贴脸:传送脱险(在家门口就去出生点)</t>
+          <t>没危险了:吃到能回血,原地歇着,血涨回14点</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -6479,7 +6467,7 @@
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>escape_tp</t>
+          <t>eat(跳过条件: 饱食度 ≥ 18) → idle(秒=8; 跳过条件: 饱食度 ≤ 17)</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -6489,19 +6477,19 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>J-A2-4</t>
+          <t>J-A2-1</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>其余情况(麦豆、没剑的麦娘、在水里、怪太多、强怪、嘎枝、着火的僵尸):跑开</t>
+          <t>小麦把贴脸的普通近战怪打掉(怪不多、不在水里、不是刚复活、怪没着火)</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -6511,12 +6499,12 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>全家</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>flee</t>
+          <t>fight</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -6533,27 +6521,27 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>J-A3-1</t>
+          <t>J-A2-2</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>身上有牛奶就喝掉,一次清掉所有坏效果</t>
+          <t>麦娘手里有剑时才还手,其余条件同小麦</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>全家</t>
+          <t>麦娘</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>drink_milk</t>
+          <t>fight</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -6570,17 +6558,17 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>J-A3-2</t>
+          <t>J-A2-3</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>没有牛奶:吃饱、待在原地别冒险,等毒过去</t>
+          <t>还在挨打,或刚复活就被怪贴脸:传送脱险(在家门口就去出生点)</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
@@ -6590,7 +6578,7 @@
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>eat(跳过条件: 饱食度 ≥ 18) → idle(秒=10)</t>
+          <t>escape_tp</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -6600,24 +6588,24 @@
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>J-A4-1</t>
+          <t>J-A2-4</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>背包里有吃的就直接吃</t>
+          <t>其余情况(麦豆、没剑的麦娘、在水里、怪太多、强怪、嘎枝、着火的僵尸):跑开</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
@@ -6627,7 +6615,7 @@
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>eat</t>
+          <t>flee</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -6644,17 +6632,17 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>J-A4-2</t>
+          <t>J-A3-1</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>身上没吃的:回家去粮箱拿面包来吃</t>
+          <t>身上有牛奶就喝掉,一次清掉所有坏效果</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
@@ -6664,7 +6652,7 @@
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件: 离家距离 ≤ 8) → take_from_chest(东西=bread|cooked_*; 地方=粮箱) → eat</t>
+          <t>drink_milk</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -6681,27 +6669,27 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>J-A4-3</t>
+          <t>J-A3-2</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>身上、粮箱都没吃的:小麦去打猎(夜里除非快饿死,否则不去),不打别人的动物</t>
+          <t>没有牛奶:吃饱、待在原地别冒险,等毒过去</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>hunt</t>
+          <t>eat(跳过条件: 饱食度 ≥ 18) → idle(秒=10)</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -6711,24 +6699,24 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>J-A5-1</t>
+          <t>J-A4-1</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>苦力怕已经贴到3格内:立刻传送走</t>
+          <t>背包里有吃的就直接吃</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
@@ -6738,7 +6726,7 @@
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>escape_tp</t>
+          <t>eat</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -6748,24 +6736,24 @@
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>J-A5-2</t>
+          <t>J-A4-2</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>其余情况:只躲苦力怕这一只,朝反方向跑到10格外</t>
+          <t>身上没吃的:回家去粮箱拿面包来吃</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
@@ -6775,7 +6763,7 @@
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>flee(东西=creeper)</t>
+          <t>go_home(跳过条件: 离家距离 ≤ 8) → take_from_chest(东西=bread|cooked_*; 地方=粮箱) → eat</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -6792,17 +6780,17 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>J-A6-1</t>
+          <t>J-A4-3</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>骷髅/掠夺者贴到5格内、血&gt;10、手上有剑:冲上去打(它们近战很弱)</t>
+          <t>身上、粮箱都没吃的:小麦去打猎(夜里除非快饿死,否则不去),不打别人的动物</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
@@ -6812,7 +6800,7 @@
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>fight</t>
+          <t>hunt</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -6822,24 +6810,24 @@
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>J-A6-2</t>
+          <t>J-A5-1</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>血≤8还在被射:传送走</t>
+          <t>苦力怕已经贴到3格内:立刻传送走</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
@@ -6866,17 +6854,17 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>J-A6-3</t>
+          <t>J-A5-2</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>其余情况:先在身前放一块泥土或圆石挡箭,再跑出射程</t>
+          <t>其余情况:只躲苦力怕这一只,朝反方向跑到10格外</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
@@ -6886,7 +6874,7 @@
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>cover_arrows(东西=dirt|cobblestone) → flee</t>
+          <t>flee(东西=creeper)</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -6903,27 +6891,27 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>J-A7-1</t>
+          <t>J-A6-1</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>氧气剩不到五分之一,或脑袋卡进方块:立刻传送走</t>
+          <t>骷髅/掠夺者贴到5格内、血&gt;10、手上有剑:冲上去打(它们近战很弱)</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>全家</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>escape_tp</t>
+          <t>fight</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -6933,24 +6921,24 @@
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>J-A7-2</t>
+          <t>J-A6-2</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>脑袋卡在方块里但传送用不了:原地挪开</t>
+          <t>血≤8还在被射:传送走</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -6960,7 +6948,7 @@
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>wander(秒=2)</t>
+          <t>escape_tp</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -6970,24 +6958,24 @@
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>J-A7-3</t>
+          <t>J-A6-3</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>其余情况:往上浮、往岸边游</t>
+          <t>其余情况:先在身前放一块泥土或圆石挡箭,再跑出射程</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
@@ -6997,7 +6985,7 @@
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>surface</t>
+          <t>cover_arrows(东西=dirt|cobblestone) → flee</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -7014,17 +7002,17 @@
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>J-A8-1</t>
+          <t>J-A7-1</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>在岩浆里:立刻传送走</t>
+          <t>氧气剩不到五分之一,或脑袋卡进方块:立刻传送走</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>A8</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -7051,17 +7039,17 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>J-A8-2</t>
+          <t>J-A7-2</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>在岩浆里但传送用不了:往最近的实地爬出去</t>
+          <t>脑袋卡在方块里但传送用不了:原地挪开</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>A8</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -7071,7 +7059,7 @@
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>escape_lava</t>
+          <t>wander(秒=2)</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
@@ -7081,24 +7069,24 @@
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>J-A8-3</t>
+          <t>J-A7-3</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>身上着火、12格内记得有水:跳进水里灭火</t>
+          <t>其余情况:往上浮、往岸边游</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>A8</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -7108,7 +7096,7 @@
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方=水源)</t>
+          <t>surface</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
@@ -7118,19 +7106,19 @@
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>J-A8-4</t>
+          <t>J-A8-1</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>着火但附近没水:挪开几步离开火源,吃饱顶住等火灭</t>
+          <t>在岩浆里:立刻传送走</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
@@ -7145,7 +7133,7 @@
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>wander(秒=3) → eat(跳过条件: 饱食度 ≥ 18)</t>
+          <t>escape_tp</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
@@ -7155,24 +7143,24 @@
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>J-A9-1</t>
+          <t>J-A8-2</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>按血量切换走路时最多能往下跳几格(现有代码,不是动作)</t>
+          <t>在岩浆里但传送用不了:往最近的实地爬出去</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>A9</t>
+          <t>A8</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
@@ -7180,7 +7168,11 @@
           <t>全家</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr"/>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>escape_lava</t>
+        </is>
+      </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
           <t>新写</t>
@@ -7188,24 +7180,24 @@
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>现在就能做</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>J-A10-1</t>
+          <t>J-A8-3</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>卡住了:传送走(escape_tp 自己决定回家还是去出生点)</t>
+          <t>身上着火、12格内记得有水:跳进水里灭火</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>A8</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
@@ -7215,7 +7207,7 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>escape_tp</t>
+          <t>goto_place(地方=水源)</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -7225,24 +7217,24 @@
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>J-A11-1</t>
+          <t>J-A8-4</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>有自家的空床、周围没怪:去睡</t>
+          <t>着火但附近没水:挪开几步离开火源,吃饱顶住等火灭</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>A11</t>
+          <t>A8</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
@@ -7252,7 +7244,7 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>sleep</t>
+          <t>wander(秒=3) → eat(跳过条件: 饱食度 ≥ 18)</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -7262,24 +7254,24 @@
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>J-A11-2</t>
+          <t>J-A9-1</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>没有空床但背包里材料够:先做一张床,放在家门口再睡</t>
+          <t>按血量切换走路时最多能往下跳几格(现有代码,不是动作)</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>A11</t>
+          <t>A9</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -7287,11 +7279,7 @@
           <t>全家</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>craft(东西=bedIWouldCraft() 选出的颜色的床(如 white_bed)) → sleep</t>
-        </is>
-      </c>
+      <c r="E52" s="7" t="inlineStr"/>
       <c r="F52" s="7" t="inlineStr">
         <is>
           <t>新写</t>
@@ -7299,24 +7287,24 @@
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>现在就能做</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>J-A11-3</t>
+          <t>J-A10-1</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>睡不了,但家里能安全过夜(有顶、有光、门洞堵上):回屋待到天亮</t>
+          <t>卡住了:传送走(escape_tp 自己决定回家还是去出生点)</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>A11</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
@@ -7326,7 +7314,7 @@
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件: 在屋里 = 1) → idle(秒=30)</t>
+          <t>escape_tp</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
@@ -7336,24 +7324,24 @@
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>J-A12-1</t>
+          <t>J-A11-1</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>每秒自动扔掉真正的杂物(现有代码,不是动作,不占身体)</t>
+          <t>有自家的空床、周围没怪:去睡</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>A12</t>
+          <t>A11</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
@@ -7361,7 +7349,11 @@
           <t>全家</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr"/>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>sleep</t>
+        </is>
+      </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
           <t>新写</t>
@@ -7369,24 +7361,24 @@
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>现在就能做</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>J-A12-2</t>
+          <t>J-A11-2</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>回家把能存的东西存进箱子</t>
+          <t>没有空床但背包里材料够:先做一张床,放在家门口再睡</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>A12</t>
+          <t>A11</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
@@ -7396,7 +7388,7 @@
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件: 离家距离 ≤ 8) → store_items</t>
+          <t>craft(东西=bedIWouldCraft() 选出的颜色的床(如 white_bed)) → sleep</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
@@ -7406,24 +7398,24 @@
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>J-A12-3</t>
+          <t>J-A11-3</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>箱子满了、身上带着空箱子:贴着家里的箱子放下再存</t>
+          <t>睡不了,但家里能安全过夜(有顶、有光、门洞堵上):回屋待到天亮</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>A12</t>
+          <t>A11</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
@@ -7433,7 +7425,7 @@
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件: 离家距离 ≤ 8) → place_chest(地方=紧贴家里现有箱子) → store_items</t>
+          <t>go_home(跳过条件: 在屋里 = 1) → idle(秒=30)</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
@@ -7443,19 +7435,19 @@
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>J-A12-4</t>
+          <t>J-A12-1</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>箱子满了、身上没空箱子但有8块木板:先做一口箱子</t>
+          <t>每秒自动扔掉真正的杂物(现有代码,不是动作,不占身体)</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
@@ -7468,11 +7460,7 @@
           <t>全家</t>
         </is>
       </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>craft(东西=chest)</t>
-        </is>
-      </c>
+      <c r="E57" s="7" t="inlineStr"/>
       <c r="F57" s="7" t="inlineStr">
         <is>
           <t>新写</t>
@@ -7480,24 +7468,24 @@
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>现在就能做</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>J-A13-1</t>
+          <t>J-A12-2</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>白天、周围安全时,去把登记过的挡箭块一块块拆回来</t>
+          <t>回家把能存的东西存进箱子</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>A13</t>
+          <t>A12</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
@@ -7507,7 +7495,7 @@
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>pickup_cover</t>
+          <t>go_home(跳过条件: 离家距离 ≤ 8) → store_items</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
@@ -7517,24 +7505,24 @@
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>J-A14</t>
+          <t>J-A12-3</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>身上面包快吃完了，就回家从粮箱拿 3 个面包揣着。</t>
+          <t>箱子满了、身上带着空箱子:贴着家里的箱子放下再存</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>A14</t>
+          <t>A12</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
@@ -7544,7 +7532,7 @@
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 24) → take_from_chest(东西：口粮（只拿面包、一次 3 个；要先加这个名字）)</t>
+          <t>go_home(跳过条件: 离家距离 ≤ 8) → place_chest(地方=紧贴家里现有箱子) → store_items</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
@@ -7561,27 +7549,27 @@
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>J-A15-1</t>
+          <t>J-A12-4</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>小麦睡前，床边只有一两只好打的怪（僵尸、蜘蛛之类），附近没有苦力怕、末影人、骷髅，自己血量足又有剑时，先打掉</t>
+          <t>箱子满了、身上没空箱子但有8块木板:先做一口箱子</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>A15</t>
+          <t>A12</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>fight</t>
+          <t>craft(东西=chest)</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
@@ -7591,24 +7579,24 @@
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>J-A15-2</t>
+          <t>J-A13-1</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>床边有怪睡不成时，回家待在屋里，等床边没怪了再去睡（常常要等到天亮）</t>
+          <t>白天、周围安全时,去把登记过的挡箭块一块块拆回来</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>A15</t>
+          <t>A13</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -7618,7 +7606,7 @@
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离≤8) → idle</t>
+          <t>pickup_cover</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
@@ -7635,27 +7623,27 @@
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>J-A16</t>
+          <t>J-A14</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>新房破了洞、地板被炸或门没了，小麦就拿上木板、半砖和门回去，按原样补上。</t>
+          <t>身上面包快吃完了，就回家从粮箱拿 3 个面包揣着。</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>A16</t>
+          <t>A14</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>take_from_chest(东西=设计定的木板；数量=新房墙缺口数 + 新房屋顶缺口数 + 4；跳过条件：新房墙缺口数 = 0 且 新房屋顶缺口数 = 0) → take_from_chest(东西=半砖；数量=新房地面裸露格数；跳过条件：新房地面裸露格数 = 0) → take_from_chest(东西=门；数量=1；跳过条件：新房有门 = 1) → goto_place(地方=新家；直到 离新家址 ≤ 6；跳过条件：离新家址 ≤ 6) → build_house(阶段=补缺口；直到 新房缺口数 = 0)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 24) → take_from_chest(东西：口粮（只拿面包、一次 3 个；要先加这个名字）)</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
@@ -7672,25 +7660,29 @@
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>J-A17</t>
+          <t>J-A15-1</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>右键把新房的门关上。</t>
+          <t>小麦睡前，床边只有一两只好打的怪（僵尸、蜘蛛之类），附近没有苦力怕、末影人、骷髅，自己血量足又有剑时，先打掉</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>A17</t>
+          <t>A15</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>全家</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="inlineStr"/>
+          <t>小麦</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>fight</t>
+        </is>
+      </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
           <t>新写</t>
@@ -7705,23 +7697,27 @@
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>J-A20</t>
+          <t>J-A15-2</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>回家</t>
+          <t>床边有怪睡不成时，回家待在屋里，等床边没怪了再去睡（常常要等到天亮）</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>A20</t>
-        </is>
-      </c>
-      <c r="D64" s="7" t="inlineStr"/>
+          <t>A15</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>全家</t>
+        </is>
+      </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>go_home</t>
+          <t>go_home(跳过条件：离家距离≤8) → idle</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
@@ -7731,34 +7727,34 @@
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>现在就能做</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>J-A21-1</t>
+          <t>J-A16</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>离他近（32 格内，夜里 16 格内），或者他没家、白天、在 96 格内：走到他跟前，把吃的丢在他身边</t>
+          <t>新房破了洞、地板被炸或门没了，小麦就拿上木板、半砖和门回去，按原样补上。</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>A21</t>
+          <t>A16</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>全家</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>give_to_family(给=分给我的那个家人；东西=正经吃的（先熟肉、再面包；不送汤和煲、金苹果、腐肉；身上留≥2 个面包）；数量=这单能给的份数；地点=他身边)</t>
+          <t>take_from_chest(东西=设计定的木板；数量=新房墙缺口数 + 新房屋顶缺口数 + 4；跳过条件：新房墙缺口数 = 0 且 新房屋顶缺口数 = 0) → take_from_chest(东西=半砖；数量=新房地面裸露格数；跳过条件：新房地面裸露格数 = 0) → take_from_chest(东西=门；数量=1；跳过条件：新房有门 = 1) → goto_place(地方=新家；直到 离新家址 ≤ 6；跳过条件：离新家址 ≤ 6) → build_house(阶段=补缺口；直到 新房缺口数 = 0)</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
@@ -7775,17 +7771,17 @@
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>J-A21-2</t>
+          <t>J-A17</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>离得远、两人的家都在粮箱旁：两人都传送回家，在粮箱旁交</t>
+          <t>右键把新房的门关上。</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>A21</t>
+          <t>A17</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
@@ -7793,11 +7789,7 @@
           <t>全家</t>
         </is>
       </c>
-      <c r="E66" s="7" t="inlineStr">
-        <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → goto_place(地方=粮箱（C-NAV-1 加的地名）) → give_to_family(给=分给我的那个家人；东西=正经吃的（先熟肉、再面包，身上留≥2 个面包）；数量=这单能给的份数；地点=粮箱旁 4 格内，他到了才丢)</t>
-        </is>
-      </c>
+      <c r="E66" s="7" t="inlineStr"/>
       <c r="F66" s="7" t="inlineStr">
         <is>
           <t>新写</t>
@@ -7812,27 +7804,23 @@
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>J-A21-3</t>
+          <t>J-A20</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>我身上没有能分的，但粮箱里有：替他回家从粮箱拿 3 份正经吃的（先面包、再熟肉），再送给他（主要是给不会开箱子、也没有家的麦豆）</t>
+          <t>回家</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>A21</t>
-        </is>
-      </c>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>全家</t>
-        </is>
-      </c>
+          <t>A20</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr"/>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → goto_place(地方=粮箱) → take_from_chest(东西=正经吃的，一次 3 份（先面包、再熟肉）；拿之前记下身上份数，差值就是替他拿的份数) → give_to_family(给=分给我的那个家人；东西=刚替他拿的；数量=替他拿的份数（不受我的保底限制）；地点=按送吃的交接地点)</t>
+          <t>go_home</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
@@ -7842,24 +7830,24 @@
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>现在就能做</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>J-A22-1</t>
+          <t>J-A21-1</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>他来我这儿交：原地站着、面朝他，东西落地就走上去捡</t>
+          <t>离他近（32 格内，夜里 16 格内），或者他没家、白天、在 96 格内：走到他跟前，把吃的丢在他身边</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>A22</t>
+          <t>A21</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
@@ -7869,7 +7857,7 @@
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>idle(站着别动、面朝送东西的家人；直到：他丢出东西了=1；最多等到锁作废) → pick_up_drop(只捡这一单丢在我 6 格内、种类数量对得上的)</t>
+          <t>give_to_family(给=分给我的那个家人；东西=正经吃的（先熟肉、再面包；不送汤和煲、金苹果、腐肉；身上留≥2 个面包）；数量=这单能给的份数；地点=他身边)</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
@@ -7886,17 +7874,17 @@
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>J-A22-2</t>
+          <t>J-A21-2</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>约好回家交：传送回家，走到粮箱旁站着等，东西落地就捡</t>
+          <t>离得远、两人的家都在粮箱旁：两人都传送回家，在粮箱旁交</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>A22</t>
+          <t>A21</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
@@ -7906,7 +7894,7 @@
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → goto_place(地方=粮箱（C-NAV-1 加的地名）) → idle(直到：他丢出东西了=1；最多等到锁作废) → pick_up_drop(只捡这一单丢在我 6 格内、种类数量对得上的)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → goto_place(地方=粮箱（C-NAV-1 加的地名）) → give_to_family(给=分给我的那个家人；东西=正经吃的（先熟肉、再面包，身上留≥2 个面包）；数量=这单能给的份数；地点=粮箱旁 4 格内，他到了才丢)</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
@@ -7923,17 +7911,17 @@
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>J-A22-3</t>
+          <t>J-A21-3</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>家人来接我：原地等他走到跟前，然后跟着他走回家</t>
+          <t>我身上没有能分的，但粮箱里有：替他回家从粮箱拿 3 份正经吃的（先面包、再熟肉），再送给他（主要是给不会开箱子、也没有家的麦豆）</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>A22</t>
+          <t>A21</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
@@ -7943,7 +7931,7 @@
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>idle(直到：离来接我的家人 ≤ 6；最多等到锁作废) → follow_player(跟=来接我的家人（执行闸只许跟家人）；直到：离全家的家 ≤ 16)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → goto_place(地方=粮箱) → take_from_chest(东西=正经吃的，一次 3 份（先面包、再熟肉）；拿之前记下身上份数，差值就是替他拿的份数) → give_to_family(给=分给我的那个家人；东西=刚替他拿的；数量=替他拿的份数（不受我的保底限制）；地点=按送吃的交接地点)</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
@@ -7960,12 +7948,12 @@
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>J-A22-4</t>
+          <t>J-A22-1</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>麦豆交给我、要我帮忙存的东西：收下后马上回家存进箱子</t>
+          <t>他来我这儿交：原地站着、面朝他，东西落地就走上去捡</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
@@ -7975,12 +7963,12 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>任意</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → store_items(存进大箱子；存完在锁里写「已存好」并删锁)</t>
+          <t>idle(站着别动、面朝送东西的家人；直到：他丢出东西了=1；最多等到锁作废) → pick_up_drop(只捡这一单丢在我 6 格内、种类数量对得上的)</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
@@ -7990,24 +7978,24 @@
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>J-A23-1</t>
+          <t>J-A22-2</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>走到他跟前，把那把工具丢在他身边</t>
+          <t>约好回家交：传送回家，走到粮箱旁站着等，东西落地就捡</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>A23</t>
+          <t>A22</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
@@ -8017,7 +8005,7 @@
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>give_to_family(给=缺这件工具的家人；东西=多余的那种工具里耐久剩得最多的一把；数量=1；地点=他身边（两人都在家附近时就在家里）)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → goto_place(地方=粮箱（C-NAV-1 加的地名）) → idle(直到：他丢出东西了=1；最多等到锁作废) → pick_up_drop(只捡这一单丢在我 6 格内、种类数量对得上的)</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
@@ -8034,27 +8022,27 @@
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>J-A24-1</t>
+          <t>J-A22-3</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>跑到他身边，只打围着他的那几只怪，打完就回去接着干原来的活</t>
+          <t>家人来接我：原地等他走到跟前，然后跟着他走回家</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>A24</t>
+          <t>A22</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>fight(护着=被围攻的家人；只打他 6 格内主动攻击的普通近战怪；离他不超过 12 格；最多 60 秒)</t>
+          <t>idle(直到：离来接我的家人 ≤ 6；最多等到锁作废) → follow_player(跟=来接我的家人（执行闸只许跟家人）；直到：离全家的家 ≤ 16)</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
@@ -8064,34 +8052,34 @@
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>缺动作</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>J-A25-1</t>
+          <t>J-A22-4</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>往能护着我的大人那边跑，躲到他身后</t>
+          <t>麦豆交给我、要我帮忙存的东西：收下后马上回家存进箱子</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>A25</t>
+          <t>A22</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>麦豆</t>
+          <t>任意</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>flee(往=能护着我的家人；到他身后 2 格（背对怪的那一侧）就站住)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → store_items(存进大箱子；存完在锁里写「已存好」并删锁)</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
@@ -8101,34 +8089,34 @@
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>J-A26-1</t>
+          <t>J-A23-1</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>朝他走过去（看得见他以后，跟着他的实时位置走）</t>
+          <t>走到他跟前，把那把工具丢在他身边</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>A26</t>
+          <t>A23</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>小麦 / 麦娘</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>walk_to_family(目标=回不了家的家人；看不见时用状态板坐标，每 10 秒刷新；最多 300 秒)</t>
+          <t>give_to_family(给=缺这件工具的家人；东西=多余的那种工具里耐久剩得最多的一把；数量=1；地点=他身边（两人都在家附近时就在家里）)</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
@@ -8145,27 +8133,27 @@
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>J-A26-2</t>
+          <t>J-A24-1</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>走到他身边后，领着他走回家，他跟丢了就停下等</t>
+          <t>跑到他身边，只打围着他的那几只怪，打完就回去接着干原来的活</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>A26</t>
+          <t>A24</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>小麦 / 麦娘</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>lead_home(被接的人=回不了家的家人；他落后超过 12 格就停下等；直到：他离全家的家 ≤ 16；最多 600 秒；离天黑秒数 ≤ 60 时放弃)</t>
+          <t>fight(护着=被围攻的家人；只打他 6 格内主动攻击的普通近战怪；离他不超过 12 格；最多 60 秒)</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
@@ -8175,24 +8163,24 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺动作</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>J-A27-1</t>
+          <t>J-A25-1</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>会存箱子的家人就在附近：走到她跟前，把能存的东西丢给她</t>
+          <t>往能护着我的大人那边跑，躲到他身后</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>A27</t>
+          <t>A25</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
@@ -8202,7 +8190,7 @@
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>give_to_family(给=能接手的家人；东西=可存的东西（不含吃的、唯一的工具、贵重）；最多 5 格；地点=她身边)</t>
+          <t>flee(往=能护着我的家人；到他身后 2 格（背对怪的那一侧）就站住)</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
@@ -8219,27 +8207,27 @@
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>J-A27-2</t>
+          <t>J-A26-1</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>离得远、两人都有家：回家，把能存的东西丢给回到家的麦娘（或小麦）</t>
+          <t>朝他走过去（看得见他以后，跟着他的实时位置走）</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>A27</t>
+          <t>A26</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>麦豆</t>
+          <t>小麦 / 麦娘</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → give_to_family(给=能接手的家人；东西=可存的东西（不含吃的、唯一的工具、贵重）；最多 5 格；地点=家里大箱子旁 4 格内，她到了才丢)</t>
+          <t>walk_to_family(目标=回不了家的家人；看不见时用状态板坐标，每 10 秒刷新；最多 300 秒)</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
@@ -8256,27 +8244,27 @@
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>J-A28-1</t>
+          <t>J-A26-2</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>把多出来的吃的存进粮箱</t>
+          <t>走到他身边后，领着他走回家，他跟丢了就停下等</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>A28</t>
+          <t>A26</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>全家</t>
+          <t>小麦 / 麦娘</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>store_items(箱子=粮箱；东西=多出来的正经吃的（先熟肉、后面包；身上留 6 份、至少 2 个面包；粮箱最多补到 12 份）)</t>
+          <t>lead_home(被接的人=回不了家的家人；他落后超过 12 格就停下等；直到：他离全家的家 ≤ 16；最多 600 秒；离天黑秒数 ≤ 60 时放弃)</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
@@ -8286,32 +8274,36 @@
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>缺动作</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>J-G3-0a</t>
+          <t>J-A27-1</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>如果库存只凑得出一种木头样式，就由代码直接定下来，不问模型。</t>
+          <t>会存箱子的家人就在附近：走到她跟前，把能存的东西丢给她</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>M3-2</t>
+          <t>A27</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="inlineStr"/>
+          <t>麦豆</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>give_to_family(给=能接手的家人；东西=可存的东西（不含吃的、唯一的工具、贵重）；最多 5 格；地点=她身边)</t>
+        </is>
+      </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
           <t>新写</t>
@@ -8326,25 +8318,29 @@
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>J-G3-0b</t>
+          <t>J-A27-2</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>如果新房里只有一种合法的家具摆法，就由代码直接定，不问模型。</t>
+          <t>离得远、两人都有家：回家，把能存的东西丢给回到家的麦娘（或小麦）</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>M3-6</t>
+          <t>A27</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>麦娘</t>
-        </is>
-      </c>
-      <c r="E81" s="7" t="inlineStr"/>
+          <t>麦豆</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → give_to_family(给=能接手的家人；东西=可存的东西（不含吃的、唯一的工具、贵重）；最多 5 格；地点=家里大箱子旁 4 格内，她到了才丢)</t>
+        </is>
+      </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
           <t>新写</t>
@@ -8359,27 +8355,27 @@
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>J-M1-0</t>
+          <t>J-A28-1</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>小麦往离出生点远的方向转一圈，程序边走边给看到的空地打分，记下最适合种田的一块。</t>
+          <t>把多出来的吃的存进粮箱</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>M1-0</t>
+          <t>A28</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>explore(方向：离出生点更远的那一侧（东/南/西/北，由代码按出生点方位算，不问模型）)</t>
+          <t>store_items(箱子=粮箱；东西=多出来的正经吃的（先熟肉、后面包；身上留 6 份、至少 2 个面包；粮箱最多补到 12 份）)</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
@@ -8389,36 +8385,32 @@
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺动作</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>J-M1-2</t>
+          <t>J-G3-0a</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>走到田里，锄完这一批地马上种上麦子，直到 9 格都种满。</t>
+          <t>如果库存只凑得出一种木头样式，就由代码直接定下来，不问模型。</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>M1-2</t>
+          <t>M3-2</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>麦娘</t>
-        </is>
-      </c>
-      <c r="E83" s="7" t="inlineStr">
-        <is>
-          <t>goto_place(地方：田；跳过条件：离田距离 ≤ 16) → till_soil(跳过条件：耕好的地 ≥ 9) → plant_seeds(跳过条件：有种子 = 0)</t>
-        </is>
-      </c>
+          <t>小麦</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr"/>
       <c r="F83" s="7" t="inlineStr">
         <is>
           <t>新写</t>
@@ -8433,17 +8425,17 @@
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>J-M1-4</t>
+          <t>J-G3-0b</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>田里攒够几株熟麦子就去收，收完当场把空出来的格子补种上。</t>
+          <t>如果新房里只有一种合法的家具摆法，就由代码直接定，不问模型。</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>M1-4</t>
+          <t>M3-6</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
@@ -8451,11 +8443,7 @@
           <t>麦娘</t>
         </is>
       </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t>goto_place(地方：田；跳过条件：离田距离 ≤ 16) → harvest_crop → plant_seeds(跳过条件：有种子 = 0)</t>
-        </is>
-      </c>
+      <c r="E84" s="7" t="inlineStr"/>
       <c r="F84" s="7" t="inlineStr">
         <is>
           <t>新写</t>
@@ -8470,17 +8458,17 @@
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>J-M1-6</t>
+          <t>J-M1-0</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>小麦从箱子拿 3 个铁锭做个铁桶，去最近的水边装一桶水，回来倒进田边挖好的一格坑里。</t>
+          <t>小麦往离出生点远的方向转一圈，程序边走边给看到的空地打分，记下最适合种田的一块。</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>M1-6</t>
+          <t>M1-0</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
@@ -8490,7 +8478,7 @@
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 24) → take_from_chest(东西：铁锭（要先加这个名字，一次拿 3 个）；跳过条件：身上有桶 ≥ 1) → craft(东西：bucket；跳过条件：身上有桶 ≥ 1) → goto_place(地方：田；跳过条件：离田距离 ≤ 16)</t>
+          <t>explore(方向：离出生点更远的那一侧（东/南/西/北，由代码按出生点方位算，不问模型）)</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
@@ -8507,17 +8495,17 @@
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>J-M1-7</t>
+          <t>J-M1-2</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>在水浇得到的地方把麦田一批批扩大，锄一批种一批，直到 64 格。</t>
+          <t>走到田里，锄完这一批地马上种上麦子，直到 9 格都种满。</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>M1-7</t>
+          <t>M1-2</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
@@ -8527,7 +8515,7 @@
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方：田；跳过条件：离田距离 ≤ 16) → till_soil(跳过条件：有水的自家田 ≥ 64) → plant_seeds(跳过条件：有种子 = 0)</t>
+          <t>goto_place(地方：田；跳过条件：离田距离 ≤ 16) → till_soil(跳过条件：耕好的地 ≥ 9) → plant_seeds(跳过条件：有种子 = 0)</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
@@ -8544,17 +8532,17 @@
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>J-M1-7b</t>
+          <t>J-M1-4</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>在水浇得到的地方把麦田一批批扩大，锄一批种一批，直到田的大小够全家吃（按实测吃掉的面包算，最少 64 格）。</t>
+          <t>田里攒够几株熟麦子就去收，收完当场把空出来的格子补种上。</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>M1-7</t>
+          <t>M1-4</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
@@ -8564,7 +8552,7 @@
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方=田；跳过条件：离田距离 ≤ 16) → till_soil(跳过条件：田格余量 ≥ 0) → plant_seeds(跳过条件：有种子 = 0)</t>
+          <t>goto_place(地方：田；跳过条件：离田距离 ≤ 16) → harvest_crop → plant_seeds(跳过条件：有种子 = 0)</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
@@ -8581,27 +8569,27 @@
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>J-M1-8</t>
+          <t>J-M1-6</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>麦豆白天去自家田里收熟麦子，当场种回去，再把小麦存进粮箱给妈妈做面包。</t>
+          <t>小麦从箱子拿 3 个铁锭做个铁桶，去最近的水边装一桶水，回来倒进田边挖好的一格坑里。</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>M1-8</t>
+          <t>M1-6</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>麦豆</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方=田；跳过条件：离田距离 ≤ 16) → harvest_crop(先拿田里收割锁，拿不到就跳过；只收自家田登记簿里的格子) → plant_seeds(收完的格子当场种回去；跳过条件：有种子 = 0) → go_home(跳过条件：离家距离 ≤ 8) → store_crop(麦豆身上只留 3 个面包、16 颗种子，小麦全部进粮箱)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 24) → take_from_chest(东西：铁锭（要先加这个名字，一次拿 3 个）；跳过条件：身上有桶 ≥ 1) → craft(东西：bucket；跳过条件：身上有桶 ≥ 1) → goto_place(地方：田；跳过条件：离田距离 ≤ 16)</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
@@ -8618,17 +8606,17 @@
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>J-M1-9</t>
+          <t>J-M1-7</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>麦娘从粮箱拿出麦豆和自己存进去的小麦，做成面包再放回粮箱。</t>
+          <t>在水浇得到的地方把麦田一批批扩大，锄一批种一批，直到 64 格。</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>M1-9</t>
+          <t>M1-7</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
@@ -8638,7 +8626,7 @@
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=小麦，从粮箱拿，拿 3 的倍数、最多 27 个) → craft(东西=bread) → store_crop(面包进粮箱（她身上照常留 3 个）)</t>
+          <t>goto_place(地方：田；跳过条件：离田距离 ≤ 16) → till_soil(跳过条件：有水的自家田 ≥ 64) → plant_seeds(跳过条件：有种子 = 0)</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
@@ -8655,17 +8643,17 @@
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>J-M2-1-1</t>
+          <t>J-M1-7b</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>麦娘白天回家，从箱子拿线合成白羊毛，配同种木板，用家里现有的工作台做床；一轮做一张，做够 3 张为止</t>
+          <t>在水浇得到的地方把麦田一批批扩大，锄一批种一批，直到田的大小够全家吃（按实测吃掉的面包算，最少 64 格）。</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>M2-1</t>
+          <t>M1-7</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
@@ -8675,7 +8663,7 @@
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离≤24) → take_from_chest(东西=线（别名待加）；跳过条件：背包线≥12 / 背包同色羊毛最多≥3) → craft(东西=white_wool；跳过条件：背包同色羊毛最多≥3) → craft(东西=white_wool；跳过条件：背包同色羊毛最多≥3) → craft(东西=white_wool；跳过条件：背包同色羊毛最多≥3) → take_from_chest(东西=原木；跳过条件：背包同种木板最多≥3 / 背包木头≥1) → craft(东西=planks；跳过条件：背包同种木板最多≥3) → craft(东西=bed)</t>
+          <t>goto_place(地方=田；跳过条件：离田距离 ≤ 16) → till_soil(跳过条件：田格余量 ≥ 0) → plant_seeds(跳过条件：有种子 = 0)</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
@@ -8692,27 +8680,27 @@
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>J-M2-1-2</t>
+          <t>J-M1-8</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>兜底：箱子里的线不够做下一张床时，小麦白天看见能打的羊就去打，凑够 3 块同色羊毛就回家做床</t>
+          <t>麦豆白天去自家田里收熟麦子，当场种回去，再把小麦存进粮箱给妈妈做面包。</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>M2-1</t>
+          <t>M1-8</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>麦豆</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>hunt(跳过条件：背包同色羊毛最多≥3 / 附近能打的羊=0) → go_home(跳过条件：背包同色羊毛最多≤2 / 离家距离≤24) → take_from_chest(东西=原木；跳过条件：背包同种木板最多≥3 / 背包木头≥1 / 背包同色羊毛最多≤2) → craft(东西=planks；跳过条件：背包同种木板最多≥3 / 背包同色羊毛最多≤2) → craft(东西=bed；跳过条件：背包同色羊毛最多≤2)</t>
+          <t>goto_place(地方=田；跳过条件：离田距离 ≤ 16) → harvest_crop(先拿田里收割锁，拿不到就跳过；只收自家田登记簿里的格子) → plant_seeds(收完的格子当场种回去；跳过条件：有种子 = 0) → go_home(跳过条件：离家距离 ≤ 8) → store_crop(麦豆身上只留 3 个面包、16 颗种子，小麦全部进粮箱)</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
@@ -8729,27 +8717,27 @@
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>J-M2-3-1</t>
+          <t>J-M1-8c</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>身上有床、家里又有人没床时，白天回家把床摆进屋里，记到下一个该有床的人名下</t>
+          <t>麦豆收熟了的麦子(照抄麦娘的 wife_harvest,门槛换成麦豆的)</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>M2-3</t>
+          <t>M1-8</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>麦娘, 小麦</t>
+          <t>麦豆</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离≤8)</t>
+          <t>go_home → harvest_crop</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
@@ -8759,34 +8747,34 @@
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>要放行动作</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>J-M3-1</t>
+          <t>J-M1-8d</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>小麦出门找地：先让服务器导出一份「别人在哪儿放过东西」的名单，再朝别人最少的方向一段一段走。每走完一段，代码就检查一次附近有没有合格的地；找到一块就记下，找到好几块就问一次模型挑哪块，然后传送回家。</t>
+          <t>麦豆把收空的地种回去(照抄 wife_plant,门槛换成麦豆的)</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>M3-1</t>
+          <t>M1-8</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>麦豆</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1。在这一步之前缺 request_footprint（跳过条件：足迹数据已就绪 = 1）) → explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1) → explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1) → explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1) → explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1) → explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1) → explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1) → explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1) → go_home(传送回旧家（/home base）。在它之前缺 mark_site：「合格的地址门朝向组合数」= 1 时代码直接记；≥ 2 时等 T-G3-2 选完再记)</t>
+          <t>go_home → plant_seeds</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
@@ -8796,24 +8784,24 @@
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>要放行动作</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>J-M3-2</t>
+          <t>J-M1-9</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>麦娘从共用箱子拿原木，劈成木板，做好半砖和门，再全部放回共用箱子。</t>
+          <t>麦娘从粮箱拿出麦豆和自己存进去的小麦，做成面包再放回粮箱。</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>M3-2</t>
+          <t>M1-9</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
@@ -8823,7 +8811,7 @@
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>take_from_chest(东西=设计定的墙/屋顶木种的原木；数量按木板、半砖、门三个缺口现算（全缺时 49 根）；跳过条件：新房木板缺口 = 0 且 新房半砖缺口 = 0 且 新房门缺口 = 0) → craft(东西=对应木种的木板；次数=上一步拿到的原木数；跳过条件：同上) → craft(东西=对应木种的半砖；次数=9（27 木板出 54 块）；跳过条件：新房半砖缺口 = 0) → craft(东西=对应木种的门；次数=1（6 木板出 3 扇）；跳过条件：新房门缺口 = 0) → store_items(东西=木板、半砖、门 → 共用箱子（必须存，别的家人看不见你的背包）)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=小麦，从粮箱拿，拿 3 的倍数、最多 27 个) → craft(东西=bread) → store_crop(面包进粮箱（她身上照常留 3 个）)</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
@@ -8840,27 +8828,27 @@
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>J-M3-3</t>
+          <t>J-M2-1-1</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>小麦从共用箱子拿墙用的木板、柱子原木和门，走到新家址，补平地面、砌墙、装门，然后传送回家。</t>
+          <t>麦娘白天回家，从箱子拿线合成白羊毛，配同种木板，用家里现有的工作台做床；一轮做一张，做够 3 张为止</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>M3-3</t>
+          <t>M2-1</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>麦娘</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>take_from_chest(东西=设计定的墙木板；数量=新房墙缺口数（最多 82）；跳过条件：背包木板 ≥ 该数) → take_from_chest(东西=柱子原木；数量=12 + ceil(地基补平格数/4)；跳过条件：背包木头 ≥ 该数) → craft(东西=补平用的木板；次数=ceil(地基补平格数/4)；跳过条件：地基补平缺口 = 0) → take_from_chest(东西=门；数量=1；跳过条件：新房有门 = 1) → goto_place(地方=新家；直到 离新家址 ≤ 6（没有「直到」时，连写 4 个相同步骤，每步跳过条件：离新家址 ≤ 6）) → build_house(阶段=补平；直到 地基补平缺口 = 0；跳过条件：地基补平缺口 = 0) → build_house(阶段=墙柱门；直到 新房墙缺口数 = 0 且 新房有门 = 1) → go_home(传送回旧家)</t>
+          <t>go_home(跳过条件：离家距离≤24) → take_from_chest(东西=线（别名待加）；跳过条件：背包线≥12 / 背包同色羊毛最多≥3) → craft(东西=white_wool；跳过条件：背包同色羊毛最多≥3) → craft(东西=white_wool；跳过条件：背包同色羊毛最多≥3) → craft(东西=white_wool；跳过条件：背包同色羊毛最多≥3) → take_from_chest(东西=原木；跳过条件：背包同种木板最多≥3 / 背包木头≥1) → craft(东西=planks；跳过条件：背包同种木板最多≥3) → craft(东西=bed)</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
@@ -8877,17 +8865,17 @@
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>J-M3-4</t>
+          <t>J-M2-1-2</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>小麦带上半砖和屋顶木板去新房，先铺地板再封顶，然后传送回家。</t>
+          <t>兜底：箱子里的线不够做下一张床时，小麦白天看见能打的羊就去打，凑够 3 块同色羊毛就回家做床</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>M3-4</t>
+          <t>M2-1</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
@@ -8897,7 +8885,7 @@
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>take_from_chest(东西=半砖；数量=新房地面裸露格数；跳过条件：新房地面裸露格数 = 0) → take_from_chest(东西=设计定的屋顶木板；数量=新房屋顶缺口数；跳过条件：新房屋顶缺口数 = 0) → goto_place(地方=新家；直到 离新家址 ≤ 6) → build_house(阶段=地板；直到 新房地面裸露格数 = 0；跳过条件：新房地面裸露格数 = 0) → build_house(阶段=屋顶；直到 新房屋顶缺口数 = 0) → go_home(传送回旧家)</t>
+          <t>hunt(跳过条件：背包同色羊毛最多≥3 / 附近能打的羊=0) → go_home(跳过条件：背包同色羊毛最多≤2 / 离家距离≤24) → take_from_chest(东西=原木；跳过条件：背包同种木板最多≥3 / 背包木头≥1 / 背包同色羊毛最多≤2) → craft(东西=planks；跳过条件：背包同种木板最多≥3 / 背包同色羊毛最多≤2) → craft(东西=bed；跳过条件：背包同色羊毛最多≤2)</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
@@ -8914,27 +8902,27 @@
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>J-M3-5a</t>
+          <t>J-M2-3-1</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>麦娘用箱子里的线合成白羊毛，再做白床，做够 3 张。</t>
+          <t>身上有床、家里又有人没床时，白天回家把床摆进屋里，记到下一个该有床的人名下</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>M3-5</t>
+          <t>M2-3</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>麦娘</t>
+          <t>麦娘, 小麦</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>take_from_chest(东西=string；数量=12×(3 − 麦家的床数)（箱子里不够就拿全部）) → take_from_chest(东西=非设计木种的木板；数量=3×(3 − 麦家的床数)；跳过条件：背包木板 ≥ 该数) → craft(东西=white_wool；次数=拿到的线 ÷ 4（每次 4 根线）) → craft(东西=white_bed；次数=白羊毛数 ÷ 3（每次 3 羊毛 + 3 木板）)</t>
+          <t>go_home(跳过条件：离家距离≤8)</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
@@ -8951,27 +8939,27 @@
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>J-M3-5b</t>
+          <t>J-M3-1</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>麦娘用木板做 6 个箱子和 1 个工作台，带在身上等着摆。</t>
+          <t>小麦出门找地：先让服务器导出一份「别人在哪儿放过东西」的名单，再朝别人最少的方向一段一段走。每走完一段，代码就检查一次附近有没有合格的地；找到一块就记下，找到好几块就问一次模型挑哪块，然后传送回家。</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>M3-5</t>
+          <t>M3-1</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>麦娘</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>take_from_chest(东西=非设计木种的木板；数量=8×(6 − 麦家的箱子数) + 4×(1 − 麦家的工作台数)；跳过条件：背包木板 ≥ 该数) → craft(东西=crafting_table；次数=1；跳过条件：麦家的工作台数 ≥ 1) → craft(东西=chest；次数=6 − 麦家的箱子数；跳过条件：麦家的箱子数 ≥ 6)</t>
+          <t>explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1。在这一步之前缺 request_footprint（跳过条件：足迹数据已就绪 = 1）) → explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1) → explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1) → explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1) → explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1) → explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1) → explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1) → explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1) → go_home(传送回旧家（/home base）。在它之前缺 mark_site：「合格的地址门朝向组合数」= 1 时代码直接记；≥ 2 时等 T-G3-2 选完再记)</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
@@ -8981,24 +8969,24 @@
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>J-M3-6</t>
+          <t>J-M3-2</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>麦娘带着床、箱子、工作台走到新房，按定好的摆法放进去，然后传送回家。</t>
+          <t>麦娘从共用箱子拿原木，劈成木板，做好半砖和门，再全部放回共用箱子。</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>M3-6</t>
+          <t>M3-2</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
@@ -9008,7 +8996,7 @@
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方=新家；直到 离新家址 ≤ 3) → go_home(传送回旧家。在它之前缺 place_furniture（摆家具，放完第一个箱子先核对领地）)</t>
+          <t>take_from_chest(东西=设计定的墙/屋顶木种的原木；数量按木板、半砖、门三个缺口现算（全缺时 49 根）；跳过条件：新房木板缺口 = 0 且 新房半砖缺口 = 0 且 新房门缺口 = 0) → craft(东西=对应木种的木板；次数=上一步拿到的原木数；跳过条件：同上) → craft(东西=对应木种的半砖；次数=9（27 木板出 54 块）；跳过条件：新房半砖缺口 = 0) → craft(东西=对应木种的门；次数=1（6 木板出 3 扇）；跳过条件：新房门缺口 = 0) → store_items(东西=木板、半砖、门 → 共用箱子（必须存，别的家人看不见你的背包）)</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
@@ -9025,17 +9013,17 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>J-M3-7a</t>
+          <t>J-M3-3</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>小麦传送回旧家，从旧箱子里把东西装满一背包，走到新房存进新箱子；来回搬，直到旧箱子空了。</t>
+          <t>小麦从共用箱子拿墙用的木板、柱子原木和门，走到新家址，补平地面、砌墙、装门，然后传送回家。</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>M3-7</t>
+          <t>M3-3</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
@@ -9045,7 +9033,7 @@
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>go_home(传送回旧家（旧箱子就在旁边）；跳过条件：离家距离 ≤ 8) → take_from_chest(箱子=旧箱子；东西=全部；背包只剩 2 格就停) → goto_place(地方=新家；直到 离新家址 ≤ 3) → store_items(箱子=新房箱子；东西=刚从旧箱子拿的全部)</t>
+          <t>take_from_chest(东西=设计定的墙木板；数量=新房墙缺口数（最多 82）；跳过条件：背包木板 ≥ 该数) → take_from_chest(东西=柱子原木；数量=12 + ceil(地基补平格数/4)；跳过条件：背包木头 ≥ 该数) → craft(东西=补平用的木板；次数=ceil(地基补平格数/4)；跳过条件：地基补平缺口 = 0) → take_from_chest(东西=门；数量=1；跳过条件：新房有门 = 1) → goto_place(地方=新家；直到 离新家址 ≤ 6（没有「直到」时，连写 4 个相同步骤，每步跳过条件：离新家址 ≤ 6）) → build_house(阶段=补平；直到 地基补平缺口 = 0；跳过条件：地基补平缺口 = 0) → build_house(阶段=墙柱门；直到 新房墙缺口数 = 0 且 新房有门 = 1) → go_home(传送回旧家)</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
@@ -9062,27 +9050,27 @@
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>J-M3-7b</t>
+          <t>J-M3-4</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>旧箱子空了以后，小麦和麦娘各自走进新房，把家设在屋里，并在自己那张床上点一下。</t>
+          <t>小麦带上半砖和屋顶木板去新房，先铺地板再封顶，然后传送回家。</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>M3-7</t>
+          <t>M3-4</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>小麦 / 麦娘</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方=新家；直到 离新家址 ≤ 3) → set_home(新房屋内一格空地（不站在床或箱子上）；扩展：同时切共用箱子指针；跳过条件：我的家离新房距离 ≤ 4) → sleep(点自己那张新床设重生点（白天也点）；跳过条件：我的重生床在新房 = 1)</t>
+          <t>take_from_chest(东西=半砖；数量=新房地面裸露格数；跳过条件：新房地面裸露格数 = 0) → take_from_chest(东西=设计定的屋顶木板；数量=新房屋顶缺口数；跳过条件：新房屋顶缺口数 = 0) → goto_place(地方=新家；直到 离新家址 ≤ 6) → build_house(阶段=地板；直到 新房地面裸露格数 = 0；跳过条件：新房地面裸露格数 = 0) → build_house(阶段=屋顶；直到 新房屋顶缺口数 = 0) → go_home(传送回旧家)</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
@@ -9099,27 +9087,27 @@
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>J-M3-7c</t>
+          <t>J-M3-5a</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>麦豆跟着小麦走到新房，把家设在屋里，在自己那张床上点一下。</t>
+          <t>麦娘用箱子里的线合成白羊毛，再做白床，做够 3 张。</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>M3-7</t>
+          <t>M3-5</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>麦豆</t>
+          <t>麦娘</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>follow_player(对象=XiaoMai；跳过条件：离新家址 ≤ 16) → goto_place(地方=新家；直到 离新家址 ≤ 3) → set_home(新房屋内一格空地；跳过条件：我的家离新房距离 ≤ 4) → sleep(点自己那张新床设重生点；跳过条件：我的重生床在新房 = 1)</t>
+          <t>take_from_chest(东西=string；数量=12×(3 − 麦家的床数)（箱子里不够就拿全部）) → take_from_chest(东西=非设计木种的木板；数量=3×(3 − 麦家的床数)；跳过条件：背包木板 ≥ 该数) → craft(东西=white_wool；次数=拿到的线 ÷ 4（每次 4 根线）) → craft(东西=white_bed；次数=白羊毛数 ÷ 3（每次 3 羊毛 + 3 木板）)</t>
         </is>
       </c>
       <c r="F102" s="7" t="inlineStr">
@@ -9136,23 +9124,27 @@
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>J-M4-1</t>
+          <t>J-M3-5b</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>往离出生点远的方向探路</t>
+          <t>麦娘用木板做 6 个箱子和 1 个工作台，带在身上等着摆。</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>M4-1</t>
-        </is>
-      </c>
-      <c r="D103" s="7" t="inlineStr"/>
+          <t>M3-5</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>麦娘</t>
+        </is>
+      </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>explore(背离出生点的方向)</t>
+          <t>take_from_chest(东西=非设计木种的木板；数量=8×(6 − 麦家的箱子数) + 4×(1 − 麦家的工作台数)；跳过条件：背包木板 ≥ 该数) → craft(东西=crafting_table；次数=1；跳过条件：麦家的工作台数 ≥ 1) → craft(东西=chest；次数=6 − 麦家的箱子数；跳过条件：麦家的箱子数 ≥ 6)</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
@@ -9162,30 +9154,34 @@
       </c>
       <c r="G103" s="7" t="inlineStr">
         <is>
-          <t>缺动作</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>J-M4-2</t>
+          <t>J-M3-6</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>去新址设家</t>
+          <t>麦娘带着床、箱子、工作台走到新房，按定好的摆法放进去，然后传送回家。</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>M4-2</t>
-        </is>
-      </c>
-      <c r="D104" s="7" t="inlineStr"/>
+          <t>M3-6</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>麦娘</t>
+        </is>
+      </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>goto_place(新家址) → set_home</t>
+          <t>goto_place(地方=新家；直到 离新家址 ≤ 3) → go_home(传送回旧家。在它之前缺 place_furniture（摆家具，放完第一个箱子先核对领地）)</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr">
@@ -9195,30 +9191,34 @@
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>J-M4-3</t>
+          <t>J-M3-7a</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>一趟趟搬旧箱子</t>
+          <t>小麦传送回旧家，从旧箱子里把东西装满一背包，走到新房存进新箱子；来回搬，直到旧箱子空了。</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>M4-3</t>
-        </is>
-      </c>
-      <c r="D105" s="7" t="inlineStr"/>
+          <t>M3-7</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>小麦</t>
+        </is>
+      </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>goto_place(旧家) → take_from_chest(旧箱子,留 6 格空) → go_home → store_items</t>
+          <t>go_home(传送回旧家（旧箱子就在旁边）；跳过条件：离家距离 ≤ 8) → take_from_chest(箱子=旧箱子；东西=全部；背包只剩 2 格就停) → goto_place(地方=新家；直到 离新家址 ≤ 3) → store_items(箱子=新房箱子；东西=刚从旧箱子拿的全部)</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr">
@@ -9228,30 +9228,34 @@
       </c>
       <c r="G105" s="7" t="inlineStr">
         <is>
-          <t>缺动作</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>J-M4-4</t>
+          <t>J-M3-7b</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>只拆清单里自家放下的方块</t>
+          <t>旧箱子空了以后，小麦和麦娘各自走进新房，把家设在屋里，并在自己那张床上点一下。</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>M4-4</t>
-        </is>
-      </c>
-      <c r="D106" s="7" t="inlineStr"/>
+          <t>M3-7</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>小麦 / 麦娘</t>
+        </is>
+      </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>goto_place(旧家)</t>
+          <t>goto_place(地方=新家；直到 离新家址 ≤ 3) → set_home(新房屋内一格空地（不站在床或箱子上）；扩展：同时切共用箱子指针；跳过条件：我的家离新房距离 ≤ 4) → sleep(点自己那张新床设重生点（白天也点）；跳过条件：我的重生床在新房 = 1)</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
@@ -9261,30 +9265,34 @@
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
-          <t>缺动作</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>J-M5-2</t>
+          <t>J-M3-7c</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>做木镐</t>
+          <t>麦豆跟着小麦走到新房，把家设在屋里，在自己那张床上点一下。</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>M5-2</t>
-        </is>
-      </c>
-      <c r="D107" s="7" t="inlineStr"/>
+          <t>M3-7</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>麦豆</t>
+        </is>
+      </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
-          <t>take_from_chest(oak_planks×3、stick×2) → craft(wooden_pickaxe)</t>
+          <t>follow_player(对象=XiaoMai；跳过条件：离新家址 ≤ 16) → goto_place(地方=新家；直到 离新家址 ≤ 3) → set_home(新房屋内一格空地；跳过条件：我的家离新房距离 ≤ 4) → sleep(点自己那张新床设重生点；跳过条件：我的重生床在新房 = 1)</t>
         </is>
       </c>
       <c r="F107" s="7" t="inlineStr">
@@ -9294,30 +9302,30 @@
       </c>
       <c r="G107" s="7" t="inlineStr">
         <is>
-          <t>现在就能做</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>J-M5-3</t>
+          <t>J-M4-1</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>进资源世界挖圆石</t>
+          <t>往离出生点远的方向探路</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>M5-3</t>
+          <t>M4-1</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr"/>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>goto_place(资源世界入口) → go_home → store_items</t>
+          <t>explore(背离出生点的方向)</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
@@ -9334,27 +9342,23 @@
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>J-M5-3b</t>
+          <t>J-M4-2</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>小麦带着镐去资源世界挖石头，挖够 64 块圆石带回家存进大箱子。</t>
+          <t>去新址设家</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>M5-3</t>
-        </is>
-      </c>
-      <c r="D109" s="7" t="inlineStr">
-        <is>
-          <t>小麦</t>
-        </is>
-      </c>
+          <t>M4-2</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr"/>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=镐（最好的一把）；跳过条件：背包里最好的镐等级 ≥ 1) → take_from_chest(东西=口粮（留底 9）；跳过条件：身上吃的 ≥ 4) → goto_place(地方=资源世界（/res go）) → mine(方块=石头（深板岩也算）；直到 背包圆石 + 箱子里圆石 ≥ 64 或 15 分钟 或 该回主世界 = 1) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(圆石进大箱子)</t>
+          <t>goto_place(新家址) → set_home</t>
         </is>
       </c>
       <c r="F109" s="7" t="inlineStr">
@@ -9364,30 +9368,30 @@
       </c>
       <c r="G109" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>J-M5-5</t>
+          <t>J-M4-3</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>做 3 把备用木剑放进箱子</t>
+          <t>一趟趟搬旧箱子</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>M5-5</t>
+          <t>M4-3</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr"/>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>take_from_chest(oak_planks×6、stick×3) → craft(wooden_sword×3) → store_items</t>
+          <t>goto_place(旧家) → take_from_chest(旧箱子,留 6 格空) → go_home → store_items</t>
         </is>
       </c>
       <c r="F110" s="7" t="inlineStr">
@@ -9397,30 +9401,30 @@
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>现在就能做</t>
+          <t>缺动作</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>J-M7-3</t>
+          <t>J-M4-4</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>麦豆跟着爸爸砍树</t>
+          <t>只拆清单里自家放下的方块</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>M7-3</t>
+          <t>M4-4</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr"/>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>follow_player(小麦) → gather_wood → store_items</t>
+          <t>goto_place(旧家)</t>
         </is>
       </c>
       <c r="F111" s="7" t="inlineStr">
@@ -9437,23 +9441,23 @@
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>J-M7-4</t>
+          <t>J-M5-2</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>没被点名时离真人太近就回家</t>
+          <t>做木镐</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>M7-4</t>
+          <t>M5-2</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr"/>
       <c r="E112" s="7" t="inlineStr">
         <is>
-          <t>go_home</t>
+          <t>take_from_chest(oak_planks×3、stick×2) → craft(wooden_pickaxe)</t>
         </is>
       </c>
       <c r="F112" s="7" t="inlineStr">
@@ -9463,34 +9467,30 @@
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>现在就能做</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>J-M7-5</t>
+          <t>J-M5-3</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>走到正在干活的家人旁边 4~8 格处，待着看。</t>
+          <t>进资源世界挖圆石</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>M7-5</t>
-        </is>
-      </c>
-      <c r="D113" s="7" t="inlineStr">
-        <is>
-          <t>麦豆</t>
-        </is>
-      </c>
+          <t>M5-3</t>
+        </is>
+      </c>
+      <c r="D113" s="7" t="inlineStr"/>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方=家人身边（停在 4~8 格外，不进田里）) → idle(30 秒；跳过条件：离最近在干活的家人距离 ≥ 17)</t>
+          <t>goto_place(资源世界入口) → go_home → store_items</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
@@ -9500,24 +9500,24 @@
       </c>
       <c r="G113" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺动作</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>J-M8-1a</t>
+          <t>J-M5-3b</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>用箱子里现成的铁锭做一把铁镐。</t>
+          <t>小麦带着镐去资源世界挖石头，挖够 64 块圆石带回家存进大箱子。</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>M8-1</t>
+          <t>M5-3</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=铁锭 3、木棍 2；跳过条件：背包铁锭 ≥ 3) → craft(东西=iron_pickaxe（要工作台）)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=镐（最好的一把）；跳过条件：背包里最好的镐等级 ≥ 1) → take_from_chest(东西=口粮（留底 9）；跳过条件：身上吃的 ≥ 4) → goto_place(地方=资源世界（/res go）) → mine(方块=石头（深板岩也算）；直到 背包圆石 + 箱子里圆石 ≥ 64 或 15 分钟 或 该回主世界 = 1) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(圆石进大箱子)</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr">
@@ -9544,27 +9544,23 @@
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>J-M8-1b</t>
+          <t>J-M5-5</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>箱子里的铁不够时：用圆石做石镐和熔炉，去资源世界挖 3 块铁矿、就地烧成铁锭，回家做铁镐。</t>
+          <t>做 3 把备用木剑放进箱子</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>M8-1</t>
-        </is>
-      </c>
-      <c r="D115" s="7" t="inlineStr">
-        <is>
-          <t>小麦</t>
-        </is>
-      </c>
+          <t>M5-5</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr"/>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=圆石 11、木棍 4、原木 4（燃料）、口粮（留底 9；跳过条件：身上吃的 ≥ 6）) → take_from_chest(东西=镐（最好的一把）；跳过条件：背包里最好的镐等级 ≥ 2) → craft(东西=stone_pickaxe；跳过条件：背包里最好的镐等级 ≥ 2) → craft(东西=furnace；跳过条件：身上有熔炉 ≥ 1) → goto_place(地方=资源世界（/res go）) → mine(矿=铁矿，下到 y≈16 开巷道；直到 背包粗铁 ≥ 3 或 25 分钟 或 该回主世界 = 1) → smelt(随身熔炉；粗铁全部，燃料原木；烧完挖回熔炉) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → craft(东西=iron_pickaxe)</t>
+          <t>take_from_chest(oak_planks×6、stick×3) → craft(wooden_sword×3) → store_items</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr">
@@ -9574,34 +9570,30 @@
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>现在就能做</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>J-M8-2</t>
+          <t>J-M7-3</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>小麦带着熔炉和燃料去资源世界挖铁，挖完就地烧成铁锭，带回家存进大箱子。</t>
+          <t>麦豆跟着爸爸砍树</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>M8-2</t>
-        </is>
-      </c>
-      <c r="D116" s="7" t="inlineStr">
-        <is>
-          <t>小麦</t>
-        </is>
-      </c>
+          <t>M7-3</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="inlineStr"/>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=镐（拿最好的一把）；跳过条件：背包里最好的镐等级 ≥ 2) → take_from_chest(东西=口粮（留底 9）；跳过条件：身上吃的 ≥ 6) → take_from_chest(东西=粗铁（全部）；跳过条件：箱子里没有粗铁) → take_from_chest(东西=圆石 8；跳过条件：身上有熔炉 ≥ 1) → craft(东西=furnace；跳过条件：身上有熔炉 ≥ 1) → take_from_chest(东西=原木（当燃料），数量 = 还差的铁锭 ÷ 1.5 向上取整，最多 24 根；跳过条件：身上的原木已经够) → goto_place(地方=资源世界（/res go）) → mine(矿=铁矿，下到 y≈16 开 1×2 巷道；顺手挖煤，看见沙砾就挖到背包燧石 ≥ 1；直到 背包粗铁 ≥ 出发时的还差铁锭 或 背包空格 ≤ 2 或 这一趟 ≥ 25 分钟 或 该回主世界 = 1) → smelt(放下随身熔炉，粗铁全部，燃料先煤后原木；烧完用镐把熔炉挖回来) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(铁锭、煤、燧石进大箱子（镐和熔炉留在身上）)</t>
+          <t>follow_player(小麦) → gather_wood → store_items</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr">
@@ -9611,34 +9603,34 @@
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺动作</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>J-M8-3a</t>
+          <t>J-M7-3c</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>回家把铁锭做成还缺的铁甲、铁剑、盾、桶和打火石，然后穿好。</t>
+          <t>麦豆在家附近砍树(只砍看得见的树,不去远处林子;离家 40 格内,照抄 child_play 的范围)</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>M8-3</t>
+          <t>M7-3</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>麦豆</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=铁锭（按能做的件现算）、木棍（按件现算）、木板 6（跳过条件：有盾牌 ≥ 1）、燧石 1（跳过条件：有打火石 ≥ 1 或 能拿到的燧石 = 0）) → craft(按缺的做，先 iron_sword、shield，再 iron_chestplate、iron_leggings、iron_helmet、iron_boots、bucket、flint_and_steel；已有的、料不够的跳过) → wear_armor(平时穿法：四件最好的护甲 + 副手盾)</t>
+          <t>gather_wood</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr">
@@ -9648,34 +9640,34 @@
       </c>
       <c r="G117" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>要放行动作</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>J-M8-3b</t>
+          <t>J-M7-3d</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t>缺燧石做打火石时，去资源世界挖沙砾拿燧石。</t>
+          <t>麦豆背包满了自己回家存箱子(照抄 wife_store)</t>
         </is>
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>M8-3</t>
+          <t>M7-3</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>麦豆</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方=资源世界（/res go）) → mine(方块=沙砾；直到 背包燧石 ≥ 2 或 15 分钟 或 该回主世界 = 1) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(燧石进大箱子)</t>
+          <t>go_home → store_items</t>
         </is>
       </c>
       <c r="F118" s="7" t="inlineStr">
@@ -9685,34 +9677,30 @@
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>要放行动作</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>J-M8-3c</t>
+          <t>J-M7-4</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>拿个空桶，去附近天然的河或湖装一桶水带在身上。</t>
+          <t>没被点名时离真人太近就回家</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>M8-3</t>
-        </is>
-      </c>
-      <c r="D119" s="7" t="inlineStr">
-        <is>
-          <t>小麦</t>
-        </is>
-      </c>
+          <t>M7-4</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="inlineStr"/>
       <c r="E119" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8 或 身上空桶 ≥ 1) → take_from_chest(东西=桶；跳过条件：身上空桶 ≥ 1) → goto_place(地方=水源（只认 C-FRM-25 认可的天然水）) → fill_bucket</t>
+          <t>go_home</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">
@@ -9722,34 +9710,34 @@
       </c>
       <c r="G119" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>J-M8-4a</t>
+          <t>J-M7-5</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t>您同意的话，用箱子里的 3 颗钻石直接做钻石镐。</t>
+          <t>走到正在干活的家人旁边 4~8 格处，待着看。</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>M8-4</t>
+          <t>M7-5</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>麦豆</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=钻石 3、木棍 2) → craft(东西=diamond_pickaxe（要工作台）)</t>
+          <t>goto_place(地方=家人身边（停在 4~8 格外，不进田里）) → idle(30 秒；跳过条件：离最近在干活的家人距离 ≥ 17)</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
@@ -9766,17 +9754,17 @@
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>J-M8-4b</t>
+          <t>J-M8-1a</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
-          <t>不用箱子里的钻石时，穿上铁甲、带上水桶，去资源世界最深处挖 3 颗钻石回来做钻石镐。</t>
+          <t>用箱子里现成的铁锭做一把铁镐。</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>M8-4</t>
+          <t>M8-1</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
@@ -9786,7 +9774,7 @@
       </c>
       <c r="E121" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=铁镐；跳过条件：背包里最好的镐等级 ≥ 3) → take_from_chest(东西=口粮（留底 9）；跳过条件：身上吃的 ≥ 8) → wear_armor(平时穿法) → goto_place(地方=资源世界（/res go）) → mine(矿=钻石，y≈−58 开巷道，岩浆安全规则按 C-CRF-22；直到 背包钻石 ≥ 3 或 25 分钟 或 该回主世界 = 1) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → craft(东西=diamond_pickaxe；跳过条件：背包钻石 ≤ 2)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=铁锭 3、木棍 2；跳过条件：背包铁锭 ≥ 3) → craft(东西=iron_pickaxe（要工作台）)</t>
         </is>
       </c>
       <c r="F121" s="7" t="inlineStr">
@@ -9803,17 +9791,17 @@
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>J-M8-5</t>
+          <t>J-M8-1b</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t>带着钻石镐和水桶去资源世界找岩浆，浇上水变成黑曜石，挖够 10 块带回家。</t>
+          <t>箱子里的铁不够时：用圆石做石镐和熔炉，去资源世界挖 3 块铁矿、就地烧成铁锭，回家做铁镐。</t>
         </is>
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>M8-5</t>
+          <t>M8-1</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
@@ -9823,7 +9811,7 @@
       </c>
       <c r="E122" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=钻石镐；跳过条件：背包里最好的镐等级 ≥ 4) → take_from_chest(东西=口粮（留底 9）；跳过条件：身上吃的 ≥ 8) → goto_place(地方=资源世界（/res go）) → explore(找岩浆：先看落点附近地表的岩浆湖，没有就下到 y≈−54 以下的洞穴；跳过条件：看得见岩浆源；最多 10 分钟) → cast_obsidian(直到 黑曜石的家底 ≥ 10（背包里的也算） 或 该回主世界 = 1) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(黑曜石进大箱子)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=圆石 11、木棍 4、原木 4（燃料）、口粮（留底 9；跳过条件：身上吃的 ≥ 6）) → take_from_chest(东西=镐（最好的一把）；跳过条件：背包里最好的镐等级 ≥ 2) → craft(东西=stone_pickaxe；跳过条件：背包里最好的镐等级 ≥ 2) → craft(东西=furnace；跳过条件：身上有熔炉 ≥ 1) → goto_place(地方=资源世界（/res go）) → mine(矿=铁矿，下到 y≈16 开巷道；直到 背包粗铁 ≥ 3 或 25 分钟 或 该回主世界 = 1) → smelt(随身熔炉；粗铁全部，燃料原木；烧完挖回熔炉) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → craft(东西=iron_pickaxe)</t>
         </is>
       </c>
       <c r="F122" s="7" t="inlineStr">
@@ -9840,17 +9828,17 @@
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>J-M8-6</t>
+          <t>J-M8-2</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>拿上 10 块黑曜石，走到您批准的位置，砌好传送门框并点着。</t>
+          <t>小麦带着熔炉和燃料去资源世界挖铁，挖完就地烧成铁锭，带回家存进大箱子。</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>M8-6</t>
+          <t>M8-2</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
@@ -9860,7 +9848,7 @@
       </c>
       <c r="E123" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=黑曜石（缺几块拿几块）、打火石（跳过条件：身上有）) → goto_place(地方=传送门位置) → build_portal(只补缺的格子，每块记进自家方块登记；用打火石点着，回读有紫色的门方块才算成)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=镐（拿最好的一把）；跳过条件：背包里最好的镐等级 ≥ 2) → take_from_chest(东西=口粮（留底 9）；跳过条件：身上吃的 ≥ 6) → take_from_chest(东西=粗铁（全部）；跳过条件：箱子里没有粗铁) → take_from_chest(东西=圆石 8；跳过条件：身上有熔炉 ≥ 1) → craft(东西=furnace；跳过条件：身上有熔炉 ≥ 1) → take_from_chest(东西=原木（当燃料），数量 = 还差的铁锭 ÷ 1.5 向上取整，最多 24 根；跳过条件：身上的原木已经够) → goto_place(地方=资源世界（/res go）) → mine(矿=铁矿，下到 y≈16 开 1×2 巷道；顺手挖煤，看见沙砾就挖到背包燧石 ≥ 1；直到 背包粗铁 ≥ 出发时的还差铁锭 或 背包空格 ≤ 2 或 这一趟 ≥ 25 分钟 或 该回主世界 = 1) → smelt(放下随身熔炉，粗铁全部，燃料先煤后原木；烧完用镐把熔炉挖回来) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(铁锭、煤、燧石进大箱子（镐和熔炉留在身上）)</t>
         </is>
       </c>
       <c r="F123" s="7" t="inlineStr">
@@ -9877,17 +9865,17 @@
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>J-M8-8a</t>
+          <t>J-M8-3a</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t>去资源世界挖金矿、烧成 5 个金锭，给金头盔备料。</t>
+          <t>回家把铁锭做成还缺的铁甲、铁剑、盾、桶和打火石，然后穿好。</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>M8-8</t>
+          <t>M8-3</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
@@ -9897,7 +9885,7 @@
       </c>
       <c r="E124" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=铁镐或更好；跳过条件：背包里最好的镐等级 ≥ 3) → take_from_chest(东西=口粮（留底 9）；跳过条件：身上吃的 ≥ 6) → take_from_chest(东西=圆石 8；跳过条件：身上有熔炉 ≥ 1) → craft(东西=furnace；跳过条件：身上有熔炉 ≥ 1) → take_from_chest(东西=原木 4（燃料）；跳过条件：身上的原木 ≥ 4) → goto_place(地方=资源世界（/res go）) → mine(矿=金矿，y≈−16 开巷道（恶地地表也行）；直到 背包粗金 + 金的家底 ≥ 5 或 25 分钟 或 该回主世界 = 1) → smelt(随身熔炉，粗金全部；烧完把熔炉挖回来) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(金锭进大箱子)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=铁锭（按能做的件现算）、木棍（按件现算）、木板 6（跳过条件：有盾牌 ≥ 1）、燧石 1（跳过条件：有打火石 ≥ 1 或 能拿到的燧石 = 0）) → craft(按缺的做，先 iron_sword、shield，再 iron_chestplate、iron_leggings、iron_helmet、iron_boots、bucket、flint_and_steel；已有的、料不够的跳过) → wear_armor(平时穿法：四件最好的护甲 + 副手盾)</t>
         </is>
       </c>
       <c r="F124" s="7" t="inlineStr">
@@ -9914,17 +9902,17 @@
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>J-M8-8b</t>
+          <t>J-M8-3b</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>出发去下界前在家收拾行李：做好金头盔戴上，从粮箱拿够口粮、从大箱子拿 64 块圆石，用不上的东西存掉。</t>
+          <t>缺燧石做打火石时，去资源世界挖沙砾拿燧石。</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>M8-8</t>
+          <t>M8-3</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
@@ -9934,7 +9922,7 @@
       </c>
       <c r="E125" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=金锭 5；跳过条件：穿着金护甲件数 ≥ 1 或 背包金头盔 ≥ 1) → craft(东西=golden_helmet；跳过条件：同上) → wear_armor(下界穿法：金头盔 + 另外三件最好的护甲 + 副手盾) → take_from_chest(东西=口粮，从粮箱拿，留底 9（打开箱子按真数重算）；直到 身上吃的 ≥ 16) → take_from_chest(东西=圆石；直到 身上的圆石 ≥ 64) → store_items(用不上的存掉，行李清单上的留着；直到 背包空格 ≥ 8)</t>
+          <t>goto_place(地方=资源世界（/res go）) → mine(方块=沙砾；直到 背包燧石 ≥ 2 或 15 分钟 或 该回主世界 = 1) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(燧石进大箱子)</t>
         </is>
       </c>
       <c r="F125" s="7" t="inlineStr">
@@ -9951,17 +9939,17 @@
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>J-M8-9</t>
+          <t>J-M8-3c</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>穿过传送门进下界，朝一个方向一段段找，看到地狱砖城堡就记下位置，然后原路回家。</t>
+          <t>拿个空桶，去附近天然的河或湖装一桶水带在身上。</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>M8-9</t>
+          <t>M8-3</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
@@ -9971,7 +9959,7 @@
       </c>
       <c r="E126" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方=传送门（主世界那一头）；跳过条件：当前维度 = 2（下界）) → wear_armor(下界穿法；跳过条件：穿着金护甲件数 ≥ 1) → use_portal(进下界；跳过条件：当前维度 = 2；第一次过去先核对落点周围 32 格有没有别人的方块，有就原路回来、作废位置、写进后台) → explore(在下界：沿一个方向一段 64 格，离门 ≤ 600 格，避开玄武岩三角洲和堡垒遗迹；直到 记得下界要塞 = 1 或 该返航 = 1) → goto_place(地方=下界那一头的门；跳过条件：当前维度 = 0) → use_portal(回主世界；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → store_items(只存可存的，行李留着)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8 或 身上空桶 ≥ 1) → take_from_chest(东西=桶；跳过条件：身上空桶 ≥ 1) → goto_place(地方=水源（只认 C-FRM-25 认可的天然水）) → fill_bucket</t>
         </is>
       </c>
       <c r="F126" s="7" t="inlineStr">
@@ -9988,17 +9976,17 @@
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>J-M8-10</t>
+          <t>J-M8-4a</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>去下界要塞的烈焰人刷怪笼旁边，举着盾一只只打烈焰人，攒烈焰棒，带回家存进箱子。</t>
+          <t>您同意的话，用箱子里的 3 颗钻石直接做钻石镐。</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>M8-10</t>
+          <t>M8-4</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
@@ -10008,7 +9996,7 @@
       </c>
       <c r="E127" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方=传送门（主世界那一头）；跳过条件：当前维度 = 2) → wear_armor(下界穿法；跳过条件：穿着金护甲件数 ≥ 1) → use_portal(进下界；跳过条件：当前维度 = 2) → goto_place(地方=烈焰人刷怪笼，停在 6~8 格外的走廊) → fight(目标=烈焰人，举盾挡火球，打死后走过去捡；直到 做眼还缺的烈焰棒 = 0（背包里的也算） 或 该返航 = 1) → goto_place(地方=下界那一头的门；跳过条件：当前维度 = 0) → use_portal(回主世界；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → store_items(烈焰棒进大箱子)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=钻石 3、木棍 2) → craft(东西=diamond_pickaxe（要工作台）)</t>
         </is>
       </c>
       <c r="F127" s="7" t="inlineStr">
@@ -10025,17 +10013,17 @@
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>J-M8-11</t>
+          <t>J-M8-4b</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
         <is>
-          <t>去下界的诡异森林，躲在自己搭的两格高小棚口，一只只打末影人，攒末影珍珠带回家。</t>
+          <t>不用箱子里的钻石时，穿上铁甲、带上水桶，去资源世界最深处挖 3 颗钻石回来做钻石镐。</t>
         </is>
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>M8-11</t>
+          <t>M8-4</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
@@ -10045,7 +10033,7 @@
       </c>
       <c r="E128" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方=传送门（主世界那一头）；跳过条件：当前维度 = 2) → wear_armor(下界穿法；跳过条件：穿着金护甲件数 ≥ 1) → use_portal(进下界；跳过条件：当前维度 = 2) → goto_place(地方=诡异森林；还不记得就在下界 explore 找青绿色的地面，最多 10 分钟) → hunt_enderman(先搭两格高小棚，一次惹一只；直到 做眼还缺的末影珍珠 = 0（背包里的也算） 或 该返航 = 1；走前拆回小棚) → goto_place(地方=下界那一头的门；跳过条件：当前维度 = 0) → use_portal(回主世界；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → store_items(末影珍珠进大箱子)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=铁镐；跳过条件：背包里最好的镐等级 ≥ 3) → take_from_chest(东西=口粮（留底 9）；跳过条件：身上吃的 ≥ 8) → wear_armor(平时穿法) → goto_place(地方=资源世界（/res go）) → mine(矿=钻石，y≈−58 开巷道，岩浆安全规则按 C-CRF-22；直到 背包钻石 ≥ 3 或 25 分钟 或 该回主世界 = 1) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → craft(东西=diamond_pickaxe；跳过条件：背包钻石 ≤ 2)</t>
         </is>
       </c>
       <c r="F128" s="7" t="inlineStr">
@@ -10062,27 +10050,27 @@
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>J-M8-12</t>
+          <t>J-M8-5</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
         <is>
-          <t>麦娘从大箱子拿烈焰棒和末影珍珠，合成末影之眼，再存回箱子。</t>
+          <t>带着钻石镐和水桶去资源世界找岩浆，浇上水变成黑曜石，挖够 10 块带回家。</t>
         </is>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>M8-12</t>
+          <t>M8-5</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>麦娘</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="E129" s="7" t="inlineStr">
         <is>
-          <t>take_from_chest(东西=烈焰棒、末影珍珠；数量按 min(能做的末影之眼数, 末影之眼缺口) 现算) → craft(东西=blaze_powder) → craft(东西=ender_eye) → store_items(末影之眼和多的烈焰粉进大箱子)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=钻石镐；跳过条件：背包里最好的镐等级 ≥ 4) → take_from_chest(东西=口粮（留底 9）；跳过条件：身上吃的 ≥ 8) → goto_place(地方=资源世界（/res go）) → explore(找岩浆：先看落点附近地表的岩浆湖，没有就下到 y≈−54 以下的洞穴；跳过条件：看得见岩浆源；最多 10 分钟) → cast_obsidian(直到 黑曜石的家底 ≥ 10（背包里的也算） 或 该回主世界 = 1) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(黑曜石进大箱子)</t>
         </is>
       </c>
       <c r="F129" s="7" t="inlineStr">
@@ -10099,17 +10087,17 @@
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>J-M8-13a</t>
+          <t>J-M8-6</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
         <is>
-          <t>带几个末影之眼出门，在两个地方各扔一次、捡回来，算出要塞大概在哪，然后传送回家。</t>
+          <t>拿上 10 块黑曜石，走到您批准的位置，砌好传送门框并点着。</t>
         </is>
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>M8-13</t>
+          <t>M8-6</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
@@ -10119,7 +10107,7 @@
       </c>
       <c r="E130" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=末影之眼 4、口粮（留底 9，直到 身上吃的 ≥ 8）) → throw_eye(在新家门口扔，记下方向，落地走过去捡) → goto_place(沿和第一次方向垂直的方向走 200 格（长距离，寻路不许挖）) → throw_eye(再扔一次、捡回；代码算两条线的交点，估计位置不在离原点 1280~2816 格内就作废重扔) → go_home(用 /home base 传送回家) → store_items(末影之眼放回大箱子)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=黑曜石（缺几块拿几块）、打火石（跳过条件：身上有）) → goto_place(地方=传送门位置) → build_portal(只补缺的格子，每块记进自家方块登记；用打火石点着，回读有紫色的门方块才算成)</t>
         </is>
       </c>
       <c r="F130" s="7" t="inlineStr">
@@ -10136,17 +10124,17 @@
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>J-M8-13b</t>
+          <t>J-M8-8a</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
         <is>
-          <t>走到算出的要塞位置，近处再扔一次眼确认，从地面斜着挖下去，找到末地传送门框，记下位置后传送回家。</t>
+          <t>去资源世界挖金矿、烧成 5 个金锭，给金头盔备料。</t>
         </is>
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>M8-13</t>
+          <t>M8-8</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
@@ -10156,7 +10144,7 @@
       </c>
       <c r="E131" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=末影之眼 3、口粮（留底 9，直到 身上吃的 ≥ 12）、圆石 64、镐（跳过条件：背包里最好的镐等级 ≥ 2）) → goto_place(地方=要塞估计位置（长距离，寻路不许挖）) → throw_eye(近处核对，眼往下钻 = 就在脚下；捡回) → dig_to_stronghold(先查 32 格内没有别人的东西和领地；楼梯形斜井往下，只挖天然方块；找到末地门框就记坐标和空门框数) → go_home(用 /home base 传送回家)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=铁镐或更好；跳过条件：背包里最好的镐等级 ≥ 3) → take_from_chest(东西=口粮（留底 9）；跳过条件：身上吃的 ≥ 6) → take_from_chest(东西=圆石 8；跳过条件：身上有熔炉 ≥ 1) → craft(东西=furnace；跳过条件：身上有熔炉 ≥ 1) → take_from_chest(东西=原木 4（燃料）；跳过条件：身上的原木 ≥ 4) → goto_place(地方=资源世界（/res go）) → mine(矿=金矿，y≈−16 开巷道（恶地地表也行）；直到 背包粗金 + 金的家底 ≥ 5 或 25 分钟 或 该回主世界 = 1) → smelt(随身熔炉，粗金全部；烧完把熔炉挖回来) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(金锭进大箱子)</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr">
@@ -10173,17 +10161,17 @@
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>J-M8-14</t>
+          <t>J-M8-8b</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
-          <t>带着末影之眼走到要塞，把空门框一个个嵌满，点亮末地传送门，然后传送回家。</t>
+          <t>出发去下界前在家收拾行李：做好金头盔戴上，从粮箱拿够口粮、从大箱子拿 64 块圆石，用不上的东西存掉。</t>
         </is>
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>M8-14</t>
+          <t>M8-8</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
@@ -10193,7 +10181,7 @@
       </c>
       <c r="E132" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=末影之眼，数量=空门框数；口粮（留底 9，直到 身上吃的 ≥ 8）) → goto_place(地方=要塞末地门（长距离，寻路不许挖）) → fill_portal_frame(每个空门框嵌一颗眼，回读中间是不是末地门) → go_home(用 /home base 传送回家)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=金锭 5；跳过条件：穿着金护甲件数 ≥ 1 或 背包金头盔 ≥ 1) → craft(东西=golden_helmet；跳过条件：同上) → wear_armor(下界穿法：金头盔 + 另外三件最好的护甲 + 副手盾) → take_from_chest(东西=口粮，从粮箱拿，留底 9（打开箱子按真数重算）；直到 身上吃的 ≥ 16) → take_from_chest(东西=圆石；直到 身上的圆石 ≥ 64) → store_items(用不上的存掉，行李清单上的留着；直到 背包空格 ≥ 8)</t>
         </is>
       </c>
       <c r="F132" s="7" t="inlineStr">
@@ -10210,17 +10198,17 @@
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>J-M8-15a</t>
+          <t>J-M8-9</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
         <is>
-          <t>在家用线和木棍做弓，用燧石、木棍、羽毛做箭，做好存进大箱子。</t>
+          <t>穿过传送门进下界，朝一个方向一段段找，看到地狱砖城堡就记下位置，然后原路回家。</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>M8-15</t>
+          <t>M8-9</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
@@ -10230,7 +10218,7 @@
       </c>
       <c r="E133" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=线 3（跳过条件：有弓 ≥ 1）、木棍、燧石、羽毛（按缺的现算）) → craft(东西=bow；跳过条件：有弓 ≥ 1) → craft(东西=arrow；直到 箭的家底 ≥ 64，材料用完就停) → store_items(东西=弓、箭，进大箱子)</t>
+          <t>goto_place(地方=传送门（主世界那一头）；跳过条件：当前维度 = 2（下界）) → wear_armor(下界穿法；跳过条件：穿着金护甲件数 ≥ 1) → use_portal(进下界；跳过条件：当前维度 = 2；第一次过去先核对落点周围 32 格有没有别人的方块，有就原路回来、作废位置、写进后台) → explore(在下界：沿一个方向一段 64 格，离门 ≤ 600 格，避开玄武岩三角洲和堡垒遗迹；直到 记得下界要塞 = 1 或 该返航 = 1) → goto_place(地方=下界那一头的门；跳过条件：当前维度 = 0) → use_portal(回主世界；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → store_items(只存可存的，行李留着)</t>
         </is>
       </c>
       <c r="F133" s="7" t="inlineStr">
@@ -10247,17 +10235,17 @@
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>J-M8-15b</t>
+          <t>J-M8-10</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t>去资源世界打鸡拿羽毛、挖沙砾拿燧石，给做箭备料。</t>
+          <t>去下界要塞的烈焰人刷怪笼旁边，举着盾一只只打烈焰人，攒烈焰棒，带回家存进箱子。</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>M8-15</t>
+          <t>M8-10</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
@@ -10267,7 +10255,7 @@
       </c>
       <c r="E134" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方=资源世界（/res go）) → hunt(目标=鸡，打死后捡羽毛；跳过条件：做箭还缺的羽毛 = 0；直到 做箭还缺的羽毛 = 0 或 15 分钟) → mine(方块=沙砾；跳过条件：做箭还缺的燧石 = 0；直到 做箭还缺的燧石 = 0 或 10 分钟) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(羽毛、燧石进大箱子)</t>
+          <t>goto_place(地方=传送门（主世界那一头）；跳过条件：当前维度 = 2) → wear_armor(下界穿法；跳过条件：穿着金护甲件数 ≥ 1) → use_portal(进下界；跳过条件：当前维度 = 2) → goto_place(地方=烈焰人刷怪笼，停在 6~8 格外的走廊) → fight(目标=烈焰人，举盾挡火球，打死后走过去捡；直到 做眼还缺的烈焰棒 = 0（背包里的也算） 或 该返航 = 1) → goto_place(地方=下界那一头的门；跳过条件：当前维度 = 0) → use_portal(回主世界；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → store_items(烈焰棒进大箱子)</t>
         </is>
       </c>
       <c r="F134" s="7" t="inlineStr">
@@ -10284,17 +10272,17 @@
     <row r="135">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>J-M8-16</t>
+          <t>J-M8-11</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
         <is>
-          <t>（等您批）带着 4 个末地水晶进末地，放在中间返回门的四边，把龙叫回来。</t>
+          <t>去下界的诡异森林，躲在自己搭的两格高小棚口，一只只打末影人，攒末影珍珠带回家。</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>M8-16</t>
+          <t>M8-11</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
@@ -10304,7 +10292,7 @@
       </c>
       <c r="E135" s="7" t="inlineStr">
         <is>
-          <t>take_from_chest(东西=末地水晶 4) → goto_place(地方=要塞末地门；跳过条件：当前维度 = 3（末地）) → use_portal(进末地；跳过条件：当前维度 = 3) → respawn_dragon(4 个水晶放在中间返回门的四边)</t>
+          <t>goto_place(地方=传送门（主世界那一头）；跳过条件：当前维度 = 2) → wear_armor(下界穿法；跳过条件：穿着金护甲件数 ≥ 1) → use_portal(进下界；跳过条件：当前维度 = 2) → goto_place(地方=诡异森林；还不记得就在下界 explore 找青绿色的地面，最多 10 分钟) → hunt_enderman(先搭两格高小棚，一次惹一只；直到 做眼还缺的末影珍珠 = 0（背包里的也算） 或 该返航 = 1；走前拆回小棚) → goto_place(地方=下界那一头的门；跳过条件：当前维度 = 0) → use_portal(回主世界；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → store_items(末影珍珠进大箱子)</t>
         </is>
       </c>
       <c r="F135" s="7" t="inlineStr">
@@ -10321,27 +10309,27 @@
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>J-M8-17a</t>
+          <t>J-M8-12</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t>进末地前在家收拾：拿上弓和 64 支箭、128 块圆石和 24 个吃的，换回四件铁甲。</t>
+          <t>麦娘从大箱子拿烈焰棒和末影珍珠，合成末影之眼，再存回箱子。</t>
         </is>
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>M8-17</t>
+          <t>M8-12</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>麦娘</t>
         </is>
       </c>
       <c r="E136" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=弓（跳过条件：身上有弓）、箭（直到 身上的箭 ≥ 64）) → take_from_chest(东西=圆石；直到 身上的圆石 ≥ 128) → take_from_chest(东西=口粮，从粮箱拿，留底 9（打开箱子按真数重算）；直到 身上吃的 ≥ 24) → wear_armor(末地穿法：四件最好的护甲 + 副手盾) → store_items(用不上的存掉，行李清单上的留着；直到 背包空格 ≥ 6)</t>
+          <t>take_from_chest(东西=烈焰棒、末影珍珠；数量按 min(能做的末影之眼数, 末影之眼缺口) 现算) → craft(东西=blaze_powder) → craft(东西=ender_eye) → store_items(末影之眼和多的烈焰粉进大箱子)</t>
         </is>
       </c>
       <c r="F136" s="7" t="inlineStr">
@@ -10358,17 +10346,17 @@
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>J-M8-17b</t>
+          <t>J-M8-13a</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
         <is>
-          <t>走到要塞，穿门进末地，先射掉柱子上的末地水晶，再趁龙落到中间时打它，打完从中间的门回家。</t>
+          <t>带几个末影之眼出门，在两个地方各扔一次、捡回来，算出要塞大概在哪，然后传送回家。</t>
         </is>
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>M8-17</t>
+          <t>M8-13</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
@@ -10378,7 +10366,7 @@
       </c>
       <c r="E137" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方=要塞末地门（长距离，寻路不许挖）；跳过条件：当前维度 = 3) → use_portal(进末地；跳过条件：当前维度 = 3) → dragon_fight(先看平台要不要搭路；射水晶，笼子里的垫高去打；趁龙落地近身打；不看末影人；血 ≤ 8 先吃，≤ 6 传送回家) → use_portal(龙死后走中间的返回门回主世界，回应结束字幕；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → store_items</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=末影之眼 4、口粮（留底 9，直到 身上吃的 ≥ 8）) → throw_eye(在新家门口扔，记下方向，落地走过去捡) → goto_place(沿和第一次方向垂直的方向走 200 格（长距离，寻路不许挖）) → throw_eye(再扔一次、捡回；代码算两条线的交点，估计位置不在离原点 1280~2816 格内就作废重扔) → go_home(用 /home base 传送回家) → store_items(末影之眼放回大箱子)</t>
         </is>
       </c>
       <c r="F137" s="7" t="inlineStr">
@@ -10395,17 +10383,17 @@
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>J-T0-1</t>
+          <t>J-M8-13b</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
         <is>
-          <t>小麦零候选时的兜底：回家核对箱子、把东西存好，在家等 1 分钟再重算。</t>
+          <t>走到算出的要塞位置，近处再扔一次眼确认，从地面斜着挖下去，找到末地传送门框，记下位置后传送回家。</t>
         </is>
       </c>
       <c r="C138" s="7" t="inlineStr">
         <is>
-          <t>T0</t>
+          <t>M8-13</t>
         </is>
       </c>
       <c r="D138" s="7" t="inlineStr">
@@ -10415,7 +10403,7 @@
       </c>
       <c r="E138" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → check_chest(只打开看、不拿；核对完先重算一次候选，有了就结束兜底；跳过条件：开箱快照距今秒数 ≤ 600) → store_items(跳过条件：可存的东西 = 0) → idle(60 秒，然后重算候选)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=末影之眼 3、口粮（留底 9，直到 身上吃的 ≥ 12）、圆石 64、镐（跳过条件：背包里最好的镐等级 ≥ 2）) → goto_place(地方=要塞估计位置（长距离，寻路不许挖）) → throw_eye(近处核对，眼往下钻 = 就在脚下；捡回) → dig_to_stronghold(先查 32 格内没有别人的东西和领地；楼梯形斜井往下，只挖天然方块；找到末地门框就记坐标和空门框数) → go_home(用 /home base 传送回家)</t>
         </is>
       </c>
       <c r="F138" s="7" t="inlineStr">
@@ -10432,27 +10420,27 @@
     <row r="139">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>J-T0-2</t>
+          <t>J-M8-14</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
         <is>
-          <t>麦娘零候选时的兜底：回家核对两口箱子，把身上的小麦做成面包、东西存好，在家等 1 分钟再重算。</t>
+          <t>带着末影之眼走到要塞，把空门框一个个嵌满，点亮末地传送门，然后传送回家。</t>
         </is>
       </c>
       <c r="C139" s="7" t="inlineStr">
         <is>
-          <t>T0</t>
+          <t>M8-14</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>麦娘</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="E139" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → check_chest(大箱子和粮箱只看不拿；跳过条件：开箱快照距今秒数 ≤ 600) → craft(东西=bread；跳过条件：有小麦 ≤ 2) → store_crop(跳过条件：能存粮 = 0) → store_items(跳过条件：可存的东西 = 0) → idle(60 秒，然后重算候选)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=末影之眼，数量=空门框数；口粮（留底 9，直到 身上吃的 ≥ 8）) → goto_place(地方=要塞末地门（长距离，寻路不许挖）) → fill_portal_frame(每个空门框嵌一颗眼，回读中间是不是末地门) → go_home(用 /home base 传送回家)</t>
         </is>
       </c>
       <c r="F139" s="7" t="inlineStr">
@@ -10469,27 +10457,27 @@
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>J-T0-3</t>
+          <t>J-M8-15a</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
-          <t>麦豆零候选时的兜底：回家门口、离真人远的地方玩一会儿（天黑就待在屋里），30 秒后重算。</t>
+          <t>在家用线和木棍做弓，用燧石、木棍、羽毛做箭，做好存进大箱子。</t>
         </is>
       </c>
       <c r="C140" s="7" t="inlineStr">
         <is>
-          <t>T0</t>
+          <t>M8-15</t>
         </is>
       </c>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>麦豆</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="E140" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 16) → wander(家门口 16 格内；跳过条件：天黑了 = 1 或 血量 ≤ 15 或 离最近真人玩家距离 ≤ 24) → idle(30 秒，然后重算候选)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=线 3（跳过条件：有弓 ≥ 1）、木棍、燧石、羽毛（按缺的现算）) → craft(东西=bow；跳过条件：有弓 ≥ 1) → craft(东西=arrow；直到 箭的家底 ≥ 64，材料用完就停) → store_items(东西=弓、箭，进大箱子)</t>
         </is>
       </c>
       <c r="F140" s="7" t="inlineStr">
@@ -10499,32 +10487,36 @@
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>J-T1-1</t>
+          <t>J-M8-15b</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
-          <t>把这一档能做的几件活连同全家现状交给模型，让它排个先后，然后照这个顺序一件件开工。</t>
+          <t>去资源世界打鸡拿羽毛、挖沙砾拿燧石，给做箭备料。</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>M8-15</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>全家</t>
-        </is>
-      </c>
-      <c r="E141" s="7" t="inlineStr"/>
+          <t>小麦</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
+          <t>goto_place(地方=资源世界（/res go）) → hunt(目标=鸡，打死后捡羽毛；跳过条件：做箭还缺的羽毛 = 0；直到 做箭还缺的羽毛 = 0 或 15 分钟) → mine(方块=沙砾；跳过条件：做箭还缺的燧石 = 0；直到 做箭还缺的燧石 = 0 或 10 分钟) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(羽毛、燧石进大箱子)</t>
+        </is>
+      </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
           <t>新写</t>
@@ -10539,25 +10531,29 @@
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>J-T1-2</t>
+          <t>J-M8-16</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr">
         <is>
-          <t>把连败的那件活、失败原话和这个小目标剩下的办法交给模型，让它只回一个编号，然后换那条做。</t>
+          <t>（等您批）带着 4 个末地水晶进末地，放在中间返回门的四边，把龙叫回来。</t>
         </is>
       </c>
       <c r="C142" s="7" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>M8-16</t>
         </is>
       </c>
       <c r="D142" s="7" t="inlineStr">
         <is>
-          <t>全家</t>
-        </is>
-      </c>
-      <c r="E142" s="7" t="inlineStr"/>
+          <t>小麦</t>
+        </is>
+      </c>
+      <c r="E142" s="7" t="inlineStr">
+        <is>
+          <t>take_from_chest(东西=末地水晶 4) → goto_place(地方=要塞末地门；跳过条件：当前维度 = 3（末地）) → use_portal(进末地；跳过条件：当前维度 = 3) → respawn_dragon(4 个水晶放在中间返回门的四边)</t>
+        </is>
+      </c>
       <c r="F142" s="7" t="inlineStr">
         <is>
           <t>新写</t>
@@ -10572,27 +10568,27 @@
     <row r="143">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>J-T8</t>
+          <t>J-M8-17a</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
         <is>
-          <t>「做同一件小目标时、30 分钟内因为同一种原因死了两次：饿死、…」这条触发的脚本</t>
+          <t>进末地前在家收拾：拿上弓和 64 支箭、128 块圆石和 24 个吃的，换回四件铁甲。</t>
         </is>
       </c>
       <c r="C143" s="7" t="inlineStr">
         <is>
-          <t>T8</t>
+          <t>M8-17</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>全家</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="E143" s="7" t="inlineStr">
         <is>
-          <t>(代码)收集候选(按这条触发的规则算出所有可选项) → (代码)只有 0 或 1 个候选(直接由代码决定,不问模型) → ask_model(≥2 个候选时问一次,只许回候选编号) → (代码)执行选中的那一项(问不到或超时:代码按固定规则兜底,不卡住)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=弓（跳过条件：身上有弓）、箭（直到 身上的箭 ≥ 64）) → take_from_chest(东西=圆石；直到 身上的圆石 ≥ 128) → take_from_chest(东西=口粮，从粮箱拿，留底 9（打开箱子按真数重算）；直到 身上吃的 ≥ 24) → wear_armor(末地穿法：四件最好的护甲 + 副手盾) → store_items(用不上的存掉，行李清单上的留着；直到 背包空格 ≥ 6)</t>
         </is>
       </c>
       <c r="F143" s="7" t="inlineStr">
@@ -10602,34 +10598,34 @@
       </c>
       <c r="G143" s="7" t="inlineStr">
         <is>
-          <t>缺动作</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>J-T10</t>
+          <t>J-M8-17b</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
         <is>
-          <t>「您（Owner）在游戏里点名叫它做某件事时，代码…」这条触发的脚本</t>
+          <t>走到要塞，穿门进末地，先射掉柱子上的末地水晶，再趁龙落到中间时打它，打完从中间的门回家。</t>
         </is>
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>M8-17</t>
         </is>
       </c>
       <c r="D144" s="7" t="inlineStr">
         <is>
-          <t>全家</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="E144" s="7" t="inlineStr">
         <is>
-          <t>(代码)收集候选(按这条触发的规则算出所有可选项) → (代码)只有 0 或 1 个候选(直接由代码决定,不问模型) → ask_model(≥2 个候选时问一次,只许回候选编号) → (代码)执行选中的那一项(问不到或超时:代码按固定规则兜底,不卡住)</t>
+          <t>goto_place(地方=要塞末地门（长距离，寻路不许挖）；跳过条件：当前维度 = 3) → use_portal(进末地；跳过条件：当前维度 = 3) → dragon_fight(先看平台要不要搭路；射水晶，笼子里的垫高去打；趁龙落地近身打；不看末影人；血 ≤ 8 先吃，≤ 6 传送回家) → use_portal(龙死后走中间的返回门回主世界，回应结束字幕；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → store_items</t>
         </is>
       </c>
       <c r="F144" s="7" t="inlineStr">
@@ -10639,34 +10635,34 @@
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
-          <t>缺动作</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t>J-T11</t>
+          <t>J-T0-1</t>
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr">
         <is>
-          <t>「房子盖好以后，如果有两种以上合法的家具摆法（比如床靠北墙还是…」这条触发的脚本</t>
+          <t>小麦零候选时的兜底：回家核对箱子、把东西存好，在家等 1 分钟再重算。</t>
         </is>
       </c>
       <c r="C145" s="7" t="inlineStr">
         <is>
-          <t>T11</t>
+          <t>T0</t>
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>全家</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="E145" s="7" t="inlineStr">
         <is>
-          <t>(代码)收集候选(按这条触发的规则算出所有可选项) → (代码)只有 0 或 1 个候选(直接由代码决定,不问模型) → ask_model(≥2 个候选时问一次,只许回候选编号) → (代码)执行选中的那一项(问不到或超时:代码按固定规则兜底,不卡住)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → check_chest(只打开看、不拿；核对完先重算一次候选，有了就结束兜底；跳过条件：开箱快照距今秒数 ≤ 600) → store_items(跳过条件：可存的东西 = 0) → idle(60 秒，然后重算候选)</t>
         </is>
       </c>
       <c r="F145" s="7" t="inlineStr">
@@ -10676,30 +10672,34 @@
       </c>
       <c r="G145" s="7" t="inlineStr">
         <is>
-          <t>缺动作</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>think_goal_order</t>
+          <t>J-T0-2</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
         <is>
-          <t>问模型给同档大目标排先后或并行</t>
+          <t>麦娘零候选时的兜底：回家核对两口箱子，把身上的小麦做成面包、东西存好，在家等 1 分钟再重算。</t>
         </is>
       </c>
       <c r="C146" s="7" t="inlineStr">
         <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="D146" s="7" t="inlineStr"/>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="D146" s="7" t="inlineStr">
+        <is>
+          <t>麦娘</t>
+        </is>
+      </c>
       <c r="E146" s="7" t="inlineStr">
         <is>
-          <t>ask_model(同档可开工的 G 编号)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → check_chest(大箱子和粮箱只看不拿；跳过条件：开箱快照距今秒数 ≤ 600) → craft(东西=bread；跳过条件：有小麦 ≤ 2) → store_crop(跳过条件：能存粮 = 0) → store_items(跳过条件：可存的东西 = 0) → idle(60 秒，然后重算候选)</t>
         </is>
       </c>
       <c r="F146" s="7" t="inlineStr">
@@ -10709,30 +10709,34 @@
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
-          <t>缺动作</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>think_home_site</t>
+          <t>J-T0-3</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
         <is>
-          <t>问模型选新家址</t>
+          <t>麦豆零候选时的兜底：回家门口、离真人远的地方玩一会儿（天黑就待在屋里），30 秒后重算。</t>
         </is>
       </c>
       <c r="C147" s="7" t="inlineStr">
         <is>
-          <t>T5</t>
-        </is>
-      </c>
-      <c r="D147" s="7" t="inlineStr"/>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="D147" s="7" t="inlineStr">
+        <is>
+          <t>麦豆</t>
+        </is>
+      </c>
       <c r="E147" s="7" t="inlineStr">
         <is>
-          <t>ask_model(候选家址编号 + 打分明细)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 16) → wander(家门口 16 格内；跳过条件：天黑了 = 1 或 血量 ≤ 15 或 离最近真人玩家距离 ≤ 24) → idle(30 秒，然后重算候选)</t>
         </is>
       </c>
       <c r="F147" s="7" t="inlineStr">
@@ -10742,32 +10746,32 @@
       </c>
       <c r="G147" s="7" t="inlineStr">
         <is>
-          <t>缺动作</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>think_house_design</t>
+          <t>J-T1-1</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
         <is>
-          <t>问模型选房子方案</t>
+          <t>把这一档能做的几件活连同全家现状交给模型，让它排个先后，然后照这个顺序一件件开工。</t>
         </is>
       </c>
       <c r="C148" s="7" t="inlineStr">
         <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="D148" s="7" t="inlineStr"/>
-      <c r="E148" s="7" t="inlineStr">
-        <is>
-          <t>ask_model(代码列出的方案编号)</t>
-        </is>
-      </c>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="D148" s="7" t="inlineStr">
+        <is>
+          <t>全家</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="inlineStr"/>
       <c r="F148" s="7" t="inlineStr">
         <is>
           <t>新写</t>
@@ -10775,32 +10779,32 @@
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
-          <t>缺动作</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>think_pick_task</t>
+          <t>J-T1-2</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
         <is>
-          <t>(已并入 J-T1-1)问模型给同档小目标排先后</t>
+          <t>把连败的那件活、失败原话和这个小目标剩下的办法交给模型，让它只回一个编号，然后换那条做。</t>
         </is>
       </c>
       <c r="C149" s="7" t="inlineStr">
         <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="D149" s="7" t="inlineStr"/>
-      <c r="E149" s="7" t="inlineStr">
-        <is>
-          <t>ask_model(同档候选编号;默认=最久没做的)</t>
-        </is>
-      </c>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="D149" s="7" t="inlineStr">
+        <is>
+          <t>全家</t>
+        </is>
+      </c>
+      <c r="E149" s="7" t="inlineStr"/>
       <c r="F149" s="7" t="inlineStr">
         <is>
           <t>新写</t>
@@ -10808,38 +10812,281 @@
       </c>
       <c r="G149" s="7" t="inlineStr">
         <is>
-          <t>缺动作</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="7" t="inlineStr">
         <is>
+          <t>J-T8</t>
+        </is>
+      </c>
+      <c r="B150" s="7" t="inlineStr">
+        <is>
+          <t>「做同一件小目标时、30 分钟内因为同一种原因死了两次：饿死、…」这条触发的脚本</t>
+        </is>
+      </c>
+      <c r="C150" s="7" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+      <c r="D150" s="7" t="inlineStr">
+        <is>
+          <t>全家</t>
+        </is>
+      </c>
+      <c r="E150" s="7" t="inlineStr">
+        <is>
+          <t>(代码)收集候选(按这条触发的规则算出所有可选项) → (代码)只有 0 或 1 个候选(直接由代码决定,不问模型) → ask_model(≥2 个候选时问一次,只许回候选编号) → (代码)执行选中的那一项(问不到或超时:代码按固定规则兜底,不卡住)</t>
+        </is>
+      </c>
+      <c r="F150" s="7" t="inlineStr">
+        <is>
+          <t>新写</t>
+        </is>
+      </c>
+      <c r="G150" s="7" t="inlineStr">
+        <is>
+          <t>缺动作</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="7" t="inlineStr">
+        <is>
+          <t>J-T10</t>
+        </is>
+      </c>
+      <c r="B151" s="7" t="inlineStr">
+        <is>
+          <t>「您（Owner）在游戏里点名叫它做某件事时，代码…」这条触发的脚本</t>
+        </is>
+      </c>
+      <c r="C151" s="7" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="D151" s="7" t="inlineStr">
+        <is>
+          <t>全家</t>
+        </is>
+      </c>
+      <c r="E151" s="7" t="inlineStr">
+        <is>
+          <t>(代码)收集候选(按这条触发的规则算出所有可选项) → (代码)只有 0 或 1 个候选(直接由代码决定,不问模型) → ask_model(≥2 个候选时问一次,只许回候选编号) → (代码)执行选中的那一项(问不到或超时:代码按固定规则兜底,不卡住)</t>
+        </is>
+      </c>
+      <c r="F151" s="7" t="inlineStr">
+        <is>
+          <t>新写</t>
+        </is>
+      </c>
+      <c r="G151" s="7" t="inlineStr">
+        <is>
+          <t>缺动作</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="7" t="inlineStr">
+        <is>
+          <t>J-T11</t>
+        </is>
+      </c>
+      <c r="B152" s="7" t="inlineStr">
+        <is>
+          <t>「房子盖好以后，如果有两种以上合法的家具摆法（比如床靠北墙还是…」这条触发的脚本</t>
+        </is>
+      </c>
+      <c r="C152" s="7" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="D152" s="7" t="inlineStr">
+        <is>
+          <t>全家</t>
+        </is>
+      </c>
+      <c r="E152" s="7" t="inlineStr">
+        <is>
+          <t>(代码)收集候选(按这条触发的规则算出所有可选项) → (代码)只有 0 或 1 个候选(直接由代码决定,不问模型) → ask_model(≥2 个候选时问一次,只许回候选编号) → (代码)执行选中的那一项(问不到或超时:代码按固定规则兜底,不卡住)</t>
+        </is>
+      </c>
+      <c r="F152" s="7" t="inlineStr">
+        <is>
+          <t>新写</t>
+        </is>
+      </c>
+      <c r="G152" s="7" t="inlineStr">
+        <is>
+          <t>缺动作</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="7" t="inlineStr">
+        <is>
+          <t>think_goal_order</t>
+        </is>
+      </c>
+      <c r="B153" s="7" t="inlineStr">
+        <is>
+          <t>问模型给同档大目标排先后或并行</t>
+        </is>
+      </c>
+      <c r="C153" s="7" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="D153" s="7" t="inlineStr"/>
+      <c r="E153" s="7" t="inlineStr">
+        <is>
+          <t>ask_model(同档可开工的 G 编号)</t>
+        </is>
+      </c>
+      <c r="F153" s="7" t="inlineStr">
+        <is>
+          <t>新写</t>
+        </is>
+      </c>
+      <c r="G153" s="7" t="inlineStr">
+        <is>
+          <t>缺动作</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="7" t="inlineStr">
+        <is>
+          <t>think_home_site</t>
+        </is>
+      </c>
+      <c r="B154" s="7" t="inlineStr">
+        <is>
+          <t>问模型选新家址</t>
+        </is>
+      </c>
+      <c r="C154" s="7" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="D154" s="7" t="inlineStr"/>
+      <c r="E154" s="7" t="inlineStr">
+        <is>
+          <t>ask_model(候选家址编号 + 打分明细)</t>
+        </is>
+      </c>
+      <c r="F154" s="7" t="inlineStr">
+        <is>
+          <t>新写</t>
+        </is>
+      </c>
+      <c r="G154" s="7" t="inlineStr">
+        <is>
+          <t>缺动作</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="7" t="inlineStr">
+        <is>
+          <t>think_house_design</t>
+        </is>
+      </c>
+      <c r="B155" s="7" t="inlineStr">
+        <is>
+          <t>问模型选房子方案</t>
+        </is>
+      </c>
+      <c r="C155" s="7" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="D155" s="7" t="inlineStr"/>
+      <c r="E155" s="7" t="inlineStr">
+        <is>
+          <t>ask_model(代码列出的方案编号)</t>
+        </is>
+      </c>
+      <c r="F155" s="7" t="inlineStr">
+        <is>
+          <t>新写</t>
+        </is>
+      </c>
+      <c r="G155" s="7" t="inlineStr">
+        <is>
+          <t>缺动作</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="7" t="inlineStr">
+        <is>
+          <t>think_pick_task</t>
+        </is>
+      </c>
+      <c r="B156" s="7" t="inlineStr">
+        <is>
+          <t>(已并入 J-T1-1)问模型给同档小目标排先后</t>
+        </is>
+      </c>
+      <c r="C156" s="7" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="D156" s="7" t="inlineStr"/>
+      <c r="E156" s="7" t="inlineStr">
+        <is>
+          <t>ask_model(同档候选编号;默认=最久没做的)</t>
+        </is>
+      </c>
+      <c r="F156" s="7" t="inlineStr">
+        <is>
+          <t>新写</t>
+        </is>
+      </c>
+      <c r="G156" s="7" t="inlineStr">
+        <is>
+          <t>缺动作</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="7" t="inlineStr">
+        <is>
           <t>think_reply</t>
         </is>
       </c>
-      <c r="B150" s="7" t="inlineStr">
+      <c r="B157" s="7" t="inlineStr">
         <is>
           <t>被点名时写一句回话,并从 3 个选项里挑一个</t>
         </is>
       </c>
-      <c r="C150" s="7" t="inlineStr">
+      <c r="C157" s="7" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="D150" s="7" t="inlineStr"/>
-      <c r="E150" s="7" t="inlineStr">
+      <c r="D157" s="7" t="inlineStr"/>
+      <c r="E157" s="7" t="inlineStr">
         <is>
           <t>ask_model(回话 + 选项:只回话/跟他走/不理) → say(模型写的那句) → follow_player(只在选了「跟他走」时;最多 120 秒)</t>
         </is>
       </c>
-      <c r="F150" s="7" t="inlineStr">
+      <c r="F157" s="7" t="inlineStr">
         <is>
           <t>新写</t>
         </is>
       </c>
-      <c r="G150" s="7" t="inlineStr">
+      <c r="G157" s="7" t="inlineStr">
         <is>
           <t>缺动作</t>
         </is>
@@ -20294,7 +20541,7 @@
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -20556,7 +20803,11 @@
           <t>学砍树和存箱子(不然「学会爸爸会的事」做不到);遇怪只跑不打。收麦子也学(不然他白天只能陪在妈妈旁边看);学会存箱子就自己存,最省事。</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr"/>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>已定(2026-09-18):按建议全学 —— 砍树、收麦子种回去、存箱子;背包满了自己存;遇怪只跑不打。</t>
+        </is>
+      </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
           <t>补充 Q18、基本状态 Q21、第二轮</t>
@@ -20577,7 +20828,11 @@
           <t>只听您(Owner)的指挥;孩子叫它时只回话、不跟着走、不接活。现在是任何人叫它都会放下手上的活跟着走 5 分钟。</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr"/>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>已定(2026-09-18 约 15:14):能,由 AI 按性格决定听不听;护栏和未成年人安全底线照旧由代码挡。(和我原来「只听 Owner」的建议不同,以 Owner 为准)</t>
+        </is>
+      </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
           <t>补充 Q20、思考触发 Q24</t>
@@ -20847,7 +21102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E465"/>
+  <dimension ref="A1:E505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -20865,27 +21120,27 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>部分</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>条目</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>问题类型</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>怎么改的</t>
         </is>
@@ -33389,6 +33644,1086 @@
       <c r="E465" s="7" t="inlineStr">
         <is>
           <t>原来:null → 现在:"上下文按 C-CTX-1 的「T5 配方」;选项按代码打分从高到低标 A~F,兜底选 A。"</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B466" s="7" t="inlineStr">
+        <is>
+          <t>M1-1</t>
+        </is>
+      </c>
+      <c r="C466" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D466" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 done_when:9 颗凑不到(线上找种子做到 3 颗就停、割草要 ≤2 颗才开工),和线上脚本对齐成 3 颗;种子不够时 M1-4/M1-7 下的找种子、割草会接着补</t>
+        </is>
+      </c>
+      <c r="E466" s="7" t="inlineStr">
+        <is>
+          <t>原来:[{"pred": "有锄头", "op": "≥", "value": 1}, {"pred": "有种子", "op": "≥", "v → 现在:[{"pred": "有锄头", "op": "≥", "value": 1}, {"pred": "有种子", "op": "≥", "v</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B467" s="7" t="inlineStr">
+        <is>
+          <t>M5-4</t>
+        </is>
+      </c>
+      <c r="C467" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D467" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 scripts:make_sword 只做木剑,挂在这里是假候选(做出木剑也推不动这个小目标)</t>
+        </is>
+      </c>
+      <c r="E467" s="7" t="inlineStr">
+        <is>
+          <t>原来:["make_sword"] → 现在:[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B468" s="7" t="inlineStr">
+        <is>
+          <t>M5-6</t>
+        </is>
+      </c>
+      <c r="C468" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D468" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 scripts:make_sword 只做木剑,挂在这里是假候选(做出木剑也推不动这个小目标)</t>
+        </is>
+      </c>
+      <c r="E468" s="7" t="inlineStr">
+        <is>
+          <t>原来:["make_sword"] → 现在:[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B469" s="7" t="inlineStr">
+        <is>
+          <t>M1-3</t>
+        </is>
+      </c>
+      <c r="C469" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D469" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 priority:对齐线上麦娘验证过的次序:粮 &gt; 田 &gt; 收拾(原来备木板排第一、收割排在锄地后面,熟了先收会被锄地挡住)</t>
+        </is>
+      </c>
+      <c r="E469" s="7" t="inlineStr">
+        <is>
+          <t>原来:3 → 现在:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B470" s="7" t="inlineStr">
+        <is>
+          <t>M1-4</t>
+        </is>
+      </c>
+      <c r="C470" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D470" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 priority:对齐线上麦娘验证过的次序:粮 &gt; 田 &gt; 收拾(原来备木板排第一、收割排在锄地后面,熟了先收会被锄地挡住)</t>
+        </is>
+      </c>
+      <c r="E470" s="7" t="inlineStr">
+        <is>
+          <t>原来:3 → 现在:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B471" s="7" t="inlineStr">
+        <is>
+          <t>M1-8</t>
+        </is>
+      </c>
+      <c r="C471" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D471" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 priority:对齐线上麦娘验证过的次序:粮 &gt; 田 &gt; 收拾(原来备木板排第一、收割排在锄地后面,熟了先收会被锄地挡住)</t>
+        </is>
+      </c>
+      <c r="E471" s="7" t="inlineStr">
+        <is>
+          <t>原来:3 → 现在:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B472" s="7" t="inlineStr">
+        <is>
+          <t>M1-1</t>
+        </is>
+      </c>
+      <c r="C472" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D472" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 priority:对齐线上麦娘验证过的次序:粮 &gt; 田 &gt; 收拾(原来备木板排第一、收割排在锄地后面,熟了先收会被锄地挡住)</t>
+        </is>
+      </c>
+      <c r="E472" s="7" t="inlineStr">
+        <is>
+          <t>原来:1 → 现在:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B473" s="7" t="inlineStr">
+        <is>
+          <t>M1-2</t>
+        </is>
+      </c>
+      <c r="C473" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D473" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 priority:对齐线上麦娘验证过的次序:粮 &gt; 田 &gt; 收拾(原来备木板排第一、收割排在锄地后面,熟了先收会被锄地挡住)</t>
+        </is>
+      </c>
+      <c r="E473" s="7" t="inlineStr">
+        <is>
+          <t>原来:2 → 现在:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B474" s="7" t="inlineStr">
+        <is>
+          <t>M1-7</t>
+        </is>
+      </c>
+      <c r="C474" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D474" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 priority:对齐线上麦娘验证过的次序:粮 &gt; 田 &gt; 收拾(原来备木板排第一、收割排在锄地后面,熟了先收会被锄地挡住)</t>
+        </is>
+      </c>
+      <c r="E474" s="7" t="inlineStr">
+        <is>
+          <t>原来:4 → 现在:2</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B475" s="7" t="inlineStr">
+        <is>
+          <t>M1-9</t>
+        </is>
+      </c>
+      <c r="C475" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D475" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 priority:对齐线上麦娘验证过的次序:粮 &gt; 田 &gt; 收拾(原来备木板排第一、收割排在锄地后面,熟了先收会被锄地挡住)</t>
+        </is>
+      </c>
+      <c r="E475" s="7" t="inlineStr">
+        <is>
+          <t>原来:5 → 现在:2</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B476" s="7" t="inlineStr">
+        <is>
+          <t>M3-2</t>
+        </is>
+      </c>
+      <c r="C476" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D476" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 priority:对齐线上麦娘验证过的次序:粮 &gt; 田 &gt; 收拾(原来备木板排第一、收割排在锄地后面,熟了先收会被锄地挡住)</t>
+        </is>
+      </c>
+      <c r="E476" s="7" t="inlineStr">
+        <is>
+          <t>原来:0 → 现在:3</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B477" s="7" t="inlineStr">
+        <is>
+          <t>M7-1</t>
+        </is>
+      </c>
+      <c r="C477" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D477" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 priority:麦豆回家排最前:线上「回家」是最高档,天黑能打断玩耍;同档时打断不了</t>
+        </is>
+      </c>
+      <c r="E477" s="7" t="inlineStr">
+        <is>
+          <t>原来:0 → 现在:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B478" s="7" t="inlineStr">
+        <is>
+          <t>M7-2</t>
+        </is>
+      </c>
+      <c r="C478" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D478" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 priority:麦豆回家排最前:线上「回家」是最高档,天黑能打断玩耍;同档时打断不了</t>
+        </is>
+      </c>
+      <c r="E478" s="7" t="inlineStr">
+        <is>
+          <t>原来:0 → 现在:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B479" s="7" t="inlineStr">
+        <is>
+          <t>M7-4</t>
+        </is>
+      </c>
+      <c r="C479" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D479" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 priority:麦豆回家排最前:线上「回家」是最高档,天黑能打断玩耍;同档时打断不了</t>
+        </is>
+      </c>
+      <c r="E479" s="7" t="inlineStr">
+        <is>
+          <t>原来:0 → 现在:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B480" s="7" t="inlineStr">
+        <is>
+          <t>M7-3</t>
+        </is>
+      </c>
+      <c r="C480" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D480" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 priority:麦豆回家排最前:线上「回家」是最高档,天黑能打断玩耍;同档时打断不了</t>
+        </is>
+      </c>
+      <c r="E480" s="7" t="inlineStr">
+        <is>
+          <t>原来:1 → 现在:2</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B481" s="7" t="inlineStr">
+        <is>
+          <t>M7-5</t>
+        </is>
+      </c>
+      <c r="C481" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D481" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 priority:麦豆回家排最前:线上「回家」是最高档,天黑能打断玩耍;同档时打断不了</t>
+        </is>
+      </c>
+      <c r="E481" s="7" t="inlineStr">
+        <is>
+          <t>原来:2 → 现在:3</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B482" s="7" t="inlineStr">
+        <is>
+          <t>M7-1</t>
+        </is>
+      </c>
+      <c r="C482" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D482" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 scripts:看爸爸砍树归 M7-3(学活),不该跟着「回家」一起升档</t>
+        </is>
+      </c>
+      <c r="E482" s="7" t="inlineStr">
+        <is>
+          <t>原来:["child_home", "child_watch_dad"] → 现在:["child_home"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B483" s="7" t="inlineStr">
+        <is>
+          <t>M2-2</t>
+        </is>
+      </c>
+      <c r="C483" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D483" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 verify_only:原文写明活归 G3 盖新房子、这里只负责验收</t>
+        </is>
+      </c>
+      <c r="E483" s="7" t="inlineStr">
+        <is>
+          <t>原来:null → 现在:true</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B484" s="7" t="inlineStr">
+        <is>
+          <t>G4</t>
+        </is>
+      </c>
+      <c r="C484" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D484" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 status:搬家要 Owner 批准,拍板第 1 件没定之前先暂停,免得「搬旧箱子」被排上</t>
+        </is>
+      </c>
+      <c r="E484" s="7" t="inlineStr">
+        <is>
+          <t>原来:4 → 现在:3</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B485" s="7" t="inlineStr">
+        <is>
+          <t>J-M1-2</t>
+        </is>
+      </c>
+      <c r="C485" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D485" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 enabled:和线上老脚本重复;步骤参数只写在自由文字里引擎读不到,「田」不是认识的地名 —— 先用线上那几条</t>
+        </is>
+      </c>
+      <c r="E485" s="7" t="inlineStr">
+        <is>
+          <t>原来:null → 现在:false</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B486" s="7" t="inlineStr">
+        <is>
+          <t>J-M1-4</t>
+        </is>
+      </c>
+      <c r="C486" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D486" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 enabled:和线上老脚本重复;步骤参数只写在自由文字里引擎读不到,「田」不是认识的地名 —— 先用线上那几条</t>
+        </is>
+      </c>
+      <c r="E486" s="7" t="inlineStr">
+        <is>
+          <t>原来:null → 现在:false</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B487" s="7" t="inlineStr">
+        <is>
+          <t>M6-1</t>
+        </is>
+      </c>
+      <c r="C487" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D487" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 scripts:挂上线上在跑的 make_base:它原来只挂在状态维持/思考触发上,2a 只按小目标派活,切换当天会停掉</t>
+        </is>
+      </c>
+      <c r="E487" s="7" t="inlineStr">
+        <is>
+          <t>原来:["wife_craft_chest"] → 现在:["make_base", "wife_craft_chest"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B488" s="7" t="inlineStr">
+        <is>
+          <t>M6-1</t>
+        </is>
+      </c>
+      <c r="C488" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D488" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 scripts:挂上线上在跑的 wife_store:它原来只挂在状态维持/思考触发上,2a 只按小目标派活,切换当天会停掉</t>
+        </is>
+      </c>
+      <c r="E488" s="7" t="inlineStr">
+        <is>
+          <t>原来:["make_base", "wife_craft_chest"] → 现在:["make_base", "wife_craft_chest", "wife_store"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B489" s="7" t="inlineStr">
+        <is>
+          <t>M5-1</t>
+        </is>
+      </c>
+      <c r="C489" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D489" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 scripts:挂上线上在跑的 guard_home:它原来只挂在状态维持/思考触发上,2a 只按小目标派活,切换当天会停掉</t>
+        </is>
+      </c>
+      <c r="E489" s="7" t="inlineStr">
+        <is>
+          <t>原来:["make_sword"] → 现在:["guard_home", "make_sword"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B490" s="7" t="inlineStr">
+        <is>
+          <t>M3-3</t>
+        </is>
+      </c>
+      <c r="C490" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D490" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 scripts:挂上线上在跑的 build_house:它原来只挂在状态维持/思考触发上,2a 只按小目标派活,切换当天会停掉</t>
+        </is>
+      </c>
+      <c r="E490" s="7" t="inlineStr">
+        <is>
+          <t>原来:["J-M3-3"] → 现在:["J-M3-3", "build_house"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B491" s="7" t="inlineStr">
+        <is>
+          <t>M3-3</t>
+        </is>
+      </c>
+      <c r="C491" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D491" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 scripts:挂上线上在跑的 get_build_mats:它原来只挂在状态维持/思考触发上,2a 只按小目标派活,切换当天会停掉</t>
+        </is>
+      </c>
+      <c r="E491" s="7" t="inlineStr">
+        <is>
+          <t>原来:["J-M3-3", "build_house"] → 现在:["J-M3-3", "build_house", "get_build_mats"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B492" s="7" t="inlineStr">
+        <is>
+          <t>M3-3</t>
+        </is>
+      </c>
+      <c r="C492" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D492" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 scripts:挂上线上在跑的 son_take_mats:它原来只挂在状态维持/思考触发上,2a 只按小目标派活,切换当天会停掉</t>
+        </is>
+      </c>
+      <c r="E492" s="7" t="inlineStr">
+        <is>
+          <t>原来:["J-M3-3", "build_house", "get_build_mats"] → 现在:["J-M3-3", "build_house", "get_build_mats", "son_take_mats"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B493" s="7" t="inlineStr">
+        <is>
+          <t>M1-4</t>
+        </is>
+      </c>
+      <c r="C493" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D493" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 scripts:挂上线上在跑的 wife_harvest:J-M1-2/J-M1-4 关掉后,由线上老脚本接住这个小目标</t>
+        </is>
+      </c>
+      <c r="E493" s="7" t="inlineStr">
+        <is>
+          <t>原来:["J-M1-2", "J-M1-4", "wife_find_seeds", "wife_gather_seeds"] → 现在:["J-M1-2", "J-M1-4", "wife_find_seeds", "wife_gather_seeds", "wife_har</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B494" s="7" t="inlineStr">
+        <is>
+          <t>M1-8</t>
+        </is>
+      </c>
+      <c r="C494" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D494" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 scripts:挂上线上在跑的 wife_harvest:J-M1-2/J-M1-4 关掉后,由线上老脚本接住这个小目标</t>
+        </is>
+      </c>
+      <c r="E494" s="7" t="inlineStr">
+        <is>
+          <t>原来:["J-M1-4", "J-M1-8"] → 现在:["J-M1-4", "J-M1-8", "wife_harvest"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B495" s="7" t="inlineStr">
+        <is>
+          <t>M1-4</t>
+        </is>
+      </c>
+      <c r="C495" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D495" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 scripts:挂上线上在跑的 wife_plant:J-M1-2/J-M1-4 关掉后,由线上老脚本接住这个小目标</t>
+        </is>
+      </c>
+      <c r="E495" s="7" t="inlineStr">
+        <is>
+          <t>原来:["J-M1-2", "J-M1-4", "wife_find_seeds", "wife_gather_seeds", "wife_har → 现在:["J-M1-2", "J-M1-4", "wife_find_seeds", "wife_gather_seeds", "wife_har</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B496" s="7" t="inlineStr">
+        <is>
+          <t>M1-8</t>
+        </is>
+      </c>
+      <c r="C496" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D496" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 scripts:挂上线上在跑的 wife_plant:J-M1-2/J-M1-4 关掉后,由线上老脚本接住这个小目标</t>
+        </is>
+      </c>
+      <c r="E496" s="7" t="inlineStr">
+        <is>
+          <t>原来:["J-M1-4", "J-M1-8", "wife_harvest"] → 现在:["J-M1-4", "J-M1-8", "wife_harvest", "wife_plant"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B497" s="7" t="inlineStr">
+        <is>
+          <t>M1-2</t>
+        </is>
+      </c>
+      <c r="C497" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D497" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 scripts:挂上线上在跑的 wife_till:J-M1-2/J-M1-4 关掉后,由线上老脚本接住这个小目标</t>
+        </is>
+      </c>
+      <c r="E497" s="7" t="inlineStr">
+        <is>
+          <t>原来:["J-M1-2", "wife_plant"] → 现在:["J-M1-2", "wife_plant", "wife_till"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B498" s="7" t="inlineStr">
+        <is>
+          <t>M3-2</t>
+        </is>
+      </c>
+      <c r="C498" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D498" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 scripts:挂上线上在跑的 wife_planks:原来只在生成器里硬挂,搬进表数据</t>
+        </is>
+      </c>
+      <c r="E498" s="7" t="inlineStr">
+        <is>
+          <t>原来:["J-G3-0a", "J-M3-2"] → 现在:["J-G3-0a", "J-M3-2", "wife_planks"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B499" s="7" t="inlineStr">
+        <is>
+          <t>M6-1</t>
+        </is>
+      </c>
+      <c r="C499" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D499" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 owner:make_base 是小麦的,M6-1 负责人加上小麦</t>
+        </is>
+      </c>
+      <c r="E499" s="7" t="inlineStr">
+        <is>
+          <t>原来:"wife" → 现在:"wife, son"</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B500" s="7" t="inlineStr">
+        <is>
+          <t>J-M1-8c</t>
+        </is>
+      </c>
+      <c r="C500" s="7" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="D500" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 麦豆收熟了的麦子(照抄麦娘的 wife_harvest,门槛换成麦豆的)</t>
+        </is>
+      </c>
+      <c r="E500" s="7" t="inlineStr">
+        <is>
+          <t>Owner 批准麦豆学活后照线上现成脚本加的</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B501" s="7" t="inlineStr">
+        <is>
+          <t>J-M1-8d</t>
+        </is>
+      </c>
+      <c r="C501" s="7" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="D501" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 麦豆把收空的地种回去(照抄 wife_plant,门槛换成麦豆的)</t>
+        </is>
+      </c>
+      <c r="E501" s="7" t="inlineStr">
+        <is>
+          <t>Owner 批准麦豆学活后照线上现成脚本加的</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B502" s="7" t="inlineStr">
+        <is>
+          <t>J-M7-3c</t>
+        </is>
+      </c>
+      <c r="C502" s="7" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="D502" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 麦豆在家附近砍树(只砍看得见的树,不去远处林子;离家 40 格内,照抄 child_play 的范围)</t>
+        </is>
+      </c>
+      <c r="E502" s="7" t="inlineStr">
+        <is>
+          <t>Owner 批准麦豆学活后照线上现成脚本加的</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B503" s="7" t="inlineStr">
+        <is>
+          <t>J-M7-3d</t>
+        </is>
+      </c>
+      <c r="C503" s="7" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="D503" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 麦豆背包满了自己回家存箱子(照抄 wife_store)</t>
+        </is>
+      </c>
+      <c r="E503" s="7" t="inlineStr">
+        <is>
+          <t>Owner 批准麦豆学活后照线上现成脚本加的</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B504" s="7" t="inlineStr">
+        <is>
+          <t>拍板11</t>
+        </is>
+      </c>
+      <c r="C504" s="7" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
+      <c r="D504" s="7" t="inlineStr">
+        <is>
+          <t>麦豆:能不能学砍树、把东西放进箱子?遇到怪是不是只跑不打?能不能再学「收麦子、种回去、存进粮箱」?背</t>
+        </is>
+      </c>
+      <c r="E504" s="7" t="inlineStr">
+        <is>
+          <t>已定(2026-09-18):按建议全学 —— 砍树、收麦子种回去、存箱子;背包满了自己存;遇怪只跑不打。</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B505" s="7" t="inlineStr">
+        <is>
+          <t>拍板12</t>
+        </is>
+      </c>
+      <c r="C505" s="7" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
+      <c r="D505" s="7" t="inlineStr">
+        <is>
+          <t>真人孩子在聊天里叫麦家「跟我来」「帮我砍树」,要不要听?</t>
+        </is>
+      </c>
+      <c r="E505" s="7" t="inlineStr">
+        <is>
+          <t>已定(2026-09-18 约 15:14):能,由 AI 按性格决定听不听;护栏和未成年人安全底线照旧由代码挡。(和我原来「只听 Owner」的建议不同,以 Owner 为准)</t>
         </is>
       </c>
     </row>
@@ -33411,19 +34746,19 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>名词</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>意思</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
@@ -33435,7 +34770,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
@@ -33447,7 +34782,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>完成标准</t>
         </is>
@@ -33459,7 +34794,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>触发条件</t>
         </is>
@@ -33471,7 +34806,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>可行性</t>
         </is>
@@ -33483,7 +34818,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>浅绿表头</t>
         </is>
@@ -33495,7 +34830,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>没有定时思考</t>
         </is>
@@ -33507,7 +34842,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>思考触发没有 T6/T7/T9</t>
         </is>
@@ -33519,7 +34854,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>每条思考触发都有脚本</t>
         </is>
@@ -33531,7 +34866,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>「需要您定」那页</t>
         </is>

--- a/ai-player/goal-table/小麦家族工作分解-填写版.xlsx
+++ b/ai-player/goal-table/小麦家族工作分解-填写版.xlsx
@@ -8747,7 +8747,7 @@
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>要放行动作</t>
+          <t>卡在代码</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>要放行动作</t>
+          <t>卡在代码</t>
         </is>
       </c>
     </row>
@@ -9640,7 +9640,7 @@
       </c>
       <c r="G117" s="7" t="inlineStr">
         <is>
-          <t>要放行动作</t>
+          <t>卡在代码</t>
         </is>
       </c>
     </row>
@@ -9652,7 +9652,7 @@
       </c>
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t>麦豆背包满了自己回家存箱子(照抄 wife_store)</t>
+          <t>麦豆身上有木头就回家存进箱子(照抄 wife_store;箱子满了被忘掉时「有箱子」变 0,不会反复空跑)</t>
         </is>
       </c>
       <c r="C118" s="7" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="D503" s="7" t="inlineStr">
         <is>
-          <t>[第三轮] 麦豆背包满了自己回家存箱子(照抄 wife_store)</t>
+          <t>[第三轮] 麦豆身上有木头就回家存进箱子(照抄 wife_store;箱子满了被忘掉时「有箱子」变 0,不会反复空跑)</t>
         </is>
       </c>
       <c r="E503" s="7" t="inlineStr">

--- a/ai-player/goal-table/小麦家族工作分解-填写版.xlsx
+++ b/ai-player/goal-table/小麦家族工作分解-填写版.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:L119"/>
+  <dimension ref="A2:L120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -702,7 +702,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>会打架的家人(现在是小麦;麦娘拿到剑、也被允许还手后也算)手上都有剑,箱子里有备用剑;麦豆只跑不打,不给他剑。为什么要做:两天打坏 82 把木剑,「手无寸铁」触发了 537 次</t>
+          <t>全家三个人(小麦、麦娘、麦豆)手上都有剑:三人各用家里箱子里 2 颗钻石自己做一把钻石剑(一共 6 颗,箱底 21 颗不动;剑递不过去、也存不进箱子,只能各做各的)。为什么:两天打坏 82 把木剑,「手无寸铁」触发 537 次;Owner 2026-09-18:「我建议是所有角色都要有武器装备」+「都还手,但有规矩」</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
@@ -713,12 +713,12 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>M5-1, M5-2, M5-3, M5-4, M5-5, M5-6</t>
+          <t>M5-1, M5-2, M5-3, M5-4, M5-6, M5-7, M5-8</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>在线会打架的家人里没剑的人数 = 0 并且 箱子里剑数 ≥ 3</t>
+          <t>在线家人里没剑的人数 = 0 并且 做过钻石剑的家人数 = 3</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>每个会打架的在线家人手上都有一把剑(麦豆只跑不打,不算)</t>
+          <t>每个在线家人手上都有一把剑(三个人都算)</t>
         </is>
       </c>
       <c r="D24" s="7" t="n">
@@ -1189,7 +1189,7 @@
       <c r="I24" s="7" t="inlineStr"/>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>在线会打架的家人里没剑的人数 = 0</t>
+          <t>在线家人里没剑的人数 = 0</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr">
@@ -1753,12 +1753,12 @@
     <row r="36">
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>M5-5</t>
+          <t>M5-6</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>箱子里常备 3 把木剑</t>
+          <t>三人各从家里箱子拿 2 颗钻石,自己做一把钻石剑(箱底永远留 21 颗;每人一辈子最多领 2 颗,由代码记账)</t>
         </is>
       </c>
       <c r="D36" s="7" t="n">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>J-M5-5</t>
+          <t>make_diamond_sword</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
@@ -1779,13 +1779,13 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr"/>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>箱子里剑数 ≥ 3</t>
+          <t>在线家人里没钻石剑的人数 = 0</t>
         </is>
       </c>
       <c r="K36" s="7" t="inlineStr">
@@ -1795,31 +1795,35 @@
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
-          <t>木剑 = 2 木板 + 1 木棍;剑断了回家拿一把就行,不用临时去合成</t>
+          <t>钻石剑 = 2 钻石 + 1 木棍;现在只数会打架的人(小麦,麦娘放行 fight 后再加一把),2 把用 4 颗,箱子里有 27 颗。「在线家人里没钻石剑的人数」和 M5-1 同一个函数(C-FAM-12,剑种当参数)。钻石按物品分类表算贵重;换下来的旧剑存进箱子当备用,不扔。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>M5-6</t>
+          <t>M6-3</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>用箱子里的钻石给会打架的家人每人做一把钻石剑(麦豆不算;等 Owner 批准)</t>
+          <t>箱子里原木不少于 64 根(掉下去才补)</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F37" s="7" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>chop_wood, find_forest, store_wood</t>
+        </is>
+      </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>G5</t>
+          <t>G6</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
@@ -1830,7 +1834,7 @@
       <c r="I37" s="7" t="inlineStr"/>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>在线家人里没钻石剑的人数 = 0</t>
+          <t>箱子里原木 ≥ 64</t>
         </is>
       </c>
       <c r="K37" s="7" t="inlineStr">
@@ -1840,19 +1844,19 @@
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>钻石剑 = 2 钻石 + 1 木棍;现在只数会打架的人(小麦,麦娘放行 fight 后再加一把),2 把用 4 颗,箱子里有 27 颗。「在线家人里没钻石剑的人数」和 M5-1 同一个函数(C-FAM-12,剑种当参数)。钻石按物品分类表算贵重;换下来的旧剑存进箱子当备用,不扔。</t>
+          <t>一棵树砍干净再走,不留半截;有树叶、周围没有人造方块才砍的护栏已经在了。现在有 343 根,已经达成</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>M6-3</t>
+          <t>M7-2</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>箱子里原木不少于 64 根(掉下去才补)</t>
+          <t>麦豆近 24 小时一次没死</t>
         </is>
       </c>
       <c r="D38" s="7" t="n">
@@ -1863,23 +1867,23 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>chop_wood, find_forest, store_wood</t>
+          <t>child_home, child_play</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>G6</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>麦豆</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr"/>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>箱子里原木 ≥ 64</t>
+          <t>近24小时麦豆死亡次数 = 0</t>
         </is>
       </c>
       <c r="K38" s="7" t="inlineStr">
@@ -1887,21 +1891,17 @@
           <t>缺判据</t>
         </is>
       </c>
-      <c r="L38" s="7" t="inlineStr">
-        <is>
-          <t>一棵树砍干净再走,不留半截;有树叶、周围没有人造方块才砍的护栏已经在了。现在有 343 根,已经达成</t>
-        </is>
-      </c>
+      <c r="L38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>M7-2</t>
+          <t>M7-4</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>麦豆近 24 小时一次没死</t>
+          <t>麦豆没被点名时,离真人玩家至少 16 格</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>child_home, child_play</t>
+          <t>J-M7-4</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
@@ -1928,7 +1928,7 @@
       <c r="I39" s="7" t="inlineStr"/>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>近24小时麦豆死亡次数 = 0</t>
+          <t>近1小时未被点名时离真人玩家最近距离 ≥ 16</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
@@ -1941,12 +1941,12 @@
     <row r="40">
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>M7-4</t>
+          <t>M8-2</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>麦豆没被点名时,离真人玩家至少 16 格</t>
+          <t>小麦去资源世界挖铁矿、就地烧成铁锭，直到家里的铁够把还缺的铁装备（铁剑、四件铁甲、盾、水桶、打火石）全部做出来。</t>
         </is>
       </c>
       <c r="D40" s="7" t="n">
@@ -1957,72 +1957,80 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>J-M7-4</t>
+          <t>J-M8-2</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>G8</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>麦豆</t>
-        </is>
-      </c>
-      <c r="I40" s="7" t="inlineStr"/>
+          <t>小麦</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>M8-1</t>
+        </is>
+      </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>近1小时未被点名时离真人玩家最近距离 ≥ 16</t>
+          <t>铁装备还差的铁锭 = 0</t>
         </is>
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
-        </is>
-      </c>
-      <c r="L40" s="7" t="inlineStr"/>
+          <t>判据动作都缺</t>
+        </is>
+      </c>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>全套一共 34 个铁锭：镐 3（M8-1 已做）+ 剑 2 + 头盔 5 + 胸甲 8 + 护腿 7 + 靴子 4 + 盾 1 + 桶 3 + 打火石 1。🔴 完成标准不用「铁的家底 ≥ 34」：钻石镐做出来以后铁镐一用坏、或者桶被田里用掉，家底就掉到 34 以下，小麦会为一件已经不需要的东西再跑一趟资源世界；也不能按「箱子里有几个铁锭」算，铁锭做成铁甲以后箱子里就少了，会一直挖。按「还差几个」算：只有缺的件真用坏了才重开，而那正是该去补的时候。粗铁按 1 锭算（一趟被打断时带回来的粗铁不会被当成不存在），下一趟带去资源世界一起烧。1.18 以后铁矿在 y≈16 附近最多，石镐就能挖；y&lt;0 挖出来的是深板岩圆石，照样能做熔炉。熔炉 = 8 圆石，烧一个 10 秒；1 块煤烧 8 个，1 根原木烧 1.5 个。每趟最多 25 分钟，背包只剩 2 格就回。只有小麦去。🔴 出发前必须「资源世界死亡不掉东西 = 1」：server/04-resource-worlds.md 明写这条没核实，死在回不去的资源世界，铁装备就永久没了。离 05:00（东京时间）重启不到 40 分钟就不出发，不到 15 分钟就当场回主世界。「在资源世界下线再上线会卡全服」这个说法没有出处，但避开重启本来就该做，护栏保留。「只在中心 ±900 格里挖」删掉：落点是插件随机给的，机器人控制不了。</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>M8-2</t>
+          <t>M1-7</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>小麦去资源世界挖铁矿、就地烧成铁锭，直到家里的铁够把还缺的铁装备（铁剑、四件铁甲、盾、水桶、打火石）全部做出来。</t>
+          <t>在田址里、水浇得到的地方把麦田扩到 64 格以上，全是湿地、几乎全种上：按估算这么大的田刚好够全家三口天天吃面包。</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>J-M8-2</t>
+          <t>J-M1-4, J-M1-7, J-M1-7b, wife_find_seeds, wife_gather_seeds</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>G8</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>麦娘</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>M8-1</t>
+          <t>M1-4, M1-6</t>
         </is>
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>铁装备还差的铁锭 = 0</t>
+          <t>田格余量 ≥ 0 并且 空着的耕地 ≤ 4</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr">
@@ -2032,19 +2040,19 @@
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>全套一共 34 个铁锭：镐 3（M8-1 已做）+ 剑 2 + 头盔 5 + 胸甲 8 + 护腿 7 + 靴子 4 + 盾 1 + 桶 3 + 打火石 1。🔴 完成标准不用「铁的家底 ≥ 34」：钻石镐做出来以后铁镐一用坏、或者桶被田里用掉，家底就掉到 34 以下，小麦会为一件已经不需要的东西再跑一趟资源世界；也不能按「箱子里有几个铁锭」算，铁锭做成铁甲以后箱子里就少了，会一直挖。按「还差几个」算：只有缺的件真用坏了才重开，而那正是该去补的时候。粗铁按 1 锭算（一趟被打断时带回来的粗铁不会被当成不存在），下一趟带去资源世界一起烧。1.18 以后铁矿在 y≈16 附近最多，石镐就能挖；y&lt;0 挖出来的是深板岩圆石，照样能做熔炉。熔炉 = 8 圆石，烧一个 10 秒；1 块煤烧 8 个，1 根原木烧 1.5 个。每趟最多 25 分钟，背包只剩 2 格就回。只有小麦去。🔴 出发前必须「资源世界死亡不掉东西 = 1」：server/04-resource-worlds.md 明写这条没核实，死在回不去的资源世界，铁装备就永久没了。离 05:00（东京时间）重启不到 40 分钟就不出发，不到 15 分钟就当场回主世界。「在资源世界下线再上线会卡全服」这个说法没有出处，但避开重启本来就该做，护栏保留。「只在中心 ±900 格里挖」删掉：落点是插件随机给的，机器人控制不了。</t>
+          <t>算账：64 格湿地整块种满，每格约 48 分钟出 1 个小麦 → 每游戏日约 27 个小麦 = 9 个面包 = 3 人 × 3 个；没水的话要约 140 格。一格水最多浇 80 格，靠边、靠角的格子邻居少，比中间长得慢一点。64 格要 64 颗种子：9 格田一茬净多约 15 颗，大约要 3~4 茬才攒够。木锄 59 次耐久，锄 64 格外加重锄，至少还要再做一把。🔴 零候选审计：原来固定 64 格。G1 的「面包盈余 ≥ 0」不成立（全家吃得比田里产的多，小麦远征路上吃的也算在内）时，G1 变回没完成，可 64 格早就达成了，没有任何小目标去扩田。改成「田格余量 ≥ 0」（C-FRM-22）：田格余量 = 有水的自家田 − 该有的田格数；该有的田格数 = 64 和按实测吃掉的面包算出的格数里取大的，再以田址实际能开的格数封顶。超了就按封顶算完成，并在后台写「田址不够大，面包仍然不够」，不让它变成永远做不完、又没人能推的死目标。</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>M1-7</t>
+          <t>M1-9</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>在田址里、水浇得到的地方把麦田扩到 64 格以上，全是湿地、几乎全种上：按估算这么大的田刚好够全家三口天天吃面包。</t>
+          <t>粮箱里的面包补到 18 个（够全家吃两天），被家人拿走就接着补。</t>
         </is>
       </c>
       <c r="D42" s="7" t="n">
@@ -2055,7 +2063,7 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>J-M1-4, J-M1-7, J-M1-7b, wife_find_seeds, wife_gather_seeds</t>
+          <t>J-M1-4, J-M1-9, wife_bread, wife_store_crop</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
@@ -2070,34 +2078,34 @@
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>M1-4, M1-6</t>
+          <t>M1-3</t>
         </is>
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>田格余量 ≥ 0 并且 空着的耕地 ≤ 4</t>
+          <t>粮箱里的面包 ≥ 18</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
-          <t>算账：64 格湿地整块种满，每格约 48 分钟出 1 个小麦 → 每游戏日约 27 个小麦 = 9 个面包 = 3 人 × 3 个；没水的话要约 140 格。一格水最多浇 80 格，靠边、靠角的格子邻居少，比中间长得慢一点。64 格要 64 颗种子：9 格田一茬净多约 15 颗，大约要 3~4 茬才攒够。木锄 59 次耐久，锄 64 格外加重锄，至少还要再做一把。🔴 零候选审计：原来固定 64 格。G1 的「面包盈余 ≥ 0」不成立（全家吃得比田里产的多，小麦远征路上吃的也算在内）时，G1 变回没完成，可 64 格早就达成了，没有任何小目标去扩田。改成「田格余量 ≥ 0」（C-FRM-22）：田格余量 = 有水的自家田 − 该有的田格数；该有的田格数 = 64 和按实测吃掉的面包算出的格数里取大的，再以田址实际能开的格数封顶。超了就按封顶算完成，并在后台写「田址不够大，面包仍然不够」，不让它变成永远做不完、又没人能推的死目标。</t>
+          <t>🔴 零候选审计补的。G1 要求粮箱常备 18 个面包，但下面只有 M1-3「第一次走通、有 3 个」：粮箱到 3 个以后，3 到 18 之间没有任何小目标管，麦娘会零候选，G1 却一直没完成。家人一拿面包（A14 口粮、小麦远征），这条就重开，是麦娘的常驻活。优先级 5：原稿的 4 和 M1-7（扩田）同档，每次都会触发 T1 去问模型「先补面包还是先扩田」，这件事代码能定——日常口粮有 A14/A4 保底，扩田本身就是在提高面包产量，所以扩田在前。G8 的 M8-7 在这个基础上再加到 34。</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>M1-9</t>
+          <t>M2-3</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>粮箱里的面包补到 18 个（够全家吃两天），被家人拿走就接着补。</t>
+          <t>把做好的床摆进屋里，每张记在一个家人名下；麦豆那张由身上有床的人替他摆</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
@@ -2108,49 +2116,49 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>J-M1-4, J-M1-9, wife_bread, wife_store_crop</t>
+          <t>J-M2-3-1</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>G1</t>
+          <t>G2</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>麦娘</t>
+          <t>麦娘 / 小麦（谁身上有床谁摆）</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>M1-3</t>
+          <t>M2-1, M2-2</t>
         </is>
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>粮箱里的面包 ≥ 18</t>
+          <t>没床的家人数 = 0 并且 家里摆着的床 ≥ 3</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>🔴 零候选审计补的。G1 要求粮箱常备 18 个面包，但下面只有 M1-3「第一次走通、有 3 个」：粮箱到 3 个以后，3 到 18 之间没有任何小目标管，麦娘会零候选，G1 却一直没完成。家人一拿面包（A14 口粮、小麦远征），这条就重开，是麦娘的常驻活。优先级 5：原稿的 4 和 M1-7（扩田）同档，每次都会触发 T1 去问模型「先补面包还是先扩田」，这件事代码能定——日常口粮有 A14/A4 保底，扩田本身就是在提高面包产量，所以扩田在前。G8 的 M8-7 在这个基础上再加到 34。</t>
+          <t>游戏里任何人都能睡任何一张没人占的床，「这是谁的床」只是我们自己记的账。重生点跟着最后睡过的那张床走；两个人不能同时睡一张床（会提示床已被占用）。现在的 sleep 只在 24 格内一张床都没有时才自己摆床，所以结构上只摆得出第一张，第二、第三张只能靠 place_bed。麦豆没有合成动作，也没有把东西交给别人的动作，所以他的床只能由做床的人直接摆进屋。</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>M2-3</t>
+          <t>M3-4</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>把做好的床摆进屋里，每张记在一个家人名下；麦豆那张由身上有床的人替他摆</t>
+          <t>小麦先把屋里 49 格地面铺满木半砖，再封上 9×9 的平屋顶。铺了半砖的地面怪物刷不出来，所以屋顶封上的那一刻，屋里就已经不刷怪了。</t>
         </is>
       </c>
       <c r="D44" s="7" t="n">
@@ -2161,27 +2169,27 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>J-M2-3-1</t>
+          <t>J-M3-4</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>G2</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>麦娘 / 小麦（谁身上有床谁摆）</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
-          <t>M2-1, M2-2</t>
+          <t>M3-3</t>
         </is>
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>没床的家人数 = 0 并且 家里摆着的床 ≥ 3</t>
+          <t>新房地面裸露格数 = 0 并且 新房屋顶缺口数 = 0</t>
         </is>
       </c>
       <c r="K44" s="7" t="inlineStr">
@@ -2191,19 +2199,19 @@
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
-          <t>游戏里任何人都能睡任何一张没人占的床，「这是谁的床」只是我们自己记的账。重生点跟着最后睡过的那张床走；两个人不能同时睡一张床（会提示床已被占用）。现在的 sleep 只在 24 格内一张床都没有时才自己摆床，所以结构上只摆得出第一张，第二、第三张只能靠 place_bed。麦豆没有合成动作，也没有把东西交给别人的动作，所以他的床只能由做床的人直接摆进屋。</t>
+          <t>1.18 起，敌对怪只在方块光照为 0 的地方刷，而且刷不到底半砖上（顶半砖和双层半砖上能刷）。人站在半砖上眼睛高出 0.5 格；放方块的伸手距离是 3.6 时，屋顶格在水平约 3.3 格内都够得着。对着同种底半砖的顶面再放一块，会合成双层半砖（完整方块，能刷怪），所以 placeAt「放之前先看目标格是不是空的」这条不能绕过。</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>M3-4</t>
+          <t>M4-3</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>小麦先把屋里 49 格地面铺满木半砖，再封上 9×9 的平屋顶。铺了半砖的地面怪物刷不出来，所以屋顶封上的那一刻，屋里就已经不刷怪了。</t>
+          <t>旧家箱子里的东西全部搬到新家</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
@@ -2214,27 +2222,27 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>J-M3-4</t>
+          <t>J-M4-3, wife_craft_chest</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>G4</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>麦娘</t>
         </is>
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>M3-3</t>
+          <t>M4-2</t>
         </is>
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>新房地面裸露格数 = 0 并且 新房屋顶缺口数 = 0</t>
+          <t>旧家箱子非空格数 = 0 并且 有箱子 = 1</t>
         </is>
       </c>
       <c r="K45" s="7" t="inlineStr">
@@ -2244,19 +2252,19 @@
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>1.18 起，敌对怪只在方块光照为 0 的地方刷，而且刷不到底半砖上（顶半砖和双层半砖上能刷）。人站在半砖上眼睛高出 0.5 格；放方块的伸手距离是 3.6 时，屋顶格在水平约 3.3 格内都够得着。对着同种底半砖的顶面再放一块，会合成双层半砖（完整方块，能刷怪），所以 placeAt「放之前先看目标格是不是空的」这条不能绕过。</t>
+          <t>keepInventory 开着,路上死了也不掉东西;大约两趟搬完</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>M4-3</t>
+          <t>M5-7</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>旧家箱子里的东西全部搬到新家</t>
+          <t>每个在线家人 4 个护甲槽都不空(什么材质都行):先用箱子里现成的 —— 8 张皮革给麦豆做皮衣,5 个铁锭给麦娘做铁头盔</t>
         </is>
       </c>
       <c r="D46" s="7" t="n">
@@ -2267,37 +2275,33 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>J-M4-3, wife_craft_chest</t>
+          <t>child_make_leather_tunic, wife_make_iron_helmet</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>G4</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>麦娘</t>
-        </is>
-      </c>
-      <c r="I46" s="7" t="inlineStr">
-        <is>
-          <t>M4-2</t>
-        </is>
-      </c>
+          <t>全家</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr"/>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>旧家箱子非空格数 = 0 并且 有箱子 = 1</t>
+          <t>在线家人里护甲空槽数 = 0</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据/动作(代码刀)</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
-          <t>keepInventory 开着,路上死了也不掉东西;大约两趟搬完</t>
+          <t>自动穿甲 wearBestArmor 对三人都生效(每 30 秒,只往空格补)。盔甲也递不过去,只能谁穿谁做。Owner 2026-09-18:「我建议是所有角色都要有武器装备」+「都还手,但有规矩」;铁锭给麦娘做头盔是 Owner 16:50 定的</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2358,7 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>小麦有一身能保命的铁装备：四件铁甲（头盔、胸甲、护腿、靴子）、铁剑、盾，外加一桶水和一个打火石（点下界传送门用）。</t>
+          <t>(铁甲三人都要,但要等 M8-2 会挖矿、会烧铁以后才开,现在不排期)小麦有一身能保命的铁装备：四件铁甲（头盔、胸甲、护腿、靴子）、铁剑、盾，外加一桶水和一个打火石（点下界传送门用）。</t>
         </is>
       </c>
       <c r="D48" s="7" t="n">
@@ -2712,12 +2716,12 @@
     <row r="55">
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>M7-5</t>
+          <t>M5-8</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>麦豆白天陪在正在干活的家人旁边（比如看妈妈种地），不跑远、不乱逛。</t>
+          <t>箱子里常备 ≥8 张皮革,补打烂的那一件(小麦缺皮革时先打牛)</t>
         </is>
       </c>
       <c r="D55" s="7" t="n">
@@ -2726,47 +2730,47 @@
       <c r="E55" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>J-M7-5</t>
-        </is>
-      </c>
+      <c r="F55" s="7" t="inlineStr"/>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>麦豆</t>
-        </is>
-      </c>
-      <c r="I55" s="7" t="inlineStr"/>
+          <t>小麦</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>M5-7</t>
+        </is>
+      </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>离最近在干活的家人距离 ≤ 16</t>
+          <t>箱子里皮革 ≥ 8</t>
         </is>
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据/动作(代码刀)</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>🔴 零候选修正：原设计靠 M1-8（帮妈妈收麦子）解决麦豆的零候选，但那要先等您放行；放行之前，麦豆的小目标要么是「不走丢、不死、不打扰孩子」这种做到了就没活的，要么是要放行才能做的砍树，他会一直零候选、一直标红。这一条只用他现在就有的 goto_place 和 idle，符合他「爱跟着大人跑」的人设，也不去打扰真人小孩。只陪在主世界、离家 64 格内、干的不是远征活的家人；停在 4~8 格外，不进田、不挡路。家人一走开，这条就重开，是麦豆的常驻活；没人在家附近干活时算完成，缺口记录记成「在等」。晚上交给 A11。</t>
+          <t>要先装打猎红线护栏(不打有名牌、被拴着、围栏里的动物,只捡自己猎物掉的东西),再加「缺皮革先打牛」(代码)。照现在的效率每天约 3 张。整套皮甲每人 24 张,不追求整套。</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>M8-4</t>
+          <t>M7-5</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>小麦有一把钻石镐（黑曜石只有钻石镐才挖得动）。</t>
+          <t>麦豆白天陪在正在干活的家人旁边（比如看妈妈种地），不跑远、不乱逛。</t>
         </is>
       </c>
       <c r="D56" s="7" t="n">
@@ -2777,27 +2781,23 @@
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>J-M8-4a, J-M8-4b</t>
+          <t>J-M7-5</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>G8</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
-        </is>
-      </c>
-      <c r="I56" s="7" t="inlineStr">
-        <is>
-          <t>M8-1</t>
-        </is>
-      </c>
+          <t>麦豆</t>
+        </is>
+      </c>
+      <c r="I56" s="7" t="inlineStr"/>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>最好的镐等级 ≥ 4</t>
+          <t>离最近在干活的家人距离 ≤ 16</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
@@ -2807,50 +2807,50 @@
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>钻石镐 = 3 钻石 + 2 木棍，要工作台。有两条路：箱子里有 27 颗钻石，您同意就直接拿 3 颗做（J-M8-4a，几秒钟）；不同意就去资源世界 y≈−58 挖（J-M8-4b，要铁镐、穿铁甲、带水桶；那一层岩浆最多，是整条链里最容易死的一次挖矿，所以出发前必须核实资源世界死了不掉东西）。这和钻石剑（M5-6）是同一个问题，一起问您。钻石镐耐久 1561，基本用不坏。</t>
+          <t>🔴 零候选修正：原设计靠 M1-8（帮妈妈收麦子）解决麦豆的零候选，但那要先等您放行；放行之前，麦豆的小目标要么是「不走丢、不死、不打扰孩子」这种做到了就没活的，要么是要放行才能做的砍树，他会一直零候选、一直标红。这一条只用他现在就有的 goto_place 和 idle，符合他「爱跟着大人跑」的人设，也不去打扰真人小孩。只陪在主世界、离家 64 格内、干的不是远征活的家人；停在 4~8 格外，不进田、不挡路。家人一走开，这条就重开，是麦豆的常驻活；没人在家附近干活时算完成，缺口记录记成「在等」。晚上交给 A11。</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>M3-7</t>
+          <t>M8-4</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>全家搬进新房：先把旧箱子里的东西全部搬进新房的箱子，再让每个人把「家」设在新房里，并在新房里自己那张床上点一下，这样以后谁死了都在新房里醒来。现在的家是你亲手定的，要你同意才搬。</t>
+          <t>小麦有一把钻石镐（黑曜石只有钻石镐才挖得动）。</t>
         </is>
       </c>
       <c r="D57" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E57" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>J-M3-7a, J-M3-7b, J-M3-7c</t>
+          <t>J-M8-4a, J-M8-4b</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>G8</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>全家</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="I57" s="7" t="inlineStr">
         <is>
-          <t>M3-6</t>
+          <t>M8-1</t>
         </is>
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>旧箱子剩余物品数 = 0 并且 共用箱子在新房里 = 1 并且 没搬进新房的家人数 = 0</t>
+          <t>最好的镐等级 ≥ 4</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr">
@@ -2860,19 +2860,19 @@
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>🔴 本服 Essentials 设的是 respawn-at-home: true + respawn-at-home-bed: true，重生顺序是「床 → 家 → 出生点」。小麦 09-17 已经在村庄那张床 (-73,72,106) 设过重生点，所以现在死了是在村庄醒，不是在旧家；光 set_home 搬不走重生点，必须在新床上点一下。set_home 还要求：脚下是实地、y ≥ 62、离出生点 ≥ 80、旁边 3 格没有水；M3-1 的选址条件已经保证这些。库存约 343 根原木（6 组）、67 根木棍、27 颗钻石，加一些零碎，一两趟就能搬完。</t>
+          <t>钻石镐 = 3 钻石 + 2 木棍，要工作台。有两条路：箱子里有 27 颗钻石，您同意就直接拿 3 颗做（J-M8-4a，几秒钟）；不同意就去资源世界 y≈−58 挖（J-M8-4b，要铁镐、穿铁甲、带水桶；那一层岩浆最多，是整条链里最容易死的一次挖矿，所以出发前必须核实资源世界死了不掉东西）。这和钻石剑（M5-6）是同一个问题，一起问您。钻石镐耐久 1561，基本用不坏。</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>M5-3</t>
+          <t>M3-7</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>从资源世界挖回 64 块圆石,放进家里箱子</t>
+          <t>全家搬进新房：先把旧箱子里的东西全部搬进新房的箱子，再让每个人把「家」设在新房里，并在新房里自己那张床上点一下，这样以后谁死了都在新房里醒来。现在的家是你亲手定的，要你同意才搬。</t>
         </is>
       </c>
       <c r="D58" s="7" t="n">
@@ -2883,27 +2883,27 @@
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>J-M5-3, J-M5-3b</t>
+          <t>J-M3-7a, J-M3-7b, J-M3-7c</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>G5</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="I58" s="7" t="inlineStr">
         <is>
-          <t>M5-2</t>
+          <t>M3-6</t>
         </is>
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>箱子里圆石 ≥ 64</t>
+          <t>旧箱子剩余物品数 = 0 并且 共用箱子在新房里 = 1 并且 没搬进新房的家人数 = 0</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
@@ -2913,19 +2913,19 @@
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
-          <t>原来挂的 J-M5-3 只有「去资源世界入口 → 回家 → 存箱子」三步，中间没有挖，改挂 J-M5-3b（带挖石头这一步，回主世界用 /home base）。前置 M5-2（有镐）按「完成过」算；镐用坏了，由 J-M5-3b 的「还要满足：最好的镐等级 ≥ 1」挡住，不会空手去。圆石是打龙路线的底料（熔炉、石镐、下界搭桥和挡火球），小麦出远门从箱子拿走 64 块后，这条会重开去补，这是对的。y &lt; 0 挖出来的深板岩圆石也算。出发前要求资源世界死了不掉东西（C-END-18）。</t>
+          <t>🔴 本服 Essentials 设的是 respawn-at-home: true + respawn-at-home-bed: true，重生顺序是「床 → 家 → 出生点」。小麦 09-17 已经在村庄那张床 (-73,72,106) 设过重生点，所以现在死了是在村庄醒，不是在旧家；光 set_home 搬不走重生点，必须在新床上点一下。set_home 还要求：脚下是实地、y ≥ 62、离出生点 ≥ 80、旁边 3 格没有水；M3-1 的选址条件已经保证这些。库存约 343 根原木（6 组）、67 根木棍、27 颗钻石，加一些零碎，一两趟就能搬完。</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>M8-5</t>
+          <t>M5-3</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>麦家攒够 10 块黑曜石（搭一个下界传送门框的量）：小麦在资源世界找到岩浆，浇上水变成黑曜石，再用钻石镐挖回来。</t>
+          <t>从资源世界挖回 64 块圆石,放进家里箱子</t>
         </is>
       </c>
       <c r="D59" s="7" t="n">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>J-M8-5</t>
+          <t>J-M5-3, J-M5-3b</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>G8</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="I59" s="7" t="inlineStr">
         <is>
-          <t>M8-3, M8-4</t>
+          <t>M5-2</t>
         </is>
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>黑曜石的家底 ≥ 10</t>
+          <t>箱子里圆石 ≥ 64</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
@@ -2966,68 +2966,72 @@
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>传送门框最少 4 宽 5 高，四个角可以不放，要 10 块。流水流过岩浆源，会把它变成黑曜石；钻石镐挖一块约 9.4 秒，别的镐挖不下来。家底把已经砌进自家门框的也算上，所以门搭好以后这条不会重开；门被人拆了、黑曜石掉了，才重开。只在资源世界做：主世界的岩浆湖可能在别人家旁边。地表岩浆湖在 1.18 以后不多，找不到就去 y≈−54 以下的洞穴（那一层岩浆最多）。掉进岩浆是最快的死法（每 0.5 秒 4 点血），出事交给常驻层 A8 直接传送走。</t>
+          <t>原来挂的 J-M5-3 只有「去资源世界入口 → 回家 → 存箱子」三步，中间没有挖，改挂 J-M5-3b（带挖石头这一步，回主世界用 /home base）。前置 M5-2（有镐）按「完成过」算；镐用坏了，由 J-M5-3b 的「还要满足：最好的镐等级 ≥ 1」挡住，不会空手去。圆石是打龙路线的底料（熔炉、石镐、下界搭桥和挡火球），小麦出远门从箱子拿走 64 块后，这条会重开去补，这是对的。y &lt; 0 挖出来的深板岩圆石也算。出发前要求资源世界死了不掉东西（C-END-18）。</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>M5-4</t>
+          <t>M8-5</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>每个会打架的在线家人都换上石剑(麦豆只跑不打,不算)</t>
+          <t>麦家攒够 10 块黑曜石（搭一个下界传送门框的量）：小麦在资源世界找到岩浆，浇上水变成黑曜石，再用钻石镐挖回来。</t>
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E60" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F60" s="7" t="inlineStr"/>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>J-M8-5</t>
+        </is>
+      </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>G5</t>
+          <t>G8</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>任意</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>M5-3</t>
+          <t>M8-3, M8-4</t>
         </is>
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>在线会打架的家人里剑等级低于石剑的人数 = 0</t>
+          <t>黑曜石的家底 ≥ 10</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>石剑 = 2 圆石 + 1 木棍;make_sword 要改成箱子里有圆石时做石剑。「在线家人里没石剑的人数」只数 roles.json 能做的动作里有 fight 的在线家人(现在只有小麦;麦娘等 C-PRM-6 放行后自动算进来),和 M5-1 同一个函数(C-FAM-12,剑种当参数)。麦豆只跑不打,不给他做石剑。换下来的木剑存进箱子当备用(算进 M5-5)。</t>
+          <t>传送门框最少 4 宽 5 高，四个角可以不放，要 10 块。流水流过岩浆源，会把它变成黑曜石；钻石镐挖一块约 9.4 秒，别的镐挖不下来。家底把已经砌进自家门框的也算上，所以门搭好以后这条不会重开；门被人拆了、黑曜石掉了，才重开。只在资源世界做：主世界的岩浆湖可能在别人家旁边。地表岩浆湖在 1.18 以后不多，找不到就去 y≈−54 以下的洞穴（那一层岩浆最多）。掉进岩浆是最快的死法（每 0.5 秒 4 点血），出事交给常驻层 A8 直接传送走。</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>M8-6</t>
+          <t>M5-4</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>在新家 32~64 格外、您在后台点了同意的位置，搭好下界传送门并且点着。</t>
+          <t>每个在线家人都有石剑或更好的剑(有钻石剑的已经算)</t>
         </is>
       </c>
       <c r="D61" s="7" t="n">
@@ -3036,62 +3040,58 @@
       <c r="E61" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>J-M8-6</t>
-        </is>
-      </c>
+      <c r="F61" s="7" t="inlineStr"/>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>G8</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>任意</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>M8-5</t>
+          <t>M5-3</t>
         </is>
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>麦家下界传送门已点亮 = 1</t>
+          <t>在线家人里剑等级低于石剑的人数 = 0</t>
         </is>
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>位置由代码挑，先写到后台等您点同意，不问模型。离新家 32~64 格：🔴 主世界的下界传送门会不停刷出僵尸猪灵（困难难度更多）；猪灵、疣猪兽从门里走过来 15 秒后会变成僵尸猪灵、僵尸疣猪兽，后者主动打人，所以不能离床和麦豆太近。选址还要避开：主世界 128 格内有别人的传送门（回来时可能从别人的门出来）；对应的下界位置（坐标 ÷ 8）32 格内有别人放的任何方块（C-END-1）——游戏在下界自动生成对应的门时会挖空一块、铺黑曜石平台，落在孩子们的下界建筑里就是毁别人的东西。第一次穿过去时再核对一次，落点周围有别人的方块就原路回来、作废这个位置、写进后台（不在公屏说）。门框每块都记进自家方块登记；被拆了、熄了，这条自动重开去修。新家还没定时，这条卡在「传送门位置已获批」上，缺口记录写「等您拍板」。</t>
+          <t>石剑 = 2 圆石 + 1 木棍;make_sword 要改成箱子里有圆石时做石剑。「在线家人里没石剑的人数」只数 roles.json 能做的动作里有 fight 的在线家人(现在只有小麦;麦娘等 C-PRM-6 放行后自动算进来),和 M5-1 同一个函数(C-FAM-12,剑种当参数)。麦豆只跑不打,不给他做石剑。换下来的木剑存进箱子当备用(算进 M5-5)。</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>M8-7</t>
+          <t>M8-6</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>麦娘给小麦备远征口粮：粮箱里常备 34 个面包（全家吃两天的 18 个，加上小麦下一趟要带走的 16 个）。</t>
+          <t>在新家 32~64 格外、您在后台点了同意的位置，搭好下界传送门并且点着。</t>
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E62" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>J-M1-4, J-M1-9, wife_bread, wife_store_crop</t>
+          <t>J-M8-6</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
@@ -3101,50 +3101,50 @@
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>麦娘</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>M1-3</t>
+          <t>M8-5</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>粮箱里的面包 ≥ 34</t>
+          <t>麦家下界传送门已点亮 = 1</t>
         </is>
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
-          <t>这是「全家一起打龙」里麦娘的那一份：她不出远门，在家把麦子做成面包。小麦出远门从粮箱拿面包，打开箱子时按真数重算，拿完粮箱里至少还剩 9 个（C-ITM-25），家里人不会因为远征挨饿。家里有人没吃的时，由家人互助那一路的规则优先，小麦身上的远征口粮照样可以分出去。面包被拿走以后这条重开，麦娘接着种、接着做。G8 优先级 9，排在 G1（先保住全家两天的 18 个，M1-9）之后。打完龙、G8 锁住以后，这条就不再算（C-ENG-23）。</t>
+          <t>位置由代码挑，先写到后台等您点同意，不问模型。离新家 32~64 格：🔴 主世界的下界传送门会不停刷出僵尸猪灵（困难难度更多）；猪灵、疣猪兽从门里走过来 15 秒后会变成僵尸猪灵、僵尸疣猪兽，后者主动打人，所以不能离床和麦豆太近。选址还要避开：主世界 128 格内有别人的传送门（回来时可能从别人的门出来）；对应的下界位置（坐标 ÷ 8）32 格内有别人放的任何方块（C-END-1）——游戏在下界自动生成对应的门时会挖空一块、铺黑曜石平台，落在孩子们的下界建筑里就是毁别人的东西。第一次穿过去时再核对一次，落点周围有别人的方块就原路回来、作废这个位置、写进后台（不在公屏说）。门框每块都记进自家方块登记；被拆了、熄了，这条自动重开去修。新家还没定时，这条卡在「传送门位置已获批」上，缺口记录写「等您拍板」。</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>M8-8</t>
+          <t>M8-7</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>每次去下界前，小麦的远征装备是齐的：头戴金头盔（猪灵就不主动打）、另外三件铁甲、铁剑、盾，身上带 16 个吃的、64 块圆石（搭桥、挡火球），背包留 8 个空格。</t>
+          <t>麦娘给小麦备远征口粮：粮箱里常备 34 个面包（全家吃两天的 18 个，加上小麦下一趟要带走的 16 个）。</t>
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E63" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>J-M8-8a, J-M8-8b</t>
+          <t>J-M1-4, J-M1-9, wife_bread, wife_store_crop</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
@@ -3154,51 +3154,55 @@
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>麦娘</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>M8-3, M8-6</t>
+          <t>M1-3</t>
         </is>
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>下界远征缺口 = 0</t>
+          <t>粮箱里的面包 ≥ 34</t>
         </is>
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>金头盔 = 5 金锭，护甲值和铁头盔一样都是 2 点，只是不耐用（77 次）。金矿要铁镐才能挖，资源世界 y≈−16 最多，恶地地表也多。🔴 金头盔不是万能的：猪灵蛮兵（在堡垒遗迹里）和疣猪兽不管你穿什么都主动打人；看到你开箱子、挖金块，猪灵照样翻脸——所以在下界不开箱子、不挖金块、不进堡垒遗迹（C-END-5）。🔴 机器人自带的换甲代码会把金头盔换回铁头盔，下界脚本期间由 C-ITM-23 关掉。「缺口」只在还有要去下界的小目标（M8-9、M8-10、M8-11）没做完时才算，都做完了就是 0，不会仗打完了还让小麦天天收拾行李。行李清单上的东西不算「可存的东西」（C-ITM-26），免得收拾好、砍树回来又存回箱子。每趟回来，吃的、圆石少了，这条就重开去补，所以下一趟出发前一定是齐的。圆石不够时，由 G5 的 M5-3（箱子里常备 64 块，G5 优先级更高）先去挖。</t>
+          <t>这是「全家一起打龙」里麦娘的那一份：她不出远门，在家把麦子做成面包。小麦出远门从粮箱拿面包，打开箱子时按真数重算，拿完粮箱里至少还剩 9 个（C-ITM-25），家里人不会因为远征挨饿。家里有人没吃的时，由家人互助那一路的规则优先，小麦身上的远征口粮照样可以分出去。面包被拿走以后这条重开，麦娘接着种、接着做。G8 优先级 9，排在 G1（先保住全家两天的 18 个，M1-9）之后。打完龙、G8 锁住以后，这条就不再算（C-ENG-23）。</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>M3-8</t>
+          <t>M8-8</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>屋里放 1 个熔炉、墙上挂 2 支火把。这两样都要先学会挖石头、挖煤，所以先暂停；不算进「房子完工」（等你定）。</t>
+          <t>每次去下界前，小麦的远征装备是齐的：头戴金头盔（猪灵就不主动打）、另外三件铁甲、铁剑、盾，身上带 16 个吃的、64 块圆石（搭桥、挡火球），背包留 8 个空格。</t>
         </is>
       </c>
       <c r="D64" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F64" s="7" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>J-M8-8a, J-M8-8b</t>
+        </is>
+      </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>G8</t>
         </is>
       </c>
       <c r="H64" s="7" t="inlineStr">
@@ -3208,12 +3212,12 @@
       </c>
       <c r="I64" s="7" t="inlineStr">
         <is>
-          <t>M3-6, M8-2</t>
+          <t>M8-3, M8-6</t>
         </is>
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>新房里的熔炉 ≥ 1 并且 新房火把数 ≥ 2</t>
+          <t>下界远征缺口 = 0</t>
         </is>
       </c>
       <c r="K64" s="7" t="inlineStr">
@@ -3223,35 +3227,31 @@
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
-          <t>熔炉 = 8 块圆石；火把 = 1 块煤或木炭 + 1 根木棍，出 4 支。🔴 地面全是底半砖，底半砖顶面不完整，火把放不上去，初稿说的「放在 7×7 正中」做不到，只能挂墙；两面墙各挂一支就够照亮整间屋。熔炉顶面也是完整方块，要和工作台一样放墙角、垫半砖。零候选审计：前置的挖矿由 M8-2 带出来（煤和熔炉都有了），所以前置改成 M3-6 + M8-2。状态仍是您设的暂停（3），代码不动；您要打开的话，还要补一条摆熔炉、挂火把的脚本。</t>
+          <t>金头盔 = 5 金锭，护甲值和铁头盔一样都是 2 点，只是不耐用（77 次）。金矿要铁镐才能挖，资源世界 y≈−16 最多，恶地地表也多。🔴 金头盔不是万能的：猪灵蛮兵（在堡垒遗迹里）和疣猪兽不管你穿什么都主动打人；看到你开箱子、挖金块，猪灵照样翻脸——所以在下界不开箱子、不挖金块、不进堡垒遗迹（C-END-5）。🔴 机器人自带的换甲代码会把金头盔换回铁头盔，下界脚本期间由 C-ITM-23 关掉。「缺口」只在还有要去下界的小目标（M8-9、M8-10、M8-11）没做完时才算，都做完了就是 0，不会仗打完了还让小麦天天收拾行李。行李清单上的东西不算「可存的东西」（C-ITM-26），免得收拾好、砍树回来又存回箱子。每趟回来，吃的、圆石少了，这条就重开去补，所以下一趟出发前一定是齐的。圆石不够时，由 G5 的 M5-3（箱子里常备 64 块，G5 优先级更高）先去挖。</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>M8-9</t>
+          <t>M3-8</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>小麦在下界找到一座下界要塞（地狱砖砌的大城堡，烈焰人只在那里出现），记下位置。</t>
+          <t>屋里放 1 个熔炉、墙上挂 2 支火把。这两样都要先学会挖石头、挖煤，所以先暂停；不算进「房子完工」（等你定）。</t>
         </is>
       </c>
       <c r="D65" s="7" t="n">
         <v>8</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F65" s="7" t="inlineStr">
-        <is>
-          <t>J-M8-9</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="F65" s="7" t="inlineStr"/>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>G8</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="H65" s="7" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="I65" s="7" t="inlineStr">
         <is>
-          <t>M8-8</t>
+          <t>M3-6, M8-2</t>
         </is>
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>记得下界要塞 = 1</t>
+          <t>新房里的熔炉 ≥ 1 并且 新房火把数 ≥ 2</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr">
@@ -3276,31 +3276,35 @@
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>🔴 危险步骤，只有小麦去；麦娘、麦豆寻路时把所有传送门当墙（C-PRM-21）。出发条件写在脚本的「还要满足」里：下界远征缺口 = 0、血 ≥ 18、饱食度 ≥ 18、传送冷却已过。什么时候往回走全由代码判断（C-END-5 的「该返航」）：血 ≤ 10、身上吃的 ≤ 4、身上圆石 ≤ 8、背包只剩 1 格、或在下界满 20 分钟，任何一条成立，就走回下界那一头的门；血 ≤ 6 或者掉进岩浆，就直接传送回家。下界没有水，A8 里「着火找水」跳过；🔴 床在下界会爆炸，A11、A15 在下界不触发（C-NAV-23）。找法：沿一个方向一段 64 格地走，扫到成片地狱砖就记下，离门最远 600 格；不进玄武岩三角洲（灰黑色、到处是坑和岩浆怪），不进堡垒遗迹。下界里只挖天然方块，离别人的东西 16 格以外；搭的桥和挡火球的圆石都记进自家方块登记。三个主要世界都开了死亡不掉东西，死了在家醒来，这一趟白跑。被打断后按 C-ENG-25 续做。人在下界不影响主世界跳夜；G2 的连续睡夜把「黄昏时不在主世界」当成不在线跳过。</t>
+          <t>熔炉 = 8 块圆石；火把 = 1 块煤或木炭 + 1 根木棍，出 4 支。🔴 地面全是底半砖，底半砖顶面不完整，火把放不上去，初稿说的「放在 7×7 正中」做不到，只能挂墙；两面墙各挂一支就够照亮整间屋。熔炉顶面也是完整方块，要和工作台一样放墙角、垫半砖。零候选审计：前置的挖矿由 M8-2 带出来（煤和熔炉都有了），所以前置改成 M3-6 + M8-2。状态仍是您设的暂停（3），代码不动；您要打开的话，还要补一条摆熔炉、挂火把的脚本。</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>M3-9</t>
+          <t>M8-9</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>出生点旁边那间 4×4 泥土房怎么处理，等你定。如果要拆，小麦只拆服务器记录能证明是它自己放的那几块泥土，周围任何东西都不碰。</t>
+          <t>小麦在下界找到一座下界要塞（地狱砖砌的大城堡，烈焰人只在那里出现），记下位置。</t>
         </is>
       </c>
       <c r="D66" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F66" s="7" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>J-M8-9</t>
+        </is>
+      </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>G8</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
@@ -3310,12 +3314,12 @@
       </c>
       <c r="I66" s="7" t="inlineStr">
         <is>
-          <t>M3-7</t>
+          <t>M8-8</t>
         </is>
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>旧房剩余方块数 = 0</t>
+          <t>记得下界要塞 = 1</t>
         </is>
       </c>
       <c r="K66" s="7" t="inlineStr">
@@ -3325,35 +3329,31 @@
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
-          <t>旧房在 (-19,63,160)，离出生点约 145 格。原来 22 格，小麦自己拆过 1 格，还剩 21 格，其中 11 格已经长成草方块（那几格也是它放的）。空手挖泥土每块约 0.75 秒。旧箱子 (-15,63,159) 要在 M3-7 清空以后才能拆，否则会撒一地东西。</t>
+          <t>🔴 危险步骤，只有小麦去；麦娘、麦豆寻路时把所有传送门当墙（C-PRM-21）。出发条件写在脚本的「还要满足」里：下界远征缺口 = 0、血 ≥ 18、饱食度 ≥ 18、传送冷却已过。什么时候往回走全由代码判断（C-END-5 的「该返航」）：血 ≤ 10、身上吃的 ≤ 4、身上圆石 ≤ 8、背包只剩 1 格、或在下界满 20 分钟，任何一条成立，就走回下界那一头的门；血 ≤ 6 或者掉进岩浆，就直接传送回家。下界没有水，A8 里「着火找水」跳过；🔴 床在下界会爆炸，A11、A15 在下界不触发（C-NAV-23）。找法：沿一个方向一段 64 格地走，扫到成片地狱砖就记下，离门最远 600 格；不进玄武岩三角洲（灰黑色、到处是坑和岩浆怪），不进堡垒遗迹。下界里只挖天然方块，离别人的东西 16 格以外；搭的桥和挡火球的圆石都记进自家方块登记。三个主要世界都开了死亡不掉东西，死了在家醒来，这一趟白跑。被打断后按 C-ENG-25 续做。人在下界不影响主世界跳夜；G2 的连续睡夜把「黄昏时不在主世界」当成不在线跳过。</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>M8-10</t>
+          <t>M3-9</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>小麦在下界要塞里打烈焰人，攒够做末影之眼还缺的烈焰棒（要几根，按家里已有的眼、粉、棒现算）。</t>
+          <t>出生点旁边那间 4×4 泥土房怎么处理，等你定。如果要拆，小麦只拆服务器记录能证明是它自己放的那几块泥土，周围任何东西都不碰。</t>
         </is>
       </c>
       <c r="D67" s="7" t="n">
         <v>9</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F67" s="7" t="inlineStr">
-        <is>
-          <t>J-M8-10</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="F67" s="7" t="inlineStr"/>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>G8</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
-          <t>M8-9</t>
+          <t>M3-7</t>
         </is>
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>做眼还缺的烈焰棒 = 0</t>
+          <t>旧房剩余方块数 = 0</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
@@ -3378,30 +3378,30 @@
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>1 根烈焰棒磨出 2 份烈焰粉，1 份粉 + 1 颗末影珍珠 = 1 个末影之眼。🔴 不再用固定的 8 根：扔眼找要塞时碎一颗，固定家底就会差半根，小麦会在找要塞的中途被拉回下界补一根；而门框本来自带的眼（每个框 1/10）又让固定数多备了。改成按账本（C-END-17）从「眼还差几颗」推回来：没找到门框时一共要 14 个眼（7 根棒），找到后按空门框数算，门点亮以后一根都不要。烈焰人 20 血，只有被玩家打死才掉棒（0~1 根），掉进岩浆就没了；一次喷 3 个火球，每个都能把人点着，副手举盾能挡。站在刷怪笼 6~8 格外的走廊，一次只对付一只，打死后走过去捡。凋灵骷髅（中了凋零交给 A3）和恶魂只躲不打。出发和返航的条件同 M8-9。</t>
+          <t>旧房在 (-19,63,160)，离出生点约 145 格。原来 22 格，小麦自己拆过 1 格，还剩 21 格，其中 11 格已经长成草方块（那几格也是它放的）。空手挖泥土每块约 0.75 秒。旧箱子 (-15,63,159) 要在 M3-7 清空以后才能拆，否则会撒一地东西。</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>M8-11</t>
+          <t>M8-10</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>小麦去下界的诡异森林打末影人，攒够做末影之眼还缺的末影珍珠。</t>
+          <t>小麦在下界要塞里打烈焰人，攒够做末影之眼还缺的烈焰棒（要几根，按家里已有的眼、粉、棒现算）。</t>
         </is>
       </c>
       <c r="D68" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E68" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>J-M8-11</t>
+          <t>J-M8-10</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="I68" s="7" t="inlineStr">
         <is>
-          <t>M8-8</t>
+          <t>M8-9</t>
         </is>
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>做眼还缺的末影珍珠 = 0</t>
+          <t>做眼还缺的烈焰棒 = 0</t>
         </is>
       </c>
       <c r="K68" s="7" t="inlineStr">
@@ -3431,30 +3431,30 @@
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
-          <t>箱子里已经有 1 颗。末影人 40 血，掉 0~1 颗珍珠，平均要打二三十只。选下界的诡异森林（青绿色的森林，末影人特别多），不选主世界的夜里：夜里待在外面，正是以前扎堆死亡的原因。🔴 这是唯一允许主动惹末影人的地方（平时 A2 规定末影人只躲不打）：先用圆石搭一个两格高的小棚（末影人 2.9 格高，钻不进来；打完拆回），视线压低，不看任何末影人的头，只对选中的那一只抬头惹它，一次只惹一只；血 ≤ 12 或同时来两只，就退回棚里；打死后走过去捡珍珠。和 M8-9、M8-10 按优先级轮着做；出发和返航的条件同 M8-9。</t>
+          <t>1 根烈焰棒磨出 2 份烈焰粉，1 份粉 + 1 颗末影珍珠 = 1 个末影之眼。🔴 不再用固定的 8 根：扔眼找要塞时碎一颗，固定家底就会差半根，小麦会在找要塞的中途被拉回下界补一根；而门框本来自带的眼（每个框 1/10）又让固定数多备了。改成按账本（C-END-17）从「眼还差几颗」推回来：没找到门框时一共要 14 个眼（7 根棒），找到后按空门框数算，门点亮以后一根都不要。烈焰人 20 血，只有被玩家打死才掉棒（0~1 根），掉进岩浆就没了；一次喷 3 个火球，每个都能把人点着，副手举盾能挡。站在刷怪笼 6~8 格外的走廊，一次只对付一只，打死后走过去捡。凋灵骷髅（中了凋零交给 A3）和恶魂只躲不打。出发和返航的条件同 M8-9。</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>M8-12</t>
+          <t>M8-11</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>麦娘在家把烈焰棒磨成粉，和末影珍珠合成末影之眼，直到家里的眼够用（没找到门框时要 14 个，找到后按空着的框数，门点亮以后就不再要）。</t>
+          <t>小麦去下界的诡异森林打末影人，攒够做末影之眼还缺的末影珍珠。</t>
         </is>
       </c>
       <c r="D69" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E69" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>J-M8-12</t>
+          <t>J-M8-11</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
@@ -3464,17 +3464,17 @@
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>麦娘</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>M8-10, M8-11</t>
+          <t>M8-8</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>末影之眼缺口 = 0</t>
+          <t>做眼还缺的末影珍珠 = 0</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
@@ -3484,30 +3484,30 @@
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>要塞的末地门框一共 12 个，每个本来就有 1/10 的机会自带一颗眼；扔出去找要塞的眼，大约 1/5 会碎。没找到门框时要 14 个 = 12 个框 + 2 个扔眼的损耗；找到门框以后只要空框的数，门点亮以后要 0 个。这两样在背包的小格子里就能合成，不用工作台。这是「全家一起打龙」里麦娘的第二份活：小麦只管打，打回来存进箱子，合成交给在家的麦娘。</t>
+          <t>箱子里已经有 1 颗。末影人 40 血，掉 0~1 颗珍珠，平均要打二三十只。选下界的诡异森林（青绿色的森林，末影人特别多），不选主世界的夜里：夜里待在外面，正是以前扎堆死亡的原因。🔴 这是唯一允许主动惹末影人的地方（平时 A2 规定末影人只躲不打）：先用圆石搭一个两格高的小棚（末影人 2.9 格高，钻不进来；打完拆回），视线压低，不看任何末影人的头，只对选中的那一只抬头惹它，一次只惹一只；血 ≤ 12 或同时来两只，就退回棚里；打死后走过去捡珍珠。和 M8-9、M8-10 按优先级轮着做；出发和返航的条件同 M8-9。</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>M8-13</t>
+          <t>M8-12</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>小麦用末影之眼找到主世界的要塞，下到里面找到末地传送门框，记下位置和还空着几个框。</t>
+          <t>麦娘在家把烈焰棒磨成粉，和末影珍珠合成末影之眼，直到家里的眼够用（没找到门框时要 14 个，找到后按空着的框数，门点亮以后就不再要）。</t>
         </is>
       </c>
       <c r="D70" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E70" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>J-M8-13a, J-M8-13b</t>
+          <t>J-M8-12</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
@@ -3517,17 +3517,17 @@
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>麦娘</t>
         </is>
       </c>
       <c r="I70" s="7" t="inlineStr">
         <is>
-          <t>M8-12</t>
+          <t>M8-10, M8-11</t>
         </is>
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>记得末地门框 = 1</t>
+          <t>末影之眼缺口 = 0</t>
         </is>
       </c>
       <c r="K70" s="7" t="inlineStr">
@@ -3537,30 +3537,30 @@
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
-          <t>主世界离原点最近的一圈要塞在 1280~2816 格外（出生点在 (8,15)，几乎就是原点），走一趟 5~11 分钟，所以天一亮就出发，回程用 /home base 传送。分成两条脚本，这样等您批准挖斜井的时候，小麦先能把位置算出来：J-M8-13a 在新家门口和垂直方向 200 格外各扔一次眼（眼会朝要塞飞一段再落下，大约 1/5 会碎，没碎的走过去捡回来），代码算出两条线的交点；J-M8-13b 走到交点附近再扔一次，眼往下钻就说明在脚下，然后挖斜井下去。🔴 要塞在地下，要在主世界挖。之前定的是「只在资源世界挖」，所以要您打开「主世界挖斜井」开关；挖之前先查 32 格内有没有别人的东西和领地，只挖天然方块，走路时寻路不许挖（现有代码 canDig=false 保持）。已经被别人挖开的，就走现成的路；这一座在别人的领地里，就按同一圈另外两座的大致方位（左右各转 120°）再去找。A20「离家 100 格就回家」把这两条当成在探路（C-NAV-22）。白天只有约 10 分钟，天黑时 A11 会把他送回家，第二天按 C-ENG-25 续做、从头走过去；想省这段路，可以给他开要塞附近的第二个家（C-END-19，等您定）。「资源世界里的要塞没用」这个说法没核实（资源世界的末地门通到哪里没查），保守起见只用主世界的要塞。</t>
+          <t>要塞的末地门框一共 12 个，每个本来就有 1/10 的机会自带一颗眼；扔出去找要塞的眼，大约 1/5 会碎。没找到门框时要 14 个 = 12 个框 + 2 个扔眼的损耗；找到门框以后只要空框的数，门点亮以后要 0 个。这两样在背包的小格子里就能合成，不用工作台。这是「全家一起打龙」里麦娘的第二份活：小麦只管打，打回来存进箱子，合成交给在家的麦娘。</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>M8-14</t>
+          <t>M8-13</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>小麦把末影之眼一个个嵌进末地传送门框，点亮通往末地的门。</t>
+          <t>小麦用末影之眼找到主世界的要塞，下到里面找到末地传送门框，记下位置和还空着几个框。</t>
         </is>
       </c>
       <c r="D71" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E71" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>J-M8-14</t>
+          <t>J-M8-13a, J-M8-13b</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
@@ -3575,12 +3575,12 @@
       </c>
       <c r="I71" s="7" t="inlineStr">
         <is>
-          <t>M8-13</t>
+          <t>M8-12</t>
         </is>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>末地门已点亮 = 1</t>
+          <t>记得末地门框 = 1</t>
         </is>
       </c>
       <c r="K71" s="7" t="inlineStr">
@@ -3590,30 +3590,30 @@
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>12 个门框都嵌上眼以后，中间 3×3 就变成末地传送门（黑色、有星星）。门框里本来就带眼的跳过；孩子们已经点亮过的也算完成，直接用。房间里的蠹虫刷怪笼不拆（它是要塞的一部分），蠹虫交给 A2 打。</t>
+          <t>主世界离原点最近的一圈要塞在 1280~2816 格外（出生点在 (8,15)，几乎就是原点），走一趟 5~11 分钟，所以天一亮就出发，回程用 /home base 传送。分成两条脚本，这样等您批准挖斜井的时候，小麦先能把位置算出来：J-M8-13a 在新家门口和垂直方向 200 格外各扔一次眼（眼会朝要塞飞一段再落下，大约 1/5 会碎，没碎的走过去捡回来），代码算出两条线的交点；J-M8-13b 走到交点附近再扔一次，眼往下钻就说明在脚下，然后挖斜井下去。🔴 要塞在地下，要在主世界挖。之前定的是「只在资源世界挖」，所以要您打开「主世界挖斜井」开关；挖之前先查 32 格内有没有别人的东西和领地，只挖天然方块，走路时寻路不许挖（现有代码 canDig=false 保持）。已经被别人挖开的，就走现成的路；这一座在别人的领地里，就按同一圈另外两座的大致方位（左右各转 120°）再去找。A20「离家 100 格就回家」把这两条当成在探路（C-NAV-22）。白天只有约 10 分钟，天黑时 A11 会把他送回家，第二天按 C-ENG-25 续做、从头走过去；想省这段路，可以给他开要塞附近的第二个家（C-END-19，等您定）。「资源世界里的要塞没用」这个说法没核实（资源世界的末地门通到哪里没查），保守起见只用主世界的要塞。</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>M8-15</t>
+          <t>M8-14</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>打龙用的一张弓和 64 支箭做好（放在箱子里也算）。</t>
+          <t>小麦把末影之眼一个个嵌进末地传送门框，点亮通往末地的门。</t>
         </is>
       </c>
       <c r="D72" s="7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E72" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>J-M8-15a, J-M8-15b</t>
+          <t>J-M8-14</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="I72" s="7" t="inlineStr">
         <is>
-          <t>M8-3</t>
+          <t>M8-13</t>
         </is>
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>有弓 ≥ 1 并且 箭的家底 ≥ 64</t>
+          <t>末地门已点亮 = 1</t>
         </is>
       </c>
       <c r="K72" s="7" t="inlineStr">
@@ -3643,30 +3643,30 @@
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
-          <t>🔴 零候选修正：原来这条挂在「点亮末地门」后面，还带着进末地的整套行李。传送门位置、主世界挖斜井都要等您批准，这段时间小麦名下的 G8 活全被前置挡住，会零候选。弓箭只要有铁装备（进资源世界安全）就能做，所以前置改成 M8-3；等批准的时候，小麦就做这个。进末地前的打包挪进 M8-17（J-M8-17a）。弓 = 3 线 + 3 木棍（箱子里有 48 根线，做 3 张床用 36 根，剩下的够）。箭 = 燧石 + 木棍 + 羽毛，一次出 4 支，64 支要做 16 次。羽毛去资源世界打鸡（家附近常年没有动物，也不打别人养的），燧石去挖沙砾。10 个末地水晶里有 2 个外面围着铁栏杆，箭射不进去，要垫圆石爬上去打。</t>
+          <t>12 个门框都嵌上眼以后，中间 3×3 就变成末地传送门（黑色、有星星）。门框里本来就带眼的跳过；孩子们已经点亮过的也算完成，直接用。房间里的蠹虫刷怪笼不拆（它是要塞的一部分），蠹虫交给 A2 打。</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>M8-16</t>
+          <t>M8-15</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>（只在龙已经被别人打死时才需要）等您同意后，小麦用 4 个末地水晶把末影龙重新叫出来。龙还活着的话，这一条自动算完成。</t>
+          <t>打龙用的一张弓和 64 支箭做好（放在箱子里也算）。</t>
         </is>
       </c>
       <c r="D73" s="7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E73" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>J-M8-16</t>
+          <t>J-M8-15a, J-M8-15b</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="I73" s="7" t="inlineStr">
         <is>
-          <t>M8-14</t>
+          <t>M8-3</t>
         </is>
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>需要复活末影龙 = 0</t>
+          <t>有弓 ≥ 1 并且 箭的家底 ≥ 64</t>
         </is>
       </c>
       <c r="K73" s="7" t="inlineStr">
@@ -3696,178 +3696,188 @@
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>「需要复活」= 龙现在不在，而且麦家没有人打败过它。服务器的末地存档里记着龙死没死，代码只读不改。孩子们去过下界和末地（7 月有人在那边死过），龙可能已经被打过了。复活要 4 个末地水晶（每个 = 7 块玻璃 + 1 个末影之眼 + 1 滴恶魂之泪），放在末地中间返回门的四边。🔴 龙回来时会把黑曜石柱按原样重建（柱子位置上别人放的东西会被换掉），当时在末地的所有人都会被龙打，所以默认不做，等您拍板。水晶的来路（玻璃要烧沙子，恶魂之泪要去下界打恶魂）还没设计，所以脚本要求身上已经有 4 个水晶；没有的话，缺口记录写「表里没下一步」，等您定了再补。</t>
+          <t>🔴 零候选修正：原来这条挂在「点亮末地门」后面，还带着进末地的整套行李。传送门位置、主世界挖斜井都要等您批准，这段时间小麦名下的 G8 活全被前置挡住，会零候选。弓箭只要有铁装备（进资源世界安全）就能做，所以前置改成 M8-3；等批准的时候，小麦就做这个。进末地前的打包挪进 M8-17（J-M8-17a）。弓 = 3 线 + 3 木棍（箱子里有 48 根线，做 3 张床用 36 根，剩下的够）。箭 = 燧石 + 木棍 + 羽毛，一次出 4 支，64 支要做 16 次。羽毛去资源世界打鸡（家附近常年没有动物，也不打别人养的），燧石去挖沙砾。10 个末地水晶里有 2 个外面围着铁栏杆，箭射不进去，要垫圆石爬上去打。</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>M8-17</t>
+          <t>M8-16</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>小麦进末地打败末影龙——全家的终极目标。</t>
+          <t>（只在龙已经被别人打死时才需要）等您同意后，小麦用 4 个末地水晶把末影龙重新叫出来。龙还活着的话，这一条自动算完成。</t>
         </is>
       </c>
       <c r="D74" s="7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E74" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
+          <t>J-M8-16</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>G8</t>
+        </is>
+      </c>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>小麦</t>
+        </is>
+      </c>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>M8-14</t>
+        </is>
+      </c>
+      <c r="J74" s="7" t="inlineStr">
+        <is>
+          <t>需要复活末影龙 = 0</t>
+        </is>
+      </c>
+      <c r="K74" s="7" t="inlineStr">
+        <is>
+          <t>判据动作都缺</t>
+        </is>
+      </c>
+      <c r="L74" s="7" t="inlineStr">
+        <is>
+          <t>「需要复活」= 龙现在不在，而且麦家没有人打败过它。服务器的末地存档里记着龙死没死，代码只读不改。孩子们去过下界和末地（7 月有人在那边死过），龙可能已经被打过了。复活要 4 个末地水晶（每个 = 7 块玻璃 + 1 个末影之眼 + 1 滴恶魂之泪），放在末地中间返回门的四边。🔴 龙回来时会把黑曜石柱按原样重建（柱子位置上别人放的东西会被换掉），当时在末地的所有人都会被龙打，所以默认不做，等您拍板。水晶的来路（玻璃要烧沙子，恶魂之泪要去下界打恶魂）还没设计，所以脚本要求身上已经有 4 个水晶；没有的话，缺口记录写「表里没下一步」，等您定了再补。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>M8-17</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>小麦进末地打败末影龙——全家的终极目标。</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="E75" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
           <t>J-M8-17a, J-M8-17b</t>
         </is>
       </c>
-      <c r="G74" s="7" t="inlineStr">
+      <c r="G75" s="7" t="inlineStr">
         <is>
           <t>G8</t>
         </is>
       </c>
-      <c r="H74" s="7" t="inlineStr">
+      <c r="H75" s="7" t="inlineStr">
         <is>
           <t>小麦</t>
         </is>
       </c>
-      <c r="I74" s="7" t="inlineStr">
+      <c r="I75" s="7" t="inlineStr">
         <is>
           <t>M8-14, M8-15, M8-16</t>
         </is>
       </c>
-      <c r="J74" s="7" t="inlineStr">
+      <c r="J75" s="7" t="inlineStr">
         <is>
           <t>打败过末影龙 = 1</t>
         </is>
       </c>
-      <c r="K74" s="7" t="inlineStr">
+      <c r="K75" s="7" t="inlineStr">
         <is>
           <t>判据动作都缺</t>
         </is>
       </c>
-      <c r="L74" s="7" t="inlineStr">
+      <c r="L75" s="7" t="inlineStr">
         <is>
           <t>进末地前先打包（J-M8-17a）：弓、64 支箭、128 块圆石（垫高、搭路）、24 个吃的、四件铁甲（末地没有猪灵，不戴金头盔）、剑、盾，背包留 6 格；缺口只在末地门已点亮、龙还活着、还没打败过时才算，打完就是 0，不会一直备料。打法（J-M8-17b）：进末地先看脚下，出生的黑曜石平台悬在主岛外面，就用圆石搭路过去；先用弓把柱子顶上的末地水晶一个个射掉（水晶会给龙回血），围着铁栏杆的两个垫圆石爬上去打；龙落到中间的返回门上时近身打，龙在天上时躲开紫色的龙息；视线压低，不看末影人；离岛边至少 8 格，掉进虚空必死。困难难度下龙一口能打掉十几点血，所以血 ≤ 8 先吃东西，≤ 6 就传送回家（死了不掉东西，只是白跑一趟）。出发条件：进末地装备缺口 = 0、血满 20、饱食度 ≥ 18、离天黑 ≥ 8 分钟（要先走到要塞）。龙死后走中间的返回门回主世界；🔴 第一次从那扇门回来会播结束字幕，机器人要回应「看完了」，否则一直卡在字幕里（C-END-15）。麦娘不会打架、人设不出远门，默认不去（问您）；麦豆绝不去。完成后 G8 锁住：以后不再给远征备料，全家回到种田、维护这些日常活。这就是 Owner 说的「最完美的大结局」，只有到这时，零候选才是正常的（缺口记录第五类）。</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>三、基本状态维持(常驻,不是目标)</t>
         </is>
       </c>
-      <c r="B77" s="4" t="n"/>
-      <c r="C77" s="4" t="n"/>
-      <c r="D77" s="4" t="n"/>
-      <c r="E77" s="4" t="n"/>
-      <c r="F77" s="4" t="n"/>
-      <c r="G77" s="4" t="n"/>
-      <c r="H77" s="4" t="n"/>
-      <c r="I77" s="4" t="n"/>
-      <c r="J77" s="4" t="n"/>
-    </row>
-    <row r="78">
-      <c r="B78" s="5" t="inlineStr">
+      <c r="B78" s="4" t="n"/>
+      <c r="C78" s="4" t="n"/>
+      <c r="D78" s="4" t="n"/>
+      <c r="E78" s="4" t="n"/>
+      <c r="F78" s="4" t="n"/>
+      <c r="G78" s="4" t="n"/>
+      <c r="H78" s="4" t="n"/>
+      <c r="I78" s="4" t="n"/>
+      <c r="J78" s="4" t="n"/>
+    </row>
+    <row r="79">
+      <c r="B79" s="5" t="inlineStr">
         <is>
           <t>基本状态维持</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
         <is>
           <t>基本状态说明</t>
         </is>
       </c>
-      <c r="D78" s="5" t="inlineStr">
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>基本状态优先级</t>
         </is>
       </c>
-      <c r="E78" s="5" t="inlineStr">
+      <c r="E79" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">基本状态(0:未评估, 1:进行中; 2:已完成; 3:暂停; 4:评估中; 默认状态为4) </t>
         </is>
       </c>
-      <c r="F78" s="5" t="inlineStr">
+      <c r="F79" s="5" t="inlineStr">
         <is>
           <t>关联实际行为脚本编号</t>
         </is>
       </c>
-      <c r="G78" s="6" t="inlineStr">
+      <c r="G79" s="6" t="inlineStr">
         <is>
           <t>触发条件(代码判据)</t>
         </is>
       </c>
-      <c r="H78" s="6" t="inlineStr">
+      <c r="H79" s="6" t="inlineStr">
         <is>
           <t>负责人</t>
         </is>
       </c>
-      <c r="I78" s="6" t="inlineStr">
+      <c r="I79" s="6" t="inlineStr">
         <is>
           <t>可行性</t>
         </is>
       </c>
-      <c r="J78" s="6" t="inlineStr">
+      <c r="J79" s="6" t="inlineStr">
         <is>
           <t>游戏机制备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>A8</t>
-        </is>
-      </c>
-      <c r="C79" s="7" t="inlineStr">
-        <is>
-          <t>不被烧死:掉进岩浆立刻传送走(传不了就往外爬);身上着火就跳进附近的水,没水就离开火源、吃饱顶住</t>
-        </is>
-      </c>
-      <c r="D79" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F79" s="7" t="inlineStr">
-        <is>
-          <t>J-A8-1, J-A8-2, J-A8-3, J-A8-4</t>
-        </is>
-      </c>
-      <c r="G79" s="7" t="inlineStr">
-        <is>
-          <t>火烧身 = 1</t>
-        </is>
-      </c>
-      <c r="H79" s="7" t="inlineStr">
-        <is>
-          <t>全家</t>
-        </is>
-      </c>
-      <c r="I79" s="7" t="inlineStr">
-        <is>
-          <t>判据动作都缺</t>
-        </is>
-      </c>
-      <c r="J79" s="7" t="inlineStr">
-        <is>
-          <t>岩浆每0.5秒扣4点(最快的死法),出来后还要烧15秒、每秒1点;火方块点着8秒;水、雨、细雪能灭火;Hard 着火的僵尸打人有概率把人点着。小麦被烧死4次。</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>A9</t>
+          <t>A8</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>不从高处摔死:血≤8时走路最多往下跳2格,平时4格(这是走路的设置,不占身体,和别的事同时生效)</t>
+          <t>不被烧死:掉进岩浆立刻传送走(传不了就往外爬);身上着火就跳进附近的水,没水就离开火源、吃饱顶住</t>
         </is>
       </c>
       <c r="D80" s="7" t="n">
@@ -3878,12 +3888,12 @@
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>J-A9-1</t>
+          <t>J-A8-1, J-A8-2, J-A8-3, J-A8-4</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>血量 ≤ 8</t>
+          <t>火烧身 = 1</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr">
@@ -3893,40 +3903,40 @@
       </c>
       <c r="I80" s="7" t="inlineStr">
         <is>
-          <t>现在就能做</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
       <c r="J80" s="7" t="inlineStr">
         <is>
-          <t>不进独占选择器,并行生效;和 A8 同为0,正是 Owner 说的「同级可以同时进行」。掉落伤害=落差-3格;寻路默认允许4格落差(扣1点),残血时就是致命一下。现有代码有效:摔死16次全在9-15/9-16,之后0次。等 A3 的判据做好后,再把触发扩成「血≤8 或 身上有坏效果」。</t>
+          <t>岩浆每0.5秒扣4点(最快的死法),出来后还要烧15秒、每秒1点;火方块点着8秒;水、雨、细雪能灭火;Hard 着火的僵尸打人有概率把人点着。小麦被烧死4次。</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>A9</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>别憋死:头在水下氧气剩一半就往上浮找岸;氧气见底或脑袋卡进方块里就立刻传送走</t>
+          <t>不从高处摔死:血≤8时走路最多往下跳2格,平时4格(这是走路的设置,不占身体,和别的事同时生效)</t>
         </is>
       </c>
       <c r="D81" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E81" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>J-A7-1, J-A7-2, J-A7-3</t>
+          <t>J-A9-1</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>喘不上气 = 1</t>
+          <t>血量 ≤ 8</t>
         </is>
       </c>
       <c r="H81" s="7" t="inlineStr">
@@ -3936,24 +3946,24 @@
       </c>
       <c r="I81" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>现在就能做</t>
         </is>
       </c>
       <c r="J81" s="7" t="inlineStr">
         <is>
-          <t>满氧气约15秒(每格约0.75秒),见底后每秒扣2点,满血再撑约10秒。窒息每0.5秒扣1点、满血10秒就死,而且没有攻击者,放在 A1 下会被当成「没危险」原地发呆,所以并进这里。现有「泡够90秒才传送」是给漂在海面上用的,对沉在水下来不及。水里真正的威胁是溺尸(小麦被溺尸杀23次),由 A2「在水里不打」处理。</t>
+          <t>不进独占选择器,并行生效;和 A8 同为0,正是 Owner 说的「同级可以同时进行」。掉落伤害=落差-3格;寻路默认允许4格落差(扣1点),残血时就是致命一下。现有代码有效:摔死16次全在9-15/9-16,之后0次。等 A3 的判据做好后,再把触发扩成「血≤8 或 身上有坏效果」。</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>A18</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>（原 T6，改成不问模型）身边的生物按代码里的一张表处理：会主动打人的，按反射规则打或躲；惹了才打人的，绝不先动手；不能打的（村民、玩家、有名字的宠物、嘎枝）只躲；表里没有的一律保持 8 格距离，并记下来给您看。</t>
+          <t>别憋死:头在水下氧气剩一半就往上浮找岸;氧气见底或脑袋卡进方块里就立刻传送走</t>
         </is>
       </c>
       <c r="D82" s="7" t="n">
@@ -3964,82 +3974,82 @@
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>guard_home</t>
+          <t>J-A7-1, J-A7-2, J-A7-3</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>16格内有表外生物 ≥ 1</t>
+          <t>喘不上气 = 1</t>
         </is>
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
-          <t>任意</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="I82" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
       <c r="J82" s="7" t="inlineStr">
         <is>
-          <t>原稿要模型给生物归类「危险/无害」并永久存盘。但 1.21.4 原版生物名单是封闭的，类别是事实，属于「能用代码判定就不问模型」；小模型一次归错（比如把嘎枝归成无害）就会永久写进忽略名单，和 memory.json 被污染那次是同一类问题。顺带发现：现在反射层的 HOSTILE_RE 把末影人和猪灵（连带僵尸猪灵，名字里含 piglin）当成主动攻击的怪，先动手会惹来一群；又漏了沼骸（bogged，射毒箭，和 A3 解毒有关）、旋风人（breeze）、嘎枝、监守者、恼鬼（vex）、唤魔者（evoker）、恶魂（ghast）、岩浆怪（magma_cube）、潜影贝（shulker）、僵尸疣猪兽（zoglin）。roles.json 里只有小麦有 fight。请和 A 层统一编号。</t>
+          <t>满氧气约15秒(每格约0.75秒),见底后每秒扣2点,满血再撑约10秒。窒息每0.5秒扣1点、满血10秒就死,而且没有攻击者,放在 A1 下会被当成「没危险」原地发呆,所以并进这里。现有「泡够90秒才传送」是给漂在海面上用的,对沉在水下来不及。水里真正的威胁是溺尸(小麦被溺尸杀23次),由 A2「在水里不打」处理。</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>A18</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>离苦力怕至少7格,绝不近战:它进6格就跑,贴到3格内直接传送走,拉到10格外才算安全</t>
+          <t>（原 T6，改成不问模型）身边的生物按代码里的一张表处理：会主动打人的，按反射规则打或躲；惹了才打人的，绝不先动手；不能打的（村民、玩家、有名字的宠物、嘎枝）只躲；表里没有的一律保持 8 格距离，并记下来给您看。</t>
         </is>
       </c>
       <c r="D83" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>J-A5-1, J-A5-2</t>
+          <t>guard_home</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>最近苦力怕距离 ≤ 6</t>
+          <t>16格内有表外生物 ≥ 1</t>
         </is>
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>全家</t>
+          <t>任意</t>
         </is>
       </c>
       <c r="I83" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>苦力怕在3格内开始点火,1.5秒后爆炸,玩家拉到7格外会熄火;Hard 贴脸爆炸远超满血20点,6格外基本无伤。苦力怕炸之前不会让人掉血,所以「掉血时重算」对它没用,必须靠实体移动事件。饱食度≤6不能疾跑,走路甩不开点着的苦力怕。</t>
+          <t>原稿要模型给生物归类「危险/无害」并永久存盘。但 1.21.4 原版生物名单是封闭的，类别是事实，属于「能用代码判定就不问模型」；小模型一次归错（比如把嘎枝归成无害）就会永久写进忽略名单，和 memory.json 被污染那次是同一类问题。顺带发现：现在反射层的 HOSTILE_RE 把末影人和猪灵（连带僵尸猪灵，名字里含 piglin）当成主动攻击的怪，先动手会惹来一群；又漏了沼骸（bogged，射毒箭，和 A3 解毒有关）、旋风人（breeze）、嘎枝、监守者、恼鬼（vex）、唤魔者（evoker）、恶魂（ghast）、岩浆怪（magma_cube）、潜影贝（shulker）、僵尸疣猪兽（zoglin）。roles.json 里只有小麦有 fight。请和 A 层统一编号。</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>A14</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>每个在线的家人背包里至少揣着 2 个面包，饿了随时能吃，不用跑回家。</t>
+          <t>离苦力怕至少7格,绝不近战:它进6格就跑,贴到3格内直接传送走,拉到10格外才算安全</t>
         </is>
       </c>
       <c r="D84" s="7" t="n">
@@ -4050,12 +4060,12 @@
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>J-A14, wife_store_crop</t>
+          <t>J-A5-1, J-A5-2</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>有面包 ≤ 1</t>
+          <t>最近苦力怕距离 ≤ 6</t>
         </is>
       </c>
       <c r="H84" s="7" t="inlineStr">
@@ -4070,48 +4080,91 @@
       </c>
       <c r="J84" s="7" t="inlineStr">
         <is>
-          <t>原来的 M1-5。这是「一直维持」不是「做一次就完」，按 Owner 的四层表属于常驻 A 层。每个机器人用自己现有的「有面包」判断自己，不需要跨机器人统计。排在 A1 保血、A2 打近战怪之后，所有干活之前。饥饿值 ≥ 18 才会自然回血，A1「生命值维持 50% 以上」要靠这一条喂饱。麦娘靠 store_crop 身上本来就留 3 个面包，一般不会触发。</t>
+          <t>苦力怕在3格内开始点火,1.5秒后爆炸,玩家拉到7格外会熄火;Hard 贴脸爆炸远超满血20点,6格外基本无伤。苦力怕炸之前不会让人掉血,所以「掉血时重算」对它没用,必须靠实体移动事件。饱食度≤6不能疾跑,走路甩不开点着的苦力怕。</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>A25</t>
+          <t>A14</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>麦豆被怪追、但还没挨打时，如果 24 格内有能护着他的大人（有剑、血够、会出手，身边没有苦力怕这类难缠的怪），而且大人不在怪那一边，就往大人身边跑、躲到他身后，让大人来打。一挨打、血不够，或者躲过去 10 秒没人出手，就照原来的办法：挨打就传送走，没挨打就自己跑开。</t>
+          <t>每个在线的家人背包里至少揣着 2 个面包，饿了随时能吃，不用跑回家。</t>
         </is>
       </c>
       <c r="D85" s="7" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="E85" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
+          <t>J-A14, wife_store_crop</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>有面包 ≤ 1</t>
+        </is>
+      </c>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>全家</t>
+        </is>
+      </c>
+      <c r="I85" s="7" t="inlineStr">
+        <is>
+          <t>判据动作都缺</t>
+        </is>
+      </c>
+      <c r="J85" s="7" t="inlineStr">
+        <is>
+          <t>原来的 M1-5。这是「一直维持」不是「做一次就完」，按 Owner 的四层表属于常驻 A 层。每个机器人用自己现有的「有面包」判断自己，不需要跨机器人统计。排在 A1 保血、A2 打近战怪之后，所有干活之前。饥饿值 ≥ 18 才会自然回血，A1「生命值维持 50% 以上」要靠这一条喂饱。麦娘靠 store_crop 身上本来就留 3 个面包，一般不会触发。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>A25</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>我现在不能打(没剑、血少、怪多)、被怪追、还没挨打时:24 格内有能护着我的大人(有剑、血够、身边没苦力怕)、而且不在怪那一边,就往他身边跑。一挨打、血不够,或躲过去 10 秒没人出手,就照原来的办法跑或传送。</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E86" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
           <t>J-A25-1</t>
         </is>
       </c>
-      <c r="G85" s="7" t="inlineStr">
-        <is>
-          <t>我会打架 = 0 并且 最近近战怪距离 ≤ 6 并且 最近苦力怕距离 ≥ 7 并且 刚挨打 = 0 并且 血量 ≥ 12 并且 能护着我的家人距离 ≤ 24 并且 往他那边跑不迎着怪 = 1</t>
-        </is>
-      </c>
-      <c r="H85" s="7" t="inlineStr">
-        <is>
-          <t>麦豆</t>
-        </is>
-      </c>
-      <c r="I85" s="7" t="inlineStr">
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>我现在不能打 = 1 并且 最近近战怪距离 ≤ 6</t>
+        </is>
+      </c>
+      <c r="H86" s="7" t="inlineStr">
+        <is>
+          <t>全家</t>
+        </is>
+      </c>
+      <c r="I86" s="7" t="inlineStr">
         <is>
           <t>判据动作都缺</t>
         </is>
       </c>
-      <c r="J85" s="7" t="inlineStr">
+      <c r="J86" s="7" t="inlineStr">
         <is>
           <t>【人设】roles.json 里麦豆的人设原话：「遇到危险就躲到大人身边或者回家」。
 【优先级 2.5】排在躲苦力怕 A5（2）之后、A2（3）之前：麦豆被追时，先看能不能躲到大人身边，不行才按 J-A2-4 自己跑。苦力怕在 7 格内时不走这条 —— 往人堆里带苦力怕，会把两个人一起炸了。
@@ -4120,58 +4173,15 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>A2</t>
-        </is>
-      </c>
-      <c r="C86" s="7" t="inlineStr">
-        <is>
-          <t>血量高于30%(&gt;6)时,把贴到4格内的普通近战怪打掉;苦力怕、末影人、强怪、嘎枝只跑不打;麦豆只跑,麦娘有剑才打</t>
-        </is>
-      </c>
-      <c r="D86" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E86" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F86" s="7" t="inlineStr">
-        <is>
-          <t>J-A2-1, J-A2-2, J-A2-3, J-A2-4</t>
-        </is>
-      </c>
-      <c r="G86" s="7" t="inlineStr">
-        <is>
-          <t>最近近战怪距离 ≤ 4 并且 血量 ≥ 6.01</t>
-        </is>
-      </c>
-      <c r="H86" s="7" t="inlineStr">
-        <is>
-          <t>全家</t>
-        </is>
-      </c>
-      <c r="I86" s="7" t="inlineStr">
-        <is>
-          <t>判据动作都缺</t>
-        </is>
-      </c>
-      <c r="J86" s="7" t="inlineStr">
-        <is>
-          <t>对应 Owner 样板的 J-4。初稿查出的真 bug 保留:满血那一支没排除苦力怕(小麦被炸死33次、其中19次死前刚还击过)、HOSTILE_RE 含 enderman、反射层绕过执行闸让没有 fight 的麦娘还击664行。creaking 是 1.21.4 新怪,打它不掉血,只能跑。guard_home 用的是恒为0的判据、1189次接活一次没开工,直接退役,不再挂在这里。</t>
-        </is>
-      </c>
-    </row>
     <row r="87">
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>A19</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>（原 T9，改成不问模型）背包只剩 2 格以内时，按代码里的物品表处理：有用的回家存箱子，明确的杂物扔掉，不认识的一律先存；钻石、铁、金、附魔的、带名字的、别人送的，永远不扔；箱子也满了，就在后台告诉您。</t>
+          <t>三人一套规矩(Owner 2026-09-18):手上有剑、血 ≥14 才开打(已在打的血 &gt;10 可以继续);只打普通怪(僵尸、尸壳、僵尸村民、蜘蛛;溺尸只在它上岸时打);8 格内怪 ≤2 只;8 格内没有苦力怕;自己不在水里;不是刚复活;目标旁边 3 格内没有真人、宠物、马、村民(Owner 16:50)。其余一律跑。</t>
         </is>
       </c>
       <c r="D87" s="7" t="n">
@@ -4182,82 +4192,82 @@
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>store_wood, wife_store</t>
+          <t>J-A2-1, J-A2-2, J-A2-3, J-A2-4</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>背包空格 ≤ 2</t>
+          <t>最近近战怪距离 ≤ 4</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>任意</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="I87" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>🔴 现在的 JUNK_RE 里有 rotten_flesh（腐肉），而另一处 EMERGENCY_FOOD_RE 把腐肉当救命粮（实测机器人曾抱着 27 块腐肉饿死）。同一样东西两份判据打架，是现存的 bug。bone（骨头）也在 JUNK_RE 里，但它能做骨粉催熟小麦，G1 种田用得上；虽然现在还没有「施骨粉」动作，也应该先存不扔。背包 36 格全满时，collectblock 当场抛错，砍树每次都失败（已查实），所以腾格子是硬需求。🔴 麦豆的 roles.json 里没有 store_items，他只能扔杂物、存不了东西。原稿让模型逐样给物品归类并永久存盘，但 1.21.4 物品名单是封闭的，归类是事实判断，不该问模型；兜底「全部存」和代码默认一样，问了也不改变结果。请和 A 层统一编号。</t>
+          <t>对应 Owner 样板的 J-4。初稿查出的真 bug 保留:满血那一支没排除苦力怕(小麦被炸死33次、其中19次死前刚还击过)、HOSTILE_RE 含 enderman、反射层绕过执行闸让没有 fight 的麦娘还击664行。creaking 是 1.21.4 新怪,打它不掉血,只能跑。guard_home 用的是恒为0的判据、1189次接活一次没开工,直接退役,不再挂在这里。</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>A19</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>不站着挨冷箭:被远程怪盯上时,弓箭手贴到5格内、血够又有剑就冲上去打;血少就传送走;其余先挡箭再拉开距离</t>
+          <t>（原 T9，改成不问模型）背包只剩 2 格以内时，按代码里的物品表处理：有用的回家存箱子，明确的杂物扔掉，不认识的一律先存；钻石、铁、金、附魔的、带名字的、别人送的，永远不扔；箱子也满了，就在后台告诉您。</t>
         </is>
       </c>
       <c r="D88" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E88" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>J-A6-1, J-A6-2, J-A6-3</t>
+          <t>store_wood, wife_store</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>被远程怪盯上 = 1</t>
+          <t>背包空格 ≤ 2</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>全家</t>
+          <t>任意</t>
         </is>
       </c>
       <c r="I88" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
       <c r="J88" s="7" t="inlineStr">
         <is>
-          <t>骷髅射程约15格、Hard 约2秒一箭、一箭最多约5点;中间一格实心方块就挡住。bogged/ghast/breeze 不在现在的 HOSTILE_RE 里,要一起补。小麦日志里放过393块挡箭块(原木187、木板99、泥土107),代码里没有收回逻辑,收回归 A13。</t>
+          <t>🔴 现在的 JUNK_RE 里有 rotten_flesh（腐肉），而另一处 EMERGENCY_FOOD_RE 把腐肉当救命粮（实测机器人曾抱着 27 块腐肉饿死）。同一样东西两份判据打架，是现存的 bug。bone（骨头）也在 JUNK_RE 里，但它能做骨粉催熟小麦，G1 种田用得上；虽然现在还没有「施骨粉」动作，也应该先存不扔。背包 36 格全满时，collectblock 当场抛错，砍树每次都失败（已查实），所以腾格子是硬需求。🔴 麦豆的 roles.json 里没有 store_items，他只能扔杂物、存不了东西。原稿让模型逐样给物品归类并永久存盘，但 1.21.4 物品名单是封闭的，归类是事实判断，不该问模型；兜底「全部存」和代码默认一样，问了也不改变结果。请和 A 层统一编号。</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>A15</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>天黑要睡时床边有怪：小麦在稳妥时先把好打的怪清掉；其它情况（以及麦娘、麦豆）回屋里等，床边一空 A4 自己接着去睡</t>
+          <t>不站着挨冷箭:被远程怪盯上时先挡箭再拉开距离;血少就传送走。射箭的怪走到面前也不冲上去砍(Owner 16:50「挡箭并跑开」)。麦豆不放挡箭方块,只跑。</t>
         </is>
       </c>
       <c r="D89" s="7" t="n">
@@ -4268,12 +4278,12 @@
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>J-A15-1, J-A15-2</t>
+          <t>J-A6-1, J-A6-2, J-A6-3</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>天黑了 = 1 并且 今晚睡着过 = 0 并且 我有自己的床 = 1 并且 我的床边有怪 ≥ 1 并且 在主世界 = 1</t>
+          <t>被远程怪盯上 = 1</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr">
@@ -4288,19 +4298,19 @@
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
-          <t>「附近有怪不能睡」只看距离不看墙：墙外 8 格内的僵尸照样让你睡不着。盒子向下算到 6 格，房子底下洞穴里的怪也会拦住你，而那种怪打不到。僵尸一旦盯上玩家（约 35 格内）就不会自己走开，常常要等到天亮被晒死。躺在床上时怪仍然能打到人。两条脚本优先级不同（清怪 1、躲 2），由代码直接选，不问模型。J-A5-1 和 A2（J-4）共用 fight 动作：A2 是挨打时还手，J-A5-1 是主动清床边。现有的 guard_home 也要补上「难缠的怪=0」。</t>
+          <t>骷髅射程约15格、Hard 约2秒一箭、一箭最多约5点;中间一格实心方块就挡住。bogged/ghast/breeze 不在现在的 HOSTILE_RE 里,要一起补。小麦日志里放过393块挡箭块(原木187、木板99、泥土107),代码里没有收回逻辑,收回归 A13。</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>A17</t>
+          <t>A15</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>进出新房以后，随手把门关上，免得夜里僵尸走进屋。</t>
+          <t>天黑要睡时床边有怪：小麦在稳妥时先把好打的怪清掉；其它情况（以及麦娘、麦豆）回屋里等，床边一空 A4 自己接着去睡</t>
         </is>
       </c>
       <c r="D90" s="7" t="n">
@@ -4311,12 +4321,12 @@
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>J-A17</t>
+          <t>J-A15-1, J-A15-2</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>新房门开着 = 1 并且 离门距离 ≥ 1.5 并且 离门距离 ≤ 4 并且 门洞里有别人 = 0</t>
+          <t>天黑了 = 1 并且 今晚睡着过 = 0 并且 我有自己的床 = 1 并且 我的床边有怪 ≥ 1 并且 在主世界 = 1</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
@@ -4331,35 +4341,35 @@
       </c>
       <c r="J90" s="7" t="inlineStr">
         <is>
-          <t>初稿的「门洞里有人」没有排除自己：自己刚走出门就站在门外那一格，条件不成立，门会一直开着。寻路器开门以后不会自己关；僵尸自己开不了木门。门开着，就又回到旧泥土房「门洞敞开、僵尸蹲在重生点」的老问题。</t>
+          <t>「附近有怪不能睡」只看距离不看墙：墙外 8 格内的僵尸照样让你睡不着。盒子向下算到 6 格，房子底下洞穴里的怪也会拦住你，而那种怪打不到。僵尸一旦盯上玩家（约 35 格内）就不会自己走开，常常要等到天亮被晒死。躺在床上时怪仍然能打到人。两条脚本优先级不同（清怪 1、躲 2），由代码直接选，不问模型。J-A5-1 和 A2（J-4）共用 fight 动作：A2 是挨打时还手，J-A5-1 是主动清床边。现有的 guard_home 也要补上「难缠的怪=0」。</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A17</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>血量保持在一半(10点)以上:掉到一半以下先脱险,再吃饱原地回血,回到14点才算好</t>
+          <t>进出新房以后，随手把门关上，免得夜里僵尸走进屋。</t>
         </is>
       </c>
       <c r="D91" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E91" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>J-A1-1, J-A1-2, J-A1-3</t>
+          <t>J-A17</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>血量 ≤ 9.99</t>
+          <t>新房门开着 = 1 并且 离门距离 ≥ 1.5 并且 离门距离 ≤ 4 并且 门洞里有别人 = 0</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
@@ -4374,19 +4384,19 @@
       </c>
       <c r="J91" s="7" t="inlineStr">
         <is>
-          <t>Hard 难度:饱食度≥18 才自然回血(每4秒1点),饱食度20且有饱和度时每0.5秒1点;回4点血约要吃掉6点饱食度(先扣饱和度),中途会掉到17而停止回血,所以回血脚本短等+重选。触发&lt;10、完成≥14 的缓冲只在 A 层;下面的 J 不再重复「血量≤9.99」。服务器 respawn-at-home=true,61% 死在家8格内 → 在家门口脱险必须去出生点。对应 Owner 样板的 J-3。</t>
+          <t>初稿的「门洞里有人」没有排除自己：自己刚走出门就站在门外那一格，条件不成立，门会一直开着。寻路器开门以后不会自己关；僵尸自己开不了木门。门开着，就又回到旧泥土房「门洞敞开、僵尸蹲在重生点」的老问题。</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>A16</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>新房盖好以后，墙、屋顶、地板或门被炸坏、被拆了，就回去按原样补上。只补计划里的那几格，不找人理论，也不在公屏说话。</t>
+          <t>血量保持在一半(10点)以上:掉到一半以下先脱险,再吃饱原地回血,回到14点才算好</t>
         </is>
       </c>
       <c r="D92" s="7" t="n">
@@ -4397,17 +4407,17 @@
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>J-A16</t>
+          <t>J-A1-1, J-A1-2, J-A1-3</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>新房完工过 = 1 并且 新房缺口数 ≥ 1 并且 离新家址 ≤ 32 并且 天黑了 = 0 并且 8格内有怪 = 0</t>
+          <t>血量 ≤ 9.99</t>
         </is>
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="I92" s="7" t="inlineStr">
@@ -4417,48 +4427,91 @@
       </c>
       <c r="J92" s="7" t="inlineStr">
         <is>
-          <t>初稿用「房子盖好了 = 1 且 缺口 ≥ 1」：如果「盖好了」是现算的，有缺口时它就是 0，两条永远不能同时成立；所以改用只记一次、永不清除的「新房完工过」，旧判据「房子盖好了」的意思不动。初稿的「离家距离 ≤ 32」在搬家之前量的是旧家，改成「离新家址」，这样也顺带保证区块已加载、扫描是实时的。苦力怕爆炸会在墙上开洞；「困难」难度下僵尸会破木门，要查服务器难度。</t>
+          <t>Hard 难度:饱食度≥18 才自然回血(每4秒1点),饱食度20且有饱和度时每0.5秒1点;回4点血约要吃掉6点饱食度(先扣饱和度),中途会掉到17而停止回血,所以回血脚本短等+重选。触发&lt;10、完成≥14 的缓冲只在 A 层;下面的 J 不再重复「血量≤9.99」。服务器 respawn-at-home=true,61% 死在家8格内 → 在家门口脱险必须去出生点。对应 Owner 样板的 J-3。</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>A24</t>
+          <t>A16</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>家人在我附近（24 格内）被一两只普通的怪围着打，我血够（≥14）、手上有剑，就过去帮他把怪打掉，打完回去接着干原来的活。怪超过 3 只、有苦力怕、有打不动的强怪，或者是惹了才打人的狼、铁傀儡这类时不去 —— 那种时候他该跑，我去了只是多搭一个人。麦豆只跑不打，永远不去帮打；麦娘要等拿到剑、也被允许还手以后才去。</t>
+          <t>新房盖好以后，墙、屋顶、地板或门被炸坏、被拆了，就回去按原样补上。只补计划里的那几格，不找人理论，也不在公屏说话。</t>
         </is>
       </c>
       <c r="D93" s="7" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="E93" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
+          <t>J-A16</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>新房完工过 = 1 并且 新房缺口数 ≥ 1 并且 离新家址 ≤ 32 并且 天黑了 = 0 并且 8格内怪数 = 0</t>
+        </is>
+      </c>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>小麦</t>
+        </is>
+      </c>
+      <c r="I93" s="7" t="inlineStr">
+        <is>
+          <t>判据动作都缺</t>
+        </is>
+      </c>
+      <c r="J93" s="7" t="inlineStr">
+        <is>
+          <t>初稿用「房子盖好了 = 1 且 缺口 ≥ 1」：如果「盖好了」是现算的，有缺口时它就是 0，两条永远不能同时成立；所以改用只记一次、永不清除的「新房完工过」，旧判据「房子盖好了」的意思不动。初稿的「离家距离 ≤ 32」在搬家之前量的是旧家，改成「离新家址」，这样也顺带保证区块已加载、扫描是实时的。苦力怕爆炸会在墙上开洞；「困难」难度下僵尸会破木门，要查服务器难度。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>A24</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>家人在我附近（24 格内）被一两只普通的怪围着打，我血够（≥14）、手上有剑，就过去帮他把怪打掉，打完回去接着干原来的活。怪超过 3 只、有苦力怕、有打不动的强怪，或者是惹了才打人的狼、铁傀儡这类时不去 —— 那种时候他该跑，我去了只是多搭一个人。麦娘、麦豆去不去帮打以后再定(Owner 这次定的是「还手」,不是「去帮别人打」)。</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E94" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
           <t>J-A24-1</t>
         </is>
       </c>
-      <c r="G93" s="7" t="inlineStr">
+      <c r="G94" s="7" t="inlineStr">
         <is>
           <t>我能去帮打的家人数 ≥ 1 并且 我是选中的帮手 = 1 并且 有剑 ≥ 1 并且 血量 ≥ 14 并且 饱食度 ≥ 8 并且 刚挨打 = 0</t>
         </is>
       </c>
-      <c r="H93" s="7" t="inlineStr">
+      <c r="H94" s="7" t="inlineStr">
         <is>
           <t>小麦（麦娘放行 fight 并有剑后也算）</t>
         </is>
       </c>
-      <c r="I93" s="7" t="inlineStr">
+      <c r="I94" s="7" t="inlineStr">
         <is>
           <t>判据动作都缺</t>
         </is>
       </c>
-      <c r="J93" s="7" t="inlineStr">
+      <c r="J94" s="7" t="inlineStr">
         <is>
           <t>【为什么用「刚挨打=0」】不用「8格内怪数=0」：家人就在我身边、怪离我 5~8 格时，我自己的 A2（4 格内才打）不管，用「8格内怪数」又会把 A24 挡住，两边都不动。所以只要求我自己没在挨打；我自己 4 格内的怪，照旧由 A2（优先级 3）先处理。
 【只打该打的】只打 A18 表里主动攻击的普通近战怪（亮处的蜘蛛只在他刚挨打时才算）。惹了才打人的中立怪（狼、铁傀儡、僵尸猪灵、末影人等）一律不碰 —— 打它们要么打不过，要么可能是别人养的。有名字、有主人的一律不打（C-SAF-20）。
@@ -4469,44 +4522,44 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="B94" s="7" t="inlineStr">
+    <row r="95">
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>A22</t>
         </is>
       </c>
-      <c r="C94" s="7" t="inlineStr">
+      <c r="C95" s="7" t="inlineStr">
         <is>
           <t>有家人正要把东西递给我（送吃的、送工具，或者我替麦豆收他要存的东西），或者来接我回家时，我别乱跑：在原地（或回家在粮箱旁）站着等，东西丢到脚边就走上去捡；是来接我的，就跟着他走；替人收下的东西，马上回家存进箱子。</t>
         </is>
       </c>
-      <c r="D94" s="7" t="n">
+      <c r="D95" s="7" t="n">
         <v>5.7</v>
       </c>
-      <c r="E94" s="7" t="n">
+      <c r="E95" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F94" s="7" t="inlineStr">
+      <c r="F95" s="7" t="inlineStr">
         <is>
           <t>J-A22-1, J-A22-2, J-A22-3, J-A22-4</t>
         </is>
       </c>
-      <c r="G94" s="7" t="inlineStr">
+      <c r="G95" s="7" t="inlineStr">
         <is>
           <t>我在等家人交接 ≥ 1 并且 真有危险 = 0</t>
         </is>
       </c>
-      <c r="H94" s="7" t="inlineStr">
+      <c r="H95" s="7" t="inlineStr">
         <is>
           <t>全家</t>
         </is>
       </c>
-      <c r="I94" s="7" t="inlineStr">
+      <c r="I95" s="7" t="inlineStr">
         <is>
           <t>判据动作都缺</t>
         </is>
       </c>
-      <c r="J94" s="7" t="inlineStr">
+      <c r="J95" s="7" t="inlineStr">
         <is>
           <t>受助的人乱跑，送的人就追不上；A22 就是让他站住。站着等不算卡住（卡住秒数只在走路步骤里计，C-NAV-4）。有危险（刚挨打或 8 格内有怪）时 A22 不成立，先按 A1/A2/A5/A25 保命；危险过去后回到 A22，送的人看他跑远了，会等他或改成回家交。
 【捡东西】原版规则里，玩家丢出的东西 2 秒内谁都捡不起来，之后谁的身体先碰到（横向约 1 格内）谁捡，丢的人自己也能捡回去，所以送的人丢完会退开，我要走到落点上。背包一格都不空就捡不了：等东西时背包满了，先扔一样真正的杂物腾格（C-ITM-11）。只捡这一单丢在我 6 格内、种类和数量对得上的东西，别处地上的东西不因为这条去捡（可能是真人孩子的）。
@@ -4515,87 +4568,87 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="B95" s="7" t="inlineStr">
-        <is>
-          <t>A4</t>
-        </is>
-      </c>
-      <c r="C95" s="7" t="inlineStr">
-        <is>
-          <t>饿到饱食度≤6、或受了伤又没吃饱(&lt;18)时:先吃身上的,没有就回家拿粮箱里的面包,再没有才让小麦去打猎;吃到18才停</t>
-        </is>
-      </c>
-      <c r="D95" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="E95" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F95" s="7" t="inlineStr">
-        <is>
-          <t>J-A4-1, J-A4-2, J-A4-3</t>
-        </is>
-      </c>
-      <c r="G95" s="7" t="inlineStr">
-        <is>
-          <t>该吃东西了 = 1</t>
-        </is>
-      </c>
-      <c r="H95" s="7" t="inlineStr">
-        <is>
-          <t>全家</t>
-        </is>
-      </c>
-      <c r="I95" s="7" t="inlineStr">
-        <is>
-          <t>判据动作都缺</t>
-        </is>
-      </c>
-      <c r="J95" s="7" t="inlineStr">
-        <is>
-          <t>Hard 难度饱食度0时每4秒掉1点血,一直掉到饿死。面包=3小麦,回5点饱食度。🔴 1.6/1.7 在 brainTick 里,废 brainLoop 时必须一起搬进 A 调度器(饿死是小麦第二大死因)。三条都做不了时 A4 让出身体,只在后台记一次「A无路可走」,不问模型;缺粮的根子交给 G1(麦娘种田做面包)。夜里没吃的且饱食度&gt;2:J-A4-3 不成立 → 让给 A11 去睡(睡觉跳夜不掉饱食度)。家附近64格内常年零动物。「粮箱里有吃的」= 粮箱里的吃的份数≥1,和 A21/A28 用同一个函数、同一张正经吃的白名单(C-FAM-3),从没开过时判开工当 1。【家人互助】三条都做不了(身上没正经吃的,粮箱空了或我自己拿不到,又不是会打猎的小麦)时,我会出现在家族状态板的「等吃的家人」里:A21 由代码选一个身上有多的家人给我送来,或者替我去粮箱拿;我这边由 A22 原地(或回家在粮箱旁)站着等,把丢到脚边的吃的捡起来。现在麦豆既没有 take_from_chest 也没有家,他缺吃的全靠这一条。</t>
-        </is>
-      </c>
-    </row>
     <row r="96">
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>A21</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>家人身上没吃的、自己又拿不到时（粮箱空了、他不会开箱子，或者他回不了家），由代码挑一个家人给他送：32 格内走过去递给他；更远就两人都传送回家，在粮箱旁交；他没家时，白天走过去（96 格内）。送的人自己至少留 4 份（家人快饿死时留 2 份；麦娘人设要留家底，留 6 份），身上至少留 2 个面包。一次给 2~3 份，快饿死时 1 份也送。身上不够，就替他回家从粮箱拿 3 份再送。</t>
+          <t>饿到饱食度≤6、或受了伤又没吃饱(&lt;18)时:先吃身上的,没有就回家拿粮箱里的面包,再没有才让小麦去打猎;吃到18才停</t>
         </is>
       </c>
       <c r="D96" s="7" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="E96" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
+          <t>J-A4-1, J-A4-2, J-A4-3</t>
+        </is>
+      </c>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>该吃东西了 = 1</t>
+        </is>
+      </c>
+      <c r="H96" s="7" t="inlineStr">
+        <is>
+          <t>全家</t>
+        </is>
+      </c>
+      <c r="I96" s="7" t="inlineStr">
+        <is>
+          <t>判据动作都缺</t>
+        </is>
+      </c>
+      <c r="J96" s="7" t="inlineStr">
+        <is>
+          <t>Hard 难度饱食度0时每4秒掉1点血,一直掉到饿死。面包=3小麦,回5点饱食度。🔴 1.6/1.7 在 brainTick 里,废 brainLoop 时必须一起搬进 A 调度器(饿死是小麦第二大死因)。三条都做不了时 A4 让出身体,只在后台记一次「A无路可走」,不问模型;缺粮的根子交给 G1(麦娘种田做面包)。夜里没吃的且饱食度&gt;2:J-A4-3 不成立 → 让给 A11 去睡(睡觉跳夜不掉饱食度)。家附近64格内常年零动物。「粮箱里有吃的」= 粮箱里的吃的份数≥1,和 A21/A28 用同一个函数、同一张正经吃的白名单(C-FAM-3),从没开过时判开工当 1。【家人互助】三条都做不了(身上没正经吃的,粮箱空了或我自己拿不到,又不是会打猎的小麦)时,我会出现在家族状态板的「等吃的家人」里:A21 由代码选一个身上有多的家人给我送来,或者替我去粮箱拿;我这边由 A22 原地(或回家在粮箱旁)站着等,把丢到脚边的吃的捡起来。现在麦豆既没有 take_from_chest 也没有家,他缺吃的全靠这一条。</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>A21</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>家人身上没吃的、自己又拿不到时（粮箱空了、他不会开箱子，或者他回不了家），由代码挑一个家人给他送：32 格内走过去递给他；更远就两人都传送回家，在粮箱旁交；他没家时，白天走过去（96 格内）。送的人自己至少留 4 份（家人快饿死时留 2 份；麦娘人设要留家底，留 6 份），身上至少留 2 个面包。一次给 2~3 份，快饿死时 1 份也送。身上不够，就替他回家从粮箱拿 3 份再送。</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E97" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
           <t>J-A21-1, J-A21-2, J-A21-3</t>
         </is>
       </c>
-      <c r="G96" s="7" t="inlineStr">
+      <c r="G97" s="7" t="inlineStr">
         <is>
           <t>等吃的家人数 ≥ 1 并且 我是选中的送吃的人 = 1 并且 血量 ≥ 12 并且 饱食度 ≥ 10 并且 8格内怪数 = 0</t>
         </is>
       </c>
-      <c r="H96" s="7" t="inlineStr">
+      <c r="H97" s="7" t="inlineStr">
         <is>
           <t>全家</t>
         </is>
       </c>
-      <c r="I96" s="7" t="inlineStr">
+      <c r="I97" s="7" t="inlineStr">
         <is>
           <t>判据动作都缺</t>
         </is>
       </c>
-      <c r="J96" s="7" t="inlineStr">
+      <c r="J97" s="7" t="inlineStr">
         <is>
           <t>【什么时候送】只在他自己拿不到时送。粮箱有吃的，而他有 take_from_chest、有家、回家没连着失败时，A4 的 J-A4-2 会让他自己传送回家拿，家人不替他跑腿。粮箱从没开过时当「有」，让他自己回去看；看到空了，快照变成 0，下一拍 A21 接手。麦豆现在既没有 take_from_chest 也没有家，他缺吃的全靠这条，多半由在家的麦娘走 J-A21-3。
 【谁送】见 C-FAM-5。先筛：在线、同一世界、没在被帮、手上没别的单、没在做比 A21 更急的 A、血≥12、饱食≥10、8 格内没怪、这单能给的份数≥1 或我能替他去粮箱拿=1。再排序：能就地交的先 → 能一次给够 3 份的先 → 离他近的先 → 能分出的多的先 → 小麦→麦娘→麦豆。几个人同时等吃的，按急的先、每个送的人只分一单。麦娘平时身上只留 3 个面包（store_crop），低于她的保底，所以她基本不从自己身上分，而是替人去粮箱拿 —— 她就在家附近，正合适。
@@ -4608,74 +4661,31 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="B97" s="7" t="inlineStr">
-        <is>
-          <t>A3</t>
-        </is>
-      </c>
-      <c r="C97" s="7" t="inlineStr">
-        <is>
-          <t>中毒或凋零了:身上有牛奶就喝;没有就吃饱、原地别冒险,等它过去</t>
-        </is>
-      </c>
-      <c r="D97" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="E97" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F97" s="7" t="inlineStr">
-        <is>
-          <t>J-A3-1, J-A3-2</t>
-        </is>
-      </c>
-      <c r="G97" s="7" t="inlineStr">
-        <is>
-          <t>身上有坏效果 ≥ 1</t>
-        </is>
-      </c>
-      <c r="H97" s="7" t="inlineStr">
-        <is>
-          <t>全家</t>
-        </is>
-      </c>
-      <c r="I97" s="7" t="inlineStr">
-        <is>
-          <t>判据动作都缺</t>
-        </is>
-      </c>
-      <c r="J97" s="7" t="inlineStr">
-        <is>
-          <t>中毒 I 每1.25秒扣1点,扣到1点就停,毒本身杀不死人;凋零 I 每2秒扣1点,能致死。来源:洞穴蜘蛛(Hard 15秒)、女巫毒药水、bogged 毒箭(4秒)、河豚/毒土豆/蜘蛛眼;凋零只来自凋灵骷髅和凋灵玫瑰。腐肉给的是饥饿不是中毒,不归这里。真危险是毒把血压到1后再挨一下,所以核心是中毒期间不冒险。血&lt;10 时 A1 优先接手,做的也是吃+歇,两边一致。</t>
-        </is>
-      </c>
-    </row>
     <row r="98">
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>不在一个地方空转:该走路却75秒没挪窝,或头顶被盖住45秒 → 传送走(人在家门口就去出生点,不在家里反复传送)</t>
+          <t>中毒或凋零了:身上有牛奶就喝;没有就吃饱、原地别冒险,等它过去</t>
         </is>
       </c>
       <c r="D98" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E98" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>J-A10-1</t>
+          <t>J-A3-1, J-A3-2</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>卡住秒数 ≥ 75</t>
+          <t>身上有坏效果 ≥ 1</t>
         </is>
       </c>
       <c r="H98" s="7" t="inlineStr">
@@ -4690,48 +4700,91 @@
       </c>
       <c r="J98" s="7" t="inlineStr">
         <is>
-          <t>麦娘199次卡住自救里65次和上一次隔≤100秒,疑似就是「在家门口卡住 → 传送回家 → 原地再卡」;escape_tp 在离家≤8时选出生点,正好断开这个循环。不挖路、不垫方块。</t>
+          <t>中毒 I 每1.25秒扣1点,扣到1点就停,毒本身杀不死人;凋零 I 每2秒扣1点,能致死。来源:洞穴蜘蛛(Hard 15秒)、女巫毒药水、bogged 毒箭(4秒)、河豚/毒土豆/蜘蛛眼;凋零只来自凋灵骷髅和凋灵玫瑰。腐肉给的是饥饿不是中毒,不归这里。真危险是毒把血压到1后再挨一下,所以核心是中毒期间不冒险。血&lt;10 时 A1 优先接手,做的也是吃+歇,两边一致。</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>A26</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>家人走丢了、自己又回不来（没有家，或者连着两次传送回家都失败），离家超过 64 格已经 3 分钟：白天、离天黑还够 5 分钟时，由小麦走过去找他，领着他走回家（麦娘只去 48 格以内）。天黑前还没到家就先放弃，第二天再来。卡在坑里出不来的，只报给您，不挖不拆。前提是他会跟着家人走。</t>
+          <t>不在一个地方空转:该走路却75秒没挪窝,或头顶被盖住45秒 → 传送走(人在家门口就去出生点,不在家里反复传送)</t>
         </is>
       </c>
       <c r="D99" s="7" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="E99" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
+          <t>J-A10-1</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>卡住秒数 ≥ 75</t>
+        </is>
+      </c>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
+          <t>全家</t>
+        </is>
+      </c>
+      <c r="I99" s="7" t="inlineStr">
+        <is>
+          <t>判据动作都缺</t>
+        </is>
+      </c>
+      <c r="J99" s="7" t="inlineStr">
+        <is>
+          <t>麦娘199次卡住自救里65次和上一次隔≤100秒,疑似就是「在家门口卡住 → 传送回家 → 原地再卡」;escape_tp 在离家≤8时选出生点,正好断开这个循环。不挖路、不垫方块。</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>A26</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>家人走丢了、自己又回不来（没有家，或者连着两次传送回家都失败），离家超过 64 格已经 3 分钟：白天、离天黑还够 5 分钟时，由小麦走过去找他，领着他走回家（麦娘只去 48 格以内）。天黑前还没到家就先放弃，第二天再来。卡在坑里出不来的，只报给您，不挖不拆。前提是他会跟着家人走。</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E100" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F100" s="7" t="inlineStr">
+        <is>
           <t>J-A26-1, J-A26-2</t>
         </is>
       </c>
-      <c r="G99" s="7" t="inlineStr">
+      <c r="G100" s="7" t="inlineStr">
         <is>
           <t>回不了家的家人数 ≥ 1 并且 我是选中的接人的 = 1 并且 离回不了家的家人距离 ≤ 160 并且 被接的人能跟着家人走 = 1 并且 天黑了 = 0 并且 离天黑秒数 ≥ 300 并且 血量 ≥ 14 并且 饱食度 ≥ 14 并且 正经吃的份数 ≥ 2 并且 在主世界 = 1</t>
         </is>
       </c>
-      <c r="H99" s="7" t="inlineStr">
+      <c r="H100" s="7" t="inlineStr">
         <is>
           <t>小麦 / 麦娘（麦娘只接 48 格内）</t>
         </is>
       </c>
-      <c r="I99" s="7" t="inlineStr">
+      <c r="I100" s="7" t="inlineStr">
         <is>
           <t>判据动作都缺</t>
         </is>
       </c>
-      <c r="J99" s="7" t="inlineStr">
+      <c r="J100" s="7" t="inlineStr">
         <is>
           <t>【只接他自己回不来的】平时走丢由他自己解决：A20 离家≥100 格就传送回家，A10 卡住就 escape_tp。这一条只管他自己回不来的情况，主要是麦豆：他的 roles.json 没有 set_home，Owner 没替他 /sethome MaiDou:base 的话，他的 go_home 一定失败（C-PRM-5）。「全家的家」= 小麦状态板上的家，小麦没有就用麦娘的。
 【他不会跟人走就不去】C-FAM-19 放行之前，「被接的人能跟着家人走」=0，这条不开工，免得小麦白走 160 格。
@@ -4741,58 +4794,15 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="B100" s="7" t="inlineStr">
-        <is>
-          <t>A11</t>
-        </is>
-      </c>
-      <c r="C100" s="7" t="inlineStr">
-        <is>
-          <t>天黑了:有自家的空床就去睡;没有但身上材料够,先做一张再睡;家里能安全过夜就回屋待着;都不行就不硬回家(回家=回死亡点)</t>
-        </is>
-      </c>
-      <c r="D100" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="E100" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F100" s="7" t="inlineStr">
-        <is>
-          <t>J-A11-1, J-A11-2, J-A11-3, child_home, sleep_night</t>
-        </is>
-      </c>
-      <c r="G100" s="7" t="inlineStr">
-        <is>
-          <t>天黑了 = 1 并且 在主世界 = 1</t>
-        </is>
-      </c>
-      <c r="H100" s="7" t="inlineStr">
-        <is>
-          <t>全家</t>
-        </is>
-      </c>
-      <c r="I100" s="7" t="inlineStr">
-        <is>
-          <t>判据动作都缺</t>
-        </is>
-      </c>
-      <c r="J100" s="7" t="inlineStr">
-        <is>
-          <t>游戏时间 12542~23459 能睡（雷雨天随时能睡）；8 格内（上下 5 格）有怪睡不着。一张床只能躺一人。床 = 3 块同色羊毛 + 3 块木板；4 根线 = 1 块白羊毛，箱子里的 48 根线 = 12 块羊毛 = 4 张床（做床归 G2）。垃圾清单 JUNK_RE 里的 white_wool 必须去掉。默认要所有在线玩家都睡着才跳夜：机器人不睡，真人孩子也跳不过夜。要不要给机器人 essentials.sleepingignored 是全服设置，交 Owner。3 天没睡，夜里会刷幻翼。困难难度僵尸能破木门，门用栅栏门（4 木棍 + 2 木板）。sleep_night、child_home 挂到这里后，要从原大目标下摘掉。🔴 只在主世界触发（C-NAV-23）：床在下界、末地会爆炸；在资源世界睡会把重生点设进会重置的世界；下界、末地没有白天黑夜，主世界天黑时把远征中的小麦拉回家也不对（J-A11-3 的回屋 = /home base 传送）。小麦从下界回到主世界时如果是夜里，这条照常接管。</t>
-        </is>
-      </c>
-    </row>
     <row r="101">
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>A20</t>
+          <t>A11</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>别走丢:在主世界离家 ≥100 格、又不在探路时,就回家</t>
+          <t>天黑了:有自家的空床就去睡;没有但身上材料够,先做一张再睡;家里能安全过夜就回屋待着;都不行就不硬回家(回家=回死亡点)</t>
         </is>
       </c>
       <c r="D101" s="7" t="n">
@@ -4803,68 +4813,111 @@
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>J-A20</t>
+          <t>J-A11-1, J-A11-2, J-A11-3, child_home, sleep_night</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
         <is>
-          <t>离家距离 ≥ 100 并且 在主世界 = 1 并且 正在探路 = 0 并且 我有家 = 1 并且 近10分钟回家失败次数 ≤ 1</t>
+          <t>天黑了 = 1 并且 在主世界 = 1</t>
         </is>
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
-          <t>任意</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="I101" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
       <c r="J101" s="7" t="inlineStr">
         <is>
-          <t>go_home 每次失败(没有家、传送冷却、被打断)都记进家族状态板的「近10分钟回家失败次数」(C-FAM-13)。触发里有「我有家=1」「近10分钟回家失败次数≤1」:没有家就根本不试,连着失败 2 次就停手 10 分钟,不在原地空转。回不来的人,离全家的家≥64 格满 3 分钟后,由 A26 让小麦(48 格内也可以是麦娘)白天走过去接他、领他走回家 —— 前提是他会「跟着家人走」(C-FAM-19)。麦豆 roles.json 没有 set_home,Owner 没替他 /sethome MaiDou:base 的话,他的 go_home 一定失败,走丢时只能靠 A26。</t>
+          <t>游戏时间 12542~23459 能睡（雷雨天随时能睡）；8 格内（上下 5 格）有怪睡不着。一张床只能躺一人。床 = 3 块同色羊毛 + 3 块木板；4 根线 = 1 块白羊毛，箱子里的 48 根线 = 12 块羊毛 = 4 张床（做床归 G2）。垃圾清单 JUNK_RE 里的 white_wool 必须去掉。默认要所有在线玩家都睡着才跳夜：机器人不睡，真人孩子也跳不过夜。要不要给机器人 essentials.sleepingignored 是全服设置，交 Owner。3 天没睡，夜里会刷幻翼。困难难度僵尸能破木门，门用栅栏门（4 木棍 + 2 木板）。sleep_night、child_home 挂到这里后，要从原大目标下摘掉。🔴 只在主世界触发（C-NAV-23）：床在下界、末地会爆炸；在资源世界睡会把重生点设进会重置的世界；下界、末地没有白天黑夜，主世界天黑时把远征中的小麦拉回家也不对（J-A11-3 的回屋 = /home base 传送）。小麦从下界回到主世界时如果是夜里，这条照常接管。</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>A23</t>
+          <t>A20</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>家人缺干活的家伙、我手上有多的，就送他一把：会打架的家人（现在是小麦）没剑，谁手上有用不上的剑就给他；种田的麦娘没锄头，谁有多的锄头就给她。麦豆只跑不打，不给他剑。只在离得近（32 格内）或两人都在家附近时顺手给，不专程跑。</t>
+          <t>别走丢:在主世界离家 ≥100 格、又不在探路时,就回家</t>
         </is>
       </c>
       <c r="D102" s="7" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="E102" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
+          <t>J-A20</t>
+        </is>
+      </c>
+      <c r="G102" s="7" t="inlineStr">
+        <is>
+          <t>离家距离 ≥ 100 并且 在主世界 = 1 并且 正在探路 = 0 并且 我有家 = 1 并且 近10分钟回家失败次数 ≤ 1</t>
+        </is>
+      </c>
+      <c r="H102" s="7" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="I102" s="7" t="inlineStr">
+        <is>
+          <t>缺判据</t>
+        </is>
+      </c>
+      <c r="J102" s="7" t="inlineStr">
+        <is>
+          <t>go_home 每次失败(没有家、传送冷却、被打断)都记进家族状态板的「近10分钟回家失败次数」(C-FAM-13)。触发里有「我有家=1」「近10分钟回家失败次数≤1」:没有家就根本不试,连着失败 2 次就停手 10 分钟,不在原地空转。回不来的人,离全家的家≥64 格满 3 分钟后,由 A26 让小麦(48 格内也可以是麦娘)白天走过去接他、领他走回家 —— 前提是他会「跟着家人走」(C-FAM-19)。麦豆 roles.json 没有 set_home,Owner 没替他 /sethome MaiDou:base 的话,他的 go_home 一定失败,走丢时只能靠 A26。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>A23</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>家人缺干活的家伙、我手上有多的就送他 —— 🔴 代码里没有递东西的动作(giveTo 只给吃的和木头,剑存不进箱子),剑和锄头眼下只能各做各的,这一条先搁着</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E103" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
           <t>J-A23-1</t>
         </is>
       </c>
-      <c r="G102" s="7" t="inlineStr">
+      <c r="G103" s="7" t="inlineStr">
         <is>
           <t>我能补工具的家人数 ≥ 1 并且 我是选中的送工具的人 = 1 并且 能顺路交给他 = 1 并且 血量 ≥ 12 并且 8格内怪数 = 0</t>
         </is>
       </c>
-      <c r="H102" s="7" t="inlineStr">
+      <c r="H103" s="7" t="inlineStr">
         <is>
           <t>全家</t>
         </is>
       </c>
-      <c r="I102" s="7" t="inlineStr">
+      <c r="I103" s="7" t="inlineStr">
         <is>
           <t>判据动作都缺</t>
         </is>
       </c>
-      <c r="J102" s="7" t="inlineStr">
+      <c r="J103" s="7" t="inlineStr">
         <is>
           <t>【工具需求表】一份表（C-FAM-12）：剑给 roles.json 里有 fight 的人，锄头给有 till_soil 的人，以后的镐给有 mine 的人。「多余」= 那种工具的件数 −（我自己用得上 ? 1 : 0），所以不会打架的人手上的剑全算多余（比如麦娘做的、麦豆捡的）。
 【送哪把】多余的里面剩余耐久最高的那把；自己留着的是最好的一把。剑不叠放，他背包得有 1 个空格（看状态板）。
@@ -4874,87 +4927,87 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="B103" s="7" t="inlineStr">
-        <is>
-          <t>A12</t>
-        </is>
-      </c>
-      <c r="C103" s="7" t="inlineStr">
-        <is>
-          <t>背包至少留4个空格:满了先扔掉真正的杂物,再回家存箱子;箱子满了就再放一口箱子</t>
-        </is>
-      </c>
-      <c r="D103" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="E103" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F103" s="7" t="inlineStr">
-        <is>
-          <t>J-A12-1, J-A12-2, J-A12-3, J-A12-4, store_wood, wife_craft_chest, wife_store</t>
-        </is>
-      </c>
-      <c r="G103" s="7" t="inlineStr">
-        <is>
-          <t>背包空格 ≤ 1</t>
-        </is>
-      </c>
-      <c r="H103" s="7" t="inlineStr">
-        <is>
-          <t>全家</t>
-        </is>
-      </c>
-      <c r="I103" s="7" t="inlineStr">
-        <is>
-          <t>判据动作都缺</t>
-        </is>
-      </c>
-      <c r="J103" s="7" t="inlineStr">
-        <is>
-          <t>背包36格一满,砍树第一下就被 collectblock 抛错。🔴 硬规则 2.5(空格≤1 → 回家存)在 brainTick 里,要和吃饭一起搬。排在最后,还要求血≥10、饱食度≥10,危险时根本抢不到身体。store_wood、wife_store、wife_craft_chest 挂到这里后,要从原大目标下摘掉。</t>
-        </is>
-      </c>
-    </row>
     <row r="104">
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>A27</t>
+          <t>A12</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>麦豆背包满了、自己又不会存箱子时，把能存的东西交给会存箱子的家人（先找麦娘）：她在 32 格内就当场交，两人都有家就回家交；接手的人收下后自己回家存进箱子。吃的、他唯一的工具和贵重东西不交。您如果同意教麦豆自己存箱子，这条就不用了。</t>
+          <t>背包至少留4个空格:满了先扔掉真正的杂物,再回家存箱子;箱子满了就再放一口箱子</t>
         </is>
       </c>
       <c r="D104" s="7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="E104" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
+          <t>J-A12-1, J-A12-2, J-A12-3, J-A12-4, store_wood, wife_craft_chest, wife_store</t>
+        </is>
+      </c>
+      <c r="G104" s="7" t="inlineStr">
+        <is>
+          <t>背包空格 ≤ 1</t>
+        </is>
+      </c>
+      <c r="H104" s="7" t="inlineStr">
+        <is>
+          <t>全家</t>
+        </is>
+      </c>
+      <c r="I104" s="7" t="inlineStr">
+        <is>
+          <t>判据动作都缺</t>
+        </is>
+      </c>
+      <c r="J104" s="7" t="inlineStr">
+        <is>
+          <t>背包36格一满,砍树第一下就被 collectblock 抛错。🔴 硬规则 2.5(空格≤1 → 回家存)在 brainTick 里,要和吃饭一起搬。排在最后,还要求血≥10、饱食度≥10,危险时根本抢不到身体。store_wood、wife_store、wife_craft_chest 挂到这里后,要从原大目标下摘掉。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>A27</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>麦豆背包满了、自己又不会存箱子时，把能存的东西交给会存箱子的家人（先找麦娘）：她在 32 格内就当场交，两人都有家就回家交；接手的人收下后自己回家存进箱子。吃的、他唯一的工具和贵重东西不交。您如果同意教麦豆自己存箱子，这条就不用了。</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E105" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
           <t>J-A27-1, J-A27-2</t>
         </is>
       </c>
-      <c r="G104" s="7" t="inlineStr">
+      <c r="G105" s="7" t="inlineStr">
         <is>
           <t>我能自己存 = 0 并且 背包空格 ≤ 1 并且 可存的东西 ≥ 1 并且 帮存交接地点 ≥ 1 并且 8格内怪数 = 0 并且 血量 ≥ 10</t>
         </is>
       </c>
-      <c r="H104" s="7" t="inlineStr">
+      <c r="H105" s="7" t="inlineStr">
         <is>
           <t>麦豆</t>
         </is>
       </c>
-      <c r="I104" s="7" t="inlineStr">
+      <c r="I105" s="7" t="inlineStr">
         <is>
           <t>判据动作都缺</t>
         </is>
       </c>
-      <c r="J104" s="7" t="inlineStr">
+      <c r="J105" s="7" t="inlineStr">
         <is>
           <t>【为什么不是「提醒」】机器人不在公屏说话。家人之间的「提醒」就是家族状态板上的数字（背包空格），后台也看得到。会存箱子的人背包满了，都由自己的 A12/A19 解决，不需要别人帮。
 【为什么只管麦豆】麦豆 roles.json 里没有 store_items，背包满了只能扔杂物。满了以后，连家人送来的吃的都捡不起来（A22），所以才需要这条。
@@ -4964,87 +5017,87 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="B105" s="7" t="inlineStr">
-        <is>
-          <t>A13</t>
-        </is>
-      </c>
-      <c r="C105" s="7" t="inlineStr">
-        <is>
-          <t>我在外面临时放的挡箭块都收回来,不留在地上(对应「地上的木头太丑」)</t>
-        </is>
-      </c>
-      <c r="D105" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="E105" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F105" s="7" t="inlineStr">
-        <is>
-          <t>J-A13-1</t>
-        </is>
-      </c>
-      <c r="G105" s="7" t="inlineStr">
-        <is>
-          <t>挡箭块没收回 ≥ 1 并且 天黑了 = 0 并且 8格内怪数 = 0 并且 血量 ≥ 14</t>
-        </is>
-      </c>
-      <c r="H105" s="7" t="inlineStr">
-        <is>
-          <t>全家</t>
-        </is>
-      </c>
-      <c r="I105" s="7" t="inlineStr">
-        <is>
-          <t>判据动作都缺</t>
-        </is>
-      </c>
-      <c r="J105" s="7" t="inlineStr">
-        <is>
-          <t>只收自己登记过的方块,不碰任何别人的东西。历史上已经放的393块(原木187、木板99、泥土107)没有坐标记录,代码找不回来:要由人用 CoreProtect 查 XiaoMai 的放置记录列清单,交 Owner 决定拆不拆,不自动拆。</t>
-        </is>
-      </c>
-    </row>
     <row r="106">
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>A28</t>
+          <t>A13</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>回到家时，身上吃的多（超过 6 份）、粮箱里又不到 6 份，就顺手把多出来的放进粮箱（最多补到 12 份），让全家谁饿了都有得拿。先放熟肉，身上至少留 2 个面包。只在已经到家时做，不专程跑回来。</t>
+          <t>我在外面临时放的挡箭块都收回来,不留在地上(对应「地上的木头太丑」)</t>
         </is>
       </c>
       <c r="D106" s="7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="E106" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
+          <t>J-A13-1</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>挡箭块没收回 ≥ 1 并且 天黑了 = 0 并且 8格内怪数 = 0 并且 血量 ≥ 14</t>
+        </is>
+      </c>
+      <c r="H106" s="7" t="inlineStr">
+        <is>
+          <t>全家</t>
+        </is>
+      </c>
+      <c r="I106" s="7" t="inlineStr">
+        <is>
+          <t>判据动作都缺</t>
+        </is>
+      </c>
+      <c r="J106" s="7" t="inlineStr">
+        <is>
+          <t>只收自己登记过的方块,不碰任何别人的东西。历史上已经放的393块(原木187、木板99、泥土107)没有坐标记录,代码找不回来:要由人用 CoreProtect 查 XiaoMai 的放置记录列清单,交 Owner 决定拆不拆,不自动拆。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>A28</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>回到家时，身上吃的多（超过 6 份）、粮箱里又不到 6 份，就顺手把多出来的放进粮箱（最多补到 12 份），让全家谁饿了都有得拿。先放熟肉，身上至少留 2 个面包。只在已经到家时做，不专程跑回来。</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E107" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
           <t>J-A28-1</t>
         </is>
       </c>
-      <c r="G106" s="7" t="inlineStr">
+      <c r="G107" s="7" t="inlineStr">
         <is>
           <t>有粮箱 ≥ 1 并且 离家距离 ≤ 8 并且 粮箱里的吃的份数 ≤ 5 并且 我能存进粮箱的吃的 ≥ 3 并且 8格内怪数 = 0</t>
         </is>
       </c>
-      <c r="H106" s="7" t="inlineStr">
+      <c r="H107" s="7" t="inlineStr">
         <is>
           <t>全家</t>
         </is>
       </c>
-      <c r="I106" s="7" t="inlineStr">
+      <c r="I107" s="7" t="inlineStr">
         <is>
           <t>判据动作都缺</t>
         </is>
       </c>
-      <c r="J106" s="7" t="inlineStr">
+      <c r="J107" s="7" t="inlineStr">
         <is>
           <t>【粮箱是全家的饭桌】小麦打猎多出来的熟肉（他曾经身上揣着 66 块熟牛肉还在饿死）放进去，麦豆、麦娘饿了就有得拿，A21 的「替他去粮箱拿」也有东西可拿。
 【阈值错开，不会来回倒腾】A14：身上面包≤1 才去粮箱拿 3 个；A28：身上超过 6 份才往粮箱放，放完还留 6 份，其中至少 2 个面包（先放熟肉）；A21：送吃的自己留 4 份。
@@ -5053,110 +5106,72 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="3" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
         <is>
           <t>四、思考触发(只有这些条件成立时才去问模型;没有任何定时思考)</t>
         </is>
       </c>
-      <c r="B109" s="4" t="n"/>
-      <c r="C109" s="4" t="n"/>
-      <c r="D109" s="4" t="n"/>
-      <c r="E109" s="4" t="n"/>
-      <c r="F109" s="4" t="n"/>
-      <c r="G109" s="4" t="n"/>
-      <c r="H109" s="4" t="n"/>
-      <c r="I109" s="4" t="n"/>
-    </row>
-    <row r="110">
-      <c r="B110" s="5" t="inlineStr">
+      <c r="B110" s="4" t="n"/>
+      <c r="C110" s="4" t="n"/>
+      <c r="D110" s="4" t="n"/>
+      <c r="E110" s="4" t="n"/>
+      <c r="F110" s="4" t="n"/>
+      <c r="G110" s="4" t="n"/>
+      <c r="H110" s="4" t="n"/>
+      <c r="I110" s="4" t="n"/>
+    </row>
+    <row r="111">
+      <c r="B111" s="5" t="inlineStr">
         <is>
           <t>思考触发编号</t>
         </is>
       </c>
-      <c r="C110" s="5" t="inlineStr">
+      <c r="C111" s="5" t="inlineStr">
         <is>
           <t>什么时候才去问模型</t>
         </is>
       </c>
-      <c r="D110" s="5" t="inlineStr">
+      <c r="D111" s="5" t="inlineStr">
         <is>
           <t>思考触发优先级(数字越低优先级越高)</t>
         </is>
       </c>
-      <c r="E110" s="5" t="inlineStr">
+      <c r="E111" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">状态(0:未开始, 1:进行中; 2:已完成; 3:暂停; 4:评估中; 默认状态为4) </t>
         </is>
       </c>
-      <c r="F110" s="5" t="inlineStr">
+      <c r="F111" s="5" t="inlineStr">
         <is>
           <t>关联实际行为脚本编号</t>
         </is>
       </c>
-      <c r="G110" s="6" t="inlineStr">
+      <c r="G111" s="6" t="inlineStr">
         <is>
           <t>触发条件(代码判据)</t>
         </is>
       </c>
-      <c r="H110" s="6" t="inlineStr">
+      <c r="H111" s="6" t="inlineStr">
         <is>
           <t>可行性</t>
         </is>
       </c>
-      <c r="I110" s="6" t="inlineStr">
+      <c r="I111" s="6" t="inlineStr">
         <is>
           <t>备注(问什么、答案怎么落地、问不到怎么办)</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="B111" s="7" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="C111" s="7" t="inlineStr">
-        <is>
-          <t>有真人在公屏叫它名字或私聊它时回一句话。「在哪、在干嘛、跟我来、停」这类固定问题由代码直接答，只有闲聊才问模型。不回另外两个机器人，每人每 10 分钟最多回 10 句，精确位置只告诉您。</t>
-        </is>
-      </c>
-      <c r="D111" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E111" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F111" s="7" t="inlineStr">
-        <is>
-          <t>think_reply</t>
-        </is>
-      </c>
-      <c r="G111" s="7" t="inlineStr">
-        <is>
-          <t>被点名 = 1 并且 说话的是真人 = 1 并且 是固定句式 = 0 并且 离上次回这个人秒数 ≥ 6 并且 离上次回话秒数 ≥ 3 并且 这人10分钟内被回句数 ≤ 9</t>
-        </is>
-      </c>
-      <c r="H111" s="7" t="inlineStr">
-        <is>
-          <t>缺判据</t>
-        </is>
-      </c>
-      <c r="I111" s="7" t="inlineStr">
-        <is>
-          <t>回答格式是 {say, give}。say 截到 30 字(提示里要求 25 字;brain.chat 现在截 40,改成 30),以 / 开头的整句丢掉。give 只能是 C-CHT-8R「能送的东西」里的一行(按中文名对),数量不超过那一行写的数、也不超过 8 个(brain.chat 现在上限 16、只认「食物/木头」两类,都改成按能送的东西对);同一个人 3 分钟只给一次（现成规则）。私聊进来的用 /msg &lt;对方&gt; 回，命令由代码拼，模型只给正文，不把私聊内容发到公屏。「你在哪」只对 Owner 报坐标，对其他人只用 C-CTX-5 的粗略区域词(家附近/田里/林子里/在外面/资源世界/下界,不带方向和距离)：新家不圈地，离人远是主要保护，公屏报坐标或「家的东北 120 格」都等于告诉全服家在哪。问不到或超时 15 秒就不说话。现状：任何人点名说「跟我来」都能让它跟着走 5 分钟（8148 行 startFollow + brainPausedUntil），而且这条绕过了 roles.json 的执行闸；谁的话算数等 Owner 定;跟完之后接着做手上原来那件小目标。按 Owner 规矩，只有被点名才说话，整个 T 层只有 T2 和 T10 会往聊天框发字。GP 开着防刷屏（实测踢过），全局 3 秒间隔保留。问模型时带什么:按 C-CTX-1 的「T2 配方」。系统段:我是谁(roles.json 的中文名和关系)+ 人格原文 + 现有回话设定里的未成年人安全底线和格式要求。🔴 现在的回话设定(brain.js 656 行 CHAT_SYSTEM)第一句写死「你叫小麦(XiaoMai)」,还带着小麦的性格,而 roles.persona() 只返回人格那一段 —— 麦娘、麦豆被点名时会自称小麦,这两句必须删掉,改由系统段按角色填。用户段从上到下:六样底包(家里人每人一句只写在干嘛、饿不饿、有没有人在帮,不写在哪;我现在的位置只用粗略区域词;大目标、小目标各一行)→ 能送的东西(中文名,不用游戏原名,免得原名被说到公屏上;家里有人缺吃的时注明「已给某某留了 N 份」)→ 对方的话(谁说的、是不是 Owner;原话放在「」里,最多 60 字,去掉 / 开头的内容;加上 C-CTX-6 记的和这个人最近 3 轮对话)→ 怎么回答 {say:…, give:{what:…, count:…}}。整个包不放坐标。总长 ≤1700 字(系统段约 1000 + 处境 ≤700)。think_reply 里写的「3 选 1 / 跟他走」以这里的 {say, give} 为准:跟不跟人走是代码的固定句式,不交给模型。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>您（Owner）在游戏里点名叫它做某件事时，代码先按小目标的叫法去对，对上了就直接插队去做；对不上但听起来像命令时，才问一次模型，把您的话对到它能做的某个小目标上。</t>
+          <t>有真人在公屏叫它名字或私聊它时回一句话。「在哪、在干嘛、跟我来、停」这类固定问题由代码直接答，只有闲聊才问模型。不回另外两个机器人，每人每 10 分钟最多回 10 句，精确位置只告诉您。</t>
         </is>
       </c>
       <c r="D112" s="7" t="n">
@@ -5167,12 +5182,12 @@
       </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>J-T10</t>
+          <t>think_reply</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
-          <t>被点名 = 1 并且 说话的是Owner = 1 并且 像是命令 = 1 并且 叫法命中小目标数 = 0 并且 离上次T10秒数 ≥ 10</t>
+          <t>被点名 = 1 并且 说话的是真人 = 1 并且 是固定句式 = 0 并且 离上次回这个人秒数 ≥ 6 并且 离上次回话秒数 ≥ 3 并且 这人10分钟内被回句数 ≤ 9</t>
         </is>
       </c>
       <c r="H112" s="7" t="inlineStr">
@@ -5182,19 +5197,19 @@
       </c>
       <c r="I112" s="7" t="inlineStr">
         <is>
-          <t>问模型时带什么:按 C-CTX-1 的「T10 配方」,从上到下:六样底包(刚做完的事给 3 件,让它听得懂「接着干」「别干了」;正在做的小目标写上第几步;家里人照写,您的话里可能提到家人)→ 您的原话(放在「」里,最多 60 字)→ 这次要你决定(把这句话对到下面哪件活上)→ 选项(本角色没完成的小目标,按优先级最多 10 个,按位置标字母,每行:短名、现在能不能开工或缺什么;最后固定一行「不是叫我做事」)→ 怎么回答 {选:C}。总长 ≤1600 字;只收选项里的字母,或原样照抄、只对得上一个选项的小目标编号。插队 = 把这个小目标放到队头，手上原来那件压在下面、保留做到第几步；插队这件做完、失败放下或您说「停」之后，接着做原来那件（Owner 规矩：事件处理完继续上一个任务直到完成）；叫法正好命中 1 条、由代码直接插队时也一样。开工条件不成立时，回一句「还做不了：缺 X」（由代码拼，不问模型）。问不到或超时 12 秒，就当普通点名交给 T2。Owner 以前要的「身边玩家的话能影响它的想法」，是靠 decide() 每轮读「玩家刚说的话」实现的；删掉 decide() 后这条路就断了，T10 是替代。默认只听 Owner，其他人的话只回、不接活。依赖 T0 的小目标层。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
+          <t>回答格式是 {say, give}。say 截到 30 字(提示里要求 25 字;brain.chat 现在截 40,改成 30),以 / 开头的整句丢掉。give 只能是 C-CHT-8R「能送的东西」里的一行(按中文名对),数量不超过那一行写的数、也不超过 8 个(brain.chat 现在上限 16、只认「食物/木头」两类,都改成按能送的东西对);同一个人 3 分钟只给一次（现成规则）。私聊进来的用 /msg &lt;对方&gt; 回，命令由代码拼，模型只给正文，不把私聊内容发到公屏。「你在哪」只对 Owner 报坐标，对其他人只用 C-CTX-5 的粗略区域词(家附近/田里/林子里/在外面/资源世界/下界,不带方向和距离)：新家不圈地，离人远是主要保护，公屏报坐标或「家的东北 120 格」都等于告诉全服家在哪。问不到或超时 15 秒就不说话。现状：任何人点名说「跟我来」都能让它跟着走 5 分钟（8148 行 startFollow + brainPausedUntil），而且这条绕过了 roles.json 的执行闸；谁的话算数等 Owner 定;跟完之后接着做手上原来那件小目标。按 Owner 规矩，只有被点名才说话，整个 T 层只有 T2 和 T10 会往聊天框发字。GP 开着防刷屏（实测踢过），全局 3 秒间隔保留。问模型时带什么:按 C-CTX-1 的「T2 配方」。系统段:我是谁(roles.json 的中文名和关系)+ 人格原文 + 现有回话设定里的未成年人安全底线和格式要求。🔴 现在的回话设定(brain.js 656 行 CHAT_SYSTEM)第一句写死「你叫小麦(XiaoMai)」,还带着小麦的性格,而 roles.persona() 只返回人格那一段 —— 麦娘、麦豆被点名时会自称小麦,这两句必须删掉,改由系统段按角色填。用户段从上到下:六样底包(家里人每人一句只写在干嘛、饿不饿、有没有人在帮,不写在哪;我现在的位置只用粗略区域词;大目标、小目标各一行)→ 能送的东西(中文名,不用游戏原名,免得原名被说到公屏上;家里有人缺吃的时注明「已给某某留了 N 份」)→ 对方的话(谁说的、是不是 Owner;原话放在「」里,最多 60 字,去掉 / 开头的内容;加上 C-CTX-6 记的和这个人最近 3 轮对话)→ 怎么回答 {say:…, give:{what:…, count:…}}。整个包不放坐标。总长 ≤1700 字(系统段约 1000 + 处境 ≤700)。think_reply 里写的「3 选 1 / 跟他走」以这里的 {say, give} 为准:跟不跟人走是代码的固定句式,不交给模型。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>T11</t>
+          <t>T10</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>房子盖好以后，如果有两种以上合法的家具摆法（比如床靠北墙还是东墙），问模型一次挑哪种；只有一种就不问。（属于 G3）</t>
+          <t>您（Owner）在游戏里点名叫它做某件事时，代码先按小目标的叫法去对，对上了就直接插队去做；对不上但听起来像命令时，才问一次模型，把您的话对到它能做的某个小目标上。</t>
         </is>
       </c>
       <c r="D113" s="7" t="n">
@@ -5205,88 +5220,88 @@
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>J-T11</t>
+          <t>J-T10</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
         <is>
-          <t>新房完工过 = 1 并且 家具布局已定 = 0 并且 合格家具布局数 ≥ 2</t>
+          <t>被点名 = 1 并且 说话的是Owner = 1 并且 像是命令 = 1 并且 叫法命中小目标数 = 0 并且 离上次T10秒数 ≥ 10</t>
         </is>
       </c>
       <c r="H113" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
       <c r="I113" s="7" t="inlineStr">
         <is>
-          <t>检查时机：「新房完工过」第一次变成 1 的那一刻（J-M3-4 完成时），以及麦娘手上没活的时刻；不定时查。几何（哪一格放什么）全部由代码算，模型只在几种合法摆法里挑喜好。问模型时带什么:按 C-CTX-1 的「T11 配方」,这是按性格挑摆法的地方,系统段必须带人设。用户段:六样底包 → 家里几口人、每张床归谁(按 C-BED-7 的床位顺序)→ 新房(屋里 7×7、门在哪面墙)→ 这次要你决定 → 选项(最多 4 种摆法,按代码排序标 A~D,每行一句方位:床靠哪面墙、箱子靠哪面墙、工作台在哪个角;代码已检查过都放得下)→ 怎么回答 {选:A, why:…}。总长 ≤1100 字;问不到或超时 25 秒选 A。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
+          <t>问模型时带什么:按 C-CTX-1 的「T10 配方」,从上到下:六样底包(刚做完的事给 3 件,让它听得懂「接着干」「别干了」;正在做的小目标写上第几步;家里人照写,您的话里可能提到家人)→ 您的原话(放在「」里,最多 60 字)→ 这次要你决定(把这句话对到下面哪件活上)→ 选项(本角色没完成的小目标,按优先级最多 10 个,按位置标字母,每行:短名、现在能不能开工或缺什么;最后固定一行「不是叫我做事」)→ 怎么回答 {选:C}。总长 ≤1600 字;只收选项里的字母,或原样照抄、只对得上一个选项的小目标编号。插队 = 把这个小目标放到队头，手上原来那件压在下面、保留做到第几步；插队这件做完、失败放下或您说「停」之后，接着做原来那件（Owner 规矩：事件处理完继续上一个任务直到完成）；叫法正好命中 1 条、由代码直接插队时也一样。开工条件不成立时，回一句「还做不了：缺 X」（由代码拼，不问模型）。问不到或超时 12 秒，就当普通点名交给 T2。Owner 以前要的「身边玩家的话能影响它的想法」，是靠 decide() 每轮读「玩家刚说的话」实现的；删掉 decide() 后这条路就断了，T10 是替代。默认只听 Owner，其他人的话只回、不接活。依赖 T0 的小目标层。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>T8</t>
+          <t>T11</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>做同一件小目标时、30 分钟内因为同一种原因死了两次：饿死、淹死、晚上被怪打死这些代码有定论的情况，由代码直接改（提前吃东西、查游泳自救、这件事改成只在白天做）；剩下有两条以上出路的，才问一次模型选。</t>
+          <t>房子盖好以后，如果有两种以上合法的家具摆法（比如床靠北墙还是东墙），问模型一次挑哪种；只有一种就不问。（属于 G3）</t>
         </is>
       </c>
       <c r="D114" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E114" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>J-T8, guard_home, make_sword, sleep_night</t>
+          <t>J-T11</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>同一小目标同因死亡次数 ≥ 2 并且 死因已有代码对策 = 0 并且 这个死因的可选对策数 ≥ 2 并且 离上次为这个死因问秒数 ≥ 3600</t>
+          <t>新房完工过 = 1 并且 家具布局已定 = 0 并且 合格家具布局数 ≥ 2</t>
         </is>
       </c>
       <c r="H114" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
       <c r="I114" s="7" t="inlineStr">
         <is>
-          <t>实测夜里真实死亡约 30 次/小时，原稿的「30 分钟内同因 ≥2 次」几乎永远成立，再配上每种死因 60 分钟冷却，就成了每小时定时问一次。所以加了两道门：「两次都在做同一个小目标」和「代码没有定论」。模型的选项按位置标字母：A 自动暂停到天亮或 30 分钟（写运行文件，不写状态 3，永远是 A）；B 前置小目标插队（能做时才列；原来那件保留进度，前置做完接着做）；最后一行是「不改」。原稿的 A/B/D 缺了 C，小模型容易答出不存在的 C，已改成连续字母。超时 12 秒或答非所问就选 A。🔴 原稿要把淹死、岩浆的死亡点周围记成危险地点，这和 Owner 说过的「死过的地方也不一定要绕开」冲突。所以岩浆只记那几格岩浆本身（反射层本来就扫岩浆）；淹死是游泳自救失灵的问题，不标记区域。latest.log 会漏记死亡 5~10 倍，只能用机器人收到的服务器广播。麦娘、麦豆没有 sleep 和 fight，暂停到天亮时只能回家待着。服务器的 playersSleepingPercentage 没有核实过，有真人在线时，机器人睡觉未必能跳过夜晚。问模型时带什么:按 C-CTX-1 的「T8 配方」,六样用完整版,从上到下:家里人(另外两人各一行;标出谁会做剑)→ 身上的东西(武器、盔甲、吃的、挡箭用的泥土圆石写在最前)→ 大目标只留这件所属的一行 → 这个小目标和它的前置(最多 3 行)→ 刚做完的事(6 件)→ 冷却/暂停中 → 我现在 → 这两次死亡(每次:几分钟前、死因原话 ≤30 字、当时白天还是夜里、在哪一片、身上有没有剑;后两项要先按 C-CTX-3 让 C-DAT-3 记下来,现在没记)→ 这次要你决定 → 选项 → 怎么回答 {选:A, why:…}。总长 ≤1800 字。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
+          <t>检查时机：「新房完工过」第一次变成 1 的那一刻（J-M3-4 完成时），以及麦娘手上没活的时刻；不定时查。几何（哪一格放什么）全部由代码算，模型只在几种合法摆法里挑喜好。问模型时带什么:按 C-CTX-1 的「T11 配方」,这是按性格挑摆法的地方,系统段必须带人设。用户段:六样底包 → 家里几口人、每张床归谁(按 C-BED-7 的床位顺序)→ 新房(屋里 7×7、门在哪面墙)→ 这次要你决定 → 选项(最多 4 种摆法,按代码排序标 A~D,每行一句方位:床靠哪面墙、箱子靠哪面墙、工作台在哪个角;代码已检查过都放得下)→ 怎么回答 {选:A, why:…}。总长 ≤1100 字;问不到或超时 25 秒选 A。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T8</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>同一个小目标连着失败 3 次时，先由代码按失败原因处理：缺材料就先做它的前置，找不到或走不到就换一个记得的地方，背包满就先腾格子，都不行就自动暂停 30 分钟。只有失败原因代码认不出、又有两条以上出路时，才问模型选。</t>
+          <t>做同一件小目标时、30 分钟内因为同一种原因死了两次：饿死、淹死、晚上被怪打死这些代码有定论的情况，由代码直接改（提前吃东西、查游泳自救、这件事改成只在白天做）；剩下有两条以上出路的，才问一次模型选。</t>
         </is>
       </c>
       <c r="D115" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E115" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>J-T1-2</t>
+          <t>J-T8, guard_home, make_sword, sleep_night</t>
         </is>
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>本小目标连败次数 ≥ 3 并且 失败原因已归类 = 0 并且 可选对策数 ≥ 2 并且 离上次为这个小目标问秒数 ≥ 1800</t>
+          <t>同一小目标同因死亡次数 ≥ 2 并且 死因已有代码对策 = 0 并且 这个死因的可选对策数 ≥ 2 并且 离上次为这个死因问秒数 ≥ 3600</t>
         </is>
       </c>
       <c r="H115" s="7" t="inlineStr">
@@ -5296,35 +5311,35 @@
       </c>
       <c r="I115" s="7" t="inlineStr">
         <is>
-          <t>以下情况由代码直接处理，不问模型：缺材料 → 先做前置（前置能开工时），否则暂停；找不到/走不到 → 换地方（有备选地点时），否则暂停；背包满 → 先跑 A-T9 腾格子再重试，这一次不计失败；被打断 → 不计数。问模型时带什么:按 C-CTX-1 的「T3 配方」,六样用完整版,从上到下:家里人(另外两人各一行,会做前置那件活的标出来)→ 家里箱子(大箱子、粮箱各一行)→ 身上的东西 → 大目标只留这件所属的一行 → 这个小目标和它的前置(最多 3 行:短名、还差多少、谁在做)→ 刚做完的事(6 件)→ 冷却/暂停中 → 我现在 → 连败原文(3 次失败的原话,每条 ≤40 字,带几分钟前)→ 这次要你决定 → 选项:按位置连续用 A、B、C… 标,每行写明是哪种对策 —— 换地方(写明去哪个登记地点、多远)、先做前置(写明哪件、还差多少)、换这个小目标下另一条没在冷却的脚本(每条一行)、暂停 30 分钟(永远是最后一行)→ 怎么回答 {选:B, why:…}。总长 ≤1900 字;只收选项里的字母;超时 12 秒或答非所问就选最后一行(暂停 30 分钟)。先做前置或换脚本时,原来这件小目标保留进度,前置做完(或放弃)就接着做原来这件。暂停 = 自动暂停 30 分钟。同一个小目标 30 分钟内又连败 3 次，直接暂停。24 小时内被自动暂停 ≥3 次，就不再自动恢复，后台标红给 Owner 看（说明这条做法本身不行，该改表）。🔴 Owner 在后台手动设的「3 暂停」，代码永远不动。这条取代现在的「放下 + 冷却 2~3 分钟」，那套实测每 13 秒一轮，一直转到天亮。C-THK-8 里的 A/B/C 只是对策的名字,给模型看时一律按位置重新标字母。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
+          <t>实测夜里真实死亡约 30 次/小时，原稿的「30 分钟内同因 ≥2 次」几乎永远成立，再配上每种死因 60 分钟冷却，就成了每小时定时问一次。所以加了两道门：「两次都在做同一个小目标」和「代码没有定论」。模型的选项按位置标字母：A 自动暂停到天亮或 30 分钟（写运行文件，不写状态 3，永远是 A）；B 前置小目标插队（能做时才列；原来那件保留进度，前置做完接着做）；最后一行是「不改」。原稿的 A/B/D 缺了 C，小模型容易答出不存在的 C，已改成连续字母。超时 12 秒或答非所问就选 A。🔴 原稿要把淹死、岩浆的死亡点周围记成危险地点，这和 Owner 说过的「死过的地方也不一定要绕开」冲突。所以岩浆只记那几格岩浆本身（反射层本来就扫岩浆）；淹死是游泳自救失灵的问题，不标记区域。latest.log 会漏记死亡 5~10 倍，只能用机器人收到的服务器广播。麦娘、麦豆没有 sleep 和 fight，暂停到天亮时只能回家待着。服务器的 playersSleepingPercentage 没有核实过，有真人在线时，机器人睡觉未必能跳过夜晚。问模型时带什么:按 C-CTX-1 的「T8 配方」,六样用完整版,从上到下:家里人(另外两人各一行;标出谁会做剑)→ 身上的东西(武器、盔甲、吃的、挡箭用的泥土圆石写在最前)→ 大目标只留这件所属的一行 → 这个小目标和它的前置(最多 3 行)→ 刚做完的事(6 件)→ 冷却/暂停中 → 我现在 → 这两次死亡(每次:几分钟前、死因原话 ≤30 字、当时白天还是夜里、在哪一片、身上有没有剑;后两项要先按 C-CTX-3 让 C-DAT-3 记下来,现在没记)→ 这次要你决定 → 选项 → 怎么回答 {选:A, why:…}。总长 ≤1800 字。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>同一档（大目标和小目标的优先级都相同）里有两件以上能开工、而且其中有还没排过先后的小目标时，才问一次模型把这一档排个先后。之后照这个顺序一件件干，名单里不出现新面孔就不再问。</t>
+          <t>同一个小目标连着失败 3 次时，先由代码按失败原因处理：缺材料就先做它的前置，找不到或走不到就换一个记得的地方，背包满就先腾格子，都不行就自动暂停 30 分钟。只有失败原因代码认不出、又有两条以上出路时，才问模型选。</t>
         </is>
       </c>
       <c r="D116" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E116" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>J-T1-1, think_goal_order, think_pick_task</t>
+          <t>J-T1-2</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>手上有小目标 = 0 并且 最高档候选数 ≥ 2 并且 最高档没排过序的候选数 ≥ 1 并且 离上次T1秒数 ≥ 60</t>
+          <t>本小目标连败次数 ≥ 3 并且 失败原因已归类 = 0 并且 可选对策数 ≥ 2 并且 离上次为这个小目标问秒数 ≥ 1800</t>
         </is>
       </c>
       <c r="H116" s="7" t="inlineStr">
@@ -5334,73 +5349,73 @@
       </c>
       <c r="I116" s="7" t="inlineStr">
         <is>
-          <t>这条取代 nextFromTask 4044 行的「候选多于 1 个就问 pickScript」。现在不管优先级是否相同都会问，违反 Owner「优先级一样时才由 AI 选」。Owner 样板里 G1/G2/G3 的优先级都是 0，一开局就会出现同档。问模型时带什么:按 C-CTX-1 的「T1 配方」,11 块全带(Owner 第②句点名的六样都用完整版),从上到下:家里人(另外两人各一行:在不在线、血和饱食度、在哪一片、在做哪个小目标第几步、身上几份吃的、缺什么、有没有人在帮)→ 家里箱子(大箱子、粮箱各一行,各最多 8 样,注明几分钟前看的)→ 身上的东西(空格数、工具带剩余耐久、吃的几份、其余最多 12 样)→ 大目标(每个一行:编号、短名、状态、优先级、还差多少)→ 小目标(这一档候选所属大目标下的,加上家人正在做的,最多 8 行:编号、短名、状态、优先级、谁在做、还差多少、开不了工的原因)→ 刚做完的事(最近 6 件,旧的在上新的在下:成没成、为什么、多久前、用了多久;再加一行最近 30 分钟死了几次、逃了几次、被打断几次)→ 冷却/暂停中(最多 4 行)→ 我现在(血、饱食度、在哪一片、离家几格、白天还是夜里、离天黑几分钟、8 格内几只怪)→ 这次要你决定(这一档有 N 件能开工,排个先后)→ 选项(按位置连续标 A~F,每行贴上属于哪个大目标、还差多少、上次做这件的结果)→ 怎么回答。总长 ≤2200 字,超了按 C-CTX-1 第五条的顺序砍,最多砍到六样底包那一档;选项、我现在、回答格式永远不砍。这一档超过 6 件时只列表里顺序前 6 件,没列的按表里顺序接在模型给的顺序后面、一起记进 order,不为它们再问。模型只回 {顺序:[B,A,C], why:不超过20字};代码认选项字母,也认原样照抄、且只对得上一个选项的小目标编号,重复的去掉、名单外的丢掉,漏掉的按表里顺序补在后面。超时：主脑 12 秒，降级时 20 秒。问不到、超时或答非所问，就按表里顺序，履历记「模型没答，按表顺序」。等回答时反射层和硬规则照常跑。「同时进行」指不同家人各做一件；一个人一次只做一件。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
+          <t>以下情况由代码直接处理，不问模型：缺材料 → 先做前置（前置能开工时），否则暂停；找不到/走不到 → 换地方（有备选地点时），否则暂停；背包满 → 先跑 A-T9 腾格子再重试，这一次不计失败；被打断 → 不计数。问模型时带什么:按 C-CTX-1 的「T3 配方」,六样用完整版,从上到下:家里人(另外两人各一行,会做前置那件活的标出来)→ 家里箱子(大箱子、粮箱各一行)→ 身上的东西 → 大目标只留这件所属的一行 → 这个小目标和它的前置(最多 3 行:短名、还差多少、谁在做)→ 刚做完的事(6 件)→ 冷却/暂停中 → 我现在 → 连败原文(3 次失败的原话,每条 ≤40 字,带几分钟前)→ 这次要你决定 → 选项:按位置连续用 A、B、C… 标,每行写明是哪种对策 —— 换地方(写明去哪个登记地点、多远)、先做前置(写明哪件、还差多少)、换这个小目标下另一条没在冷却的脚本(每条一行)、暂停 30 分钟(永远是最后一行)→ 怎么回答 {选:B, why:…}。总长 ≤1900 字;只收选项里的字母;超时 12 秒或答非所问就选最后一行(暂停 30 分钟)。先做前置或换脚本时,原来这件小目标保留进度,前置做完(或放弃)就接着做原来这件。暂停 = 自动暂停 30 分钟。同一个小目标 30 分钟内又连败 3 次，直接暂停。24 小时内被自动暂停 ≥3 次，就不再自动恢复，后台标红给 Owner 看（说明这条做法本身不行，该改表）。🔴 Owner 在后台手动设的「3 暂停」，代码永远不动。这条取代现在的「放下 + 冷却 2~3 分钟」，那套实测每 13 秒一轮，一直转到天亮。C-THK-8 里的 A/B/C 只是对策的名字,给模型看时一律按位置重新标字母。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>家离出生点太近、或旁边有别人的房子时，从小麦沿路记下的合格新家址里挑一块（合格指：平地、远离人、水边能种地、附近有树）。两块以上才问模型，只有一块就直接用。选好的只是「待您确认」，您在后台点同意之前，谁都不搬。</t>
+          <t>同一档（大目标和小目标的优先级都相同）里有两件以上能开工、而且其中有还没排过先后的小目标时，才问一次模型把这一档排个先后。之后照这个顺序一件件干，名单里不出现新面孔就不再问。</t>
         </is>
       </c>
       <c r="D117" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E117" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>find_forest, make_base, think_home_site</t>
+          <t>J-T1-1, think_goal_order, think_pick_task</t>
         </is>
       </c>
       <c r="G117" s="7" t="inlineStr">
         <is>
-          <t>需要搬家 = 1 并且 新家址已定 = 0 并且 候选家址数 ≥ 2 并且 离上次T5秒数 ≥ 600</t>
+          <t>手上有小目标 = 0 并且 最高档候选数 ≥ 2 并且 最高档没排过序的候选数 ≥ 1 并且 离上次T1秒数 ≥ 60</t>
         </is>
       </c>
       <c r="H117" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
       <c r="I117" s="7" t="inlineStr">
         <is>
-          <t>0 块候选时：派小麦往离出生点更远、没去过的方向 explore（方向由代码定），不问模型。只有 1 块时：直接写成待批。问模型时带什么:按 C-CTX-1 的「T5 配方」:六样底包 → 大目标补上 G3、G4 两行 → 现在的家为什么要搬(离出生点几格、32 格内有几块别人的方块)→ 这次要你决定 → 选项(最多 6 块候选地,按代码打分从高到低标 A~F:在家的哪个方向多远、离出生点、离林子、离水各多远、平地多大、附近别人方块数、代码打分)→ 怎么回答 {选:A, why:…}。总长 ≤1300 字;只收选项里的字母。问不到或超时 25 秒：选 A（代码打分最高的一块）。到了现场复查不合格，就把那块删掉，剩 ≥2 块才再问，两次至少隔 10 分钟。耕地必须在水平 4 格以内、和水同高或低一格才算湿润，否则会退回泥土、作物也长得慢；现在没有水桶和放方块的动作，只能选天然水边。作物要光照（露天白天就够）。🔴 不圈地：新家没有领地保护。⚠️ BlueMap 是公开的（已取消密码），默认还显示在线玩家的位置；离人远只能减少路过的人，挡不住专门来找的人，这一点要让 Owner 知道。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
+          <t>这条取代 nextFromTask 4044 行的「候选多于 1 个就问 pickScript」。现在不管优先级是否相同都会问，违反 Owner「优先级一样时才由 AI 选」。Owner 样板里 G1/G2/G3 的优先级都是 0，一开局就会出现同档。问模型时带什么:按 C-CTX-1 的「T1 配方」,11 块全带(Owner 第②句点名的六样都用完整版),从上到下:家里人(另外两人各一行:在不在线、血和饱食度、在哪一片、在做哪个小目标第几步、身上几份吃的、缺什么、有没有人在帮)→ 家里箱子(大箱子、粮箱各一行,各最多 8 样,注明几分钟前看的)→ 身上的东西(空格数、工具带剩余耐久、吃的几份、其余最多 12 样)→ 大目标(每个一行:编号、短名、状态、优先级、还差多少)→ 小目标(这一档候选所属大目标下的,加上家人正在做的,最多 8 行:编号、短名、状态、优先级、谁在做、还差多少、开不了工的原因)→ 刚做完的事(最近 6 件,旧的在上新的在下:成没成、为什么、多久前、用了多久;再加一行最近 30 分钟死了几次、逃了几次、被打断几次)→ 冷却/暂停中(最多 4 行)→ 我现在(血、饱食度、在哪一片、离家几格、白天还是夜里、离天黑几分钟、8 格内几只怪)→ 这次要你决定(这一档有 N 件能开工,排个先后)→ 选项(按位置连续标 A~F,每行贴上属于哪个大目标、还差多少、上次做这件的结果)→ 怎么回答。总长 ≤2200 字,超了按 C-CTX-1 第五条的顺序砍,最多砍到六样底包那一档;选项、我现在、回答格式永远不砍。这一档超过 6 件时只列表里顺序前 6 件,没列的按表里顺序接在模型给的顺序后面、一起记进 order,不为它们再问。模型只回 {顺序:[B,A,C], why:不超过20字};代码认选项字母,也认原样照抄、且只对得上一个选项的小目标编号,重复的去掉、名单外的丢掉,漏掉的按表里顺序补在后面。超时：主脑 12 秒，降级时 20 秒。问不到、超时或答非所问，就按表里顺序，履历记「模型没答，按表顺序」。等回答时反射层和硬规则照常跑。「同时进行」指不同家人各做一件；一个人一次只做一件。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>新家址经您同意、还没定房子样式、而且库存够凑出两种以上木头搭配时，问一次模型挑木头搭配（墙、柱子、屋顶各用哪种木头）和门朝哪；大小、平顶、木半砖地面都按 G3 定死（9×9 外框，屋里 7×7），不在选项里。只有一种搭配够就由代码直接定（J-G3-0a）。泥土不在选项里，房子一定带门。</t>
+          <t>家离出生点太近、或旁边有别人的房子时，从小麦沿路记下的合格新家址里挑一块（合格指：平地、远离人、水边能种地、附近有树）。两块以上才问模型，只有一块就直接用。选好的只是「待您确认」，您在后台点同意之前，谁都不搬。</t>
         </is>
       </c>
       <c r="D118" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E118" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F118" s="7" t="inlineStr">
         <is>
-          <t>build_house, get_build_mats, son_take_mats, think_house_design</t>
+          <t>find_forest, make_base, think_home_site</t>
         </is>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
-          <t>新家址已批 = 1 并且 新房设计已定 = 0 并且 合格木种组合数 ≥ 2</t>
+          <t>需要搬家 = 1 并且 新家址已定 = 0 并且 候选家址数 ≥ 2 并且 离上次T5秒数 ≥ 600</t>
         </is>
       </c>
       <c r="H118" s="7" t="inlineStr">
@@ -5410,43 +5425,81 @@
       </c>
       <c r="I118" s="7" t="inlineStr">
         <is>
-          <t>大小以 G3 为准：9×9 外框、屋里 7×7、墙高 3、平顶、木半砖地面；用量以 M3-2 为准：木板 163 块（墙 82 + 屋顶 81）、柱子原木 12 根、木半砖 49 块、门 1 扇，结构合计约 196 块木板（49 根原木）另加 12 根柱子原木。原稿这里的 7×7/9×7 两种尺寸、平顶/台阶边两种屋顶和「能住下全家的最小尺寸」和 G3、M3-2 对不上，已删掉。触发改读 C-BLD-9R「合格木种组合数」，和 J-G3-0a（=1 时代码直接定）是同一个函数。库存（M3-2 记的）：橡木 232 根什么搭配都够；樱花 83 根够墙加屋顶；桦木 28 根（112 块木板）只够墙或屋顶其中一样。床 = 3 块同色羊毛 + 3 块任意木板；打一只没剪过毛的羊掉 1 块羊毛，3 张床要 9 只羊。hunt 必须避开栅栏里、有名字、在别人建筑旁边的羊（孩子们养的）。🔴 门必须有：床周围水平 8 格、上下 5 格内有敌对怪就睡不了觉，门洞敞着，夜里怪会进屋。旧泥土房没有拆除动作（没有 mine/dig），会留在原地，拆不拆等 Owner 定（M3-9）。这条取代 actBuildHouse（3332 行）里直接调用 designHouse。问模型时带什么:按 C-CTX-1 的「T4 配方」,这是按性格挑样式的地方,系统段必须带人设。用户段:六样底包 → 木料(家里箱子和身上的原木、木板,按木种合计,注明箱子几分钟前看的)→ 家里几口人、要放几张床 → 新家址(平地多大、林子在哪个方向、水在哪个方向、门能朝哪几个方向)→ 这次要你决定 → 选项(C-BLD-9R 列出的最多 6 种凑得够的搭配,按位置标 A~F:墙、柱子、屋顶各用什么木头、要多少、现有多少;代码先列三处同一种木头的,再列混搭的,同类里按用完后剩下的原木从多到少排)→ 怎么回答 {选:B, 门:南, why:…},门只收新家址里列出的方向,不合法就用兜底的门朝向。总长 ≤1500 字。问不到或超时 25 秒的兜底：选 A（代码排第 1 的搭配）+ 门朝记得的林子（没有就朝南）。一座房子只设计一次；家址变了，或 Owner 在后台清掉设计，才会再问。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
+          <t>0 块候选时：派小麦往离出生点更远、没去过的方向 explore（方向由代码定），不问模型。只有 1 块时：直接写成待批。问模型时带什么:按 C-CTX-1 的「T5 配方」:六样底包 → 大目标补上 G3、G4 两行 → 现在的家为什么要搬(离出生点几格、32 格内有几块别人的方块)→ 这次要你决定 → 选项(最多 6 块候选地,按代码打分从高到低标 A~F:在家的哪个方向多远、离出生点、离林子、离水各多远、平地多大、附近别人方块数、代码打分)→ 怎么回答 {选:A, why:…}。总长 ≤1300 字;只收选项里的字母。问不到或超时 25 秒：选 A（代码打分最高的一块）。到了现场复查不合格，就把那块删掉，剩 ≥2 块才再问，两次至少隔 10 分钟。耕地必须在水平 4 格以内、和水同高或低一格才算湿润，否则会退回泥土、作物也长得慢；现在没有水桶和放方块的动作，只能选天然水边。作物要光照（露天白天就够）。🔴 不圈地：新家没有领地保护。⚠️ BlueMap 是公开的（已取消密码），默认还显示在线玩家的位置；离人远只能减少路过的人，挡不住专门来找的人，这一点要让 Owner 知道。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>T0</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>平时（没有任何一条思考触发成立时）机器人只跑代码，照着目标表一件件干，一次模型都不问。某个人一件能开工的小目标都没有，本身就说明目标表有漏洞——只有打完末影龙的大结局才该出现。这时代码当场在后台记一条「目标表缺口」：是谁、什么时候、他名下每一条小目标为什么做不了（差哪个数、在等哪条、被您暂停、还是他根本没有这个本事），连同他自己的血和饱食度、身上带着什么、刚做完的几件事、家里另外两人在干什么缺什么。只是在等庄稼长熟、等天亮这类很快会自己解开的，记成「在等」。记完不问模型、不在公屏说话，由代码兜底：天黑就回家；先回家把箱子打开核对一次（箱子里的数记旧了，也会把能干的活误判成不能干）；小麦缺的是「没找到林子/没见过动物」就出去找一圈，否则回家把东西存好；麦娘把小麦做成面包、把东西存好；麦豆在家门口离人远的地方玩。一有能开工的小目标，马上回去干。等您拍板、缺本事、表里没下一步这几类当场标红；「在等」持续 30 分钟也标红「该补表了」；打完龙的大结局不标红。</t>
+          <t>新家址经您同意、还没定房子样式、而且库存够凑出两种以上木头搭配时，问一次模型挑木头搭配（墙、柱子、屋顶各用哪种木头）和门朝哪；大小、平顶、木半砖地面都按 G3 定死（9×9 外框，屋里 7×7），不在选项里。只有一种搭配够就由代码直接定（J-G3-0a）。泥土不在选项里，房子一定带门。</t>
         </is>
       </c>
       <c r="D119" s="7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E119" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
+          <t>build_house, get_build_mats, son_take_mats, think_house_design</t>
+        </is>
+      </c>
+      <c r="G119" s="7" t="inlineStr">
+        <is>
+          <t>新家址已批 = 1 并且 新房设计已定 = 0 并且 合格木种组合数 ≥ 2</t>
+        </is>
+      </c>
+      <c r="H119" s="7" t="inlineStr">
+        <is>
+          <t>判据动作都缺</t>
+        </is>
+      </c>
+      <c r="I119" s="7" t="inlineStr">
+        <is>
+          <t>大小以 G3 为准：9×9 外框、屋里 7×7、墙高 3、平顶、木半砖地面；用量以 M3-2 为准：木板 163 块（墙 82 + 屋顶 81）、柱子原木 12 根、木半砖 49 块、门 1 扇，结构合计约 196 块木板（49 根原木）另加 12 根柱子原木。原稿这里的 7×7/9×7 两种尺寸、平顶/台阶边两种屋顶和「能住下全家的最小尺寸」和 G3、M3-2 对不上，已删掉。触发改读 C-BLD-9R「合格木种组合数」，和 J-G3-0a（=1 时代码直接定）是同一个函数。库存（M3-2 记的）：橡木 232 根什么搭配都够；樱花 83 根够墙加屋顶；桦木 28 根（112 块木板）只够墙或屋顶其中一样。床 = 3 块同色羊毛 + 3 块任意木板；打一只没剪过毛的羊掉 1 块羊毛，3 张床要 9 只羊。hunt 必须避开栅栏里、有名字、在别人建筑旁边的羊（孩子们养的）。🔴 门必须有：床周围水平 8 格、上下 5 格内有敌对怪就睡不了觉，门洞敞着，夜里怪会进屋。旧泥土房没有拆除动作（没有 mine/dig），会留在原地，拆不拆等 Owner 定（M3-9）。这条取代 actBuildHouse（3332 行）里直接调用 designHouse。问模型时带什么:按 C-CTX-1 的「T4 配方」,这是按性格挑样式的地方,系统段必须带人设。用户段:六样底包 → 木料(家里箱子和身上的原木、木板,按木种合计,注明箱子几分钟前看的)→ 家里几口人、要放几张床 → 新家址(平地多大、林子在哪个方向、水在哪个方向、门能朝哪几个方向)→ 这次要你决定 → 选项(C-BLD-9R 列出的最多 6 种凑得够的搭配,按位置标 A~F:墙、柱子、屋顶各用什么木头、要多少、现有多少;代码先列三处同一种木头的,再列混搭的,同类里按用完后剩下的原木从多到少排)→ 怎么回答 {选:B, 门:南, why:…},门只收新家址里列出的方向,不合法就用兜底的门朝向。总长 ≤1500 字。问不到或超时 25 秒的兜底：选 A（代码排第 1 的搭配）+ 门朝记得的林子（没有就朝南）。一座房子只设计一次；家址变了，或 Owner 在后台清掉设计，才会再问。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="inlineStr">
+        <is>
+          <t>平时（没有任何一条思考触发成立时）机器人只跑代码，照着目标表一件件干，一次模型都不问。某个人一件能开工的小目标都没有，本身就说明目标表有漏洞——只有打完末影龙的大结局才该出现。这时代码当场在后台记一条「目标表缺口」：是谁、什么时候、他名下每一条小目标为什么做不了（差哪个数、在等哪条、被您暂停、还是他根本没有这个本事），连同他自己的血和饱食度、身上带着什么、刚做完的几件事、家里另外两人在干什么缺什么。只是在等庄稼长熟、等天亮这类很快会自己解开的，记成「在等」。记完不问模型、不在公屏说话，由代码兜底：天黑就回家；先回家把箱子打开核对一次（箱子里的数记旧了，也会把能干的活误判成不能干）；小麦缺的是「没找到林子/没见过动物」就出去找一圈，否则回家把东西存好；麦娘把小麦做成面包、把东西存好；麦豆在家门口离人远的地方玩。一有能开工的小目标，马上回去干。等您拍板、缺本事、表里没下一步这几类当场标红；「在等」持续 30 分钟也标红「该补表了」；打完龙的大结局不标红。</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E120" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F120" s="7" t="inlineStr">
+        <is>
           <t>J-T0-1, J-T0-2, J-T0-3, find_forest</t>
         </is>
       </c>
-      <c r="G119" s="7" t="inlineStr">
+      <c r="G120" s="7" t="inlineStr">
         <is>
           <t>任何思考触发成立 = 0</t>
         </is>
       </c>
-      <c r="H119" s="7" t="inlineStr">
+      <c r="H120" s="7" t="inlineStr">
         <is>
           <t>判据动作都缺</t>
         </is>
       </c>
-      <c r="I119" s="7" t="inlineStr">
+      <c r="I120" s="7" t="inlineStr">
         <is>
           <t>已只读核对服务器上的 ~/mcbot/bot.real.js。问模型的地方共 6 处：decide（3962 行 TASK_MODE=0 分支、4013 行零候选分支）；pickScript（4044 行，候选多于 1 个就问，不看是不是同一档）；plan（7523 行，planLoop 每 1 秒一次）；designHouse（3332 行）；chat（8204 行）。makeTask/reviewTask 在第 23 行被导入，但全文件没有调用。反射层 reflexTick 每秒跑一次纯代码，不受影响。小目标的 done_when 一成立，就按表拿下一个；紧急事件先处理，但不动进度指针。🔴 Owner 2026-09-18 定性：「一直没有事情做」只该出现在打完末影龙的大结局，零候选是目标表的漏洞，不是交给模型去救的正常状态。4013 行零候选时每 2.5 秒调一次 decide() 的分支删掉（C-THK-1），换成缺口记录（C-ENG-21）+ 纯代码兜底；THINK_MODE 开不开，这里都不问模型、不往公屏说话。缺口记录只给您在后台看，不给模型：开始时记一条，结束时补写持续多久、兜底做了什么；同一组原因 10 分钟内只加次数。内容按您点名的六样：大目标（每个的状态和优先级）；小目标（他名下每条为什么被跳过：已完成 / 您设了暂停 / 前置没完成（哪条、卡在谁手里）/ 开工条件不成立（哪个判据、现在的值和门槛）/ 自动暂停到几点 / 冷却还剩几秒 / 执行闸缺哪个动作 / 家人已认领）；刚做完的 6 件事；自己的状态（血、饱食度、在哪个世界哪一片、天色、离天黑几分钟）；身上的东西（背包摘要）；家里人（另外两人在不在线、在做哪个小目标、身上几份吃的、缺什么）。另加「死大目标」：没完成、没暂停，但全家没有一条它下面的小目标能开工。拼装函数和问模型的上下文包共用同一个（第②路的 C-CTX-1），只是不截短。缺口分五类：① 在等（只被天黑、庄稼没熟、冷却、自动暂停、今天资源世界次数、等家人做出来这类会自己变的条件挡住）；② 等您拍板；③ 缺本事（执行闸没放行、动作还没做）；④ 表里没下一步；⑤ 大结局（G8 已完成并锁住）。②③④ 满 1 分钟、① 满 30 分钟，后台标红「该补表了」；⑤ 永不标红。兜底顺序（每一步做完都重算候选，一有候选立刻回去干活）：① 天黑了 → 交给 A11（只在主世界触发：回家睡或回屋待着）；② 开箱快照超过 600 秒 → 回家开箱核对（只看不拿，C-ITM-24），核对完先重算一次；③ 白天、「卡在找得到就能解开的原因」= 1（C-THK-10）、自己有 explore（现在只有小麦）→ find_forest 出去找一圈；④ 按角色跑 J-T0-1（小麦：回家存东西、等 1 分钟）/ J-T0-2（麦娘：做面包、存东西）/ J-T0-3（麦豆：家门口离真人远的地方玩）。🔴 兜底只做安全、可撤回的事：不提前合成（合成不可逆，会吃掉别处要的料），不出远门，不问模型。晚上不出门：夜里待在外面，正是以前家门口扎堆死亡的原因。另有两条引擎规则专门减少假缺口：前置按「完成过」算（C-ENG-22），打完龙以后 G8 锁住（C-ENG-23）。</t>
         </is>
@@ -5463,7 +5516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G157"/>
+  <dimension ref="A1:G159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6489,7 +6542,7 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>小麦把贴脸的普通近战怪打掉(怪不多、不在水里、不是刚复活、怪没着火)</t>
+          <t>按规矩把贴脸的普通怪打掉(三人共用)</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -6499,7 +6552,7 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -6563,7 +6616,7 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>还在挨打,或刚复活就被怪贴脸:传送脱险(在家门口就去出生点)</t>
+          <t>还在挨打,或刚复活就被怪贴脸:传送脱险(小麦、麦娘在家门口就去出生点;麦豆不去出生点,在家附近躲)</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
@@ -6600,7 +6653,7 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>其余情况(麦豆、没剑的麦娘、在水里、怪太多、强怪、嘎枝、着火的僵尸):跑开</t>
+          <t>其余情况一律跑:没剑、血 &lt;14(已在打的 ≤10)、怪 &gt;2 只、有苦力怕、在水里、刚复活、不是普通怪、旁边有人或宠物</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
@@ -9544,23 +9597,23 @@
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>J-M5-5</t>
+          <t>J-M7-3</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>做 3 把备用木剑放进箱子</t>
+          <t>麦豆跟着爸爸砍树</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>M5-5</t>
+          <t>M7-3</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr"/>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>take_from_chest(oak_planks×6、stick×3) → craft(wooden_sword×3) → store_items</t>
+          <t>follow_player(小麦) → gather_wood → store_items</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr">
@@ -9570,19 +9623,19 @@
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>现在就能做</t>
+          <t>缺动作</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>J-M7-3</t>
+          <t>J-M7-3c</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>麦豆跟着爸爸砍树</t>
+          <t>麦豆在家附近砍树(只砍看得见的树,不去远处林子;离家 40 格内,照抄 child_play 的范围)</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
@@ -9590,10 +9643,14 @@
           <t>M7-3</t>
         </is>
       </c>
-      <c r="D116" s="7" t="inlineStr"/>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>麦豆</t>
+        </is>
+      </c>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>follow_player(小麦) → gather_wood → store_items</t>
+          <t>gather_wood</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr">
@@ -9603,19 +9660,19 @@
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>缺动作</t>
+          <t>卡在代码</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>J-M7-3c</t>
+          <t>J-M7-3d</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>麦豆在家附近砍树(只砍看得见的树,不去远处林子;离家 40 格内,照抄 child_play 的范围)</t>
+          <t>麦豆身上有木头就回家存进箱子(照抄 wife_store;箱子满了被忘掉时「有箱子」变 0,不会反复空跑)</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
@@ -9630,7 +9687,7 @@
       </c>
       <c r="E117" s="7" t="inlineStr">
         <is>
-          <t>gather_wood</t>
+          <t>go_home → store_items</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr">
@@ -9640,34 +9697,30 @@
       </c>
       <c r="G117" s="7" t="inlineStr">
         <is>
-          <t>卡在代码</t>
+          <t>要放行动作</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>J-M7-3d</t>
+          <t>J-M7-4</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t>麦豆身上有木头就回家存进箱子(照抄 wife_store;箱子满了被忘掉时「有箱子」变 0,不会反复空跑)</t>
+          <t>没被点名时离真人太近就回家</t>
         </is>
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>M7-3</t>
-        </is>
-      </c>
-      <c r="D118" s="7" t="inlineStr">
-        <is>
-          <t>麦豆</t>
-        </is>
-      </c>
+          <t>M7-4</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr"/>
       <c r="E118" s="7" t="inlineStr">
         <is>
-          <t>go_home → store_items</t>
+          <t>go_home</t>
         </is>
       </c>
       <c r="F118" s="7" t="inlineStr">
@@ -9677,30 +9730,34 @@
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
-          <t>要放行动作</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>J-M7-4</t>
+          <t>J-M7-5</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>没被点名时离真人太近就回家</t>
+          <t>走到正在干活的家人旁边 4~8 格处，待着看。</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>M7-4</t>
-        </is>
-      </c>
-      <c r="D119" s="7" t="inlineStr"/>
+          <t>M7-5</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t>麦豆</t>
+        </is>
+      </c>
       <c r="E119" s="7" t="inlineStr">
         <is>
-          <t>go_home</t>
+          <t>goto_place(地方=家人身边（停在 4~8 格外，不进田里）) → idle(30 秒；跳过条件：离最近在干活的家人距离 ≥ 17)</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">
@@ -9710,34 +9767,34 @@
       </c>
       <c r="G119" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>J-M7-5</t>
+          <t>J-M8-1a</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t>走到正在干活的家人旁边 4~8 格处，待着看。</t>
+          <t>用箱子里现成的铁锭做一把铁镐。</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>M7-5</t>
+          <t>M8-1</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>麦豆</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方=家人身边（停在 4~8 格外，不进田里）) → idle(30 秒；跳过条件：离最近在干活的家人距离 ≥ 17)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=铁锭 3、木棍 2；跳过条件：背包铁锭 ≥ 3) → craft(东西=iron_pickaxe（要工作台）)</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
@@ -9754,12 +9811,12 @@
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>J-M8-1a</t>
+          <t>J-M8-1b</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
-          <t>用箱子里现成的铁锭做一把铁镐。</t>
+          <t>箱子里的铁不够时：用圆石做石镐和熔炉，去资源世界挖 3 块铁矿、就地烧成铁锭，回家做铁镐。</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
@@ -9774,7 +9831,7 @@
       </c>
       <c r="E121" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=铁锭 3、木棍 2；跳过条件：背包铁锭 ≥ 3) → craft(东西=iron_pickaxe（要工作台）)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=圆石 11、木棍 4、原木 4（燃料）、口粮（留底 9；跳过条件：身上吃的 ≥ 6）) → take_from_chest(东西=镐（最好的一把）；跳过条件：背包里最好的镐等级 ≥ 2) → craft(东西=stone_pickaxe；跳过条件：背包里最好的镐等级 ≥ 2) → craft(东西=furnace；跳过条件：身上有熔炉 ≥ 1) → goto_place(地方=资源世界（/res go）) → mine(矿=铁矿，下到 y≈16 开巷道；直到 背包粗铁 ≥ 3 或 25 分钟 或 该回主世界 = 1) → smelt(随身熔炉；粗铁全部，燃料原木；烧完挖回熔炉) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → craft(东西=iron_pickaxe)</t>
         </is>
       </c>
       <c r="F121" s="7" t="inlineStr">
@@ -9791,17 +9848,17 @@
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>J-M8-1b</t>
+          <t>J-M8-2</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t>箱子里的铁不够时：用圆石做石镐和熔炉，去资源世界挖 3 块铁矿、就地烧成铁锭，回家做铁镐。</t>
+          <t>小麦带着熔炉和燃料去资源世界挖铁，挖完就地烧成铁锭，带回家存进大箱子。</t>
         </is>
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>M8-1</t>
+          <t>M8-2</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
@@ -9811,7 +9868,7 @@
       </c>
       <c r="E122" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=圆石 11、木棍 4、原木 4（燃料）、口粮（留底 9；跳过条件：身上吃的 ≥ 6）) → take_from_chest(东西=镐（最好的一把）；跳过条件：背包里最好的镐等级 ≥ 2) → craft(东西=stone_pickaxe；跳过条件：背包里最好的镐等级 ≥ 2) → craft(东西=furnace；跳过条件：身上有熔炉 ≥ 1) → goto_place(地方=资源世界（/res go）) → mine(矿=铁矿，下到 y≈16 开巷道；直到 背包粗铁 ≥ 3 或 25 分钟 或 该回主世界 = 1) → smelt(随身熔炉；粗铁全部，燃料原木；烧完挖回熔炉) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → craft(东西=iron_pickaxe)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=镐（拿最好的一把）；跳过条件：背包里最好的镐等级 ≥ 2) → take_from_chest(东西=口粮（留底 9）；跳过条件：身上吃的 ≥ 6) → take_from_chest(东西=粗铁（全部）；跳过条件：箱子里没有粗铁) → take_from_chest(东西=圆石 8；跳过条件：身上有熔炉 ≥ 1) → craft(东西=furnace；跳过条件：身上有熔炉 ≥ 1) → take_from_chest(东西=原木（当燃料），数量 = 还差的铁锭 ÷ 1.5 向上取整，最多 24 根；跳过条件：身上的原木已经够) → goto_place(地方=资源世界（/res go）) → mine(矿=铁矿，下到 y≈16 开 1×2 巷道；顺手挖煤，看见沙砾就挖到背包燧石 ≥ 1；直到 背包粗铁 ≥ 出发时的还差铁锭 或 背包空格 ≤ 2 或 这一趟 ≥ 25 分钟 或 该回主世界 = 1) → smelt(放下随身熔炉，粗铁全部，燃料先煤后原木；烧完用镐把熔炉挖回来) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(铁锭、煤、燧石进大箱子（镐和熔炉留在身上）)</t>
         </is>
       </c>
       <c r="F122" s="7" t="inlineStr">
@@ -9828,17 +9885,17 @@
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>J-M8-2</t>
+          <t>J-M8-3a</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>小麦带着熔炉和燃料去资源世界挖铁，挖完就地烧成铁锭，带回家存进大箱子。</t>
+          <t>回家把铁锭做成还缺的铁甲、铁剑、盾、桶和打火石，然后穿好。</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>M8-2</t>
+          <t>M8-3</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
@@ -9848,7 +9905,7 @@
       </c>
       <c r="E123" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=镐（拿最好的一把）；跳过条件：背包里最好的镐等级 ≥ 2) → take_from_chest(东西=口粮（留底 9）；跳过条件：身上吃的 ≥ 6) → take_from_chest(东西=粗铁（全部）；跳过条件：箱子里没有粗铁) → take_from_chest(东西=圆石 8；跳过条件：身上有熔炉 ≥ 1) → craft(东西=furnace；跳过条件：身上有熔炉 ≥ 1) → take_from_chest(东西=原木（当燃料），数量 = 还差的铁锭 ÷ 1.5 向上取整，最多 24 根；跳过条件：身上的原木已经够) → goto_place(地方=资源世界（/res go）) → mine(矿=铁矿，下到 y≈16 开 1×2 巷道；顺手挖煤，看见沙砾就挖到背包燧石 ≥ 1；直到 背包粗铁 ≥ 出发时的还差铁锭 或 背包空格 ≤ 2 或 这一趟 ≥ 25 分钟 或 该回主世界 = 1) → smelt(放下随身熔炉，粗铁全部，燃料先煤后原木；烧完用镐把熔炉挖回来) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(铁锭、煤、燧石进大箱子（镐和熔炉留在身上）)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=铁锭（按能做的件现算）、木棍（按件现算）、木板 6（跳过条件：有盾牌 ≥ 1）、燧石 1（跳过条件：有打火石 ≥ 1 或 能拿到的燧石 = 0）) → craft(按缺的做，先 iron_sword、shield，再 iron_chestplate、iron_leggings、iron_helmet、iron_boots、bucket、flint_and_steel；已有的、料不够的跳过) → wear_armor(平时穿法：四件最好的护甲 + 副手盾)</t>
         </is>
       </c>
       <c r="F123" s="7" t="inlineStr">
@@ -9865,12 +9922,12 @@
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>J-M8-3a</t>
+          <t>J-M8-3b</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t>回家把铁锭做成还缺的铁甲、铁剑、盾、桶和打火石，然后穿好。</t>
+          <t>缺燧石做打火石时，去资源世界挖沙砾拿燧石。</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
@@ -9885,7 +9942,7 @@
       </c>
       <c r="E124" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=铁锭（按能做的件现算）、木棍（按件现算）、木板 6（跳过条件：有盾牌 ≥ 1）、燧石 1（跳过条件：有打火石 ≥ 1 或 能拿到的燧石 = 0）) → craft(按缺的做，先 iron_sword、shield，再 iron_chestplate、iron_leggings、iron_helmet、iron_boots、bucket、flint_and_steel；已有的、料不够的跳过) → wear_armor(平时穿法：四件最好的护甲 + 副手盾)</t>
+          <t>goto_place(地方=资源世界（/res go）) → mine(方块=沙砾；直到 背包燧石 ≥ 2 或 15 分钟 或 该回主世界 = 1) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(燧石进大箱子)</t>
         </is>
       </c>
       <c r="F124" s="7" t="inlineStr">
@@ -9902,12 +9959,12 @@
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>J-M8-3b</t>
+          <t>J-M8-3c</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>缺燧石做打火石时，去资源世界挖沙砾拿燧石。</t>
+          <t>拿个空桶，去附近天然的河或湖装一桶水带在身上。</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
@@ -9922,7 +9979,7 @@
       </c>
       <c r="E125" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方=资源世界（/res go）) → mine(方块=沙砾；直到 背包燧石 ≥ 2 或 15 分钟 或 该回主世界 = 1) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(燧石进大箱子)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8 或 身上空桶 ≥ 1) → take_from_chest(东西=桶；跳过条件：身上空桶 ≥ 1) → goto_place(地方=水源（只认 C-FRM-25 认可的天然水）) → fill_bucket</t>
         </is>
       </c>
       <c r="F125" s="7" t="inlineStr">
@@ -9939,17 +9996,17 @@
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>J-M8-3c</t>
+          <t>J-M8-4a</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>拿个空桶，去附近天然的河或湖装一桶水带在身上。</t>
+          <t>您同意的话，用箱子里的 3 颗钻石直接做钻石镐。</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>M8-3</t>
+          <t>M8-4</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
@@ -9959,7 +10016,7 @@
       </c>
       <c r="E126" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8 或 身上空桶 ≥ 1) → take_from_chest(东西=桶；跳过条件：身上空桶 ≥ 1) → goto_place(地方=水源（只认 C-FRM-25 认可的天然水）) → fill_bucket</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=钻石 3、木棍 2) → craft(东西=diamond_pickaxe（要工作台）)</t>
         </is>
       </c>
       <c r="F126" s="7" t="inlineStr">
@@ -9976,12 +10033,12 @@
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>J-M8-4a</t>
+          <t>J-M8-4b</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>您同意的话，用箱子里的 3 颗钻石直接做钻石镐。</t>
+          <t>不用箱子里的钻石时，穿上铁甲、带上水桶，去资源世界最深处挖 3 颗钻石回来做钻石镐。</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
@@ -9996,7 +10053,7 @@
       </c>
       <c r="E127" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=钻石 3、木棍 2) → craft(东西=diamond_pickaxe（要工作台）)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=铁镐；跳过条件：背包里最好的镐等级 ≥ 3) → take_from_chest(东西=口粮（留底 9）；跳过条件：身上吃的 ≥ 8) → wear_armor(平时穿法) → goto_place(地方=资源世界（/res go）) → mine(矿=钻石，y≈−58 开巷道，岩浆安全规则按 C-CRF-22；直到 背包钻石 ≥ 3 或 25 分钟 或 该回主世界 = 1) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → craft(东西=diamond_pickaxe；跳过条件：背包钻石 ≤ 2)</t>
         </is>
       </c>
       <c r="F127" s="7" t="inlineStr">
@@ -10013,17 +10070,17 @@
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>J-M8-4b</t>
+          <t>J-M8-5</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
         <is>
-          <t>不用箱子里的钻石时，穿上铁甲、带上水桶，去资源世界最深处挖 3 颗钻石回来做钻石镐。</t>
+          <t>带着钻石镐和水桶去资源世界找岩浆，浇上水变成黑曜石，挖够 10 块带回家。</t>
         </is>
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>M8-4</t>
+          <t>M8-5</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
@@ -10033,7 +10090,7 @@
       </c>
       <c r="E128" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=铁镐；跳过条件：背包里最好的镐等级 ≥ 3) → take_from_chest(东西=口粮（留底 9）；跳过条件：身上吃的 ≥ 8) → wear_armor(平时穿法) → goto_place(地方=资源世界（/res go）) → mine(矿=钻石，y≈−58 开巷道，岩浆安全规则按 C-CRF-22；直到 背包钻石 ≥ 3 或 25 分钟 或 该回主世界 = 1) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → craft(东西=diamond_pickaxe；跳过条件：背包钻石 ≤ 2)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=钻石镐；跳过条件：背包里最好的镐等级 ≥ 4) → take_from_chest(东西=口粮（留底 9）；跳过条件：身上吃的 ≥ 8) → goto_place(地方=资源世界（/res go）) → explore(找岩浆：先看落点附近地表的岩浆湖，没有就下到 y≈−54 以下的洞穴；跳过条件：看得见岩浆源；最多 10 分钟) → cast_obsidian(直到 黑曜石的家底 ≥ 10（背包里的也算） 或 该回主世界 = 1) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(黑曜石进大箱子)</t>
         </is>
       </c>
       <c r="F128" s="7" t="inlineStr">
@@ -10050,17 +10107,17 @@
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>J-M8-5</t>
+          <t>J-M8-6</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
         <is>
-          <t>带着钻石镐和水桶去资源世界找岩浆，浇上水变成黑曜石，挖够 10 块带回家。</t>
+          <t>拿上 10 块黑曜石，走到您批准的位置，砌好传送门框并点着。</t>
         </is>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>M8-5</t>
+          <t>M8-6</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
@@ -10070,7 +10127,7 @@
       </c>
       <c r="E129" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=钻石镐；跳过条件：背包里最好的镐等级 ≥ 4) → take_from_chest(东西=口粮（留底 9）；跳过条件：身上吃的 ≥ 8) → goto_place(地方=资源世界（/res go）) → explore(找岩浆：先看落点附近地表的岩浆湖，没有就下到 y≈−54 以下的洞穴；跳过条件：看得见岩浆源；最多 10 分钟) → cast_obsidian(直到 黑曜石的家底 ≥ 10（背包里的也算） 或 该回主世界 = 1) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(黑曜石进大箱子)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=黑曜石（缺几块拿几块）、打火石（跳过条件：身上有）) → goto_place(地方=传送门位置) → build_portal(只补缺的格子，每块记进自家方块登记；用打火石点着，回读有紫色的门方块才算成)</t>
         </is>
       </c>
       <c r="F129" s="7" t="inlineStr">
@@ -10087,17 +10144,17 @@
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>J-M8-6</t>
+          <t>J-M8-8a</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
         <is>
-          <t>拿上 10 块黑曜石，走到您批准的位置，砌好传送门框并点着。</t>
+          <t>去资源世界挖金矿、烧成 5 个金锭，给金头盔备料。</t>
         </is>
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>M8-6</t>
+          <t>M8-8</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
@@ -10107,7 +10164,7 @@
       </c>
       <c r="E130" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=黑曜石（缺几块拿几块）、打火石（跳过条件：身上有）) → goto_place(地方=传送门位置) → build_portal(只补缺的格子，每块记进自家方块登记；用打火石点着，回读有紫色的门方块才算成)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=铁镐或更好；跳过条件：背包里最好的镐等级 ≥ 3) → take_from_chest(东西=口粮（留底 9）；跳过条件：身上吃的 ≥ 6) → take_from_chest(东西=圆石 8；跳过条件：身上有熔炉 ≥ 1) → craft(东西=furnace；跳过条件：身上有熔炉 ≥ 1) → take_from_chest(东西=原木 4（燃料）；跳过条件：身上的原木 ≥ 4) → goto_place(地方=资源世界（/res go）) → mine(矿=金矿，y≈−16 开巷道（恶地地表也行）；直到 背包粗金 + 金的家底 ≥ 5 或 25 分钟 或 该回主世界 = 1) → smelt(随身熔炉，粗金全部；烧完把熔炉挖回来) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(金锭进大箱子)</t>
         </is>
       </c>
       <c r="F130" s="7" t="inlineStr">
@@ -10124,12 +10181,12 @@
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>J-M8-8a</t>
+          <t>J-M8-8b</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
         <is>
-          <t>去资源世界挖金矿、烧成 5 个金锭，给金头盔备料。</t>
+          <t>出发去下界前在家收拾行李：做好金头盔戴上，从粮箱拿够口粮、从大箱子拿 64 块圆石，用不上的东西存掉。</t>
         </is>
       </c>
       <c r="C131" s="7" t="inlineStr">
@@ -10144,7 +10201,7 @@
       </c>
       <c r="E131" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=铁镐或更好；跳过条件：背包里最好的镐等级 ≥ 3) → take_from_chest(东西=口粮（留底 9）；跳过条件：身上吃的 ≥ 6) → take_from_chest(东西=圆石 8；跳过条件：身上有熔炉 ≥ 1) → craft(东西=furnace；跳过条件：身上有熔炉 ≥ 1) → take_from_chest(东西=原木 4（燃料）；跳过条件：身上的原木 ≥ 4) → goto_place(地方=资源世界（/res go）) → mine(矿=金矿，y≈−16 开巷道（恶地地表也行）；直到 背包粗金 + 金的家底 ≥ 5 或 25 分钟 或 该回主世界 = 1) → smelt(随身熔炉，粗金全部；烧完把熔炉挖回来) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(金锭进大箱子)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=金锭 5；跳过条件：穿着金护甲件数 ≥ 1 或 背包金头盔 ≥ 1) → craft(东西=golden_helmet；跳过条件：同上) → wear_armor(下界穿法：金头盔 + 另外三件最好的护甲 + 副手盾) → take_from_chest(东西=口粮，从粮箱拿，留底 9（打开箱子按真数重算）；直到 身上吃的 ≥ 16) → take_from_chest(东西=圆石；直到 身上的圆石 ≥ 64) → store_items(用不上的存掉，行李清单上的留着；直到 背包空格 ≥ 8)</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr">
@@ -10161,17 +10218,17 @@
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>J-M8-8b</t>
+          <t>J-M8-9</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
-          <t>出发去下界前在家收拾行李：做好金头盔戴上，从粮箱拿够口粮、从大箱子拿 64 块圆石，用不上的东西存掉。</t>
+          <t>穿过传送门进下界，朝一个方向一段段找，看到地狱砖城堡就记下位置，然后原路回家。</t>
         </is>
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>M8-8</t>
+          <t>M8-9</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
@@ -10181,7 +10238,7 @@
       </c>
       <c r="E132" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=金锭 5；跳过条件：穿着金护甲件数 ≥ 1 或 背包金头盔 ≥ 1) → craft(东西=golden_helmet；跳过条件：同上) → wear_armor(下界穿法：金头盔 + 另外三件最好的护甲 + 副手盾) → take_from_chest(东西=口粮，从粮箱拿，留底 9（打开箱子按真数重算）；直到 身上吃的 ≥ 16) → take_from_chest(东西=圆石；直到 身上的圆石 ≥ 64) → store_items(用不上的存掉，行李清单上的留着；直到 背包空格 ≥ 8)</t>
+          <t>goto_place(地方=传送门（主世界那一头）；跳过条件：当前维度 = 2（下界）) → wear_armor(下界穿法；跳过条件：穿着金护甲件数 ≥ 1) → use_portal(进下界；跳过条件：当前维度 = 2；第一次过去先核对落点周围 32 格有没有别人的方块，有就原路回来、作废位置、写进后台) → explore(在下界：沿一个方向一段 64 格，离门 ≤ 600 格，避开玄武岩三角洲和堡垒遗迹；直到 记得下界要塞 = 1 或 该返航 = 1) → goto_place(地方=下界那一头的门；跳过条件：当前维度 = 0) → use_portal(回主世界；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → store_items(只存可存的，行李留着)</t>
         </is>
       </c>
       <c r="F132" s="7" t="inlineStr">
@@ -10198,17 +10255,17 @@
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>J-M8-9</t>
+          <t>J-M8-10</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
         <is>
-          <t>穿过传送门进下界，朝一个方向一段段找，看到地狱砖城堡就记下位置，然后原路回家。</t>
+          <t>去下界要塞的烈焰人刷怪笼旁边，举着盾一只只打烈焰人，攒烈焰棒，带回家存进箱子。</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>M8-9</t>
+          <t>M8-10</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
@@ -10218,7 +10275,7 @@
       </c>
       <c r="E133" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方=传送门（主世界那一头）；跳过条件：当前维度 = 2（下界）) → wear_armor(下界穿法；跳过条件：穿着金护甲件数 ≥ 1) → use_portal(进下界；跳过条件：当前维度 = 2；第一次过去先核对落点周围 32 格有没有别人的方块，有就原路回来、作废位置、写进后台) → explore(在下界：沿一个方向一段 64 格，离门 ≤ 600 格，避开玄武岩三角洲和堡垒遗迹；直到 记得下界要塞 = 1 或 该返航 = 1) → goto_place(地方=下界那一头的门；跳过条件：当前维度 = 0) → use_portal(回主世界；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → store_items(只存可存的，行李留着)</t>
+          <t>goto_place(地方=传送门（主世界那一头）；跳过条件：当前维度 = 2) → wear_armor(下界穿法；跳过条件：穿着金护甲件数 ≥ 1) → use_portal(进下界；跳过条件：当前维度 = 2) → goto_place(地方=烈焰人刷怪笼，停在 6~8 格外的走廊) → fight(目标=烈焰人，举盾挡火球，打死后走过去捡；直到 做眼还缺的烈焰棒 = 0（背包里的也算） 或 该返航 = 1) → goto_place(地方=下界那一头的门；跳过条件：当前维度 = 0) → use_portal(回主世界；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → store_items(烈焰棒进大箱子)</t>
         </is>
       </c>
       <c r="F133" s="7" t="inlineStr">
@@ -10235,17 +10292,17 @@
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>J-M8-10</t>
+          <t>J-M8-11</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t>去下界要塞的烈焰人刷怪笼旁边，举着盾一只只打烈焰人，攒烈焰棒，带回家存进箱子。</t>
+          <t>去下界的诡异森林，躲在自己搭的两格高小棚口，一只只打末影人，攒末影珍珠带回家。</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>M8-10</t>
+          <t>M8-11</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
@@ -10255,7 +10312,7 @@
       </c>
       <c r="E134" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方=传送门（主世界那一头）；跳过条件：当前维度 = 2) → wear_armor(下界穿法；跳过条件：穿着金护甲件数 ≥ 1) → use_portal(进下界；跳过条件：当前维度 = 2) → goto_place(地方=烈焰人刷怪笼，停在 6~8 格外的走廊) → fight(目标=烈焰人，举盾挡火球，打死后走过去捡；直到 做眼还缺的烈焰棒 = 0（背包里的也算） 或 该返航 = 1) → goto_place(地方=下界那一头的门；跳过条件：当前维度 = 0) → use_portal(回主世界；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → store_items(烈焰棒进大箱子)</t>
+          <t>goto_place(地方=传送门（主世界那一头）；跳过条件：当前维度 = 2) → wear_armor(下界穿法；跳过条件：穿着金护甲件数 ≥ 1) → use_portal(进下界；跳过条件：当前维度 = 2) → goto_place(地方=诡异森林；还不记得就在下界 explore 找青绿色的地面，最多 10 分钟) → hunt_enderman(先搭两格高小棚，一次惹一只；直到 做眼还缺的末影珍珠 = 0（背包里的也算） 或 该返航 = 1；走前拆回小棚) → goto_place(地方=下界那一头的门；跳过条件：当前维度 = 0) → use_portal(回主世界；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → store_items(末影珍珠进大箱子)</t>
         </is>
       </c>
       <c r="F134" s="7" t="inlineStr">
@@ -10272,27 +10329,27 @@
     <row r="135">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>J-M8-11</t>
+          <t>J-M8-12</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
         <is>
-          <t>去下界的诡异森林，躲在自己搭的两格高小棚口，一只只打末影人，攒末影珍珠带回家。</t>
+          <t>麦娘从大箱子拿烈焰棒和末影珍珠，合成末影之眼，再存回箱子。</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>M8-11</t>
+          <t>M8-12</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>麦娘</t>
         </is>
       </c>
       <c r="E135" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方=传送门（主世界那一头）；跳过条件：当前维度 = 2) → wear_armor(下界穿法；跳过条件：穿着金护甲件数 ≥ 1) → use_portal(进下界；跳过条件：当前维度 = 2) → goto_place(地方=诡异森林；还不记得就在下界 explore 找青绿色的地面，最多 10 分钟) → hunt_enderman(先搭两格高小棚，一次惹一只；直到 做眼还缺的末影珍珠 = 0（背包里的也算） 或 该返航 = 1；走前拆回小棚) → goto_place(地方=下界那一头的门；跳过条件：当前维度 = 0) → use_portal(回主世界；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → store_items(末影珍珠进大箱子)</t>
+          <t>take_from_chest(东西=烈焰棒、末影珍珠；数量按 min(能做的末影之眼数, 末影之眼缺口) 现算) → craft(东西=blaze_powder) → craft(东西=ender_eye) → store_items(末影之眼和多的烈焰粉进大箱子)</t>
         </is>
       </c>
       <c r="F135" s="7" t="inlineStr">
@@ -10309,27 +10366,27 @@
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>J-M8-12</t>
+          <t>J-M8-13a</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t>麦娘从大箱子拿烈焰棒和末影珍珠，合成末影之眼，再存回箱子。</t>
+          <t>带几个末影之眼出门，在两个地方各扔一次、捡回来，算出要塞大概在哪，然后传送回家。</t>
         </is>
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>M8-12</t>
+          <t>M8-13</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>麦娘</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="E136" s="7" t="inlineStr">
         <is>
-          <t>take_from_chest(东西=烈焰棒、末影珍珠；数量按 min(能做的末影之眼数, 末影之眼缺口) 现算) → craft(东西=blaze_powder) → craft(东西=ender_eye) → store_items(末影之眼和多的烈焰粉进大箱子)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=末影之眼 4、口粮（留底 9，直到 身上吃的 ≥ 8）) → throw_eye(在新家门口扔，记下方向，落地走过去捡) → goto_place(沿和第一次方向垂直的方向走 200 格（长距离，寻路不许挖）) → throw_eye(再扔一次、捡回；代码算两条线的交点，估计位置不在离原点 1280~2816 格内就作废重扔) → go_home(用 /home base 传送回家) → store_items(末影之眼放回大箱子)</t>
         </is>
       </c>
       <c r="F136" s="7" t="inlineStr">
@@ -10346,12 +10403,12 @@
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>J-M8-13a</t>
+          <t>J-M8-13b</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
         <is>
-          <t>带几个末影之眼出门，在两个地方各扔一次、捡回来，算出要塞大概在哪，然后传送回家。</t>
+          <t>走到算出的要塞位置，近处再扔一次眼确认，从地面斜着挖下去，找到末地传送门框，记下位置后传送回家。</t>
         </is>
       </c>
       <c r="C137" s="7" t="inlineStr">
@@ -10366,7 +10423,7 @@
       </c>
       <c r="E137" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=末影之眼 4、口粮（留底 9，直到 身上吃的 ≥ 8）) → throw_eye(在新家门口扔，记下方向，落地走过去捡) → goto_place(沿和第一次方向垂直的方向走 200 格（长距离，寻路不许挖）) → throw_eye(再扔一次、捡回；代码算两条线的交点，估计位置不在离原点 1280~2816 格内就作废重扔) → go_home(用 /home base 传送回家) → store_items(末影之眼放回大箱子)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=末影之眼 3、口粮（留底 9，直到 身上吃的 ≥ 12）、圆石 64、镐（跳过条件：背包里最好的镐等级 ≥ 2）) → goto_place(地方=要塞估计位置（长距离，寻路不许挖）) → throw_eye(近处核对，眼往下钻 = 就在脚下；捡回) → dig_to_stronghold(先查 32 格内没有别人的东西和领地；楼梯形斜井往下，只挖天然方块；找到末地门框就记坐标和空门框数) → go_home(用 /home base 传送回家)</t>
         </is>
       </c>
       <c r="F137" s="7" t="inlineStr">
@@ -10383,17 +10440,17 @@
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>J-M8-13b</t>
+          <t>J-M8-14</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
         <is>
-          <t>走到算出的要塞位置，近处再扔一次眼确认，从地面斜着挖下去，找到末地传送门框，记下位置后传送回家。</t>
+          <t>带着末影之眼走到要塞，把空门框一个个嵌满，点亮末地传送门，然后传送回家。</t>
         </is>
       </c>
       <c r="C138" s="7" t="inlineStr">
         <is>
-          <t>M8-13</t>
+          <t>M8-14</t>
         </is>
       </c>
       <c r="D138" s="7" t="inlineStr">
@@ -10403,7 +10460,7 @@
       </c>
       <c r="E138" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=末影之眼 3、口粮（留底 9，直到 身上吃的 ≥ 12）、圆石 64、镐（跳过条件：背包里最好的镐等级 ≥ 2）) → goto_place(地方=要塞估计位置（长距离，寻路不许挖）) → throw_eye(近处核对，眼往下钻 = 就在脚下；捡回) → dig_to_stronghold(先查 32 格内没有别人的东西和领地；楼梯形斜井往下，只挖天然方块；找到末地门框就记坐标和空门框数) → go_home(用 /home base 传送回家)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=末影之眼，数量=空门框数；口粮（留底 9，直到 身上吃的 ≥ 8）) → goto_place(地方=要塞末地门（长距离，寻路不许挖）) → fill_portal_frame(每个空门框嵌一颗眼，回读中间是不是末地门) → go_home(用 /home base 传送回家)</t>
         </is>
       </c>
       <c r="F138" s="7" t="inlineStr">
@@ -10420,17 +10477,17 @@
     <row r="139">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>J-M8-14</t>
+          <t>J-M8-15a</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
         <is>
-          <t>带着末影之眼走到要塞，把空门框一个个嵌满，点亮末地传送门，然后传送回家。</t>
+          <t>在家用线和木棍做弓，用燧石、木棍、羽毛做箭，做好存进大箱子。</t>
         </is>
       </c>
       <c r="C139" s="7" t="inlineStr">
         <is>
-          <t>M8-14</t>
+          <t>M8-15</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
@@ -10440,7 +10497,7 @@
       </c>
       <c r="E139" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=末影之眼，数量=空门框数；口粮（留底 9，直到 身上吃的 ≥ 8）) → goto_place(地方=要塞末地门（长距离，寻路不许挖）) → fill_portal_frame(每个空门框嵌一颗眼，回读中间是不是末地门) → go_home(用 /home base 传送回家)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=线 3（跳过条件：有弓 ≥ 1）、木棍、燧石、羽毛（按缺的现算）) → craft(东西=bow；跳过条件：有弓 ≥ 1) → craft(东西=arrow；直到 箭的家底 ≥ 64，材料用完就停) → store_items(东西=弓、箭，进大箱子)</t>
         </is>
       </c>
       <c r="F139" s="7" t="inlineStr">
@@ -10457,12 +10514,12 @@
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>J-M8-15a</t>
+          <t>J-M8-15b</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
-          <t>在家用线和木棍做弓，用燧石、木棍、羽毛做箭，做好存进大箱子。</t>
+          <t>去资源世界打鸡拿羽毛、挖沙砾拿燧石，给做箭备料。</t>
         </is>
       </c>
       <c r="C140" s="7" t="inlineStr">
@@ -10477,7 +10534,7 @@
       </c>
       <c r="E140" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=线 3（跳过条件：有弓 ≥ 1）、木棍、燧石、羽毛（按缺的现算）) → craft(东西=bow；跳过条件：有弓 ≥ 1) → craft(东西=arrow；直到 箭的家底 ≥ 64，材料用完就停) → store_items(东西=弓、箭，进大箱子)</t>
+          <t>goto_place(地方=资源世界（/res go）) → hunt(目标=鸡，打死后捡羽毛；跳过条件：做箭还缺的羽毛 = 0；直到 做箭还缺的羽毛 = 0 或 15 分钟) → mine(方块=沙砾；跳过条件：做箭还缺的燧石 = 0；直到 做箭还缺的燧石 = 0 或 10 分钟) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(羽毛、燧石进大箱子)</t>
         </is>
       </c>
       <c r="F140" s="7" t="inlineStr">
@@ -10494,17 +10551,17 @@
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>J-M8-15b</t>
+          <t>J-M8-16</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
-          <t>去资源世界打鸡拿羽毛、挖沙砾拿燧石，给做箭备料。</t>
+          <t>（等您批）带着 4 个末地水晶进末地，放在中间返回门的四边，把龙叫回来。</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>M8-15</t>
+          <t>M8-16</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
@@ -10514,7 +10571,7 @@
       </c>
       <c r="E141" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方=资源世界（/res go）) → hunt(目标=鸡，打死后捡羽毛；跳过条件：做箭还缺的羽毛 = 0；直到 做箭还缺的羽毛 = 0 或 15 分钟) → mine(方块=沙砾；跳过条件：做箭还缺的燧石 = 0；直到 做箭还缺的燧石 = 0 或 10 分钟) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(羽毛、燧石进大箱子)</t>
+          <t>take_from_chest(东西=末地水晶 4) → goto_place(地方=要塞末地门；跳过条件：当前维度 = 3（末地）) → use_portal(进末地；跳过条件：当前维度 = 3) → respawn_dragon(4 个水晶放在中间返回门的四边)</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr">
@@ -10531,17 +10588,17 @@
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>J-M8-16</t>
+          <t>J-M8-17a</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr">
         <is>
-          <t>（等您批）带着 4 个末地水晶进末地，放在中间返回门的四边，把龙叫回来。</t>
+          <t>进末地前在家收拾：拿上弓和 64 支箭、128 块圆石和 24 个吃的，换回四件铁甲。</t>
         </is>
       </c>
       <c r="C142" s="7" t="inlineStr">
         <is>
-          <t>M8-16</t>
+          <t>M8-17</t>
         </is>
       </c>
       <c r="D142" s="7" t="inlineStr">
@@ -10551,7 +10608,7 @@
       </c>
       <c r="E142" s="7" t="inlineStr">
         <is>
-          <t>take_from_chest(东西=末地水晶 4) → goto_place(地方=要塞末地门；跳过条件：当前维度 = 3（末地）) → use_portal(进末地；跳过条件：当前维度 = 3) → respawn_dragon(4 个水晶放在中间返回门的四边)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=弓（跳过条件：身上有弓）、箭（直到 身上的箭 ≥ 64）) → take_from_chest(东西=圆石；直到 身上的圆石 ≥ 128) → take_from_chest(东西=口粮，从粮箱拿，留底 9（打开箱子按真数重算）；直到 身上吃的 ≥ 24) → wear_armor(末地穿法：四件最好的护甲 + 副手盾) → store_items(用不上的存掉，行李清单上的留着；直到 背包空格 ≥ 6)</t>
         </is>
       </c>
       <c r="F142" s="7" t="inlineStr">
@@ -10568,12 +10625,12 @@
     <row r="143">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>J-M8-17a</t>
+          <t>J-M8-17b</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
         <is>
-          <t>进末地前在家收拾：拿上弓和 64 支箭、128 块圆石和 24 个吃的，换回四件铁甲。</t>
+          <t>走到要塞，穿门进末地，先射掉柱子上的末地水晶，再趁龙落到中间时打它，打完从中间的门回家。</t>
         </is>
       </c>
       <c r="C143" s="7" t="inlineStr">
@@ -10588,7 +10645,7 @@
       </c>
       <c r="E143" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=弓（跳过条件：身上有弓）、箭（直到 身上的箭 ≥ 64）) → take_from_chest(东西=圆石；直到 身上的圆石 ≥ 128) → take_from_chest(东西=口粮，从粮箱拿，留底 9（打开箱子按真数重算）；直到 身上吃的 ≥ 24) → wear_armor(末地穿法：四件最好的护甲 + 副手盾) → store_items(用不上的存掉，行李清单上的留着；直到 背包空格 ≥ 6)</t>
+          <t>goto_place(地方=要塞末地门（长距离，寻路不许挖）；跳过条件：当前维度 = 3) → use_portal(进末地；跳过条件：当前维度 = 3) → dragon_fight(先看平台要不要搭路；射水晶，笼子里的垫高去打；趁龙落地近身打；不看末影人；血 ≤ 8 先吃，≤ 6 传送回家) → use_portal(龙死后走中间的返回门回主世界，回应结束字幕；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → store_items</t>
         </is>
       </c>
       <c r="F143" s="7" t="inlineStr">
@@ -10605,17 +10662,17 @@
     <row r="144">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>J-M8-17b</t>
+          <t>J-T0-1</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
         <is>
-          <t>走到要塞，穿门进末地，先射掉柱子上的末地水晶，再趁龙落到中间时打它，打完从中间的门回家。</t>
+          <t>小麦零候选时的兜底：回家核对箱子、把东西存好，在家等 1 分钟再重算。</t>
         </is>
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
-          <t>M8-17</t>
+          <t>T0</t>
         </is>
       </c>
       <c r="D144" s="7" t="inlineStr">
@@ -10625,7 +10682,7 @@
       </c>
       <c r="E144" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方=要塞末地门（长距离，寻路不许挖）；跳过条件：当前维度 = 3) → use_portal(进末地；跳过条件：当前维度 = 3) → dragon_fight(先看平台要不要搭路；射水晶，笼子里的垫高去打；趁龙落地近身打；不看末影人；血 ≤ 8 先吃，≤ 6 传送回家) → use_portal(龙死后走中间的返回门回主世界，回应结束字幕；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → store_items</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → check_chest(只打开看、不拿；核对完先重算一次候选，有了就结束兜底；跳过条件：开箱快照距今秒数 ≤ 600) → store_items(跳过条件：可存的东西 = 0) → idle(60 秒，然后重算候选)</t>
         </is>
       </c>
       <c r="F144" s="7" t="inlineStr">
@@ -10642,12 +10699,12 @@
     <row r="145">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t>J-T0-1</t>
+          <t>J-T0-2</t>
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr">
         <is>
-          <t>小麦零候选时的兜底：回家核对箱子、把东西存好，在家等 1 分钟再重算。</t>
+          <t>麦娘零候选时的兜底：回家核对两口箱子，把身上的小麦做成面包、东西存好，在家等 1 分钟再重算。</t>
         </is>
       </c>
       <c r="C145" s="7" t="inlineStr">
@@ -10657,12 +10714,12 @@
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>麦娘</t>
         </is>
       </c>
       <c r="E145" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → check_chest(只打开看、不拿；核对完先重算一次候选，有了就结束兜底；跳过条件：开箱快照距今秒数 ≤ 600) → store_items(跳过条件：可存的东西 = 0) → idle(60 秒，然后重算候选)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → check_chest(大箱子和粮箱只看不拿；跳过条件：开箱快照距今秒数 ≤ 600) → craft(东西=bread；跳过条件：有小麦 ≤ 2) → store_crop(跳过条件：能存粮 = 0) → store_items(跳过条件：可存的东西 = 0) → idle(60 秒，然后重算候选)</t>
         </is>
       </c>
       <c r="F145" s="7" t="inlineStr">
@@ -10679,12 +10736,12 @@
     <row r="146">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>J-T0-2</t>
+          <t>J-T0-3</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
         <is>
-          <t>麦娘零候选时的兜底：回家核对两口箱子，把身上的小麦做成面包、东西存好，在家等 1 分钟再重算。</t>
+          <t>麦豆零候选时的兜底：回家门口、离真人远的地方玩一会儿（天黑就待在屋里），30 秒后重算。</t>
         </is>
       </c>
       <c r="C146" s="7" t="inlineStr">
@@ -10694,12 +10751,12 @@
       </c>
       <c r="D146" s="7" t="inlineStr">
         <is>
-          <t>麦娘</t>
+          <t>麦豆</t>
         </is>
       </c>
       <c r="E146" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → check_chest(大箱子和粮箱只看不拿；跳过条件：开箱快照距今秒数 ≤ 600) → craft(东西=bread；跳过条件：有小麦 ≤ 2) → store_crop(跳过条件：能存粮 = 0) → store_items(跳过条件：可存的东西 = 0) → idle(60 秒，然后重算候选)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 16) → wander(家门口 16 格内；跳过条件：天黑了 = 1 或 血量 ≤ 15 或 离最近真人玩家距离 ≤ 24) → idle(30 秒，然后重算候选)</t>
         </is>
       </c>
       <c r="F146" s="7" t="inlineStr">
@@ -10709,36 +10766,32 @@
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>J-T0-3</t>
+          <t>J-T1-1</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
         <is>
-          <t>麦豆零候选时的兜底：回家门口、离真人远的地方玩一会儿（天黑就待在屋里），30 秒后重算。</t>
+          <t>把这一档能做的几件活连同全家现状交给模型，让它排个先后，然后照这个顺序一件件开工。</t>
         </is>
       </c>
       <c r="C147" s="7" t="inlineStr">
         <is>
-          <t>T0</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>麦豆</t>
-        </is>
-      </c>
-      <c r="E147" s="7" t="inlineStr">
-        <is>
-          <t>go_home(跳过条件：离家距离 ≤ 16) → wander(家门口 16 格内；跳过条件：天黑了 = 1 或 血量 ≤ 15 或 离最近真人玩家距离 ≤ 24) → idle(30 秒，然后重算候选)</t>
-        </is>
-      </c>
+          <t>全家</t>
+        </is>
+      </c>
+      <c r="E147" s="7" t="inlineStr"/>
       <c r="F147" s="7" t="inlineStr">
         <is>
           <t>新写</t>
@@ -10746,24 +10799,24 @@
       </c>
       <c r="G147" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>J-T1-1</t>
+          <t>J-T1-2</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
         <is>
-          <t>把这一档能做的几件活连同全家现状交给模型，让它排个先后，然后照这个顺序一件件开工。</t>
+          <t>把连败的那件活、失败原话和这个小目标剩下的办法交给模型，让它只回一个编号，然后换那条做。</t>
         </is>
       </c>
       <c r="C148" s="7" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D148" s="7" t="inlineStr">
@@ -10786,17 +10839,17 @@
     <row r="149">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>J-T1-2</t>
+          <t>J-T8</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
         <is>
-          <t>把连败的那件活、失败原话和这个小目标剩下的办法交给模型，让它只回一个编号，然后换那条做。</t>
+          <t>「做同一件小目标时、30 分钟内因为同一种原因死了两次：饿死、…」这条触发的脚本</t>
         </is>
       </c>
       <c r="C149" s="7" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T8</t>
         </is>
       </c>
       <c r="D149" s="7" t="inlineStr">
@@ -10804,7 +10857,11 @@
           <t>全家</t>
         </is>
       </c>
-      <c r="E149" s="7" t="inlineStr"/>
+      <c r="E149" s="7" t="inlineStr">
+        <is>
+          <t>(代码)收集候选(按这条触发的规则算出所有可选项) → (代码)只有 0 或 1 个候选(直接由代码决定,不问模型) → ask_model(≥2 个候选时问一次,只许回候选编号) → (代码)执行选中的那一项(问不到或超时:代码按固定规则兜底,不卡住)</t>
+        </is>
+      </c>
       <c r="F149" s="7" t="inlineStr">
         <is>
           <t>新写</t>
@@ -10812,24 +10869,24 @@
       </c>
       <c r="G149" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺动作</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>J-T8</t>
+          <t>J-T10</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr">
         <is>
-          <t>「做同一件小目标时、30 分钟内因为同一种原因死了两次：饿死、…」这条触发的脚本</t>
+          <t>「您（Owner）在游戏里点名叫它做某件事时，代码…」这条触发的脚本</t>
         </is>
       </c>
       <c r="C150" s="7" t="inlineStr">
         <is>
-          <t>T8</t>
+          <t>T10</t>
         </is>
       </c>
       <c r="D150" s="7" t="inlineStr">
@@ -10856,17 +10913,17 @@
     <row r="151">
       <c r="A151" s="7" t="inlineStr">
         <is>
-          <t>J-T10</t>
+          <t>J-T11</t>
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr">
         <is>
-          <t>「您（Owner）在游戏里点名叫它做某件事时，代码…」这条触发的脚本</t>
+          <t>「房子盖好以后，如果有两种以上合法的家具摆法（比如床靠北墙还是…」这条触发的脚本</t>
         </is>
       </c>
       <c r="C151" s="7" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T11</t>
         </is>
       </c>
       <c r="D151" s="7" t="inlineStr">
@@ -10893,27 +10950,27 @@
     <row r="152">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t>J-T11</t>
+          <t>child_make_leather_tunic</t>
         </is>
       </c>
       <c r="B152" s="7" t="inlineStr">
         <is>
-          <t>「房子盖好以后，如果有两种以上合法的家具摆法（比如床靠北墙还是…」这条触发的脚本</t>
+          <t>麦豆用箱子里 8 张皮革给自己做一件皮衣</t>
         </is>
       </c>
       <c r="C152" s="7" t="inlineStr">
         <is>
-          <t>T11</t>
+          <t>M5-7</t>
         </is>
       </c>
       <c r="D152" s="7" t="inlineStr">
         <is>
-          <t>全家</t>
+          <t>麦豆</t>
         </is>
       </c>
       <c r="E152" s="7" t="inlineStr">
         <is>
-          <t>(代码)收集候选(按这条触发的规则算出所有可选项) → (代码)只有 0 或 1 个候选(直接由代码决定,不问模型) → ask_model(≥2 个候选时问一次,只许回候选编号) → (代码)执行选中的那一项(问不到或超时:代码按固定规则兜底,不卡住)</t>
+          <t>go_home → take_from_chest(皮革) → craft(leather_chestplate)</t>
         </is>
       </c>
       <c r="F152" s="7" t="inlineStr">
@@ -10923,30 +10980,34 @@
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
-          <t>缺动作</t>
+          <t>缺判据/动作(代码刀)</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t>think_goal_order</t>
+          <t>make_diamond_sword</t>
         </is>
       </c>
       <c r="B153" s="7" t="inlineStr">
         <is>
-          <t>问模型给同档大目标排先后或并行</t>
+          <t>用家里箱子的 2 颗钻石给自己做一把钻石剑</t>
         </is>
       </c>
       <c r="C153" s="7" t="inlineStr">
         <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="D153" s="7" t="inlineStr"/>
+          <t>M5-6</t>
+        </is>
+      </c>
+      <c r="D153" s="7" t="inlineStr">
+        <is>
+          <t>全家</t>
+        </is>
+      </c>
       <c r="E153" s="7" t="inlineStr">
         <is>
-          <t>ask_model(同档可开工的 G 编号)</t>
+          <t>go_home → take_from_chest(钻石) → take_from_chest(木棍) → craft(diamond_sword)</t>
         </is>
       </c>
       <c r="F153" s="7" t="inlineStr">
@@ -10956,30 +11017,30 @@
       </c>
       <c r="G153" s="7" t="inlineStr">
         <is>
-          <t>缺动作</t>
+          <t>缺判据/动作(代码刀)</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t>think_home_site</t>
+          <t>think_goal_order</t>
         </is>
       </c>
       <c r="B154" s="7" t="inlineStr">
         <is>
-          <t>问模型选新家址</t>
+          <t>问模型给同档大目标排先后或并行</t>
         </is>
       </c>
       <c r="C154" s="7" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D154" s="7" t="inlineStr"/>
       <c r="E154" s="7" t="inlineStr">
         <is>
-          <t>ask_model(候选家址编号 + 打分明细)</t>
+          <t>ask_model(同档可开工的 G 编号)</t>
         </is>
       </c>
       <c r="F154" s="7" t="inlineStr">
@@ -10996,23 +11057,23 @@
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
         <is>
-          <t>think_house_design</t>
+          <t>think_home_site</t>
         </is>
       </c>
       <c r="B155" s="7" t="inlineStr">
         <is>
-          <t>问模型选房子方案</t>
+          <t>问模型选新家址</t>
         </is>
       </c>
       <c r="C155" s="7" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D155" s="7" t="inlineStr"/>
       <c r="E155" s="7" t="inlineStr">
         <is>
-          <t>ask_model(代码列出的方案编号)</t>
+          <t>ask_model(候选家址编号 + 打分明细)</t>
         </is>
       </c>
       <c r="F155" s="7" t="inlineStr">
@@ -11029,23 +11090,23 @@
     <row r="156">
       <c r="A156" s="7" t="inlineStr">
         <is>
-          <t>think_pick_task</t>
+          <t>think_house_design</t>
         </is>
       </c>
       <c r="B156" s="7" t="inlineStr">
         <is>
-          <t>(已并入 J-T1-1)问模型给同档小目标排先后</t>
+          <t>问模型选房子方案</t>
         </is>
       </c>
       <c r="C156" s="7" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D156" s="7" t="inlineStr"/>
       <c r="E156" s="7" t="inlineStr">
         <is>
-          <t>ask_model(同档候选编号;默认=最久没做的)</t>
+          <t>ask_model(代码列出的方案编号)</t>
         </is>
       </c>
       <c r="F156" s="7" t="inlineStr">
@@ -11062,33 +11123,103 @@
     <row r="157">
       <c r="A157" s="7" t="inlineStr">
         <is>
-          <t>think_reply</t>
+          <t>think_pick_task</t>
         </is>
       </c>
       <c r="B157" s="7" t="inlineStr">
         <is>
-          <t>被点名时写一句回话,并从 3 个选项里挑一个</t>
+          <t>(已并入 J-T1-1)问模型给同档小目标排先后</t>
         </is>
       </c>
       <c r="C157" s="7" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D157" s="7" t="inlineStr"/>
       <c r="E157" s="7" t="inlineStr">
         <is>
+          <t>ask_model(同档候选编号;默认=最久没做的)</t>
+        </is>
+      </c>
+      <c r="F157" s="7" t="inlineStr">
+        <is>
+          <t>新写</t>
+        </is>
+      </c>
+      <c r="G157" s="7" t="inlineStr">
+        <is>
+          <t>缺动作</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="7" t="inlineStr">
+        <is>
+          <t>think_reply</t>
+        </is>
+      </c>
+      <c r="B158" s="7" t="inlineStr">
+        <is>
+          <t>被点名时写一句回话,并从 3 个选项里挑一个</t>
+        </is>
+      </c>
+      <c r="C158" s="7" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="D158" s="7" t="inlineStr"/>
+      <c r="E158" s="7" t="inlineStr">
+        <is>
           <t>ask_model(回话 + 选项:只回话/跟他走/不理) → say(模型写的那句) → follow_player(只在选了「跟他走」时;最多 120 秒)</t>
         </is>
       </c>
-      <c r="F157" s="7" t="inlineStr">
+      <c r="F158" s="7" t="inlineStr">
         <is>
           <t>新写</t>
         </is>
       </c>
-      <c r="G157" s="7" t="inlineStr">
+      <c r="G158" s="7" t="inlineStr">
         <is>
           <t>缺动作</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="7" t="inlineStr">
+        <is>
+          <t>wife_make_iron_helmet</t>
+        </is>
+      </c>
+      <c r="B159" s="7" t="inlineStr">
+        <is>
+          <t>麦娘用箱子里 5 个铁锭给自己做一个铁头盔</t>
+        </is>
+      </c>
+      <c r="C159" s="7" t="inlineStr">
+        <is>
+          <t>M5-7</t>
+        </is>
+      </c>
+      <c r="D159" s="7" t="inlineStr">
+        <is>
+          <t>麦娘</t>
+        </is>
+      </c>
+      <c r="E159" s="7" t="inlineStr">
+        <is>
+          <t>go_home → take_from_chest(铁锭) → craft(iron_helmet)</t>
+        </is>
+      </c>
+      <c r="F159" s="7" t="inlineStr">
+        <is>
+          <t>新写</t>
+        </is>
+      </c>
+      <c r="G159" s="7" t="inlineStr">
+        <is>
+          <t>缺判据/动作(代码刀)</t>
         </is>
       </c>
     </row>
@@ -20535,7 +20666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -20740,7 +20871,11 @@
           <t>一把钻石剑顶 26 把木剑,两天打坏了 82 把木剑、常常空手打怪,有了当场解决。如果这些钻石另有用处(比如留给孩子),就不碰。镐建议也用箱子里的 3 颗 —— 自己去最深处挖是整条打龙路线里最容易死的一步。剑只发给会打架的人(现在只有小麦,麦娘您同意她还手之后也算),麦豆只跑不打所以不发。</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr"/>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>已定(2026-09-18 约 16:10):做 3 把钻石剑,用 6 颗,三人各一把,剩 21 颗不动。</t>
+        </is>
+      </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
           <t>补充 Q16、第二轮</t>
@@ -20782,7 +20917,11 @@
           <t>她现在其实一直在还手,但手里没剑(近 13 小时死了 41 次,大多被僵尸打死)。建议:有剑才打,没剑就跑。末地不去:她人设不出远门。</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr"/>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>已定(2026-09-18 约 16:10):「都还手,但有规矩」—— 三个人一样:手上有剑、血够、只有一两只普通怪(僵尸、蜘蛛这类)才打;苦力怕、怪太多、在水里、血少时一律跑。Owner 同时说:「我建议是所有角色都要有武器装备」。</t>
+        </is>
+      </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
           <t>基本状态 Q21、第二轮</t>
@@ -20805,7 +20944,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>已定(2026-09-18):按建议全学 —— 砍树、收麦子种回去、存箱子;背包满了自己存;遇怪只跑不打。</t>
+          <t>已定(2026-09-18 15:14):按建议全学 —— 砍树、收麦子种回去、存箱子;背包满了自己存。「遇怪只跑不打」那半句已被 16:10 的决定取代:三个人都配武器,按规矩还手。</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -20916,7 +21055,11 @@
           <t>先做镐 —— 打龙路线的第一步,镐能挖回更多铁,桶以后再做。</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr"/>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>已定(2026-09-18 约 16:50):5 个铁锭先给麦娘做铁头盔(铁镐、铁桶等学会挖铁再说)。</t>
+        </is>
+      </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
           <t>第二轮·结局链</t>
@@ -21088,6 +21231,90 @@
       <c r="E26" s="7" t="inlineStr">
         <is>
           <t>第二轮·问模型的上下文</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>麦豆要有自己的剑,只能让他学会「回家开箱子拿东西」和「自己做东西」(家里人之间没法递剑)。可以吗?</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr"/>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>已定(约 16:50):可以。只限固定清单:吃的、木板、原木、种子、小麦,加做剑用的 2 颗钻石和木棍。</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>第三轮·武装全家</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>怪就在真人小孩、别人的宠物、马或村民旁边时,机器人要不要照样挥剑?</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr"/>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>已定(约 16:50):不打,先拉开距离。</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>第三轮·武装全家</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>骷髅这种射箭的怪已经走到机器人面前(5 格内),手上有剑、血也够,打还是跑?</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr"/>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>已定(约 16:50):挡箭并跑开。</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>第三轮·武装全家</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>3 把钻石剑用坏以后,箱子里剩下的 21 颗钻石动不动?</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr"/>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>按默认(约 16:50 报给 Owner,没反对):不动,到时先告诉 Owner 再定。</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>第三轮·武装全家</t>
         </is>
       </c>
     </row>
@@ -21102,7 +21329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E505"/>
+  <dimension ref="A1:E541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -34696,7 +34923,7 @@
       </c>
       <c r="E504" s="7" t="inlineStr">
         <is>
-          <t>已定(2026-09-18):按建议全学 —— 砍树、收麦子种回去、存箱子;背包满了自己存;遇怪只跑不打。</t>
+          <t>已定(2026-09-18 15:14):按建议全学 —— 砍树、收麦子种回去、存箱子;背包满了自己存。「遇怪只跑不打」那半句已被 16:10 的决定取代:三个人都配武器,按规矩还手。</t>
         </is>
       </c>
     </row>
@@ -34708,22 +34935,994 @@
       </c>
       <c r="B505" s="7" t="inlineStr">
         <is>
+          <t>拍板8</t>
+        </is>
+      </c>
+      <c r="C505" s="7" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
+      <c r="D505" s="7" t="inlineStr">
+        <is>
+          <t>家里箱子里的 27 颗钻石能不能给全家做钻石剑?另外,做钻石镐只要其中 3 颗:直接用箱子里的,还是</t>
+        </is>
+      </c>
+      <c r="E505" s="7" t="inlineStr">
+        <is>
+          <t>已定(2026-09-18 约 16:10):做 3 把钻石剑,用 6 颗,三人各一把,剩 21 颗不动。</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B506" s="7" t="inlineStr">
+        <is>
+          <t>拍板10</t>
+        </is>
+      </c>
+      <c r="C506" s="7" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
+      <c r="D506" s="7" t="inlineStr">
+        <is>
+          <t>麦娘遇到僵尸:要「能自保的妈妈」(给她剑、会还手),还是「一见怪就躲回家的妈妈」?打龙时麦娘要不要跟</t>
+        </is>
+      </c>
+      <c r="E506" s="7" t="inlineStr">
+        <is>
+          <t>已定(2026-09-18 约 16:10):「都还手,但有规矩」—— 三个人一样:手上有剑、血够、只有一两只普通怪(僵尸、蜘蛛这类)才打;苦力怕、怪太多、在水里、血少时一律跑。Owner 同时说:「我建议是所有角色都要有武器装备」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B507" s="7" t="inlineStr">
+        <is>
           <t>拍板12</t>
         </is>
       </c>
-      <c r="C505" s="7" t="inlineStr">
+      <c r="C507" s="7" t="inlineStr">
         <is>
           <t>已定</t>
         </is>
       </c>
-      <c r="D505" s="7" t="inlineStr">
+      <c r="D507" s="7" t="inlineStr">
         <is>
           <t>真人孩子在聊天里叫麦家「跟我来」「帮我砍树」,要不要听?</t>
         </is>
       </c>
-      <c r="E505" s="7" t="inlineStr">
+      <c r="E507" s="7" t="inlineStr">
         <is>
           <t>已定(2026-09-18 约 15:14):能,由 AI 按性格决定听不听;护栏和未成年人安全底线照旧由代码挡。(和我原来「只听 Owner」的建议不同,以 Owner 为准)</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B508" s="7" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+      <c r="C508" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D508" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 desc:Owner 定了三人都配武器</t>
+        </is>
+      </c>
+      <c r="E508" s="7" t="inlineStr">
+        <is>
+          <t>原来:"会打架的家人(现在是小麦;麦娘拿到剑、也被允许还手后也算)手上都有剑,箱子里有备用剑;麦豆只跑不打,不给他剑。为什么要做:两天打坏 82  → 现在:"全家三个人(小麦、麦娘、麦豆)手上都有剑:三人各用家里箱子里 2 颗钻石自己做一把钻石剑(一共 6 颗,箱底 21 颗不动;剑递不过去、也</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B509" s="7" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+      <c r="C509" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D509" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 owner:三人都有份</t>
+        </is>
+      </c>
+      <c r="E509" s="7" t="inlineStr">
+        <is>
+          <t>原来:"son" → 现在:"全家"</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B510" s="7" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+      <c r="C510" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D510" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 done_when:删掉「箱子里剑数 ≥3」:代码 STORE_NEVER 永远不把剑存进箱子,这条做不到</t>
+        </is>
+      </c>
+      <c r="E510" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">原来:[{"pred": "在线会打架的家人里没剑的人数", "op": "=", "value": 0}, {"pred": "箱子里剑数",  → 现在:[{"pred": "在线家人里没剑的人数", "op": "=", "value": 0}, {"pred": "做过钻石剑的家人数", </t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B511" s="7" t="inlineStr">
+        <is>
+          <t>M5-1</t>
+        </is>
+      </c>
+      <c r="C511" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D511" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 desc:Owner 2026-09-18:「我建议是所有角色都要有武器装备」+「都还手,但有规矩」</t>
+        </is>
+      </c>
+      <c r="E511" s="7" t="inlineStr">
+        <is>
+          <t>原来:"每个会打架的在线家人手上都有一把剑(麦豆只跑不打,不算)" → 现在:"每个在线家人手上都有一把剑(三个人都算)"</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B512" s="7" t="inlineStr">
+        <is>
+          <t>M5-1</t>
+        </is>
+      </c>
+      <c r="C512" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D512" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 done_when:不再分「会打架的家人」</t>
+        </is>
+      </c>
+      <c r="E512" s="7" t="inlineStr">
+        <is>
+          <t>原来:[{"pred": "在线会打架的家人里没剑的人数", "op": "=", "value": 0}] → 现在:[{"pred": "在线家人里没剑的人数", "op": "=", "value": 0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B513" s="7" t="inlineStr">
+        <is>
+          <t>M5-4</t>
+        </is>
+      </c>
+      <c r="C513" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D513" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 desc:删掉「麦豆不算」</t>
+        </is>
+      </c>
+      <c r="E513" s="7" t="inlineStr">
+        <is>
+          <t>原来:"每个会打架的在线家人都换上石剑(麦豆只跑不打,不算)" → 现在:"每个在线家人都有石剑或更好的剑(有钻石剑的已经算)"</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B514" s="7" t="inlineStr">
+        <is>
+          <t>M5-4</t>
+        </is>
+      </c>
+      <c r="C514" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D514" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 done_when:三人都算</t>
+        </is>
+      </c>
+      <c r="E514" s="7" t="inlineStr">
+        <is>
+          <t>原来:[{"pred": "在线会打架的家人里剑等级低于石剑的人数", "op": "=", "value": 0}] → 现在:[{"pred": "在线家人里剑等级低于石剑的人数", "op": "=", "value": 0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B515" s="7" t="inlineStr">
+        <is>
+          <t>M5-6</t>
+        </is>
+      </c>
+      <c r="C515" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D515" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 desc:Owner 批准「做 3 把钻石剑」</t>
+        </is>
+      </c>
+      <c r="E515" s="7" t="inlineStr">
+        <is>
+          <t>原来:"用箱子里的钻石给会打架的家人每人做一把钻石剑(麦豆不算;等 Owner 批准)" → 现在:"三人各从家里箱子拿 2 颗钻石,自己做一把钻石剑(箱底永远留 21 颗;每人一辈子最多领 2 颗,由代码记账)"</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B516" s="7" t="inlineStr">
+        <is>
+          <t>M5-6</t>
+        </is>
+      </c>
+      <c r="C516" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D516" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 owner:三人各做各的</t>
+        </is>
+      </c>
+      <c r="E516" s="7" t="inlineStr">
+        <is>
+          <t>原来:"son" → 现在:"全家"</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B517" s="7" t="inlineStr">
+        <is>
+          <t>M5-6</t>
+        </is>
+      </c>
+      <c r="C517" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D517" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 status:Owner 已批准,解除暂停</t>
+        </is>
+      </c>
+      <c r="E517" s="7" t="inlineStr">
+        <is>
+          <t>原来:3 → 现在:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B518" s="7" t="inlineStr">
+        <is>
+          <t>M8-3</t>
+        </is>
+      </c>
+      <c r="C518" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D518" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 desc:Owner:所有角色都要有装备</t>
+        </is>
+      </c>
+      <c r="E518" s="7" t="inlineStr">
+        <is>
+          <t>原来:"小麦有一身能保命的铁装备：四件铁甲（头盔、胸甲、护腿、靴子）、铁剑、盾，外加一桶水和一个打火石（点下界传送门用）。" → 现在:"(铁甲三人都要,但要等 M8-2 会挖矿、会烧铁以后才开,现在不排期)小麦有一身能保命的铁装备：四件铁甲（头盔、胸甲、护腿、靴子）、铁剑、</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B519" s="7" t="inlineStr">
+        <is>
+          <t>M5-5</t>
+        </is>
+      </c>
+      <c r="C519" s="7" t="inlineStr">
+        <is>
+          <t>删除</t>
+        </is>
+      </c>
+      <c r="D519" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 箱子里常备 3 把木剑:做不到</t>
+        </is>
+      </c>
+      <c r="E519" s="7" t="inlineStr">
+        <is>
+          <t>代码 STORE_NEVER 永远不把剑存进箱子,也没有递剑的办法</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B520" s="7" t="inlineStr">
+        <is>
+          <t>J-M5-5</t>
+        </is>
+      </c>
+      <c r="C520" s="7" t="inlineStr">
+        <is>
+          <t>删除</t>
+        </is>
+      </c>
+      <c r="D520" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 箱子里常备 3 把木剑:做不到</t>
+        </is>
+      </c>
+      <c r="E520" s="7" t="inlineStr">
+        <is>
+          <t>代码 STORE_NEVER 永远不把剑存进箱子,也没有递剑的办法</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B521" s="7" t="inlineStr">
+        <is>
+          <t>make_diamond_sword</t>
+        </is>
+      </c>
+      <c r="C521" s="7" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="D521" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 用家里箱子的 2 颗钻石给自己做一把钻石剑</t>
+        </is>
+      </c>
+      <c r="E521" s="7" t="inlineStr">
+        <is>
+          <t>Owner 批准做 3 把钻石剑。依次放行:小麦 → 麦娘 → 麦豆(麦豆要先有 take_from_chest 和 craft,Owner 16:50 同意)</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B522" s="7" t="inlineStr">
+        <is>
+          <t>M5-7/M5-8</t>
+        </is>
+      </c>
+      <c r="C522" s="7" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="D522" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 全家护甲两个小目标</t>
+        </is>
+      </c>
+      <c r="E522" s="7" t="inlineStr">
+        <is>
+          <t>Owner 2026-09-18:「我建议是所有角色都要有武器装备」+「都还手,但有规矩」</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B523" s="7" t="inlineStr">
+        <is>
+          <t>child_make_leather_tunic</t>
+        </is>
+      </c>
+      <c r="C523" s="7" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="D523" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 麦豆用箱子里 8 张皮革给自己做一件皮衣</t>
+        </is>
+      </c>
+      <c r="E523" s="7" t="inlineStr">
+        <is>
+          <t>麦豆从来没穿过胸甲。做好后 wearBestArmor 30 秒内自动穿上。缺判据:我胸甲空着、箱子里皮革;take 要加「皮革」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B524" s="7" t="inlineStr">
+        <is>
+          <t>wife_make_iron_helmet</t>
+        </is>
+      </c>
+      <c r="C524" s="7" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="D524" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 麦娘用箱子里 5 个铁锭给自己做一个铁头盔</t>
+        </is>
+      </c>
+      <c r="E524" s="7" t="inlineStr">
+        <is>
+          <t>Owner 16:50 定:5 个铁锭先给麦娘做头盔(不做铁镐、铁桶)。缺判据:我头盔空着、箱子里铁锭;take 要加「铁锭」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B525" s="7" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C525" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D525" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 desc:Owner 2026-09-18:「我建议是所有角色都要有武器装备」+「都还手,但有规矩」</t>
+        </is>
+      </c>
+      <c r="E525" s="7" t="inlineStr">
+        <is>
+          <t>原来:"血量高于30%(&gt;6)时,把贴到4格内的普通近战怪打掉;苦力怕、末影人、强怪、嘎枝只跑不打;麦豆只跑,麦娘有剑才打" → 现在:"三人一套规矩(Owner 2026-09-18):手上有剑、血 ≥14 才开打(已在打的血 &gt;10 可以继续);只打普通怪(僵尸、尸壳、僵</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B526" s="7" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C526" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D526" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 trigger:门槛挪进脚本的还要满足,触发只看怪贴近</t>
+        </is>
+      </c>
+      <c r="E526" s="7" t="inlineStr">
+        <is>
+          <t>原来:[{"pred": "最近近战怪距离", "op": "≤", "value": 4}, {"pred": "血量", "op": "≥", → 现在:[{"pred": "最近近战怪距离", "op": "≤", "value": 4}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B527" s="7" t="inlineStr">
+        <is>
+          <t>J-A2-1</t>
+        </is>
+      </c>
+      <c r="C527" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D527" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 desc:三人一套规矩</t>
+        </is>
+      </c>
+      <c r="E527" s="7" t="inlineStr">
+        <is>
+          <t>原来:"小麦把贴脸的普通近战怪打掉(怪不多、不在水里、不是刚复活、怪没着火)" → 现在:"按规矩把贴脸的普通怪打掉(三人共用)"</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B528" s="7" t="inlineStr">
+        <is>
+          <t>J-A2-1</t>
+        </is>
+      </c>
+      <c r="C528" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D528" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 owner:三人一套规矩</t>
+        </is>
+      </c>
+      <c r="E528" s="7" t="inlineStr">
+        <is>
+          <t>原来:"son" → 现在:"全家"</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B529" s="7" t="inlineStr">
+        <is>
+          <t>J-A2-1</t>
+        </is>
+      </c>
+      <c r="C529" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D529" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 trigger:开工条件是「任一成立」,原来把全部门槛写在这里是陷阱</t>
+        </is>
+      </c>
+      <c r="E529" s="7" t="inlineStr">
+        <is>
+          <t>原来:[{"pred": "最近怪能打", "op": "=", "value": 1}, {"pred": "血量", "op": "≥", " → 现在:[{"pred": "最近怪能打", "op": "=", "value": 1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B530" s="7" t="inlineStr">
+        <is>
+          <t>J-A2-2</t>
+        </is>
+      </c>
+      <c r="C530" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D530" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 enabled:并进 J-A2-1:三人一套规矩,不再单写麦娘</t>
+        </is>
+      </c>
+      <c r="E530" s="7" t="inlineStr">
+        <is>
+          <t>原来:null → 现在:false</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B531" s="7" t="inlineStr">
+        <is>
+          <t>J-A2-3</t>
+        </is>
+      </c>
+      <c r="C531" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D531" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 desc:平级会话 7ec16f3a:麦豆不去出生点</t>
+        </is>
+      </c>
+      <c r="E531" s="7" t="inlineStr">
+        <is>
+          <t>原来:"还在挨打,或刚复活就被怪贴脸:传送脱险(在家门口就去出生点)" → 现在:"还在挨打,或刚复活就被怪贴脸:传送脱险(小麦、麦娘在家门口就去出生点;麦豆不去出生点,在家附近躲)"</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B532" s="7" t="inlineStr">
+        <is>
+          <t>J-A2-4</t>
+        </is>
+      </c>
+      <c r="C532" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D532" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 desc:三人一套规矩</t>
+        </is>
+      </c>
+      <c r="E532" s="7" t="inlineStr">
+        <is>
+          <t>原来:"其余情况(麦豆、没剑的麦娘、在水里、怪太多、强怪、嘎枝、着火的僵尸):跑开" → 现在:"其余情况一律跑:没剑、血 &lt;14(已在打的 ≤10)、怪 &gt;2 只、有苦力怕、在水里、刚复活、不是普通怪、旁边有人或宠物"</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B533" s="7" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="C533" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D533" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 desc:Owner 16:50</t>
+        </is>
+      </c>
+      <c r="E533" s="7" t="inlineStr">
+        <is>
+          <t>原来:"不站着挨冷箭:被远程怪盯上时,弓箭手贴到5格内、血够又有剑就冲上去打;血少就传送走;其余先挡箭再拉开距离" → 现在:"不站着挨冷箭:被远程怪盯上时先挡箭再拉开距离;血少就传送走。射箭的怪走到面前也不冲上去砍(Owner 16:50「挡箭并跑开」)。麦豆不放</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B534" s="7" t="inlineStr">
+        <is>
+          <t>J-A6-1</t>
+        </is>
+      </c>
+      <c r="C534" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D534" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 enabled:Owner 16:50:射箭的怪到 5 格内也「挡箭并跑开」,不冲</t>
+        </is>
+      </c>
+      <c r="E534" s="7" t="inlineStr">
+        <is>
+          <t>原来:null → 现在:false</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B535" s="7" t="inlineStr">
+        <is>
+          <t>A23</t>
+        </is>
+      </c>
+      <c r="C535" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D535" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 desc:调研查实递不过去</t>
+        </is>
+      </c>
+      <c r="E535" s="7" t="inlineStr">
+        <is>
+          <t>原来:"家人缺干活的家伙、我手上有多的，就送他一把：会打架的家人（现在是小麦）没剑，谁手上有用不上的剑就给他；种田的麦娘没锄头，谁有多的锄头就给她 → 现在:"家人缺干活的家伙、我手上有多的就送他 —— 🔴 代码里没有递东西的动作(giveTo 只给吃的和木头,剑存不进箱子),剑和锄头眼下只能各做</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B536" s="7" t="inlineStr">
+        <is>
+          <t>A24</t>
+        </is>
+      </c>
+      <c r="C536" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D536" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 desc:Owner 定了三人都还手,但没定帮打</t>
+        </is>
+      </c>
+      <c r="E536" s="7" t="inlineStr">
+        <is>
+          <t>原来:"家人在我附近（24 格内）被一两只普通的怪围着打，我血够（≥14）、手上有剑，就过去帮他把怪打掉，打完回去接着干原来的活。怪超过 3 只、 → 现在:"家人在我附近（24 格内）被一两只普通的怪围着打，我血够（≥14）、手上有剑，就过去帮他把怪打掉，打完回去接着干原来的活。怪超过 3 只、</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B537" s="7" t="inlineStr">
+        <is>
+          <t>A25</t>
+        </is>
+      </c>
+      <c r="C537" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D537" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 owner:三人都可能「现在不能打」</t>
+        </is>
+      </c>
+      <c r="E537" s="7" t="inlineStr">
+        <is>
+          <t>原来:"child" → 现在:"全家"</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B538" s="7" t="inlineStr">
+        <is>
+          <t>A25</t>
+        </is>
+      </c>
+      <c r="C538" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D538" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 trigger:从「我会打架=0」改成「我现在不能打=1」(没剑、血少、怪多),三人都适用</t>
+        </is>
+      </c>
+      <c r="E538" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">原来:[{"pred": "我会打架", "op": "=", "value": 0}, {"pred": "最近近战怪距离", "op": "≤ → 现在:[{"pred": "我现在不能打", "op": "=", "value": 1}, {"pred": "最近近战怪距离", "op": </t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B539" s="7" t="inlineStr">
+        <is>
+          <t>A25</t>
+        </is>
+      </c>
+      <c r="C539" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D539" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 改 desc:三人都适用</t>
+        </is>
+      </c>
+      <c r="E539" s="7" t="inlineStr">
+        <is>
+          <t>原来:"麦豆被怪追、但还没挨打时，如果 24 格内有能护着他的大人（有剑、血够、会出手，身边没有苦力怕这类难缠的怪），而且大人不在怪那一边，就往大 → 现在:"我现在不能打(没剑、血少、怪多)、被怪追、还没挨打时:24 格内有能护着我的大人(有剑、血够、身边没苦力怕)、而且不在怪那一边,就往他身边</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B540" s="7" t="inlineStr">
+        <is>
+          <t>全表</t>
+        </is>
+      </c>
+      <c r="C540" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D540" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 「8格内有怪」换成「8格内怪数」4 处</t>
+        </is>
+      </c>
+      <c r="E540" s="7" t="inlineStr">
+        <is>
+          <t>线上「8格内有怪」读 h.position 出错被吞,永远返回 0(bot.real.js:3844-3848),guard_home 因此从没开工过</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B541" s="7" t="inlineStr">
+        <is>
+          <t>拍板16</t>
+        </is>
+      </c>
+      <c r="C541" s="7" t="inlineStr">
+        <is>
+          <t>已定</t>
+        </is>
+      </c>
+      <c r="D541" s="7" t="inlineStr">
+        <is>
+          <t>箱子里只有 5 个铁锭:先给小麦做铁镐,还是先做铁桶给田里补水?</t>
+        </is>
+      </c>
+      <c r="E541" s="7" t="inlineStr">
+        <is>
+          <t>已定(2026-09-18 约 16:50):5 个铁锭先给麦娘做铁头盔(铁镐、铁桶等学会挖铁再说)。</t>
         </is>
       </c>
     </row>

--- a/ai-player/goal-table/小麦家族工作分解-填写版.xlsx
+++ b/ai-player/goal-table/小麦家族工作分解-填写版.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>J-M1-4, wife_bread, wife_craft_chest, wife_get_crop_chest, wife_store_crop</t>
+          <t>J-M1-4, wife_bread, wife_craft_chest, wife_get_crop_chest, wife_logs_to_planks, wife_store_crop</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>wife_find_seeds, wife_gather_seeds, wife_make_hoe, wife_take_planks</t>
+          <t>wife_find_seeds, wife_gather_seeds, wife_logs_to_planks, wife_make_hoe, wife_take_planks</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>⏳ 过渡:搬家(拍板第 1 件)定之前,挂在这里的 build_house / get_build_mats / son_take_mats 仍在现在的家把房子盖完(线上老行为,不倒退);定了搬以后改成在新家址盖。 门是 2 格高的物品，要点门洞下面那块地面的顶面放，朝向跟人的朝向走。墙的判定只看实心不实心，不看方块名（泥土长成草那次的教训）。站位必须站在墙格以外的格子上，不能用「离中心多远」来判断。僵尸自己开不了木门。</t>
+          <t>🔴 盖房硬约束(2026-09-18 实测小麦被自己的房子关住,20 分钟失败 110 次):① 任何一步都不许把方块放进盖房人正站的格子、头顶那格和门洞;② 每放一块之前,代码先算「放完以后我还走得出去吗」(站的格子到屋外有通路),走不出去就先走出去再放;③ 同一块连着被服务器拒绝 3 次,就换下一块或收工,不原地重试。这三条由代码判断,不问模型。 ⏳ 过渡:搬家(拍板第 1 件)定之前,挂在这里的 build_house / get_build_mats / son_take_mats 仍在现在的家把房子盖完(线上老行为,不倒退);定了搬以后改成在新家址盖。 门是 2 格高的物品，要点门洞下面那块地面的顶面放，朝向跟人的朝向走。墙的判定只看实心不实心，不看方块名（泥土长成草那次的教训）。站位必须站在墙格以外的格子上，不能用「离中心多远」来判断。僵尸自己开不了木门。</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
-          <t>1.18 起，敌对怪只在方块光照为 0 的地方刷，而且刷不到底半砖上（顶半砖和双层半砖上能刷）。人站在半砖上眼睛高出 0.5 格；放方块的伸手距离是 3.6 时，屋顶格在水平约 3.3 格内都够得着。对着同种底半砖的顶面再放一块，会合成双层半砖（完整方块，能刷怪），所以 placeAt「放之前先看目标格是不是空的」这条不能绕过。</t>
+          <t>🔴 盖房硬约束(2026-09-18 实测小麦被自己的房子关住,20 分钟失败 110 次):① 任何一步都不许把方块放进盖房人正站的格子、头顶那格和门洞;② 每放一块之前,代码先算「放完以后我还走得出去吗」(站的格子到屋外有通路),走不出去就先走出去再放;③ 同一块连着被服务器拒绝 3 次,就换下一块或收工,不原地重试。这三条由代码判断,不问模型。 1.18 起，敌对怪只在方块光照为 0 的地方刷，而且刷不到底半砖上（顶半砖和双层半砖上能刷）。人站在半砖上眼睛高出 0.5 格；放方块的伸手距离是 3.6 时，屋顶格在水平约 3.3 格内都够得着。对着同种底半砖的顶面再放一块，会合成双层半砖（完整方块，能刷怪），所以 placeAt「放之前先看目标格是不是空的」这条不能绕过。</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G159"/>
+  <dimension ref="A1:G160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11189,35 +11189,72 @@
     <row r="159">
       <c r="A159" s="7" t="inlineStr">
         <is>
+          <t>wife_logs_to_planks</t>
+        </is>
+      </c>
+      <c r="B159" s="7" t="inlineStr">
+        <is>
+          <t>麦娘从箱子拿原木做成 8 块同种木板(缺锄头或没地方存粮时)</t>
+        </is>
+      </c>
+      <c r="C159" s="7" t="inlineStr">
+        <is>
+          <t>M1-1</t>
+        </is>
+      </c>
+      <c r="D159" s="7" t="inlineStr">
+        <is>
+          <t>麦娘</t>
+        </is>
+      </c>
+      <c r="E159" s="7" t="inlineStr">
+        <is>
+          <t>go_home → store_items → take_from_chest(原木) → craft(planks) → craft(planks)</t>
+        </is>
+      </c>
+      <c r="F159" s="7" t="inlineStr">
+        <is>
+          <t>新写</t>
+        </is>
+      </c>
+      <c r="G159" s="7" t="inlineStr">
+        <is>
+          <t>缺判据/动作(代码刀)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="7" t="inlineStr">
+        <is>
           <t>wife_make_iron_helmet</t>
         </is>
       </c>
-      <c r="B159" s="7" t="inlineStr">
+      <c r="B160" s="7" t="inlineStr">
         <is>
           <t>麦娘用箱子里 5 个铁锭给自己做一个铁头盔</t>
         </is>
       </c>
-      <c r="C159" s="7" t="inlineStr">
+      <c r="C160" s="7" t="inlineStr">
         <is>
           <t>M5-7</t>
         </is>
       </c>
-      <c r="D159" s="7" t="inlineStr">
+      <c r="D160" s="7" t="inlineStr">
         <is>
           <t>麦娘</t>
         </is>
       </c>
-      <c r="E159" s="7" t="inlineStr">
+      <c r="E160" s="7" t="inlineStr">
         <is>
           <t>go_home → take_from_chest(铁锭) → craft(iron_helmet)</t>
         </is>
       </c>
-      <c r="F159" s="7" t="inlineStr">
+      <c r="F160" s="7" t="inlineStr">
         <is>
           <t>新写</t>
         </is>
       </c>
-      <c r="G159" s="7" t="inlineStr">
+      <c r="G160" s="7" t="inlineStr">
         <is>
           <t>缺判据/动作(代码刀)</t>
         </is>
@@ -21329,7 +21366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E541"/>
+  <dimension ref="A1:E544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -35923,6 +35960,87 @@
       <c r="E541" s="7" t="inlineStr">
         <is>
           <t>已定(2026-09-18 约 16:50):5 个铁锭先给麦娘做铁头盔(铁镐、铁桶等学会挖铁再说)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B542" s="7" t="inlineStr">
+        <is>
+          <t>M3-3</t>
+        </is>
+      </c>
+      <c r="C542" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D542" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 加盖房硬约束:不把自己关在里面、不堵门、被拒 3 次换块</t>
+        </is>
+      </c>
+      <c r="E542" s="7" t="inlineStr">
+        <is>
+          <t>平级会话实测小麦被困;根因待 fork 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B543" s="7" t="inlineStr">
+        <is>
+          <t>M3-4</t>
+        </is>
+      </c>
+      <c r="C543" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D543" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 加盖房硬约束:不把自己关在里面、不堵门、被拒 3 次换块</t>
+        </is>
+      </c>
+      <c r="E543" s="7" t="inlineStr">
+        <is>
+          <t>平级会话实测小麦被困;根因待 fork 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B544" s="7" t="inlineStr">
+        <is>
+          <t>wife_logs_to_planks</t>
+        </is>
+      </c>
+      <c r="C544" s="7" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="D544" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 麦娘从箱子拿原木做成 8 块同种木板(缺锄头或没地方存粮时)</t>
+        </is>
+      </c>
+      <c r="E544" s="7" t="inlineStr">
+        <is>
+          <t>平级会话实测:wife_take_planks 10 次只成 1 次,箱子里只有原木。先存后拿、连做两次 → 8 块同种木板(minecraft-data 每张</t>
         </is>
       </c>
     </row>

--- a/ai-player/goal-table/小麦家族工作分解-填写版.xlsx
+++ b/ai-player/goal-table/小麦家族工作分解-填写版.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:L120"/>
+  <dimension ref="A2:L121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>🔴 盖房硬约束(2026-09-18 实测小麦被自己的房子关住,20 分钟失败 110 次):① 任何一步都不许把方块放进盖房人正站的格子、头顶那格和门洞;② 每放一块之前,代码先算「放完以后我还走得出去吗」(站的格子到屋外有通路),走不出去就先走出去再放;③ 同一块连着被服务器拒绝 3 次,就换下一块或收工,不原地重试。这三条由代码判断,不问模型。 ⏳ 过渡:搬家(拍板第 1 件)定之前,挂在这里的 build_house / get_build_mats / son_take_mats 仍在现在的家把房子盖完(线上老行为,不倒退);定了搬以后改成在新家址盖。 门是 2 格高的物品，要点门洞下面那块地面的顶面放，朝向跟人的朝向走。墙的判定只看实心不实心，不看方块名（泥土长成草那次的教训）。站位必须站在墙格以外的格子上，不能用「离中心多远」来判断。僵尸自己开不了木门。</t>
+          <t>🔴 放方块硬约束(补充):④「在不在屋里 / 在不在盖房的位置」必须连高度一起算,站在屋顶上不算在屋里,不许从没封好的屋顶洞穿过;⑤ 门洞那一列永远空着,什么都不许放(包括会掉下来填进去的方块);⑥ 盖房材料排除会下落的方块(沙子、红沙、沙砾、各色混凝土粉末、铁砧等),没有别的材料就不盖;⑦ 服务器拒绝过的格子永久划掉,房子可以算「完成(跳过 N 格)」,否则脚本会一直把人派回去;⑧ 开工前先查目标格在不在别人的领地里,在就标「这里做不了」、不去试。麦家现在没有任何领地(Owner 定的),所以【任何领地都是别人的】—— 数据来源待定:服务器拒绝记录,或后台导出领地范围。 🔴 盖房硬约束(2026-09-18 实测小麦被自己的房子关住,20 分钟失败 110 次):① 任何一步都不许把方块放进盖房人正站的格子、头顶那格和门洞;② 每放一块之前,代码先算「放完以后我还走得出去吗」(站的格子到屋外有通路),走不出去就先走出去再放;③ 同一块连着被服务器拒绝 3 次,就换下一块或收工,不原地重试。这三条由代码判断,不问模型。 ⏳ 过渡:搬家(拍板第 1 件)定之前,挂在这里的 build_house / get_build_mats / son_take_mats 仍在现在的家把房子盖完(线上老行为,不倒退);定了搬以后改成在新家址盖。 门是 2 格高的物品，要点门洞下面那块地面的顶面放，朝向跟人的朝向走。墙的判定只看实心不实心，不看方块名（泥土长成草那次的教训）。站位必须站在墙格以外的格子上，不能用「离中心多远」来判断。僵尸自己开不了木门。</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>游戏里任何人都能睡任何一张没人占的床，「这是谁的床」只是我们自己记的账。重生点跟着最后睡过的那张床走；两个人不能同时睡一张床（会提示床已被占用）。现在的 sleep 只在 24 格内一张床都没有时才自己摆床，所以结构上只摆得出第一张，第二、第三张只能靠 place_bed。麦豆没有合成动作，也没有把东西交给别人的动作，所以他的床只能由做床的人直接摆进屋。</t>
+          <t>🔴 床的硬约束:只睡自己或自家的床(自己放的、或 family.json 登记的),绝不躺别人的床(实测挑中了孩子领地里孩子的床);「走得到」要用真实路径算 —— 寻路的 goto 把「没有路」也当成功。 🔴 放方块硬约束(补充):④「在不在屋里 / 在不在盖房的位置」必须连高度一起算,站在屋顶上不算在屋里,不许从没封好的屋顶洞穿过;⑤ 门洞那一列永远空着,什么都不许放(包括会掉下来填进去的方块);⑥ 盖房材料排除会下落的方块(沙子、红沙、沙砾、各色混凝土粉末、铁砧等),没有别的材料就不盖;⑦ 服务器拒绝过的格子永久划掉,房子可以算「完成(跳过 N 格)」,否则脚本会一直把人派回去;⑧ 开工前先查目标格在不在别人的领地里,在就标「这里做不了」、不去试。麦家现在没有任何领地(Owner 定的),所以【任何领地都是别人的】—— 数据来源待定:服务器拒绝记录,或后台导出领地范围。 游戏里任何人都能睡任何一张没人占的床，「这是谁的床」只是我们自己记的账。重生点跟着最后睡过的那张床走；两个人不能同时睡一张床（会提示床已被占用）。现在的 sleep 只在 24 格内一张床都没有时才自己摆床，所以结构上只摆得出第一张，第二、第三张只能靠 place_bed。麦豆没有合成动作，也没有把东西交给别人的动作，所以他的床只能由做床的人直接摆进屋。</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
-          <t>🔴 盖房硬约束(2026-09-18 实测小麦被自己的房子关住,20 分钟失败 110 次):① 任何一步都不许把方块放进盖房人正站的格子、头顶那格和门洞;② 每放一块之前,代码先算「放完以后我还走得出去吗」(站的格子到屋外有通路),走不出去就先走出去再放;③ 同一块连着被服务器拒绝 3 次,就换下一块或收工,不原地重试。这三条由代码判断,不问模型。 1.18 起，敌对怪只在方块光照为 0 的地方刷，而且刷不到底半砖上（顶半砖和双层半砖上能刷）。人站在半砖上眼睛高出 0.5 格；放方块的伸手距离是 3.6 时，屋顶格在水平约 3.3 格内都够得着。对着同种底半砖的顶面再放一块，会合成双层半砖（完整方块，能刷怪），所以 placeAt「放之前先看目标格是不是空的」这条不能绕过。</t>
+          <t>🔴 放方块硬约束(补充):④「在不在屋里 / 在不在盖房的位置」必须连高度一起算,站在屋顶上不算在屋里,不许从没封好的屋顶洞穿过;⑤ 门洞那一列永远空着,什么都不许放(包括会掉下来填进去的方块);⑥ 盖房材料排除会下落的方块(沙子、红沙、沙砾、各色混凝土粉末、铁砧等),没有别的材料就不盖;⑦ 服务器拒绝过的格子永久划掉,房子可以算「完成(跳过 N 格)」,否则脚本会一直把人派回去;⑧ 开工前先查目标格在不在别人的领地里,在就标「这里做不了」、不去试。麦家现在没有任何领地(Owner 定的),所以【任何领地都是别人的】—— 数据来源待定:服务器拒绝记录,或后台导出领地范围。 🔴 盖房硬约束(2026-09-18 实测小麦被自己的房子关住,20 分钟失败 110 次):① 任何一步都不许把方块放进盖房人正站的格子、头顶那格和门洞;② 每放一块之前,代码先算「放完以后我还走得出去吗」(站的格子到屋外有通路),走不出去就先走出去再放;③ 同一块连着被服务器拒绝 3 次,就换下一块或收工,不原地重试。这三条由代码判断,不问模型。 1.18 起，敌对怪只在方块光照为 0 的地方刷，而且刷不到底半砖上（顶半砖和双层半砖上能刷）。人站在半砖上眼睛高出 0.5 格；放方块的伸手距离是 3.6 时，屋顶格在水平约 3.3 格内都够得着。对着同种底半砖的顶面再放一块，会合成双层半砖（完整方块，能刷怪），所以 placeAt「放之前先看目标格是不是空的」这条不能绕过。</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
-          <t>GP 在本服的设定是「新玩家放第一个箱子，自动圈一块半径 4 的地」。2026-09-18 已把两个 AI 账号的 griefprevention.createclaims 设成 false，按设计能挡住这条路，但没在游戏里实测过，麦豆的账号也不一定在那两个里面，所以只让麦娘放箱子，并且放完第一个就核对。箱子正上方要留空才能打开（放在半砖上的箱子，头顶还有 1 格空，够用）。Java 版里床和箱子都能放在半砖上，下面会空出半格，这是正常的。工作台顶面是完整方块，放在墙角、垫在半砖上以后，头顶只剩 1 格：僵尸、骷髅、苦力怕都太高；蜘蛛宽 1.4 格，被两面墙挡住，所以不会刷怪。</t>
+          <t>🔴 放方块硬约束(补充):④「在不在屋里 / 在不在盖房的位置」必须连高度一起算,站在屋顶上不算在屋里,不许从没封好的屋顶洞穿过;⑤ 门洞那一列永远空着,什么都不许放(包括会掉下来填进去的方块);⑥ 盖房材料排除会下落的方块(沙子、红沙、沙砾、各色混凝土粉末、铁砧等),没有别的材料就不盖;⑦ 服务器拒绝过的格子永久划掉,房子可以算「完成(跳过 N 格)」,否则脚本会一直把人派回去;⑧ 开工前先查目标格在不在别人的领地里,在就标「这里做不了」、不去试。麦家现在没有任何领地(Owner 定的),所以【任何领地都是别人的】—— 数据来源待定:服务器拒绝记录,或后台导出领地范围。 GP 在本服的设定是「新玩家放第一个箱子，自动圈一块半径 4 的地」。2026-09-18 已把两个 AI 账号的 griefprevention.createclaims 设成 false，按设计能挡住这条路，但没在游戏里实测过，麦豆的账号也不一定在那两个里面，所以只让麦娘放箱子，并且放完第一个就核对。箱子正上方要留空才能打开（放在半砖上的箱子，头顶还有 1 格空，够用）。Java 版里床和箱子都能放在半砖上，下面会空出半格，这是正常的。工作台顶面是完整方块，放在墙角、垫在半砖上以后，头顶只剩 1 格：僵尸、骷髅、苦力怕都太高；蜘蛛宽 1.4 格，被两面墙挡住，所以不会刷怪。</t>
         </is>
       </c>
     </row>
@@ -4176,28 +4176,24 @@
     <row r="87">
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A29</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>三人一套规矩(Owner 2026-09-18):手上有剑、血 ≥14 才开打(已在打的血 &gt;10 可以继续);只打普通怪(僵尸、尸壳、僵尸村民、蜘蛛;溺尸只在它上岸时打);8 格内怪 ≤2 只;8 格内没有苦力怕;自己不在水里;不是刚复活;目标旁边 3 格内没有真人、宠物、马、村民(Owner 16:50)。其余一律跑。</t>
+          <t>卡住自救(常驻,三人):不管手上有没有活、是不是在「没事干」,只要位置超过 75 秒没动、又没有反射在处理(打、跑、游、睡),就触发卡住自救。等活不是关掉自救的理由。</t>
         </is>
       </c>
       <c r="D87" s="7" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="E87" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F87" s="7" t="inlineStr">
-        <is>
-          <t>J-A2-1, J-A2-2, J-A2-3, J-A2-4</t>
-        </is>
-      </c>
+      <c r="F87" s="7" t="inlineStr"/>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>最近近战怪距离 ≤ 4</t>
+          <t>原地不动秒数 ≥ 75 并且 反射在处理 = 0</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
@@ -4207,24 +4203,24 @@
       </c>
       <c r="I87" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>要改代码(恢复被零候选兜底清零的计时)</t>
         </is>
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>对应 Owner 样板的 J-4。初稿查出的真 bug 保留:满血那一支没排除苦力怕(小麦被炸死33次、其中19次死前刚还击过)、HOSTILE_RE 含 enderman、反射层绕过执行闸让没有 fight 的麦娘还击664行。creaking 是 1.21.4 新怪,打它不掉血,只能跑。guard_home 用的是恒为0的判据、1189次接活一次没开工,直接退役,不再挂在这里。</t>
+          <t>实测:这条自救以前 40 次成功 35 次(61~164 秒内拉出来);05:17 JST 零候选兜底上线后,兜底每一拍都把「卡住计时」清零,40 分钟里 0 次触发,小麦被自己的房子关住出不来。fork 1 查实(2026-09-18):小麦从没封好的屋顶洞掉进屋里(「在不在屋里」只看平面);洞那一列在孩子的领地里,服务器拒了 379 次,程序从不划掉被拒的格子;门口一列疑被下落的沙堵住;零候选兜底每拍清零「卡住计时」,75 秒自救从 05:17 起再没触发(之前 40 次成 35 次);睡觉挑最近的床,挑中了孩子领地里孩子的床。</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>A19</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>（原 T9，改成不问模型）背包只剩 2 格以内时，按代码里的物品表处理：有用的回家存箱子，明确的杂物扔掉，不认识的一律先存；钻石、铁、金、附魔的、带名字的、别人送的，永远不扔；箱子也满了，就在后台告诉您。</t>
+          <t>三人一套规矩(Owner 2026-09-18):手上有剑、血 ≥14 才开打(已在打的血 &gt;10 可以继续);只打普通怪(僵尸、尸壳、僵尸村民、蜘蛛;溺尸只在它上岸时打);8 格内怪 ≤2 只;8 格内没有苦力怕;自己不在水里;不是刚复活;目标旁边 3 格内没有真人、宠物、马、村民(Owner 16:50)。其余一律跑。</t>
         </is>
       </c>
       <c r="D88" s="7" t="n">
@@ -4235,82 +4231,82 @@
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>store_wood, wife_store</t>
+          <t>J-A2-1, J-A2-2, J-A2-3, J-A2-4</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>背包空格 ≤ 2</t>
+          <t>最近近战怪距离 ≤ 4</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>任意</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="I88" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
       <c r="J88" s="7" t="inlineStr">
         <is>
-          <t>🔴 现在的 JUNK_RE 里有 rotten_flesh（腐肉），而另一处 EMERGENCY_FOOD_RE 把腐肉当救命粮（实测机器人曾抱着 27 块腐肉饿死）。同一样东西两份判据打架，是现存的 bug。bone（骨头）也在 JUNK_RE 里，但它能做骨粉催熟小麦，G1 种田用得上；虽然现在还没有「施骨粉」动作，也应该先存不扔。背包 36 格全满时，collectblock 当场抛错，砍树每次都失败（已查实），所以腾格子是硬需求。🔴 麦豆的 roles.json 里没有 store_items，他只能扔杂物、存不了东西。原稿让模型逐样给物品归类并永久存盘，但 1.21.4 物品名单是封闭的，归类是事实判断，不该问模型；兜底「全部存」和代码默认一样，问了也不改变结果。请和 A 层统一编号。</t>
+          <t>对应 Owner 样板的 J-4。初稿查出的真 bug 保留:满血那一支没排除苦力怕(小麦被炸死33次、其中19次死前刚还击过)、HOSTILE_RE 含 enderman、反射层绕过执行闸让没有 fight 的麦娘还击664行。creaking 是 1.21.4 新怪,打它不掉血,只能跑。guard_home 用的是恒为0的判据、1189次接活一次没开工,直接退役,不再挂在这里。</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>A19</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>不站着挨冷箭:被远程怪盯上时先挡箭再拉开距离;血少就传送走。射箭的怪走到面前也不冲上去砍(Owner 16:50「挡箭并跑开」)。麦豆不放挡箭方块,只跑。</t>
+          <t>（原 T9，改成不问模型）背包只剩 2 格以内时，按代码里的物品表处理：有用的回家存箱子，明确的杂物扔掉，不认识的一律先存；钻石、铁、金、附魔的、带名字的、别人送的，永远不扔；箱子也满了，就在后台告诉您。</t>
         </is>
       </c>
       <c r="D89" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E89" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>J-A6-1, J-A6-2, J-A6-3</t>
+          <t>store_wood, wife_store</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>被远程怪盯上 = 1</t>
+          <t>背包空格 ≤ 2</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>全家</t>
+          <t>任意</t>
         </is>
       </c>
       <c r="I89" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
-          <t>骷髅射程约15格、Hard 约2秒一箭、一箭最多约5点;中间一格实心方块就挡住。bogged/ghast/breeze 不在现在的 HOSTILE_RE 里,要一起补。小麦日志里放过393块挡箭块(原木187、木板99、泥土107),代码里没有收回逻辑,收回归 A13。</t>
+          <t>🔴 现在的 JUNK_RE 里有 rotten_flesh（腐肉），而另一处 EMERGENCY_FOOD_RE 把腐肉当救命粮（实测机器人曾抱着 27 块腐肉饿死）。同一样东西两份判据打架，是现存的 bug。bone（骨头）也在 JUNK_RE 里，但它能做骨粉催熟小麦，G1 种田用得上；虽然现在还没有「施骨粉」动作，也应该先存不扔。背包 36 格全满时，collectblock 当场抛错，砍树每次都失败（已查实），所以腾格子是硬需求。🔴 麦豆的 roles.json 里没有 store_items，他只能扔杂物、存不了东西。原稿让模型逐样给物品归类并永久存盘，但 1.21.4 物品名单是封闭的，归类是事实判断，不该问模型；兜底「全部存」和代码默认一样，问了也不改变结果。请和 A 层统一编号。</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>A15</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>天黑要睡时床边有怪：小麦在稳妥时先把好打的怪清掉；其它情况（以及麦娘、麦豆）回屋里等，床边一空 A4 自己接着去睡</t>
+          <t>不站着挨冷箭:被远程怪盯上时先挡箭再拉开距离;血少就传送走。射箭的怪走到面前也不冲上去砍(Owner 16:50「挡箭并跑开」)。麦豆不放挡箭方块,只跑。</t>
         </is>
       </c>
       <c r="D90" s="7" t="n">
@@ -4321,12 +4317,12 @@
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>J-A15-1, J-A15-2</t>
+          <t>J-A6-1, J-A6-2, J-A6-3</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>天黑了 = 1 并且 今晚睡着过 = 0 并且 我有自己的床 = 1 并且 我的床边有怪 ≥ 1 并且 在主世界 = 1</t>
+          <t>被远程怪盯上 = 1</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
@@ -4341,19 +4337,19 @@
       </c>
       <c r="J90" s="7" t="inlineStr">
         <is>
-          <t>「附近有怪不能睡」只看距离不看墙：墙外 8 格内的僵尸照样让你睡不着。盒子向下算到 6 格，房子底下洞穴里的怪也会拦住你，而那种怪打不到。僵尸一旦盯上玩家（约 35 格内）就不会自己走开，常常要等到天亮被晒死。躺在床上时怪仍然能打到人。两条脚本优先级不同（清怪 1、躲 2），由代码直接选，不问模型。J-A5-1 和 A2（J-4）共用 fight 动作：A2 是挨打时还手，J-A5-1 是主动清床边。现有的 guard_home 也要补上「难缠的怪=0」。</t>
+          <t>骷髅射程约15格、Hard 约2秒一箭、一箭最多约5点;中间一格实心方块就挡住。bogged/ghast/breeze 不在现在的 HOSTILE_RE 里,要一起补。小麦日志里放过393块挡箭块(原木187、木板99、泥土107),代码里没有收回逻辑,收回归 A13。</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>A17</t>
+          <t>A15</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>进出新房以后，随手把门关上，免得夜里僵尸走进屋。</t>
+          <t>天黑要睡时床边有怪：小麦在稳妥时先把好打的怪清掉；其它情况（以及麦娘、麦豆）回屋里等，床边一空 A4 自己接着去睡</t>
         </is>
       </c>
       <c r="D91" s="7" t="n">
@@ -4364,12 +4360,12 @@
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>J-A17</t>
+          <t>J-A15-1, J-A15-2</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>新房门开着 = 1 并且 离门距离 ≥ 1.5 并且 离门距离 ≤ 4 并且 门洞里有别人 = 0</t>
+          <t>天黑了 = 1 并且 今晚睡着过 = 0 并且 我有自己的床 = 1 并且 我的床边有怪 ≥ 1 并且 在主世界 = 1</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
@@ -4384,35 +4380,35 @@
       </c>
       <c r="J91" s="7" t="inlineStr">
         <is>
-          <t>初稿的「门洞里有人」没有排除自己：自己刚走出门就站在门外那一格，条件不成立，门会一直开着。寻路器开门以后不会自己关；僵尸自己开不了木门。门开着，就又回到旧泥土房「门洞敞开、僵尸蹲在重生点」的老问题。</t>
+          <t>「附近有怪不能睡」只看距离不看墙：墙外 8 格内的僵尸照样让你睡不着。盒子向下算到 6 格，房子底下洞穴里的怪也会拦住你，而那种怪打不到。僵尸一旦盯上玩家（约 35 格内）就不会自己走开，常常要等到天亮被晒死。躺在床上时怪仍然能打到人。两条脚本优先级不同（清怪 1、躲 2），由代码直接选，不问模型。J-A5-1 和 A2（J-4）共用 fight 动作：A2 是挨打时还手，J-A5-1 是主动清床边。现有的 guard_home 也要补上「难缠的怪=0」。</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A17</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>血量保持在一半(10点)以上:掉到一半以下先脱险,再吃饱原地回血,回到14点才算好</t>
+          <t>进出新房以后，随手把门关上，免得夜里僵尸走进屋。</t>
         </is>
       </c>
       <c r="D92" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E92" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>J-A1-1, J-A1-2, J-A1-3</t>
+          <t>J-A17</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>血量 ≤ 9.99</t>
+          <t>新房门开着 = 1 并且 离门距离 ≥ 1.5 并且 离门距离 ≤ 4 并且 门洞里有别人 = 0</t>
         </is>
       </c>
       <c r="H92" s="7" t="inlineStr">
@@ -4427,19 +4423,19 @@
       </c>
       <c r="J92" s="7" t="inlineStr">
         <is>
-          <t>Hard 难度:饱食度≥18 才自然回血(每4秒1点),饱食度20且有饱和度时每0.5秒1点;回4点血约要吃掉6点饱食度(先扣饱和度),中途会掉到17而停止回血,所以回血脚本短等+重选。触发&lt;10、完成≥14 的缓冲只在 A 层;下面的 J 不再重复「血量≤9.99」。服务器 respawn-at-home=true,61% 死在家8格内 → 在家门口脱险必须去出生点。对应 Owner 样板的 J-3。</t>
+          <t>初稿的「门洞里有人」没有排除自己：自己刚走出门就站在门外那一格，条件不成立，门会一直开着。寻路器开门以后不会自己关；僵尸自己开不了木门。门开着，就又回到旧泥土房「门洞敞开、僵尸蹲在重生点」的老问题。</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>A16</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>新房盖好以后，墙、屋顶、地板或门被炸坏、被拆了，就回去按原样补上。只补计划里的那几格，不找人理论，也不在公屏说话。</t>
+          <t>血量保持在一半(10点)以上:掉到一半以下先脱险,再吃饱原地回血,回到14点才算好</t>
         </is>
       </c>
       <c r="D93" s="7" t="n">
@@ -4450,17 +4446,17 @@
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>J-A16</t>
+          <t>J-A1-1, J-A1-2, J-A1-3</t>
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>新房完工过 = 1 并且 新房缺口数 ≥ 1 并且 离新家址 ≤ 32 并且 天黑了 = 0 并且 8格内怪数 = 0</t>
+          <t>血量 ≤ 9.99</t>
         </is>
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="I93" s="7" t="inlineStr">
@@ -4470,48 +4466,91 @@
       </c>
       <c r="J93" s="7" t="inlineStr">
         <is>
-          <t>初稿用「房子盖好了 = 1 且 缺口 ≥ 1」：如果「盖好了」是现算的，有缺口时它就是 0，两条永远不能同时成立；所以改用只记一次、永不清除的「新房完工过」，旧判据「房子盖好了」的意思不动。初稿的「离家距离 ≤ 32」在搬家之前量的是旧家，改成「离新家址」，这样也顺带保证区块已加载、扫描是实时的。苦力怕爆炸会在墙上开洞；「困难」难度下僵尸会破木门，要查服务器难度。</t>
+          <t>Hard 难度:饱食度≥18 才自然回血(每4秒1点),饱食度20且有饱和度时每0.5秒1点;回4点血约要吃掉6点饱食度(先扣饱和度),中途会掉到17而停止回血,所以回血脚本短等+重选。触发&lt;10、完成≥14 的缓冲只在 A 层;下面的 J 不再重复「血量≤9.99」。服务器 respawn-at-home=true,61% 死在家8格内 → 在家门口脱险必须去出生点。对应 Owner 样板的 J-3。</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>A24</t>
+          <t>A16</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>家人在我附近（24 格内）被一两只普通的怪围着打，我血够（≥14）、手上有剑，就过去帮他把怪打掉，打完回去接着干原来的活。怪超过 3 只、有苦力怕、有打不动的强怪，或者是惹了才打人的狼、铁傀儡这类时不去 —— 那种时候他该跑，我去了只是多搭一个人。麦娘、麦豆去不去帮打以后再定(Owner 这次定的是「还手」,不是「去帮别人打」)。</t>
+          <t>新房盖好以后，墙、屋顶、地板或门被炸坏、被拆了，就回去按原样补上。只补计划里的那几格，不找人理论，也不在公屏说话。</t>
         </is>
       </c>
       <c r="D94" s="7" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="E94" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
+          <t>J-A16</t>
+        </is>
+      </c>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>新房完工过 = 1 并且 新房缺口数 ≥ 1 并且 离新家址 ≤ 32 并且 天黑了 = 0 并且 8格内怪数 = 0</t>
+        </is>
+      </c>
+      <c r="H94" s="7" t="inlineStr">
+        <is>
+          <t>小麦</t>
+        </is>
+      </c>
+      <c r="I94" s="7" t="inlineStr">
+        <is>
+          <t>判据动作都缺</t>
+        </is>
+      </c>
+      <c r="J94" s="7" t="inlineStr">
+        <is>
+          <t>🔴 放方块硬约束(补充):④「在不在屋里 / 在不在盖房的位置」必须连高度一起算,站在屋顶上不算在屋里,不许从没封好的屋顶洞穿过;⑤ 门洞那一列永远空着,什么都不许放(包括会掉下来填进去的方块);⑥ 盖房材料排除会下落的方块(沙子、红沙、沙砾、各色混凝土粉末、铁砧等),没有别的材料就不盖;⑦ 服务器拒绝过的格子永久划掉,房子可以算「完成(跳过 N 格)」,否则脚本会一直把人派回去;⑧ 开工前先查目标格在不在别人的领地里,在就标「这里做不了」、不去试。麦家现在没有任何领地(Owner 定的),所以【任何领地都是别人的】—— 数据来源待定:服务器拒绝记录,或后台导出领地范围。 初稿用「房子盖好了 = 1 且 缺口 ≥ 1」：如果「盖好了」是现算的，有缺口时它就是 0，两条永远不能同时成立；所以改用只记一次、永不清除的「新房完工过」，旧判据「房子盖好了」的意思不动。初稿的「离家距离 ≤ 32」在搬家之前量的是旧家，改成「离新家址」，这样也顺带保证区块已加载、扫描是实时的。苦力怕爆炸会在墙上开洞；「困难」难度下僵尸会破木门，要查服务器难度。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>A24</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>家人在我附近（24 格内）被一两只普通的怪围着打，我血够（≥14）、手上有剑，就过去帮他把怪打掉，打完回去接着干原来的活。怪超过 3 只、有苦力怕、有打不动的强怪，或者是惹了才打人的狼、铁傀儡这类时不去 —— 那种时候他该跑，我去了只是多搭一个人。麦娘、麦豆去不去帮打以后再定(Owner 这次定的是「还手」,不是「去帮别人打」)。</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E95" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
           <t>J-A24-1</t>
         </is>
       </c>
-      <c r="G94" s="7" t="inlineStr">
+      <c r="G95" s="7" t="inlineStr">
         <is>
           <t>我能去帮打的家人数 ≥ 1 并且 我是选中的帮手 = 1 并且 有剑 ≥ 1 并且 血量 ≥ 14 并且 饱食度 ≥ 8 并且 刚挨打 = 0</t>
         </is>
       </c>
-      <c r="H94" s="7" t="inlineStr">
+      <c r="H95" s="7" t="inlineStr">
         <is>
           <t>小麦（麦娘放行 fight 并有剑后也算）</t>
         </is>
       </c>
-      <c r="I94" s="7" t="inlineStr">
+      <c r="I95" s="7" t="inlineStr">
         <is>
           <t>判据动作都缺</t>
         </is>
       </c>
-      <c r="J94" s="7" t="inlineStr">
+      <c r="J95" s="7" t="inlineStr">
         <is>
           <t>【为什么用「刚挨打=0」】不用「8格内怪数=0」：家人就在我身边、怪离我 5~8 格时，我自己的 A2（4 格内才打）不管，用「8格内怪数」又会把 A24 挡住，两边都不动。所以只要求我自己没在挨打；我自己 4 格内的怪，照旧由 A2（优先级 3）先处理。
 【只打该打的】只打 A18 表里主动攻击的普通近战怪（亮处的蜘蛛只在他刚挨打时才算）。惹了才打人的中立怪（狼、铁傀儡、僵尸猪灵、末影人等）一律不碰 —— 打它们要么打不过，要么可能是别人养的。有名字、有主人的一律不打（C-SAF-20）。
@@ -4522,44 +4561,44 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="B95" s="7" t="inlineStr">
+    <row r="96">
+      <c r="B96" s="7" t="inlineStr">
         <is>
           <t>A22</t>
         </is>
       </c>
-      <c r="C95" s="7" t="inlineStr">
+      <c r="C96" s="7" t="inlineStr">
         <is>
           <t>有家人正要把东西递给我（送吃的、送工具，或者我替麦豆收他要存的东西），或者来接我回家时，我别乱跑：在原地（或回家在粮箱旁）站着等，东西丢到脚边就走上去捡；是来接我的，就跟着他走；替人收下的东西，马上回家存进箱子。</t>
         </is>
       </c>
-      <c r="D95" s="7" t="n">
+      <c r="D96" s="7" t="n">
         <v>5.7</v>
       </c>
-      <c r="E95" s="7" t="n">
+      <c r="E96" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F95" s="7" t="inlineStr">
+      <c r="F96" s="7" t="inlineStr">
         <is>
           <t>J-A22-1, J-A22-2, J-A22-3, J-A22-4</t>
         </is>
       </c>
-      <c r="G95" s="7" t="inlineStr">
+      <c r="G96" s="7" t="inlineStr">
         <is>
           <t>我在等家人交接 ≥ 1 并且 真有危险 = 0</t>
         </is>
       </c>
-      <c r="H95" s="7" t="inlineStr">
+      <c r="H96" s="7" t="inlineStr">
         <is>
           <t>全家</t>
         </is>
       </c>
-      <c r="I95" s="7" t="inlineStr">
+      <c r="I96" s="7" t="inlineStr">
         <is>
           <t>判据动作都缺</t>
         </is>
       </c>
-      <c r="J95" s="7" t="inlineStr">
+      <c r="J96" s="7" t="inlineStr">
         <is>
           <t>受助的人乱跑，送的人就追不上；A22 就是让他站住。站着等不算卡住（卡住秒数只在走路步骤里计，C-NAV-4）。有危险（刚挨打或 8 格内有怪）时 A22 不成立，先按 A1/A2/A5/A25 保命；危险过去后回到 A22，送的人看他跑远了，会等他或改成回家交。
 【捡东西】原版规则里，玩家丢出的东西 2 秒内谁都捡不起来，之后谁的身体先碰到（横向约 1 格内）谁捡，丢的人自己也能捡回去，所以送的人丢完会退开，我要走到落点上。背包一格都不空就捡不了：等东西时背包满了，先扔一样真正的杂物腾格（C-ITM-11）。只捡这一单丢在我 6 格内、种类和数量对得上的东西，别处地上的东西不因为这条去捡（可能是真人孩子的）。
@@ -4568,87 +4607,87 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="B96" s="7" t="inlineStr">
-        <is>
-          <t>A4</t>
-        </is>
-      </c>
-      <c r="C96" s="7" t="inlineStr">
-        <is>
-          <t>饿到饱食度≤6、或受了伤又没吃饱(&lt;18)时:先吃身上的,没有就回家拿粮箱里的面包,再没有才让小麦去打猎;吃到18才停</t>
-        </is>
-      </c>
-      <c r="D96" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="E96" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F96" s="7" t="inlineStr">
-        <is>
-          <t>J-A4-1, J-A4-2, J-A4-3</t>
-        </is>
-      </c>
-      <c r="G96" s="7" t="inlineStr">
-        <is>
-          <t>该吃东西了 = 1</t>
-        </is>
-      </c>
-      <c r="H96" s="7" t="inlineStr">
-        <is>
-          <t>全家</t>
-        </is>
-      </c>
-      <c r="I96" s="7" t="inlineStr">
-        <is>
-          <t>判据动作都缺</t>
-        </is>
-      </c>
-      <c r="J96" s="7" t="inlineStr">
-        <is>
-          <t>Hard 难度饱食度0时每4秒掉1点血,一直掉到饿死。面包=3小麦,回5点饱食度。🔴 1.6/1.7 在 brainTick 里,废 brainLoop 时必须一起搬进 A 调度器(饿死是小麦第二大死因)。三条都做不了时 A4 让出身体,只在后台记一次「A无路可走」,不问模型;缺粮的根子交给 G1(麦娘种田做面包)。夜里没吃的且饱食度&gt;2:J-A4-3 不成立 → 让给 A11 去睡(睡觉跳夜不掉饱食度)。家附近64格内常年零动物。「粮箱里有吃的」= 粮箱里的吃的份数≥1,和 A21/A28 用同一个函数、同一张正经吃的白名单(C-FAM-3),从没开过时判开工当 1。【家人互助】三条都做不了(身上没正经吃的,粮箱空了或我自己拿不到,又不是会打猎的小麦)时,我会出现在家族状态板的「等吃的家人」里:A21 由代码选一个身上有多的家人给我送来,或者替我去粮箱拿;我这边由 A22 原地(或回家在粮箱旁)站着等,把丢到脚边的吃的捡起来。现在麦豆既没有 take_from_chest 也没有家,他缺吃的全靠这一条。</t>
-        </is>
-      </c>
-    </row>
     <row r="97">
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>A21</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>家人身上没吃的、自己又拿不到时（粮箱空了、他不会开箱子，或者他回不了家），由代码挑一个家人给他送：32 格内走过去递给他；更远就两人都传送回家，在粮箱旁交；他没家时，白天走过去（96 格内）。送的人自己至少留 4 份（家人快饿死时留 2 份；麦娘人设要留家底，留 6 份），身上至少留 2 个面包。一次给 2~3 份，快饿死时 1 份也送。身上不够，就替他回家从粮箱拿 3 份再送。</t>
+          <t>饿到饱食度≤6、或受了伤又没吃饱(&lt;18)时:先吃身上的,没有就回家拿粮箱里的面包,再没有才让小麦去打猎;吃到18才停</t>
         </is>
       </c>
       <c r="D97" s="7" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="E97" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
+          <t>J-A4-1, J-A4-2, J-A4-3</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>该吃东西了 = 1</t>
+        </is>
+      </c>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>全家</t>
+        </is>
+      </c>
+      <c r="I97" s="7" t="inlineStr">
+        <is>
+          <t>判据动作都缺</t>
+        </is>
+      </c>
+      <c r="J97" s="7" t="inlineStr">
+        <is>
+          <t>Hard 难度饱食度0时每4秒掉1点血,一直掉到饿死。面包=3小麦,回5点饱食度。🔴 1.6/1.7 在 brainTick 里,废 brainLoop 时必须一起搬进 A 调度器(饿死是小麦第二大死因)。三条都做不了时 A4 让出身体,只在后台记一次「A无路可走」,不问模型;缺粮的根子交给 G1(麦娘种田做面包)。夜里没吃的且饱食度&gt;2:J-A4-3 不成立 → 让给 A11 去睡(睡觉跳夜不掉饱食度)。家附近64格内常年零动物。「粮箱里有吃的」= 粮箱里的吃的份数≥1,和 A21/A28 用同一个函数、同一张正经吃的白名单(C-FAM-3),从没开过时判开工当 1。【家人互助】三条都做不了(身上没正经吃的,粮箱空了或我自己拿不到,又不是会打猎的小麦)时,我会出现在家族状态板的「等吃的家人」里:A21 由代码选一个身上有多的家人给我送来,或者替我去粮箱拿;我这边由 A22 原地(或回家在粮箱旁)站着等,把丢到脚边的吃的捡起来。现在麦豆既没有 take_from_chest 也没有家,他缺吃的全靠这一条。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>A21</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>家人身上没吃的、自己又拿不到时（粮箱空了、他不会开箱子，或者他回不了家），由代码挑一个家人给他送：32 格内走过去递给他；更远就两人都传送回家，在粮箱旁交；他没家时，白天走过去（96 格内）。送的人自己至少留 4 份（家人快饿死时留 2 份；麦娘人设要留家底，留 6 份），身上至少留 2 个面包。一次给 2~3 份，快饿死时 1 份也送。身上不够，就替他回家从粮箱拿 3 份再送。</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E98" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
           <t>J-A21-1, J-A21-2, J-A21-3</t>
         </is>
       </c>
-      <c r="G97" s="7" t="inlineStr">
+      <c r="G98" s="7" t="inlineStr">
         <is>
           <t>等吃的家人数 ≥ 1 并且 我是选中的送吃的人 = 1 并且 血量 ≥ 12 并且 饱食度 ≥ 10 并且 8格内怪数 = 0</t>
         </is>
       </c>
-      <c r="H97" s="7" t="inlineStr">
+      <c r="H98" s="7" t="inlineStr">
         <is>
           <t>全家</t>
         </is>
       </c>
-      <c r="I97" s="7" t="inlineStr">
+      <c r="I98" s="7" t="inlineStr">
         <is>
           <t>判据动作都缺</t>
         </is>
       </c>
-      <c r="J97" s="7" t="inlineStr">
+      <c r="J98" s="7" t="inlineStr">
         <is>
           <t>【什么时候送】只在他自己拿不到时送。粮箱有吃的，而他有 take_from_chest、有家、回家没连着失败时，A4 的 J-A4-2 会让他自己传送回家拿，家人不替他跑腿。粮箱从没开过时当「有」，让他自己回去看；看到空了，快照变成 0，下一拍 A21 接手。麦豆现在既没有 take_from_chest 也没有家，他缺吃的全靠这条，多半由在家的麦娘走 J-A21-3。
 【谁送】见 C-FAM-5。先筛：在线、同一世界、没在被帮、手上没别的单、没在做比 A21 更急的 A、血≥12、饱食≥10、8 格内没怪、这单能给的份数≥1 或我能替他去粮箱拿=1。再排序：能就地交的先 → 能一次给够 3 份的先 → 离他近的先 → 能分出的多的先 → 小麦→麦娘→麦豆。几个人同时等吃的，按急的先、每个送的人只分一单。麦娘平时身上只留 3 个面包（store_crop），低于她的保底，所以她基本不从自己身上分，而是替人去粮箱拿 —— 她就在家附近，正合适。
@@ -4661,74 +4700,31 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="B98" s="7" t="inlineStr">
-        <is>
-          <t>A3</t>
-        </is>
-      </c>
-      <c r="C98" s="7" t="inlineStr">
-        <is>
-          <t>中毒或凋零了:身上有牛奶就喝;没有就吃饱、原地别冒险,等它过去</t>
-        </is>
-      </c>
-      <c r="D98" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="E98" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F98" s="7" t="inlineStr">
-        <is>
-          <t>J-A3-1, J-A3-2</t>
-        </is>
-      </c>
-      <c r="G98" s="7" t="inlineStr">
-        <is>
-          <t>身上有坏效果 ≥ 1</t>
-        </is>
-      </c>
-      <c r="H98" s="7" t="inlineStr">
-        <is>
-          <t>全家</t>
-        </is>
-      </c>
-      <c r="I98" s="7" t="inlineStr">
-        <is>
-          <t>判据动作都缺</t>
-        </is>
-      </c>
-      <c r="J98" s="7" t="inlineStr">
-        <is>
-          <t>中毒 I 每1.25秒扣1点,扣到1点就停,毒本身杀不死人;凋零 I 每2秒扣1点,能致死。来源:洞穴蜘蛛(Hard 15秒)、女巫毒药水、bogged 毒箭(4秒)、河豚/毒土豆/蜘蛛眼;凋零只来自凋灵骷髅和凋灵玫瑰。腐肉给的是饥饿不是中毒,不归这里。真危险是毒把血压到1后再挨一下,所以核心是中毒期间不冒险。血&lt;10 时 A1 优先接手,做的也是吃+歇,两边一致。</t>
-        </is>
-      </c>
-    </row>
     <row r="99">
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>不在一个地方空转:该走路却75秒没挪窝,或头顶被盖住45秒 → 传送走(人在家门口就去出生点,不在家里反复传送)</t>
+          <t>中毒或凋零了:身上有牛奶就喝;没有就吃饱、原地别冒险,等它过去</t>
         </is>
       </c>
       <c r="D99" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E99" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>J-A10-1</t>
+          <t>J-A3-1, J-A3-2</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>卡住秒数 ≥ 75</t>
+          <t>身上有坏效果 ≥ 1</t>
         </is>
       </c>
       <c r="H99" s="7" t="inlineStr">
@@ -4743,48 +4739,91 @@
       </c>
       <c r="J99" s="7" t="inlineStr">
         <is>
-          <t>麦娘199次卡住自救里65次和上一次隔≤100秒,疑似就是「在家门口卡住 → 传送回家 → 原地再卡」;escape_tp 在离家≤8时选出生点,正好断开这个循环。不挖路、不垫方块。</t>
+          <t>中毒 I 每1.25秒扣1点,扣到1点就停,毒本身杀不死人;凋零 I 每2秒扣1点,能致死。来源:洞穴蜘蛛(Hard 15秒)、女巫毒药水、bogged 毒箭(4秒)、河豚/毒土豆/蜘蛛眼;凋零只来自凋灵骷髅和凋灵玫瑰。腐肉给的是饥饿不是中毒,不归这里。真危险是毒把血压到1后再挨一下,所以核心是中毒期间不冒险。血&lt;10 时 A1 优先接手,做的也是吃+歇,两边一致。</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>A26</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>家人走丢了、自己又回不来（没有家，或者连着两次传送回家都失败），离家超过 64 格已经 3 分钟：白天、离天黑还够 5 分钟时，由小麦走过去找他，领着他走回家（麦娘只去 48 格以内）。天黑前还没到家就先放弃，第二天再来。卡在坑里出不来的，只报给您，不挖不拆。前提是他会跟着家人走。</t>
+          <t>不在一个地方空转:该走路却75秒没挪窝,或头顶被盖住45秒 → 传送走(人在家门口就去出生点,不在家里反复传送)</t>
         </is>
       </c>
       <c r="D100" s="7" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="E100" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
+          <t>J-A10-1</t>
+        </is>
+      </c>
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>卡住秒数 ≥ 75</t>
+        </is>
+      </c>
+      <c r="H100" s="7" t="inlineStr">
+        <is>
+          <t>全家</t>
+        </is>
+      </c>
+      <c r="I100" s="7" t="inlineStr">
+        <is>
+          <t>判据动作都缺</t>
+        </is>
+      </c>
+      <c r="J100" s="7" t="inlineStr">
+        <is>
+          <t>麦娘199次卡住自救里65次和上一次隔≤100秒,疑似就是「在家门口卡住 → 传送回家 → 原地再卡」;escape_tp 在离家≤8时选出生点,正好断开这个循环。不挖路、不垫方块。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>A26</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>家人走丢了、自己又回不来（没有家，或者连着两次传送回家都失败），离家超过 64 格已经 3 分钟：白天、离天黑还够 5 分钟时，由小麦走过去找他，领着他走回家（麦娘只去 48 格以内）。天黑前还没到家就先放弃，第二天再来。卡在坑里出不来的，只报给您，不挖不拆。前提是他会跟着家人走。</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E101" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
           <t>J-A26-1, J-A26-2</t>
         </is>
       </c>
-      <c r="G100" s="7" t="inlineStr">
+      <c r="G101" s="7" t="inlineStr">
         <is>
           <t>回不了家的家人数 ≥ 1 并且 我是选中的接人的 = 1 并且 离回不了家的家人距离 ≤ 160 并且 被接的人能跟着家人走 = 1 并且 天黑了 = 0 并且 离天黑秒数 ≥ 300 并且 血量 ≥ 14 并且 饱食度 ≥ 14 并且 正经吃的份数 ≥ 2 并且 在主世界 = 1</t>
         </is>
       </c>
-      <c r="H100" s="7" t="inlineStr">
+      <c r="H101" s="7" t="inlineStr">
         <is>
           <t>小麦 / 麦娘（麦娘只接 48 格内）</t>
         </is>
       </c>
-      <c r="I100" s="7" t="inlineStr">
+      <c r="I101" s="7" t="inlineStr">
         <is>
           <t>判据动作都缺</t>
         </is>
       </c>
-      <c r="J100" s="7" t="inlineStr">
+      <c r="J101" s="7" t="inlineStr">
         <is>
           <t>【只接他自己回不来的】平时走丢由他自己解决：A20 离家≥100 格就传送回家，A10 卡住就 escape_tp。这一条只管他自己回不来的情况，主要是麦豆：他的 roles.json 没有 set_home，Owner 没替他 /sethome MaiDou:base 的话，他的 go_home 一定失败（C-PRM-5）。「全家的家」= 小麦状态板上的家，小麦没有就用麦娘的。
 【他不会跟人走就不去】C-FAM-19 放行之前，「被接的人能跟着家人走」=0，这条不开工，免得小麦白走 160 格。
@@ -4794,58 +4833,15 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="B101" s="7" t="inlineStr">
-        <is>
-          <t>A11</t>
-        </is>
-      </c>
-      <c r="C101" s="7" t="inlineStr">
-        <is>
-          <t>天黑了:有自家的空床就去睡;没有但身上材料够,先做一张再睡;家里能安全过夜就回屋待着;都不行就不硬回家(回家=回死亡点)</t>
-        </is>
-      </c>
-      <c r="D101" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="E101" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F101" s="7" t="inlineStr">
-        <is>
-          <t>J-A11-1, J-A11-2, J-A11-3, child_home, sleep_night</t>
-        </is>
-      </c>
-      <c r="G101" s="7" t="inlineStr">
-        <is>
-          <t>天黑了 = 1 并且 在主世界 = 1</t>
-        </is>
-      </c>
-      <c r="H101" s="7" t="inlineStr">
-        <is>
-          <t>全家</t>
-        </is>
-      </c>
-      <c r="I101" s="7" t="inlineStr">
-        <is>
-          <t>判据动作都缺</t>
-        </is>
-      </c>
-      <c r="J101" s="7" t="inlineStr">
-        <is>
-          <t>游戏时间 12542~23459 能睡（雷雨天随时能睡）；8 格内（上下 5 格）有怪睡不着。一张床只能躺一人。床 = 3 块同色羊毛 + 3 块木板；4 根线 = 1 块白羊毛，箱子里的 48 根线 = 12 块羊毛 = 4 张床（做床归 G2）。垃圾清单 JUNK_RE 里的 white_wool 必须去掉。默认要所有在线玩家都睡着才跳夜：机器人不睡，真人孩子也跳不过夜。要不要给机器人 essentials.sleepingignored 是全服设置，交 Owner。3 天没睡，夜里会刷幻翼。困难难度僵尸能破木门，门用栅栏门（4 木棍 + 2 木板）。sleep_night、child_home 挂到这里后，要从原大目标下摘掉。🔴 只在主世界触发（C-NAV-23）：床在下界、末地会爆炸；在资源世界睡会把重生点设进会重置的世界；下界、末地没有白天黑夜，主世界天黑时把远征中的小麦拉回家也不对（J-A11-3 的回屋 = /home base 传送）。小麦从下界回到主世界时如果是夜里，这条照常接管。</t>
-        </is>
-      </c>
-    </row>
     <row r="102">
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>A20</t>
+          <t>A11</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>别走丢:在主世界离家 ≥100 格、又不在探路时,就回家</t>
+          <t>天黑了:有自家的空床就去睡;没有但身上材料够,先做一张再睡;家里能安全过夜就回屋待着;都不行就不硬回家(回家=回死亡点)</t>
         </is>
       </c>
       <c r="D102" s="7" t="n">
@@ -4856,68 +4852,111 @@
       </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>J-A20</t>
+          <t>J-A11-1, J-A11-2, J-A11-3, child_home, sleep_night</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>离家距离 ≥ 100 并且 在主世界 = 1 并且 正在探路 = 0 并且 我有家 = 1 并且 近10分钟回家失败次数 ≤ 1</t>
+          <t>天黑了 = 1 并且 在主世界 = 1</t>
         </is>
       </c>
       <c r="H102" s="7" t="inlineStr">
         <is>
-          <t>任意</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="I102" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
       <c r="J102" s="7" t="inlineStr">
         <is>
-          <t>go_home 每次失败(没有家、传送冷却、被打断)都记进家族状态板的「近10分钟回家失败次数」(C-FAM-13)。触发里有「我有家=1」「近10分钟回家失败次数≤1」:没有家就根本不试,连着失败 2 次就停手 10 分钟,不在原地空转。回不来的人,离全家的家≥64 格满 3 分钟后,由 A26 让小麦(48 格内也可以是麦娘)白天走过去接他、领他走回家 —— 前提是他会「跟着家人走」(C-FAM-19)。麦豆 roles.json 没有 set_home,Owner 没替他 /sethome MaiDou:base 的话,他的 go_home 一定失败,走丢时只能靠 A26。</t>
+          <t>🔴 床的硬约束:只睡自己或自家的床(自己放的、或 family.json 登记的),绝不躺别人的床(实测挑中了孩子领地里孩子的床);「走得到」要用真实路径算 —— 寻路的 goto 把「没有路」也当成功。 游戏时间 12542~23459 能睡（雷雨天随时能睡）；8 格内（上下 5 格）有怪睡不着。一张床只能躺一人。床 = 3 块同色羊毛 + 3 块木板；4 根线 = 1 块白羊毛，箱子里的 48 根线 = 12 块羊毛 = 4 张床（做床归 G2）。垃圾清单 JUNK_RE 里的 white_wool 必须去掉。默认要所有在线玩家都睡着才跳夜：机器人不睡，真人孩子也跳不过夜。要不要给机器人 essentials.sleepingignored 是全服设置，交 Owner。3 天没睡，夜里会刷幻翼。困难难度僵尸能破木门，门用栅栏门（4 木棍 + 2 木板）。sleep_night、child_home 挂到这里后，要从原大目标下摘掉。🔴 只在主世界触发（C-NAV-23）：床在下界、末地会爆炸；在资源世界睡会把重生点设进会重置的世界；下界、末地没有白天黑夜，主世界天黑时把远征中的小麦拉回家也不对（J-A11-3 的回屋 = /home base 传送）。小麦从下界回到主世界时如果是夜里，这条照常接管。</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>A23</t>
+          <t>A20</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>家人缺干活的家伙、我手上有多的就送他 —— 🔴 代码里没有递东西的动作(giveTo 只给吃的和木头,剑存不进箱子),剑和锄头眼下只能各做各的,这一条先搁着</t>
+          <t>别走丢:在主世界离家 ≥100 格、又不在探路时,就回家</t>
         </is>
       </c>
       <c r="D103" s="7" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="E103" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
+          <t>J-A20</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>离家距离 ≥ 100 并且 在主世界 = 1 并且 正在探路 = 0 并且 我有家 = 1 并且 近10分钟回家失败次数 ≤ 1</t>
+        </is>
+      </c>
+      <c r="H103" s="7" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="I103" s="7" t="inlineStr">
+        <is>
+          <t>缺判据</t>
+        </is>
+      </c>
+      <c r="J103" s="7" t="inlineStr">
+        <is>
+          <t>go_home 每次失败(没有家、传送冷却、被打断)都记进家族状态板的「近10分钟回家失败次数」(C-FAM-13)。触发里有「我有家=1」「近10分钟回家失败次数≤1」:没有家就根本不试,连着失败 2 次就停手 10 分钟,不在原地空转。回不来的人,离全家的家≥64 格满 3 分钟后,由 A26 让小麦(48 格内也可以是麦娘)白天走过去接他、领他走回家 —— 前提是他会「跟着家人走」(C-FAM-19)。麦豆 roles.json 没有 set_home,Owner 没替他 /sethome MaiDou:base 的话,他的 go_home 一定失败,走丢时只能靠 A26。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>A23</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>家人缺干活的家伙、我手上有多的就送他 —— 🔴 代码里没有递东西的动作(giveTo 只给吃的和木头,剑存不进箱子),剑和锄头眼下只能各做各的,这一条先搁着</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E104" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F104" s="7" t="inlineStr">
+        <is>
           <t>J-A23-1</t>
         </is>
       </c>
-      <c r="G103" s="7" t="inlineStr">
+      <c r="G104" s="7" t="inlineStr">
         <is>
           <t>我能补工具的家人数 ≥ 1 并且 我是选中的送工具的人 = 1 并且 能顺路交给他 = 1 并且 血量 ≥ 12 并且 8格内怪数 = 0</t>
         </is>
       </c>
-      <c r="H103" s="7" t="inlineStr">
+      <c r="H104" s="7" t="inlineStr">
         <is>
           <t>全家</t>
         </is>
       </c>
-      <c r="I103" s="7" t="inlineStr">
+      <c r="I104" s="7" t="inlineStr">
         <is>
           <t>判据动作都缺</t>
         </is>
       </c>
-      <c r="J103" s="7" t="inlineStr">
+      <c r="J104" s="7" t="inlineStr">
         <is>
           <t>【工具需求表】一份表（C-FAM-12）：剑给 roles.json 里有 fight 的人，锄头给有 till_soil 的人，以后的镐给有 mine 的人。「多余」= 那种工具的件数 −（我自己用得上 ? 1 : 0），所以不会打架的人手上的剑全算多余（比如麦娘做的、麦豆捡的）。
 【送哪把】多余的里面剩余耐久最高的那把；自己留着的是最好的一把。剑不叠放，他背包得有 1 个空格（看状态板）。
@@ -4927,87 +4966,87 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="B104" s="7" t="inlineStr">
-        <is>
-          <t>A12</t>
-        </is>
-      </c>
-      <c r="C104" s="7" t="inlineStr">
-        <is>
-          <t>背包至少留4个空格:满了先扔掉真正的杂物,再回家存箱子;箱子满了就再放一口箱子</t>
-        </is>
-      </c>
-      <c r="D104" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="E104" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F104" s="7" t="inlineStr">
-        <is>
-          <t>J-A12-1, J-A12-2, J-A12-3, J-A12-4, store_wood, wife_craft_chest, wife_store</t>
-        </is>
-      </c>
-      <c r="G104" s="7" t="inlineStr">
-        <is>
-          <t>背包空格 ≤ 1</t>
-        </is>
-      </c>
-      <c r="H104" s="7" t="inlineStr">
-        <is>
-          <t>全家</t>
-        </is>
-      </c>
-      <c r="I104" s="7" t="inlineStr">
-        <is>
-          <t>判据动作都缺</t>
-        </is>
-      </c>
-      <c r="J104" s="7" t="inlineStr">
-        <is>
-          <t>背包36格一满,砍树第一下就被 collectblock 抛错。🔴 硬规则 2.5(空格≤1 → 回家存)在 brainTick 里,要和吃饭一起搬。排在最后,还要求血≥10、饱食度≥10,危险时根本抢不到身体。store_wood、wife_store、wife_craft_chest 挂到这里后,要从原大目标下摘掉。</t>
-        </is>
-      </c>
-    </row>
     <row r="105">
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>A27</t>
+          <t>A12</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>麦豆背包满了、自己又不会存箱子时，把能存的东西交给会存箱子的家人（先找麦娘）：她在 32 格内就当场交，两人都有家就回家交；接手的人收下后自己回家存进箱子。吃的、他唯一的工具和贵重东西不交。您如果同意教麦豆自己存箱子，这条就不用了。</t>
+          <t>背包至少留4个空格:满了先扔掉真正的杂物,再回家存箱子;箱子满了就再放一口箱子</t>
         </is>
       </c>
       <c r="D105" s="7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="E105" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
+          <t>J-A12-1, J-A12-2, J-A12-3, J-A12-4, store_wood, wife_craft_chest, wife_store</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>背包空格 ≤ 1</t>
+        </is>
+      </c>
+      <c r="H105" s="7" t="inlineStr">
+        <is>
+          <t>全家</t>
+        </is>
+      </c>
+      <c r="I105" s="7" t="inlineStr">
+        <is>
+          <t>判据动作都缺</t>
+        </is>
+      </c>
+      <c r="J105" s="7" t="inlineStr">
+        <is>
+          <t>背包36格一满,砍树第一下就被 collectblock 抛错。🔴 硬规则 2.5(空格≤1 → 回家存)在 brainTick 里,要和吃饭一起搬。排在最后,还要求血≥10、饱食度≥10,危险时根本抢不到身体。store_wood、wife_store、wife_craft_chest 挂到这里后,要从原大目标下摘掉。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>A27</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>麦豆背包满了、自己又不会存箱子时，把能存的东西交给会存箱子的家人（先找麦娘）：她在 32 格内就当场交，两人都有家就回家交；接手的人收下后自己回家存进箱子。吃的、他唯一的工具和贵重东西不交。您如果同意教麦豆自己存箱子，这条就不用了。</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E106" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
           <t>J-A27-1, J-A27-2</t>
         </is>
       </c>
-      <c r="G105" s="7" t="inlineStr">
+      <c r="G106" s="7" t="inlineStr">
         <is>
           <t>我能自己存 = 0 并且 背包空格 ≤ 1 并且 可存的东西 ≥ 1 并且 帮存交接地点 ≥ 1 并且 8格内怪数 = 0 并且 血量 ≥ 10</t>
         </is>
       </c>
-      <c r="H105" s="7" t="inlineStr">
+      <c r="H106" s="7" t="inlineStr">
         <is>
           <t>麦豆</t>
         </is>
       </c>
-      <c r="I105" s="7" t="inlineStr">
+      <c r="I106" s="7" t="inlineStr">
         <is>
           <t>判据动作都缺</t>
         </is>
       </c>
-      <c r="J105" s="7" t="inlineStr">
+      <c r="J106" s="7" t="inlineStr">
         <is>
           <t>【为什么不是「提醒」】机器人不在公屏说话。家人之间的「提醒」就是家族状态板上的数字（背包空格），后台也看得到。会存箱子的人背包满了，都由自己的 A12/A19 解决，不需要别人帮。
 【为什么只管麦豆】麦豆 roles.json 里没有 store_items，背包满了只能扔杂物。满了以后，连家人送来的吃的都捡不起来（A22），所以才需要这条。
@@ -5017,87 +5056,87 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="B106" s="7" t="inlineStr">
-        <is>
-          <t>A13</t>
-        </is>
-      </c>
-      <c r="C106" s="7" t="inlineStr">
-        <is>
-          <t>我在外面临时放的挡箭块都收回来,不留在地上(对应「地上的木头太丑」)</t>
-        </is>
-      </c>
-      <c r="D106" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="E106" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F106" s="7" t="inlineStr">
-        <is>
-          <t>J-A13-1</t>
-        </is>
-      </c>
-      <c r="G106" s="7" t="inlineStr">
-        <is>
-          <t>挡箭块没收回 ≥ 1 并且 天黑了 = 0 并且 8格内怪数 = 0 并且 血量 ≥ 14</t>
-        </is>
-      </c>
-      <c r="H106" s="7" t="inlineStr">
-        <is>
-          <t>全家</t>
-        </is>
-      </c>
-      <c r="I106" s="7" t="inlineStr">
-        <is>
-          <t>判据动作都缺</t>
-        </is>
-      </c>
-      <c r="J106" s="7" t="inlineStr">
-        <is>
-          <t>只收自己登记过的方块,不碰任何别人的东西。历史上已经放的393块(原木187、木板99、泥土107)没有坐标记录,代码找不回来:要由人用 CoreProtect 查 XiaoMai 的放置记录列清单,交 Owner 决定拆不拆,不自动拆。</t>
-        </is>
-      </c>
-    </row>
     <row r="107">
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>A28</t>
+          <t>A13</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>回到家时，身上吃的多（超过 6 份）、粮箱里又不到 6 份，就顺手把多出来的放进粮箱（最多补到 12 份），让全家谁饿了都有得拿。先放熟肉，身上至少留 2 个面包。只在已经到家时做，不专程跑回来。</t>
+          <t>我在外面临时放的挡箭块都收回来,不留在地上(对应「地上的木头太丑」)</t>
         </is>
       </c>
       <c r="D107" s="7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="E107" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
+          <t>J-A13-1</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>挡箭块没收回 ≥ 1 并且 天黑了 = 0 并且 8格内怪数 = 0 并且 血量 ≥ 14</t>
+        </is>
+      </c>
+      <c r="H107" s="7" t="inlineStr">
+        <is>
+          <t>全家</t>
+        </is>
+      </c>
+      <c r="I107" s="7" t="inlineStr">
+        <is>
+          <t>判据动作都缺</t>
+        </is>
+      </c>
+      <c r="J107" s="7" t="inlineStr">
+        <is>
+          <t>只收自己登记过的方块,不碰任何别人的东西。历史上已经放的393块(原木187、木板99、泥土107)没有坐标记录,代码找不回来:要由人用 CoreProtect 查 XiaoMai 的放置记录列清单,交 Owner 决定拆不拆,不自动拆。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>A28</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>回到家时，身上吃的多（超过 6 份）、粮箱里又不到 6 份，就顺手把多出来的放进粮箱（最多补到 12 份），让全家谁饿了都有得拿。先放熟肉，身上至少留 2 个面包。只在已经到家时做，不专程跑回来。</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E108" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
           <t>J-A28-1</t>
         </is>
       </c>
-      <c r="G107" s="7" t="inlineStr">
+      <c r="G108" s="7" t="inlineStr">
         <is>
           <t>有粮箱 ≥ 1 并且 离家距离 ≤ 8 并且 粮箱里的吃的份数 ≤ 5 并且 我能存进粮箱的吃的 ≥ 3 并且 8格内怪数 = 0</t>
         </is>
       </c>
-      <c r="H107" s="7" t="inlineStr">
+      <c r="H108" s="7" t="inlineStr">
         <is>
           <t>全家</t>
         </is>
       </c>
-      <c r="I107" s="7" t="inlineStr">
+      <c r="I108" s="7" t="inlineStr">
         <is>
           <t>判据动作都缺</t>
         </is>
       </c>
-      <c r="J107" s="7" t="inlineStr">
+      <c r="J108" s="7" t="inlineStr">
         <is>
           <t>【粮箱是全家的饭桌】小麦打猎多出来的熟肉（他曾经身上揣着 66 块熟牛肉还在饿死）放进去，麦豆、麦娘饿了就有得拿，A21 的「替他去粮箱拿」也有东西可拿。
 【阈值错开，不会来回倒腾】A14：身上面包≤1 才去粮箱拿 3 个；A28：身上超过 6 份才往粮箱放，放完还留 6 份，其中至少 2 个面包（先放熟肉）；A21：送吃的自己留 4 份。
@@ -5106,110 +5145,72 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="3" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
         <is>
           <t>四、思考触发(只有这些条件成立时才去问模型;没有任何定时思考)</t>
         </is>
       </c>
-      <c r="B110" s="4" t="n"/>
-      <c r="C110" s="4" t="n"/>
-      <c r="D110" s="4" t="n"/>
-      <c r="E110" s="4" t="n"/>
-      <c r="F110" s="4" t="n"/>
-      <c r="G110" s="4" t="n"/>
-      <c r="H110" s="4" t="n"/>
-      <c r="I110" s="4" t="n"/>
-    </row>
-    <row r="111">
-      <c r="B111" s="5" t="inlineStr">
+      <c r="B111" s="4" t="n"/>
+      <c r="C111" s="4" t="n"/>
+      <c r="D111" s="4" t="n"/>
+      <c r="E111" s="4" t="n"/>
+      <c r="F111" s="4" t="n"/>
+      <c r="G111" s="4" t="n"/>
+      <c r="H111" s="4" t="n"/>
+      <c r="I111" s="4" t="n"/>
+    </row>
+    <row r="112">
+      <c r="B112" s="5" t="inlineStr">
         <is>
           <t>思考触发编号</t>
         </is>
       </c>
-      <c r="C111" s="5" t="inlineStr">
+      <c r="C112" s="5" t="inlineStr">
         <is>
           <t>什么时候才去问模型</t>
         </is>
       </c>
-      <c r="D111" s="5" t="inlineStr">
+      <c r="D112" s="5" t="inlineStr">
         <is>
           <t>思考触发优先级(数字越低优先级越高)</t>
         </is>
       </c>
-      <c r="E111" s="5" t="inlineStr">
+      <c r="E112" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">状态(0:未开始, 1:进行中; 2:已完成; 3:暂停; 4:评估中; 默认状态为4) </t>
         </is>
       </c>
-      <c r="F111" s="5" t="inlineStr">
+      <c r="F112" s="5" t="inlineStr">
         <is>
           <t>关联实际行为脚本编号</t>
         </is>
       </c>
-      <c r="G111" s="6" t="inlineStr">
+      <c r="G112" s="6" t="inlineStr">
         <is>
           <t>触发条件(代码判据)</t>
         </is>
       </c>
-      <c r="H111" s="6" t="inlineStr">
+      <c r="H112" s="6" t="inlineStr">
         <is>
           <t>可行性</t>
         </is>
       </c>
-      <c r="I111" s="6" t="inlineStr">
+      <c r="I112" s="6" t="inlineStr">
         <is>
           <t>备注(问什么、答案怎么落地、问不到怎么办)</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="B112" s="7" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="C112" s="7" t="inlineStr">
-        <is>
-          <t>有真人在公屏叫它名字或私聊它时回一句话。「在哪、在干嘛、跟我来、停」这类固定问题由代码直接答，只有闲聊才问模型。不回另外两个机器人，每人每 10 分钟最多回 10 句，精确位置只告诉您。</t>
-        </is>
-      </c>
-      <c r="D112" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E112" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F112" s="7" t="inlineStr">
-        <is>
-          <t>think_reply</t>
-        </is>
-      </c>
-      <c r="G112" s="7" t="inlineStr">
-        <is>
-          <t>被点名 = 1 并且 说话的是真人 = 1 并且 是固定句式 = 0 并且 离上次回这个人秒数 ≥ 6 并且 离上次回话秒数 ≥ 3 并且 这人10分钟内被回句数 ≤ 9</t>
-        </is>
-      </c>
-      <c r="H112" s="7" t="inlineStr">
-        <is>
-          <t>缺判据</t>
-        </is>
-      </c>
-      <c r="I112" s="7" t="inlineStr">
-        <is>
-          <t>回答格式是 {say, give}。say 截到 30 字(提示里要求 25 字;brain.chat 现在截 40,改成 30),以 / 开头的整句丢掉。give 只能是 C-CHT-8R「能送的东西」里的一行(按中文名对),数量不超过那一行写的数、也不超过 8 个(brain.chat 现在上限 16、只认「食物/木头」两类,都改成按能送的东西对);同一个人 3 分钟只给一次（现成规则）。私聊进来的用 /msg &lt;对方&gt; 回，命令由代码拼，模型只给正文，不把私聊内容发到公屏。「你在哪」只对 Owner 报坐标，对其他人只用 C-CTX-5 的粗略区域词(家附近/田里/林子里/在外面/资源世界/下界,不带方向和距离)：新家不圈地，离人远是主要保护，公屏报坐标或「家的东北 120 格」都等于告诉全服家在哪。问不到或超时 15 秒就不说话。现状：任何人点名说「跟我来」都能让它跟着走 5 分钟（8148 行 startFollow + brainPausedUntil），而且这条绕过了 roles.json 的执行闸；谁的话算数等 Owner 定;跟完之后接着做手上原来那件小目标。按 Owner 规矩，只有被点名才说话，整个 T 层只有 T2 和 T10 会往聊天框发字。GP 开着防刷屏（实测踢过），全局 3 秒间隔保留。问模型时带什么:按 C-CTX-1 的「T2 配方」。系统段:我是谁(roles.json 的中文名和关系)+ 人格原文 + 现有回话设定里的未成年人安全底线和格式要求。🔴 现在的回话设定(brain.js 656 行 CHAT_SYSTEM)第一句写死「你叫小麦(XiaoMai)」,还带着小麦的性格,而 roles.persona() 只返回人格那一段 —— 麦娘、麦豆被点名时会自称小麦,这两句必须删掉,改由系统段按角色填。用户段从上到下:六样底包(家里人每人一句只写在干嘛、饿不饿、有没有人在帮,不写在哪;我现在的位置只用粗略区域词;大目标、小目标各一行)→ 能送的东西(中文名,不用游戏原名,免得原名被说到公屏上;家里有人缺吃的时注明「已给某某留了 N 份」)→ 对方的话(谁说的、是不是 Owner;原话放在「」里,最多 60 字,去掉 / 开头的内容;加上 C-CTX-6 记的和这个人最近 3 轮对话)→ 怎么回答 {say:…, give:{what:…, count:…}}。整个包不放坐标。总长 ≤1700 字(系统段约 1000 + 处境 ≤700)。think_reply 里写的「3 选 1 / 跟他走」以这里的 {say, give} 为准:跟不跟人走是代码的固定句式,不交给模型。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>您（Owner）在游戏里点名叫它做某件事时，代码先按小目标的叫法去对，对上了就直接插队去做；对不上但听起来像命令时，才问一次模型，把您的话对到它能做的某个小目标上。</t>
+          <t>有真人在公屏叫它名字或私聊它时回一句话。「在哪、在干嘛、跟我来、停」这类固定问题由代码直接答，只有闲聊才问模型。不回另外两个机器人，每人每 10 分钟最多回 10 句，精确位置只告诉您。</t>
         </is>
       </c>
       <c r="D113" s="7" t="n">
@@ -5220,12 +5221,12 @@
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>J-T10</t>
+          <t>think_reply</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
         <is>
-          <t>被点名 = 1 并且 说话的是Owner = 1 并且 像是命令 = 1 并且 叫法命中小目标数 = 0 并且 离上次T10秒数 ≥ 10</t>
+          <t>被点名 = 1 并且 说话的是真人 = 1 并且 是固定句式 = 0 并且 离上次回这个人秒数 ≥ 6 并且 离上次回话秒数 ≥ 3 并且 这人10分钟内被回句数 ≤ 9</t>
         </is>
       </c>
       <c r="H113" s="7" t="inlineStr">
@@ -5235,19 +5236,19 @@
       </c>
       <c r="I113" s="7" t="inlineStr">
         <is>
-          <t>问模型时带什么:按 C-CTX-1 的「T10 配方」,从上到下:六样底包(刚做完的事给 3 件,让它听得懂「接着干」「别干了」;正在做的小目标写上第几步;家里人照写,您的话里可能提到家人)→ 您的原话(放在「」里,最多 60 字)→ 这次要你决定(把这句话对到下面哪件活上)→ 选项(本角色没完成的小目标,按优先级最多 10 个,按位置标字母,每行:短名、现在能不能开工或缺什么;最后固定一行「不是叫我做事」)→ 怎么回答 {选:C}。总长 ≤1600 字;只收选项里的字母,或原样照抄、只对得上一个选项的小目标编号。插队 = 把这个小目标放到队头，手上原来那件压在下面、保留做到第几步；插队这件做完、失败放下或您说「停」之后，接着做原来那件（Owner 规矩：事件处理完继续上一个任务直到完成）；叫法正好命中 1 条、由代码直接插队时也一样。开工条件不成立时，回一句「还做不了：缺 X」（由代码拼，不问模型）。问不到或超时 12 秒，就当普通点名交给 T2。Owner 以前要的「身边玩家的话能影响它的想法」，是靠 decide() 每轮读「玩家刚说的话」实现的；删掉 decide() 后这条路就断了，T10 是替代。默认只听 Owner，其他人的话只回、不接活。依赖 T0 的小目标层。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
+          <t>回答格式是 {say, give}。say 截到 30 字(提示里要求 25 字;brain.chat 现在截 40,改成 30),以 / 开头的整句丢掉。give 只能是 C-CHT-8R「能送的东西」里的一行(按中文名对),数量不超过那一行写的数、也不超过 8 个(brain.chat 现在上限 16、只认「食物/木头」两类,都改成按能送的东西对);同一个人 3 分钟只给一次（现成规则）。私聊进来的用 /msg &lt;对方&gt; 回，命令由代码拼，模型只给正文，不把私聊内容发到公屏。「你在哪」只对 Owner 报坐标，对其他人只用 C-CTX-5 的粗略区域词(家附近/田里/林子里/在外面/资源世界/下界,不带方向和距离)：新家不圈地，离人远是主要保护，公屏报坐标或「家的东北 120 格」都等于告诉全服家在哪。问不到或超时 15 秒就不说话。现状：任何人点名说「跟我来」都能让它跟着走 5 分钟（8148 行 startFollow + brainPausedUntil），而且这条绕过了 roles.json 的执行闸；谁的话算数等 Owner 定;跟完之后接着做手上原来那件小目标。按 Owner 规矩，只有被点名才说话，整个 T 层只有 T2 和 T10 会往聊天框发字。GP 开着防刷屏（实测踢过），全局 3 秒间隔保留。问模型时带什么:按 C-CTX-1 的「T2 配方」。系统段:我是谁(roles.json 的中文名和关系)+ 人格原文 + 现有回话设定里的未成年人安全底线和格式要求。🔴 现在的回话设定(brain.js 656 行 CHAT_SYSTEM)第一句写死「你叫小麦(XiaoMai)」,还带着小麦的性格,而 roles.persona() 只返回人格那一段 —— 麦娘、麦豆被点名时会自称小麦,这两句必须删掉,改由系统段按角色填。用户段从上到下:六样底包(家里人每人一句只写在干嘛、饿不饿、有没有人在帮,不写在哪;我现在的位置只用粗略区域词;大目标、小目标各一行)→ 能送的东西(中文名,不用游戏原名,免得原名被说到公屏上;家里有人缺吃的时注明「已给某某留了 N 份」)→ 对方的话(谁说的、是不是 Owner;原话放在「」里,最多 60 字,去掉 / 开头的内容;加上 C-CTX-6 记的和这个人最近 3 轮对话)→ 怎么回答 {say:…, give:{what:…, count:…}}。整个包不放坐标。总长 ≤1700 字(系统段约 1000 + 处境 ≤700)。think_reply 里写的「3 选 1 / 跟他走」以这里的 {say, give} 为准:跟不跟人走是代码的固定句式,不交给模型。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>T11</t>
+          <t>T10</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>房子盖好以后，如果有两种以上合法的家具摆法（比如床靠北墙还是东墙），问模型一次挑哪种；只有一种就不问。（属于 G3）</t>
+          <t>您（Owner）在游戏里点名叫它做某件事时，代码先按小目标的叫法去对，对上了就直接插队去做；对不上但听起来像命令时，才问一次模型，把您的话对到它能做的某个小目标上。</t>
         </is>
       </c>
       <c r="D114" s="7" t="n">
@@ -5258,88 +5259,88 @@
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>J-T11</t>
+          <t>J-T10</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>新房完工过 = 1 并且 家具布局已定 = 0 并且 合格家具布局数 ≥ 2</t>
+          <t>被点名 = 1 并且 说话的是Owner = 1 并且 像是命令 = 1 并且 叫法命中小目标数 = 0 并且 离上次T10秒数 ≥ 10</t>
         </is>
       </c>
       <c r="H114" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
       <c r="I114" s="7" t="inlineStr">
         <is>
-          <t>检查时机：「新房完工过」第一次变成 1 的那一刻（J-M3-4 完成时），以及麦娘手上没活的时刻；不定时查。几何（哪一格放什么）全部由代码算，模型只在几种合法摆法里挑喜好。问模型时带什么:按 C-CTX-1 的「T11 配方」,这是按性格挑摆法的地方,系统段必须带人设。用户段:六样底包 → 家里几口人、每张床归谁(按 C-BED-7 的床位顺序)→ 新房(屋里 7×7、门在哪面墙)→ 这次要你决定 → 选项(最多 4 种摆法,按代码排序标 A~D,每行一句方位:床靠哪面墙、箱子靠哪面墙、工作台在哪个角;代码已检查过都放得下)→ 怎么回答 {选:A, why:…}。总长 ≤1100 字;问不到或超时 25 秒选 A。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
+          <t>问模型时带什么:按 C-CTX-1 的「T10 配方」,从上到下:六样底包(刚做完的事给 3 件,让它听得懂「接着干」「别干了」;正在做的小目标写上第几步;家里人照写,您的话里可能提到家人)→ 您的原话(放在「」里,最多 60 字)→ 这次要你决定(把这句话对到下面哪件活上)→ 选项(本角色没完成的小目标,按优先级最多 10 个,按位置标字母,每行:短名、现在能不能开工或缺什么;最后固定一行「不是叫我做事」)→ 怎么回答 {选:C}。总长 ≤1600 字;只收选项里的字母,或原样照抄、只对得上一个选项的小目标编号。插队 = 把这个小目标放到队头，手上原来那件压在下面、保留做到第几步；插队这件做完、失败放下或您说「停」之后，接着做原来那件（Owner 规矩：事件处理完继续上一个任务直到完成）；叫法正好命中 1 条、由代码直接插队时也一样。开工条件不成立时，回一句「还做不了：缺 X」（由代码拼，不问模型）。问不到或超时 12 秒，就当普通点名交给 T2。Owner 以前要的「身边玩家的话能影响它的想法」，是靠 decide() 每轮读「玩家刚说的话」实现的；删掉 decide() 后这条路就断了，T10 是替代。默认只听 Owner，其他人的话只回、不接活。依赖 T0 的小目标层。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>T8</t>
+          <t>T11</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>做同一件小目标时、30 分钟内因为同一种原因死了两次：饿死、淹死、晚上被怪打死这些代码有定论的情况，由代码直接改（提前吃东西、查游泳自救、这件事改成只在白天做）；剩下有两条以上出路的，才问一次模型选。</t>
+          <t>房子盖好以后，如果有两种以上合法的家具摆法（比如床靠北墙还是东墙），问模型一次挑哪种；只有一种就不问。（属于 G3）</t>
         </is>
       </c>
       <c r="D115" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E115" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>J-T8, guard_home, make_sword, sleep_night</t>
+          <t>J-T11</t>
         </is>
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>同一小目标同因死亡次数 ≥ 2 并且 死因已有代码对策 = 0 并且 这个死因的可选对策数 ≥ 2 并且 离上次为这个死因问秒数 ≥ 3600</t>
+          <t>新房完工过 = 1 并且 家具布局已定 = 0 并且 合格家具布局数 ≥ 2</t>
         </is>
       </c>
       <c r="H115" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
       <c r="I115" s="7" t="inlineStr">
         <is>
-          <t>实测夜里真实死亡约 30 次/小时，原稿的「30 分钟内同因 ≥2 次」几乎永远成立，再配上每种死因 60 分钟冷却，就成了每小时定时问一次。所以加了两道门：「两次都在做同一个小目标」和「代码没有定论」。模型的选项按位置标字母：A 自动暂停到天亮或 30 分钟（写运行文件，不写状态 3，永远是 A）；B 前置小目标插队（能做时才列；原来那件保留进度，前置做完接着做）；最后一行是「不改」。原稿的 A/B/D 缺了 C，小模型容易答出不存在的 C，已改成连续字母。超时 12 秒或答非所问就选 A。🔴 原稿要把淹死、岩浆的死亡点周围记成危险地点，这和 Owner 说过的「死过的地方也不一定要绕开」冲突。所以岩浆只记那几格岩浆本身（反射层本来就扫岩浆）；淹死是游泳自救失灵的问题，不标记区域。latest.log 会漏记死亡 5~10 倍，只能用机器人收到的服务器广播。麦娘、麦豆没有 sleep 和 fight，暂停到天亮时只能回家待着。服务器的 playersSleepingPercentage 没有核实过，有真人在线时，机器人睡觉未必能跳过夜晚。问模型时带什么:按 C-CTX-1 的「T8 配方」,六样用完整版,从上到下:家里人(另外两人各一行;标出谁会做剑)→ 身上的东西(武器、盔甲、吃的、挡箭用的泥土圆石写在最前)→ 大目标只留这件所属的一行 → 这个小目标和它的前置(最多 3 行)→ 刚做完的事(6 件)→ 冷却/暂停中 → 我现在 → 这两次死亡(每次:几分钟前、死因原话 ≤30 字、当时白天还是夜里、在哪一片、身上有没有剑;后两项要先按 C-CTX-3 让 C-DAT-3 记下来,现在没记)→ 这次要你决定 → 选项 → 怎么回答 {选:A, why:…}。总长 ≤1800 字。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
+          <t>检查时机：「新房完工过」第一次变成 1 的那一刻（J-M3-4 完成时），以及麦娘手上没活的时刻；不定时查。几何（哪一格放什么）全部由代码算，模型只在几种合法摆法里挑喜好。问模型时带什么:按 C-CTX-1 的「T11 配方」,这是按性格挑摆法的地方,系统段必须带人设。用户段:六样底包 → 家里几口人、每张床归谁(按 C-BED-7 的床位顺序)→ 新房(屋里 7×7、门在哪面墙)→ 这次要你决定 → 选项(最多 4 种摆法,按代码排序标 A~D,每行一句方位:床靠哪面墙、箱子靠哪面墙、工作台在哪个角;代码已检查过都放得下)→ 怎么回答 {选:A, why:…}。总长 ≤1100 字;问不到或超时 25 秒选 A。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T8</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>同一个小目标连着失败 3 次时，先由代码按失败原因处理：缺材料就先做它的前置，找不到或走不到就换一个记得的地方，背包满就先腾格子，都不行就自动暂停 30 分钟。只有失败原因代码认不出、又有两条以上出路时，才问模型选。</t>
+          <t>做同一件小目标时、30 分钟内因为同一种原因死了两次：饿死、淹死、晚上被怪打死这些代码有定论的情况，由代码直接改（提前吃东西、查游泳自救、这件事改成只在白天做）；剩下有两条以上出路的，才问一次模型选。</t>
         </is>
       </c>
       <c r="D116" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E116" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>J-T1-2</t>
+          <t>J-T8, guard_home, make_sword, sleep_night</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>本小目标连败次数 ≥ 3 并且 失败原因已归类 = 0 并且 可选对策数 ≥ 2 并且 离上次为这个小目标问秒数 ≥ 1800</t>
+          <t>同一小目标同因死亡次数 ≥ 2 并且 死因已有代码对策 = 0 并且 这个死因的可选对策数 ≥ 2 并且 离上次为这个死因问秒数 ≥ 3600</t>
         </is>
       </c>
       <c r="H116" s="7" t="inlineStr">
@@ -5349,35 +5350,35 @@
       </c>
       <c r="I116" s="7" t="inlineStr">
         <is>
-          <t>以下情况由代码直接处理，不问模型：缺材料 → 先做前置（前置能开工时），否则暂停；找不到/走不到 → 换地方（有备选地点时），否则暂停；背包满 → 先跑 A-T9 腾格子再重试，这一次不计失败；被打断 → 不计数。问模型时带什么:按 C-CTX-1 的「T3 配方」,六样用完整版,从上到下:家里人(另外两人各一行,会做前置那件活的标出来)→ 家里箱子(大箱子、粮箱各一行)→ 身上的东西 → 大目标只留这件所属的一行 → 这个小目标和它的前置(最多 3 行:短名、还差多少、谁在做)→ 刚做完的事(6 件)→ 冷却/暂停中 → 我现在 → 连败原文(3 次失败的原话,每条 ≤40 字,带几分钟前)→ 这次要你决定 → 选项:按位置连续用 A、B、C… 标,每行写明是哪种对策 —— 换地方(写明去哪个登记地点、多远)、先做前置(写明哪件、还差多少)、换这个小目标下另一条没在冷却的脚本(每条一行)、暂停 30 分钟(永远是最后一行)→ 怎么回答 {选:B, why:…}。总长 ≤1900 字;只收选项里的字母;超时 12 秒或答非所问就选最后一行(暂停 30 分钟)。先做前置或换脚本时,原来这件小目标保留进度,前置做完(或放弃)就接着做原来这件。暂停 = 自动暂停 30 分钟。同一个小目标 30 分钟内又连败 3 次，直接暂停。24 小时内被自动暂停 ≥3 次，就不再自动恢复，后台标红给 Owner 看（说明这条做法本身不行，该改表）。🔴 Owner 在后台手动设的「3 暂停」，代码永远不动。这条取代现在的「放下 + 冷却 2~3 分钟」，那套实测每 13 秒一轮，一直转到天亮。C-THK-8 里的 A/B/C 只是对策的名字,给模型看时一律按位置重新标字母。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
+          <t>实测夜里真实死亡约 30 次/小时，原稿的「30 分钟内同因 ≥2 次」几乎永远成立，再配上每种死因 60 分钟冷却，就成了每小时定时问一次。所以加了两道门：「两次都在做同一个小目标」和「代码没有定论」。模型的选项按位置标字母：A 自动暂停到天亮或 30 分钟（写运行文件，不写状态 3，永远是 A）；B 前置小目标插队（能做时才列；原来那件保留进度，前置做完接着做）；最后一行是「不改」。原稿的 A/B/D 缺了 C，小模型容易答出不存在的 C，已改成连续字母。超时 12 秒或答非所问就选 A。🔴 原稿要把淹死、岩浆的死亡点周围记成危险地点，这和 Owner 说过的「死过的地方也不一定要绕开」冲突。所以岩浆只记那几格岩浆本身（反射层本来就扫岩浆）；淹死是游泳自救失灵的问题，不标记区域。latest.log 会漏记死亡 5~10 倍，只能用机器人收到的服务器广播。麦娘、麦豆没有 sleep 和 fight，暂停到天亮时只能回家待着。服务器的 playersSleepingPercentage 没有核实过，有真人在线时，机器人睡觉未必能跳过夜晚。问模型时带什么:按 C-CTX-1 的「T8 配方」,六样用完整版,从上到下:家里人(另外两人各一行;标出谁会做剑)→ 身上的东西(武器、盔甲、吃的、挡箭用的泥土圆石写在最前)→ 大目标只留这件所属的一行 → 这个小目标和它的前置(最多 3 行)→ 刚做完的事(6 件)→ 冷却/暂停中 → 我现在 → 这两次死亡(每次:几分钟前、死因原话 ≤30 字、当时白天还是夜里、在哪一片、身上有没有剑;后两项要先按 C-CTX-3 让 C-DAT-3 记下来,现在没记)→ 这次要你决定 → 选项 → 怎么回答 {选:A, why:…}。总长 ≤1800 字。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>同一档（大目标和小目标的优先级都相同）里有两件以上能开工、而且其中有还没排过先后的小目标时，才问一次模型把这一档排个先后。之后照这个顺序一件件干，名单里不出现新面孔就不再问。</t>
+          <t>同一个小目标连着失败 3 次时，先由代码按失败原因处理：缺材料就先做它的前置，找不到或走不到就换一个记得的地方，背包满就先腾格子，都不行就自动暂停 30 分钟。只有失败原因代码认不出、又有两条以上出路时，才问模型选。</t>
         </is>
       </c>
       <c r="D117" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E117" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>J-T1-1, think_goal_order, think_pick_task</t>
+          <t>J-T1-2</t>
         </is>
       </c>
       <c r="G117" s="7" t="inlineStr">
         <is>
-          <t>手上有小目标 = 0 并且 最高档候选数 ≥ 2 并且 最高档没排过序的候选数 ≥ 1 并且 离上次T1秒数 ≥ 60</t>
+          <t>本小目标连败次数 ≥ 3 并且 失败原因已归类 = 0 并且 可选对策数 ≥ 2 并且 离上次为这个小目标问秒数 ≥ 1800</t>
         </is>
       </c>
       <c r="H117" s="7" t="inlineStr">
@@ -5387,73 +5388,73 @@
       </c>
       <c r="I117" s="7" t="inlineStr">
         <is>
-          <t>这条取代 nextFromTask 4044 行的「候选多于 1 个就问 pickScript」。现在不管优先级是否相同都会问，违反 Owner「优先级一样时才由 AI 选」。Owner 样板里 G1/G2/G3 的优先级都是 0，一开局就会出现同档。问模型时带什么:按 C-CTX-1 的「T1 配方」,11 块全带(Owner 第②句点名的六样都用完整版),从上到下:家里人(另外两人各一行:在不在线、血和饱食度、在哪一片、在做哪个小目标第几步、身上几份吃的、缺什么、有没有人在帮)→ 家里箱子(大箱子、粮箱各一行,各最多 8 样,注明几分钟前看的)→ 身上的东西(空格数、工具带剩余耐久、吃的几份、其余最多 12 样)→ 大目标(每个一行:编号、短名、状态、优先级、还差多少)→ 小目标(这一档候选所属大目标下的,加上家人正在做的,最多 8 行:编号、短名、状态、优先级、谁在做、还差多少、开不了工的原因)→ 刚做完的事(最近 6 件,旧的在上新的在下:成没成、为什么、多久前、用了多久;再加一行最近 30 分钟死了几次、逃了几次、被打断几次)→ 冷却/暂停中(最多 4 行)→ 我现在(血、饱食度、在哪一片、离家几格、白天还是夜里、离天黑几分钟、8 格内几只怪)→ 这次要你决定(这一档有 N 件能开工,排个先后)→ 选项(按位置连续标 A~F,每行贴上属于哪个大目标、还差多少、上次做这件的结果)→ 怎么回答。总长 ≤2200 字,超了按 C-CTX-1 第五条的顺序砍,最多砍到六样底包那一档;选项、我现在、回答格式永远不砍。这一档超过 6 件时只列表里顺序前 6 件,没列的按表里顺序接在模型给的顺序后面、一起记进 order,不为它们再问。模型只回 {顺序:[B,A,C], why:不超过20字};代码认选项字母,也认原样照抄、且只对得上一个选项的小目标编号,重复的去掉、名单外的丢掉,漏掉的按表里顺序补在后面。超时：主脑 12 秒，降级时 20 秒。问不到、超时或答非所问，就按表里顺序，履历记「模型没答，按表顺序」。等回答时反射层和硬规则照常跑。「同时进行」指不同家人各做一件；一个人一次只做一件。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
+          <t>以下情况由代码直接处理，不问模型：缺材料 → 先做前置（前置能开工时），否则暂停；找不到/走不到 → 换地方（有备选地点时），否则暂停；背包满 → 先跑 A-T9 腾格子再重试，这一次不计失败；被打断 → 不计数。问模型时带什么:按 C-CTX-1 的「T3 配方」,六样用完整版,从上到下:家里人(另外两人各一行,会做前置那件活的标出来)→ 家里箱子(大箱子、粮箱各一行)→ 身上的东西 → 大目标只留这件所属的一行 → 这个小目标和它的前置(最多 3 行:短名、还差多少、谁在做)→ 刚做完的事(6 件)→ 冷却/暂停中 → 我现在 → 连败原文(3 次失败的原话,每条 ≤40 字,带几分钟前)→ 这次要你决定 → 选项:按位置连续用 A、B、C… 标,每行写明是哪种对策 —— 换地方(写明去哪个登记地点、多远)、先做前置(写明哪件、还差多少)、换这个小目标下另一条没在冷却的脚本(每条一行)、暂停 30 分钟(永远是最后一行)→ 怎么回答 {选:B, why:…}。总长 ≤1900 字;只收选项里的字母;超时 12 秒或答非所问就选最后一行(暂停 30 分钟)。先做前置或换脚本时,原来这件小目标保留进度,前置做完(或放弃)就接着做原来这件。暂停 = 自动暂停 30 分钟。同一个小目标 30 分钟内又连败 3 次，直接暂停。24 小时内被自动暂停 ≥3 次，就不再自动恢复，后台标红给 Owner 看（说明这条做法本身不行，该改表）。🔴 Owner 在后台手动设的「3 暂停」，代码永远不动。这条取代现在的「放下 + 冷却 2~3 分钟」，那套实测每 13 秒一轮，一直转到天亮。C-THK-8 里的 A/B/C 只是对策的名字,给模型看时一律按位置重新标字母。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>家离出生点太近、或旁边有别人的房子时，从小麦沿路记下的合格新家址里挑一块（合格指：平地、远离人、水边能种地、附近有树）。两块以上才问模型，只有一块就直接用。选好的只是「待您确认」，您在后台点同意之前，谁都不搬。</t>
+          <t>同一档（大目标和小目标的优先级都相同）里有两件以上能开工、而且其中有还没排过先后的小目标时，才问一次模型把这一档排个先后。之后照这个顺序一件件干，名单里不出现新面孔就不再问。</t>
         </is>
       </c>
       <c r="D118" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E118" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F118" s="7" t="inlineStr">
         <is>
-          <t>find_forest, make_base, think_home_site</t>
+          <t>J-T1-1, think_goal_order, think_pick_task</t>
         </is>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
-          <t>需要搬家 = 1 并且 新家址已定 = 0 并且 候选家址数 ≥ 2 并且 离上次T5秒数 ≥ 600</t>
+          <t>手上有小目标 = 0 并且 最高档候选数 ≥ 2 并且 最高档没排过序的候选数 ≥ 1 并且 离上次T1秒数 ≥ 60</t>
         </is>
       </c>
       <c r="H118" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
       <c r="I118" s="7" t="inlineStr">
         <is>
-          <t>0 块候选时：派小麦往离出生点更远、没去过的方向 explore（方向由代码定），不问模型。只有 1 块时：直接写成待批。问模型时带什么:按 C-CTX-1 的「T5 配方」:六样底包 → 大目标补上 G3、G4 两行 → 现在的家为什么要搬(离出生点几格、32 格内有几块别人的方块)→ 这次要你决定 → 选项(最多 6 块候选地,按代码打分从高到低标 A~F:在家的哪个方向多远、离出生点、离林子、离水各多远、平地多大、附近别人方块数、代码打分)→ 怎么回答 {选:A, why:…}。总长 ≤1300 字;只收选项里的字母。问不到或超时 25 秒：选 A（代码打分最高的一块）。到了现场复查不合格，就把那块删掉，剩 ≥2 块才再问，两次至少隔 10 分钟。耕地必须在水平 4 格以内、和水同高或低一格才算湿润，否则会退回泥土、作物也长得慢；现在没有水桶和放方块的动作，只能选天然水边。作物要光照（露天白天就够）。🔴 不圈地：新家没有领地保护。⚠️ BlueMap 是公开的（已取消密码），默认还显示在线玩家的位置；离人远只能减少路过的人，挡不住专门来找的人，这一点要让 Owner 知道。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
+          <t>这条取代 nextFromTask 4044 行的「候选多于 1 个就问 pickScript」。现在不管优先级是否相同都会问，违反 Owner「优先级一样时才由 AI 选」。Owner 样板里 G1/G2/G3 的优先级都是 0，一开局就会出现同档。问模型时带什么:按 C-CTX-1 的「T1 配方」,11 块全带(Owner 第②句点名的六样都用完整版),从上到下:家里人(另外两人各一行:在不在线、血和饱食度、在哪一片、在做哪个小目标第几步、身上几份吃的、缺什么、有没有人在帮)→ 家里箱子(大箱子、粮箱各一行,各最多 8 样,注明几分钟前看的)→ 身上的东西(空格数、工具带剩余耐久、吃的几份、其余最多 12 样)→ 大目标(每个一行:编号、短名、状态、优先级、还差多少)→ 小目标(这一档候选所属大目标下的,加上家人正在做的,最多 8 行:编号、短名、状态、优先级、谁在做、还差多少、开不了工的原因)→ 刚做完的事(最近 6 件,旧的在上新的在下:成没成、为什么、多久前、用了多久;再加一行最近 30 分钟死了几次、逃了几次、被打断几次)→ 冷却/暂停中(最多 4 行)→ 我现在(血、饱食度、在哪一片、离家几格、白天还是夜里、离天黑几分钟、8 格内几只怪)→ 这次要你决定(这一档有 N 件能开工,排个先后)→ 选项(按位置连续标 A~F,每行贴上属于哪个大目标、还差多少、上次做这件的结果)→ 怎么回答。总长 ≤2200 字,超了按 C-CTX-1 第五条的顺序砍,最多砍到六样底包那一档;选项、我现在、回答格式永远不砍。这一档超过 6 件时只列表里顺序前 6 件,没列的按表里顺序接在模型给的顺序后面、一起记进 order,不为它们再问。模型只回 {顺序:[B,A,C], why:不超过20字};代码认选项字母,也认原样照抄、且只对得上一个选项的小目标编号,重复的去掉、名单外的丢掉,漏掉的按表里顺序补在后面。超时：主脑 12 秒，降级时 20 秒。问不到、超时或答非所问，就按表里顺序，履历记「模型没答，按表顺序」。等回答时反射层和硬规则照常跑。「同时进行」指不同家人各做一件；一个人一次只做一件。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>新家址经您同意、还没定房子样式、而且库存够凑出两种以上木头搭配时，问一次模型挑木头搭配（墙、柱子、屋顶各用哪种木头）和门朝哪；大小、平顶、木半砖地面都按 G3 定死（9×9 外框，屋里 7×7），不在选项里。只有一种搭配够就由代码直接定（J-G3-0a）。泥土不在选项里，房子一定带门。</t>
+          <t>家离出生点太近、或旁边有别人的房子时，从小麦沿路记下的合格新家址里挑一块（合格指：平地、远离人、水边能种地、附近有树）。两块以上才问模型，只有一块就直接用。选好的只是「待您确认」，您在后台点同意之前，谁都不搬。</t>
         </is>
       </c>
       <c r="D119" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E119" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>build_house, get_build_mats, son_take_mats, think_house_design</t>
+          <t>find_forest, make_base, think_home_site</t>
         </is>
       </c>
       <c r="G119" s="7" t="inlineStr">
         <is>
-          <t>新家址已批 = 1 并且 新房设计已定 = 0 并且 合格木种组合数 ≥ 2</t>
+          <t>需要搬家 = 1 并且 新家址已定 = 0 并且 候选家址数 ≥ 2 并且 离上次T5秒数 ≥ 600</t>
         </is>
       </c>
       <c r="H119" s="7" t="inlineStr">
@@ -5463,43 +5464,81 @@
       </c>
       <c r="I119" s="7" t="inlineStr">
         <is>
-          <t>大小以 G3 为准：9×9 外框、屋里 7×7、墙高 3、平顶、木半砖地面；用量以 M3-2 为准：木板 163 块（墙 82 + 屋顶 81）、柱子原木 12 根、木半砖 49 块、门 1 扇，结构合计约 196 块木板（49 根原木）另加 12 根柱子原木。原稿这里的 7×7/9×7 两种尺寸、平顶/台阶边两种屋顶和「能住下全家的最小尺寸」和 G3、M3-2 对不上，已删掉。触发改读 C-BLD-9R「合格木种组合数」，和 J-G3-0a（=1 时代码直接定）是同一个函数。库存（M3-2 记的）：橡木 232 根什么搭配都够；樱花 83 根够墙加屋顶；桦木 28 根（112 块木板）只够墙或屋顶其中一样。床 = 3 块同色羊毛 + 3 块任意木板；打一只没剪过毛的羊掉 1 块羊毛，3 张床要 9 只羊。hunt 必须避开栅栏里、有名字、在别人建筑旁边的羊（孩子们养的）。🔴 门必须有：床周围水平 8 格、上下 5 格内有敌对怪就睡不了觉，门洞敞着，夜里怪会进屋。旧泥土房没有拆除动作（没有 mine/dig），会留在原地，拆不拆等 Owner 定（M3-9）。这条取代 actBuildHouse（3332 行）里直接调用 designHouse。问模型时带什么:按 C-CTX-1 的「T4 配方」,这是按性格挑样式的地方,系统段必须带人设。用户段:六样底包 → 木料(家里箱子和身上的原木、木板,按木种合计,注明箱子几分钟前看的)→ 家里几口人、要放几张床 → 新家址(平地多大、林子在哪个方向、水在哪个方向、门能朝哪几个方向)→ 这次要你决定 → 选项(C-BLD-9R 列出的最多 6 种凑得够的搭配,按位置标 A~F:墙、柱子、屋顶各用什么木头、要多少、现有多少;代码先列三处同一种木头的,再列混搭的,同类里按用完后剩下的原木从多到少排)→ 怎么回答 {选:B, 门:南, why:…},门只收新家址里列出的方向,不合法就用兜底的门朝向。总长 ≤1500 字。问不到或超时 25 秒的兜底：选 A（代码排第 1 的搭配）+ 门朝记得的林子（没有就朝南）。一座房子只设计一次；家址变了，或 Owner 在后台清掉设计，才会再问。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
+          <t>0 块候选时：派小麦往离出生点更远、没去过的方向 explore（方向由代码定），不问模型。只有 1 块时：直接写成待批。问模型时带什么:按 C-CTX-1 的「T5 配方」:六样底包 → 大目标补上 G3、G4 两行 → 现在的家为什么要搬(离出生点几格、32 格内有几块别人的方块)→ 这次要你决定 → 选项(最多 6 块候选地,按代码打分从高到低标 A~F:在家的哪个方向多远、离出生点、离林子、离水各多远、平地多大、附近别人方块数、代码打分)→ 怎么回答 {选:A, why:…}。总长 ≤1300 字;只收选项里的字母。问不到或超时 25 秒：选 A（代码打分最高的一块）。到了现场复查不合格，就把那块删掉，剩 ≥2 块才再问，两次至少隔 10 分钟。耕地必须在水平 4 格以内、和水同高或低一格才算湿润，否则会退回泥土、作物也长得慢；现在没有水桶和放方块的动作，只能选天然水边。作物要光照（露天白天就够）。🔴 不圈地：新家没有领地保护。⚠️ BlueMap 是公开的（已取消密码），默认还显示在线玩家的位置；离人远只能减少路过的人，挡不住专门来找的人，这一点要让 Owner 知道。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t>T0</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>平时（没有任何一条思考触发成立时）机器人只跑代码，照着目标表一件件干，一次模型都不问。某个人一件能开工的小目标都没有，本身就说明目标表有漏洞——只有打完末影龙的大结局才该出现。这时代码当场在后台记一条「目标表缺口」：是谁、什么时候、他名下每一条小目标为什么做不了（差哪个数、在等哪条、被您暂停、还是他根本没有这个本事），连同他自己的血和饱食度、身上带着什么、刚做完的几件事、家里另外两人在干什么缺什么。只是在等庄稼长熟、等天亮这类很快会自己解开的，记成「在等」。记完不问模型、不在公屏说话，由代码兜底：天黑就回家；先回家把箱子打开核对一次（箱子里的数记旧了，也会把能干的活误判成不能干）；小麦缺的是「没找到林子/没见过动物」就出去找一圈，否则回家把东西存好；麦娘把小麦做成面包、把东西存好；麦豆在家门口离人远的地方玩。一有能开工的小目标，马上回去干。等您拍板、缺本事、表里没下一步这几类当场标红；「在等」持续 30 分钟也标红「该补表了」；打完龙的大结局不标红。</t>
+          <t>新家址经您同意、还没定房子样式、而且库存够凑出两种以上木头搭配时，问一次模型挑木头搭配（墙、柱子、屋顶各用哪种木头）和门朝哪；大小、平顶、木半砖地面都按 G3 定死（9×9 外框，屋里 7×7），不在选项里。只有一种搭配够就由代码直接定（J-G3-0a）。泥土不在选项里，房子一定带门。</t>
         </is>
       </c>
       <c r="D120" s="7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E120" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
+          <t>build_house, get_build_mats, son_take_mats, think_house_design</t>
+        </is>
+      </c>
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t>新家址已批 = 1 并且 新房设计已定 = 0 并且 合格木种组合数 ≥ 2</t>
+        </is>
+      </c>
+      <c r="H120" s="7" t="inlineStr">
+        <is>
+          <t>判据动作都缺</t>
+        </is>
+      </c>
+      <c r="I120" s="7" t="inlineStr">
+        <is>
+          <t>大小以 G3 为准：9×9 外框、屋里 7×7、墙高 3、平顶、木半砖地面；用量以 M3-2 为准：木板 163 块（墙 82 + 屋顶 81）、柱子原木 12 根、木半砖 49 块、门 1 扇，结构合计约 196 块木板（49 根原木）另加 12 根柱子原木。原稿这里的 7×7/9×7 两种尺寸、平顶/台阶边两种屋顶和「能住下全家的最小尺寸」和 G3、M3-2 对不上，已删掉。触发改读 C-BLD-9R「合格木种组合数」，和 J-G3-0a（=1 时代码直接定）是同一个函数。库存（M3-2 记的）：橡木 232 根什么搭配都够；樱花 83 根够墙加屋顶；桦木 28 根（112 块木板）只够墙或屋顶其中一样。床 = 3 块同色羊毛 + 3 块任意木板；打一只没剪过毛的羊掉 1 块羊毛，3 张床要 9 只羊。hunt 必须避开栅栏里、有名字、在别人建筑旁边的羊（孩子们养的）。🔴 门必须有：床周围水平 8 格、上下 5 格内有敌对怪就睡不了觉，门洞敞着，夜里怪会进屋。旧泥土房没有拆除动作（没有 mine/dig），会留在原地，拆不拆等 Owner 定（M3-9）。这条取代 actBuildHouse（3332 行）里直接调用 designHouse。问模型时带什么:按 C-CTX-1 的「T4 配方」,这是按性格挑样式的地方,系统段必须带人设。用户段:六样底包 → 木料(家里箱子和身上的原木、木板,按木种合计,注明箱子几分钟前看的)→ 家里几口人、要放几张床 → 新家址(平地多大、林子在哪个方向、水在哪个方向、门能朝哪几个方向)→ 这次要你决定 → 选项(C-BLD-9R 列出的最多 6 种凑得够的搭配,按位置标 A~F:墙、柱子、屋顶各用什么木头、要多少、现有多少;代码先列三处同一种木头的,再列混搭的,同类里按用完后剩下的原木从多到少排)→ 怎么回答 {选:B, 门:南, why:…},门只收新家址里列出的方向,不合法就用兜底的门朝向。总长 ≤1500 字。问不到或超时 25 秒的兜底：选 A（代码排第 1 的搭配）+ 门朝记得的林子（没有就朝南）。一座房子只设计一次；家址变了，或 Owner 在后台清掉设计，才会再问。共同规矩见 C-CTX-1;回答校验、超时兜底和全文留档见 C-THK-5R。</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" s="7" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="inlineStr">
+        <is>
+          <t>平时（没有任何一条思考触发成立时）机器人只跑代码，照着目标表一件件干，一次模型都不问。某个人一件能开工的小目标都没有，本身就说明目标表有漏洞——只有打完末影龙的大结局才该出现。这时代码当场在后台记一条「目标表缺口」：是谁、什么时候、他名下每一条小目标为什么做不了（差哪个数、在等哪条、被您暂停、还是他根本没有这个本事），连同他自己的血和饱食度、身上带着什么、刚做完的几件事、家里另外两人在干什么缺什么。只是在等庄稼长熟、等天亮这类很快会自己解开的，记成「在等」。记完不问模型、不在公屏说话，由代码兜底：天黑就回家；先回家把箱子打开核对一次（箱子里的数记旧了，也会把能干的活误判成不能干）；小麦缺的是「没找到林子/没见过动物」就出去找一圈，否则回家把东西存好；麦娘把小麦做成面包、把东西存好；麦豆在家门口离人远的地方玩。一有能开工的小目标，马上回去干。等您拍板、缺本事、表里没下一步这几类当场标红；「在等」持续 30 分钟也标红「该补表了」；打完龙的大结局不标红。</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E121" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F121" s="7" t="inlineStr">
+        <is>
           <t>J-T0-1, J-T0-2, J-T0-3, find_forest</t>
         </is>
       </c>
-      <c r="G120" s="7" t="inlineStr">
+      <c r="G121" s="7" t="inlineStr">
         <is>
           <t>任何思考触发成立 = 0</t>
         </is>
       </c>
-      <c r="H120" s="7" t="inlineStr">
+      <c r="H121" s="7" t="inlineStr">
         <is>
           <t>判据动作都缺</t>
         </is>
       </c>
-      <c r="I120" s="7" t="inlineStr">
+      <c r="I121" s="7" t="inlineStr">
         <is>
           <t>已只读核对服务器上的 ~/mcbot/bot.real.js。问模型的地方共 6 处：decide（3962 行 TASK_MODE=0 分支、4013 行零候选分支）；pickScript（4044 行，候选多于 1 个就问，不看是不是同一档）；plan（7523 行，planLoop 每 1 秒一次）；designHouse（3332 行）；chat（8204 行）。makeTask/reviewTask 在第 23 行被导入，但全文件没有调用。反射层 reflexTick 每秒跑一次纯代码，不受影响。小目标的 done_when 一成立，就按表拿下一个；紧急事件先处理，但不动进度指针。🔴 Owner 2026-09-18 定性：「一直没有事情做」只该出现在打完末影龙的大结局，零候选是目标表的漏洞，不是交给模型去救的正常状态。4013 行零候选时每 2.5 秒调一次 decide() 的分支删掉（C-THK-1），换成缺口记录（C-ENG-21）+ 纯代码兜底；THINK_MODE 开不开，这里都不问模型、不往公屏说话。缺口记录只给您在后台看，不给模型：开始时记一条，结束时补写持续多久、兜底做了什么；同一组原因 10 分钟内只加次数。内容按您点名的六样：大目标（每个的状态和优先级）；小目标（他名下每条为什么被跳过：已完成 / 您设了暂停 / 前置没完成（哪条、卡在谁手里）/ 开工条件不成立（哪个判据、现在的值和门槛）/ 自动暂停到几点 / 冷却还剩几秒 / 执行闸缺哪个动作 / 家人已认领）；刚做完的 6 件事；自己的状态（血、饱食度、在哪个世界哪一片、天色、离天黑几分钟）；身上的东西（背包摘要）；家里人（另外两人在不在线、在做哪个小目标、身上几份吃的、缺什么）。另加「死大目标」：没完成、没暂停，但全家没有一条它下面的小目标能开工。拼装函数和问模型的上下文包共用同一个（第②路的 C-CTX-1），只是不截短。缺口分五类：① 在等（只被天黑、庄稼没熟、冷却、自动暂停、今天资源世界次数、等家人做出来这类会自己变的条件挡住）；② 等您拍板；③ 缺本事（执行闸没放行、动作还没做）；④ 表里没下一步；⑤ 大结局（G8 已完成并锁住）。②③④ 满 1 分钟、① 满 30 分钟，后台标红「该补表了」；⑤ 永不标红。兜底顺序（每一步做完都重算候选，一有候选立刻回去干活）：① 天黑了 → 交给 A11（只在主世界触发：回家睡或回屋待着）；② 开箱快照超过 600 秒 → 回家开箱核对（只看不拿，C-ITM-24），核对完先重算一次；③ 白天、「卡在找得到就能解开的原因」= 1（C-THK-10）、自己有 explore（现在只有小麦）→ find_forest 出去找一圈；④ 按角色跑 J-T0-1（小麦：回家存东西、等 1 分钟）/ J-T0-2（麦娘：做面包、存东西）/ J-T0-3（麦豆：家门口离真人远的地方玩）。🔴 兜底只做安全、可撤回的事：不提前合成（合成不可逆，会吃掉别处要的料），不出远门，不问模型。晚上不出门：夜里待在外面，正是以前家门口扎堆死亡的原因。另有两条引擎规则专门减少假缺口：前置按「完成过」算（C-ENG-22），打完龙以后 G8 锁住（C-ENG-23）。</t>
         </is>
@@ -21366,7 +21405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E544"/>
+  <dimension ref="A1:E554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -36041,6 +36080,276 @@
       <c r="E544" s="7" t="inlineStr">
         <is>
           <t>平级会话实测:wife_take_planks 10 次只成 1 次,箱子里只有原木。先存后拿、连做两次 → 8 块同种木板(minecraft-data 每张</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B545" s="7" t="inlineStr">
+        <is>
+          <t>M3-3</t>
+        </is>
+      </c>
+      <c r="C545" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D545" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 加放方块硬约束 ④~⑧(高度、门洞、不用下落方块、被拒永久划掉、不碰领地)</t>
+        </is>
+      </c>
+      <c r="E545" s="7" t="inlineStr">
+        <is>
+          <t>fork 1 查实(2026-09-18):小麦从没封好的屋顶洞掉进屋里(「在不在屋里」只看平面);洞那一列在孩子的领地里,服务器拒了 379 次,程序从不划掉</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B546" s="7" t="inlineStr">
+        <is>
+          <t>M3-4</t>
+        </is>
+      </c>
+      <c r="C546" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D546" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 加放方块硬约束 ④~⑧(高度、门洞、不用下落方块、被拒永久划掉、不碰领地)</t>
+        </is>
+      </c>
+      <c r="E546" s="7" t="inlineStr">
+        <is>
+          <t>fork 1 查实(2026-09-18):小麦从没封好的屋顶洞掉进屋里(「在不在屋里」只看平面);洞那一列在孩子的领地里,服务器拒了 379 次,程序从不划掉</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B547" s="7" t="inlineStr">
+        <is>
+          <t>M3-6</t>
+        </is>
+      </c>
+      <c r="C547" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D547" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 加放方块硬约束 ④~⑧(高度、门洞、不用下落方块、被拒永久划掉、不碰领地)</t>
+        </is>
+      </c>
+      <c r="E547" s="7" t="inlineStr">
+        <is>
+          <t>fork 1 查实(2026-09-18):小麦从没封好的屋顶洞掉进屋里(「在不在屋里」只看平面);洞那一列在孩子的领地里,服务器拒了 379 次,程序从不划掉</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B548" s="7" t="inlineStr">
+        <is>
+          <t>M2-3</t>
+        </is>
+      </c>
+      <c r="C548" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D548" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 加放方块硬约束 ④~⑧(高度、门洞、不用下落方块、被拒永久划掉、不碰领地)</t>
+        </is>
+      </c>
+      <c r="E548" s="7" t="inlineStr">
+        <is>
+          <t>fork 1 查实(2026-09-18):小麦从没封好的屋顶洞掉进屋里(「在不在屋里」只看平面);洞那一列在孩子的领地里,服务器拒了 379 次,程序从不划掉</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B549" s="7" t="inlineStr">
+        <is>
+          <t>A16</t>
+        </is>
+      </c>
+      <c r="C549" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D549" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 加放方块硬约束 ④~⑧(高度、门洞、不用下落方块、被拒永久划掉、不碰领地)</t>
+        </is>
+      </c>
+      <c r="E549" s="7" t="inlineStr">
+        <is>
+          <t>fork 1 查实(2026-09-18):小麦从没封好的屋顶洞掉进屋里(「在不在屋里」只看平面);洞那一列在孩子的领地里,服务器拒了 379 次,程序从不划掉</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B550" s="7" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="C550" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D550" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 加床的硬约束:只睡自家的床、走得到要用真实路径</t>
+        </is>
+      </c>
+      <c r="E550" s="7" t="inlineStr">
+        <is>
+          <t>fork 1 查实(2026-09-18):小麦从没封好的屋顶洞掉进屋里(「在不在屋里」只看平面);洞那一列在孩子的领地里,服务器拒了 379 次,程序从不划掉</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B551" s="7" t="inlineStr">
+        <is>
+          <t>M2-3</t>
+        </is>
+      </c>
+      <c r="C551" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D551" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 加床的硬约束:只睡自家的床、走得到要用真实路径</t>
+        </is>
+      </c>
+      <c r="E551" s="7" t="inlineStr">
+        <is>
+          <t>fork 1 查实(2026-09-18):小麦从没封好的屋顶洞掉进屋里(「在不在屋里」只看平面);洞那一列在孩子的领地里,服务器拒了 379 次,程序从不划掉</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B552" s="7" t="inlineStr">
+        <is>
+          <t>A11</t>
+        </is>
+      </c>
+      <c r="C552" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D552" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 加床的硬约束:只睡自家的床、走得到要用真实路径</t>
+        </is>
+      </c>
+      <c r="E552" s="7" t="inlineStr">
+        <is>
+          <t>fork 1 查实(2026-09-18):小麦从没封好的屋顶洞掉进屋里(「在不在屋里」只看平面);洞那一列在孩子的领地里,服务器拒了 379 次,程序从不划掉</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B553" s="7" t="inlineStr">
+        <is>
+          <t>J-M2-3-1</t>
+        </is>
+      </c>
+      <c r="C553" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D553" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 加床的硬约束:只睡自家的床、走得到要用真实路径</t>
+        </is>
+      </c>
+      <c r="E553" s="7" t="inlineStr">
+        <is>
+          <t>fork 1 查实(2026-09-18):小麦从没封好的屋顶洞掉进屋里(「在不在屋里」只看平面);洞那一列在孩子的领地里,服务器拒了 379 次,程序从不划掉</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B554" s="7" t="inlineStr">
+        <is>
+          <t>A29</t>
+        </is>
+      </c>
+      <c r="C554" s="7" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="D554" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 卡住自救改成常驻状态维持,零候选时也要生效</t>
+        </is>
+      </c>
+      <c r="E554" s="7" t="inlineStr">
+        <is>
+          <t>fork 1 查实(2026-09-18):小麦从没封好的屋顶洞掉进屋里(「在不在屋里」只看平面);洞那一列在孩子的领地里,服务器拒了 379 次,程序从不划掉</t>
         </is>
       </c>
     </row>

--- a/ai-player/goal-table/小麦家族工作分解-填写版.xlsx
+++ b/ai-player/goal-table/小麦家族工作分解-填写版.xlsx
@@ -1493,7 +1493,7 @@
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
-          <t>水边田址上刚锄好的湿耕地不会退回泥土，所以「锄一批再种」没问题；只有 Owner 选了家门口干地时，才会碰到「锄好约 1 分钟就变回泥土」，那时由 J-M1-2 下一轮把退回的格子重锄重种，慢慢凑满。wife_till 关掉（开 = false），它要先锄满 9 格才轮到播种。作物要亮度 ≥ 9 才长、≥ 8 或头顶见天才种得活；露天的田夜里也照长。从高处跳下落到耕地上（下落超过半格）会把它踩回泥土、麦子掉出来——孩子们和寻路时的机器人都可能踩，被踩的格子由登记簿记成「空」，交给 J-M1-2 补。完成状态每次重算：哪格空了，M1-2 自动回到没完成，J-M1-2 再开工补上。🔴 前置 M1-0 标成「必须现在成立」（C-ENG-22 的例外）：家搬走、田址失效时，不能继续在 300 格外的旧田上干（旁边没人，庄稼也不长），要等新田址定下来；M1-1 仍按「完成过」算（种子一种下去就少于 9 颗，按现在算会把自己卡死）。</t>
+          <t>🔴 田要留走道:防踩耕地的护栏不许机器人站在耕地上,而种、收都要站在够得着的地方(代码上限 3.6 格)。所以每一格耕地到最近一块能站的非耕地,水平距离都要 ≤3 格,比如每 5 格宽留 1 格走道。不然田中间的格子永远种不上也收不了(实测:麦娘田里两格被四面耕地围住,1.5 小时空转 10 轮)。 水边田址上刚锄好的湿耕地不会退回泥土，所以「锄一批再种」没问题；只有 Owner 选了家门口干地时，才会碰到「锄好约 1 分钟就变回泥土」，那时由 J-M1-2 下一轮把退回的格子重锄重种，慢慢凑满。wife_till 关掉（开 = false），它要先锄满 9 格才轮到播种。作物要亮度 ≥ 9 才长、≥ 8 或头顶见天才种得活；露天的田夜里也照长。从高处跳下落到耕地上（下落超过半格）会把它踩回泥土、麦子掉出来——孩子们和寻路时的机器人都可能踩，被踩的格子由登记簿记成「空」，交给 J-M1-2 补。完成状态每次重算：哪格空了，M1-2 自动回到没完成，J-M1-2 再开工补上。🔴 前置 M1-0 标成「必须现在成立」（C-ENG-22 的例外）：家搬走、田址失效时，不能继续在 300 格外的旧田上干（旁边没人，庄稼也不长），要等新田址定下来；M1-1 仍按「完成过」算（种子一种下去就少于 9 颗，按现在算会把自己卡死）。</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>🔴 放方块硬约束(补充):④「在不在屋里 / 在不在盖房的位置」必须连高度一起算,站在屋顶上不算在屋里,不许从没封好的屋顶洞穿过;⑤ 门洞那一列永远空着,什么都不许放(包括会掉下来填进去的方块);⑥ 盖房材料排除会下落的方块(沙子、红沙、沙砾、各色混凝土粉末、铁砧等),没有别的材料就不盖;⑦ 服务器拒绝过的格子永久划掉,房子可以算「完成(跳过 N 格)」,否则脚本会一直把人派回去;⑧ 开工前先查目标格在不在别人的领地里,在就标「这里做不了」、不去试。麦家现在没有任何领地(Owner 定的),所以【任何领地都是别人的】—— 数据来源待定:服务器拒绝记录,或后台导出领地范围。 🔴 盖房硬约束(2026-09-18 实测小麦被自己的房子关住,20 分钟失败 110 次):① 任何一步都不许把方块放进盖房人正站的格子、头顶那格和门洞;② 每放一块之前,代码先算「放完以后我还走得出去吗」(站的格子到屋外有通路),走不出去就先走出去再放;③ 同一块连着被服务器拒绝 3 次,就换下一块或收工,不原地重试。这三条由代码判断,不问模型。 ⏳ 过渡:搬家(拍板第 1 件)定之前,挂在这里的 build_house / get_build_mats / son_take_mats 仍在现在的家把房子盖完(线上老行为,不倒退);定了搬以后改成在新家址盖。 门是 2 格高的物品，要点门洞下面那块地面的顶面放，朝向跟人的朝向走。墙的判定只看实心不实心，不看方块名（泥土长成草那次的教训）。站位必须站在墙格以外的格子上，不能用「离中心多远」来判断。僵尸自己开不了木门。</t>
+          <t>⑨ 自家箱子正上方那一格永远空着,不许放任何实心方块 —— MC 规则:箱子头顶有实心方块就打不开(2026-09-18 17:13 起家里那口箱子被压住,三个人开箱全部失败)。 🔴 放方块硬约束(补充):④「在不在屋里 / 在不在盖房的位置」必须连高度一起算,站在屋顶上不算在屋里,不许从没封好的屋顶洞穿过;⑤ 门洞那一列永远空着,什么都不许放(包括会掉下来填进去的方块);⑥ 盖房材料排除会下落的方块(沙子、红沙、沙砾、各色混凝土粉末、铁砧等),没有别的材料就不盖;⑦ 服务器拒绝过的格子永久划掉,房子可以算「完成(跳过 N 格)」,否则脚本会一直把人派回去;⑧ 开工前先查目标格在不在别人的领地里,在就标「这里做不了」、不去试。麦家现在没有任何领地(Owner 定的),所以【任何领地都是别人的】—— 数据来源待定:服务器拒绝记录,或后台导出领地范围。 🔴 盖房硬约束(2026-09-18 实测小麦被自己的房子关住,20 分钟失败 110 次):① 任何一步都不许把方块放进盖房人正站的格子、头顶那格和门洞;② 每放一块之前,代码先算「放完以后我还走得出去吗」(站的格子到屋外有通路),走不出去就先走出去再放;③ 同一块连着被服务器拒绝 3 次,就换下一块或收工,不原地重试。这三条由代码判断,不问模型。 ⏳ 过渡:搬家(拍板第 1 件)定之前,挂在这里的 build_house / get_build_mats / son_take_mats 仍在现在的家把房子盖完(线上老行为,不倒退);定了搬以后改成在新家址盖。 门是 2 格高的物品，要点门洞下面那块地面的顶面放，朝向跟人的朝向走。墙的判定只看实心不实心，不看方块名（泥土长成草那次的教训）。站位必须站在墙格以外的格子上，不能用「离中心多远」来判断。僵尸自己开不了木门。</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>算账：64 格湿地整块种满，每格约 48 分钟出 1 个小麦 → 每游戏日约 27 个小麦 = 9 个面包 = 3 人 × 3 个；没水的话要约 140 格。一格水最多浇 80 格，靠边、靠角的格子邻居少，比中间长得慢一点。64 格要 64 颗种子：9 格田一茬净多约 15 颗，大约要 3~4 茬才攒够。木锄 59 次耐久，锄 64 格外加重锄，至少还要再做一把。🔴 零候选审计：原来固定 64 格。G1 的「面包盈余 ≥ 0」不成立（全家吃得比田里产的多，小麦远征路上吃的也算在内）时，G1 变回没完成，可 64 格早就达成了，没有任何小目标去扩田。改成「田格余量 ≥ 0」（C-FRM-22）：田格余量 = 有水的自家田 − 该有的田格数；该有的田格数 = 64 和按实测吃掉的面包算出的格数里取大的，再以田址实际能开的格数封顶。超了就按封顶算完成，并在后台写「田址不够大，面包仍然不够」，不让它变成永远做不完、又没人能推的死目标。</t>
+          <t>🔴 田要留走道:防踩耕地的护栏不许机器人站在耕地上,而种、收都要站在够得着的地方(代码上限 3.6 格)。所以每一格耕地到最近一块能站的非耕地,水平距离都要 ≤3 格,比如每 5 格宽留 1 格走道。不然田中间的格子永远种不上也收不了(实测:麦娘田里两格被四面耕地围住,1.5 小时空转 10 轮)。 算账：64 格湿地整块种满，每格约 48 分钟出 1 个小麦 → 每游戏日约 27 个小麦 = 9 个面包 = 3 人 × 3 个；没水的话要约 140 格。一格水最多浇 80 格，靠边、靠角的格子邻居少，比中间长得慢一点。64 格要 64 颗种子：9 格田一茬净多约 15 颗，大约要 3~4 茬才攒够。木锄 59 次耐久，锄 64 格外加重锄，至少还要再做一把。🔴 零候选审计：原来固定 64 格。G1 的「面包盈余 ≥ 0」不成立（全家吃得比田里产的多，小麦远征路上吃的也算在内）时，G1 变回没完成，可 64 格早就达成了，没有任何小目标去扩田。改成「田格余量 ≥ 0」（C-FRM-22）：田格余量 = 有水的自家田 − 该有的田格数；该有的田格数 = 64 和按实测吃掉的面包算出的格数里取大的，再以田址实际能开的格数封顶。超了就按封顶算完成，并在后台写「田址不够大，面包仍然不够」，不让它变成永远做不完、又没人能推的死目标。</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>🔴 床的硬约束:只睡自己或自家的床(自己放的、或 family.json 登记的),绝不躺别人的床(实测挑中了孩子领地里孩子的床);「走得到」要用真实路径算 —— 寻路的 goto 把「没有路」也当成功。 🔴 放方块硬约束(补充):④「在不在屋里 / 在不在盖房的位置」必须连高度一起算,站在屋顶上不算在屋里,不许从没封好的屋顶洞穿过;⑤ 门洞那一列永远空着,什么都不许放(包括会掉下来填进去的方块);⑥ 盖房材料排除会下落的方块(沙子、红沙、沙砾、各色混凝土粉末、铁砧等),没有别的材料就不盖;⑦ 服务器拒绝过的格子永久划掉,房子可以算「完成(跳过 N 格)」,否则脚本会一直把人派回去;⑧ 开工前先查目标格在不在别人的领地里,在就标「这里做不了」、不去试。麦家现在没有任何领地(Owner 定的),所以【任何领地都是别人的】—— 数据来源待定:服务器拒绝记录,或后台导出领地范围。 游戏里任何人都能睡任何一张没人占的床，「这是谁的床」只是我们自己记的账。重生点跟着最后睡过的那张床走；两个人不能同时睡一张床（会提示床已被占用）。现在的 sleep 只在 24 格内一张床都没有时才自己摆床，所以结构上只摆得出第一张，第二、第三张只能靠 place_bed。麦豆没有合成动作，也没有把东西交给别人的动作，所以他的床只能由做床的人直接摆进屋。</t>
+          <t>⑨ 自家箱子正上方那一格永远空着,不许放任何实心方块 —— MC 规则:箱子头顶有实心方块就打不开(2026-09-18 17:13 起家里那口箱子被压住,三个人开箱全部失败)。 🔴 床的硬约束:只睡自己或自家的床(自己放的、或 family.json 登记的),绝不躺别人的床(实测挑中了孩子领地里孩子的床);「走得到」要用真实路径算 —— 寻路的 goto 把「没有路」也当成功。 🔴 放方块硬约束(补充):④「在不在屋里 / 在不在盖房的位置」必须连高度一起算,站在屋顶上不算在屋里,不许从没封好的屋顶洞穿过;⑤ 门洞那一列永远空着,什么都不许放(包括会掉下来填进去的方块);⑥ 盖房材料排除会下落的方块(沙子、红沙、沙砾、各色混凝土粉末、铁砧等),没有别的材料就不盖;⑦ 服务器拒绝过的格子永久划掉,房子可以算「完成(跳过 N 格)」,否则脚本会一直把人派回去;⑧ 开工前先查目标格在不在别人的领地里,在就标「这里做不了」、不去试。麦家现在没有任何领地(Owner 定的),所以【任何领地都是别人的】—— 数据来源待定:服务器拒绝记录,或后台导出领地范围。 游戏里任何人都能睡任何一张没人占的床，「这是谁的床」只是我们自己记的账。重生点跟着最后睡过的那张床走；两个人不能同时睡一张床（会提示床已被占用）。现在的 sleep 只在 24 格内一张床都没有时才自己摆床，所以结构上只摆得出第一张，第二、第三张只能靠 place_bed。麦豆没有合成动作，也没有把东西交给别人的动作，所以他的床只能由做床的人直接摆进屋。</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
-          <t>🔴 放方块硬约束(补充):④「在不在屋里 / 在不在盖房的位置」必须连高度一起算,站在屋顶上不算在屋里,不许从没封好的屋顶洞穿过;⑤ 门洞那一列永远空着,什么都不许放(包括会掉下来填进去的方块);⑥ 盖房材料排除会下落的方块(沙子、红沙、沙砾、各色混凝土粉末、铁砧等),没有别的材料就不盖;⑦ 服务器拒绝过的格子永久划掉,房子可以算「完成(跳过 N 格)」,否则脚本会一直把人派回去;⑧ 开工前先查目标格在不在别人的领地里,在就标「这里做不了」、不去试。麦家现在没有任何领地(Owner 定的),所以【任何领地都是别人的】—— 数据来源待定:服务器拒绝记录,或后台导出领地范围。 🔴 盖房硬约束(2026-09-18 实测小麦被自己的房子关住,20 分钟失败 110 次):① 任何一步都不许把方块放进盖房人正站的格子、头顶那格和门洞;② 每放一块之前,代码先算「放完以后我还走得出去吗」(站的格子到屋外有通路),走不出去就先走出去再放;③ 同一块连着被服务器拒绝 3 次,就换下一块或收工,不原地重试。这三条由代码判断,不问模型。 1.18 起，敌对怪只在方块光照为 0 的地方刷，而且刷不到底半砖上（顶半砖和双层半砖上能刷）。人站在半砖上眼睛高出 0.5 格；放方块的伸手距离是 3.6 时，屋顶格在水平约 3.3 格内都够得着。对着同种底半砖的顶面再放一块，会合成双层半砖（完整方块，能刷怪），所以 placeAt「放之前先看目标格是不是空的」这条不能绕过。</t>
+          <t>⑨ 自家箱子正上方那一格永远空着,不许放任何实心方块 —— MC 规则:箱子头顶有实心方块就打不开(2026-09-18 17:13 起家里那口箱子被压住,三个人开箱全部失败)。 🔴 放方块硬约束(补充):④「在不在屋里 / 在不在盖房的位置」必须连高度一起算,站在屋顶上不算在屋里,不许从没封好的屋顶洞穿过;⑤ 门洞那一列永远空着,什么都不许放(包括会掉下来填进去的方块);⑥ 盖房材料排除会下落的方块(沙子、红沙、沙砾、各色混凝土粉末、铁砧等),没有别的材料就不盖;⑦ 服务器拒绝过的格子永久划掉,房子可以算「完成(跳过 N 格)」,否则脚本会一直把人派回去;⑧ 开工前先查目标格在不在别人的领地里,在就标「这里做不了」、不去试。麦家现在没有任何领地(Owner 定的),所以【任何领地都是别人的】—— 数据来源待定:服务器拒绝记录,或后台导出领地范围。 🔴 盖房硬约束(2026-09-18 实测小麦被自己的房子关住,20 分钟失败 110 次):① 任何一步都不许把方块放进盖房人正站的格子、头顶那格和门洞;② 每放一块之前,代码先算「放完以后我还走得出去吗」(站的格子到屋外有通路),走不出去就先走出去再放;③ 同一块连着被服务器拒绝 3 次,就换下一块或收工,不原地重试。这三条由代码判断,不问模型。 1.18 起，敌对怪只在方块光照为 0 的地方刷，而且刷不到底半砖上（顶半砖和双层半砖上能刷）。人站在半砖上眼睛高出 0.5 格；放方块的伸手距离是 3.6 时，屋顶格在水平约 3.3 格内都够得着。对着同种底半砖的顶面再放一块，会合成双层半砖（完整方块，能刷怪），所以 placeAt「放之前先看目标格是不是空的」这条不能绕过。</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>keepInventory 开着,路上死了也不掉东西;大约两趟搬完</t>
+          <t>⑨ 自家箱子正上方那一格永远空着,不许放任何实心方块 —— MC 规则:箱子头顶有实心方块就打不开(2026-09-18 17:13 起家里那口箱子被压住,三个人开箱全部失败)。 keepInventory 开着,路上死了也不掉东西;大约两趟搬完</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
-          <t>🔴 放方块硬约束(补充):④「在不在屋里 / 在不在盖房的位置」必须连高度一起算,站在屋顶上不算在屋里,不许从没封好的屋顶洞穿过;⑤ 门洞那一列永远空着,什么都不许放(包括会掉下来填进去的方块);⑥ 盖房材料排除会下落的方块(沙子、红沙、沙砾、各色混凝土粉末、铁砧等),没有别的材料就不盖;⑦ 服务器拒绝过的格子永久划掉,房子可以算「完成(跳过 N 格)」,否则脚本会一直把人派回去;⑧ 开工前先查目标格在不在别人的领地里,在就标「这里做不了」、不去试。麦家现在没有任何领地(Owner 定的),所以【任何领地都是别人的】—— 数据来源待定:服务器拒绝记录,或后台导出领地范围。 GP 在本服的设定是「新玩家放第一个箱子，自动圈一块半径 4 的地」。2026-09-18 已把两个 AI 账号的 griefprevention.createclaims 设成 false，按设计能挡住这条路，但没在游戏里实测过，麦豆的账号也不一定在那两个里面，所以只让麦娘放箱子，并且放完第一个就核对。箱子正上方要留空才能打开（放在半砖上的箱子，头顶还有 1 格空，够用）。Java 版里床和箱子都能放在半砖上，下面会空出半格，这是正常的。工作台顶面是完整方块，放在墙角、垫在半砖上以后，头顶只剩 1 格：僵尸、骷髅、苦力怕都太高；蜘蛛宽 1.4 格，被两面墙挡住，所以不会刷怪。</t>
+          <t>⑨ 自家箱子正上方那一格永远空着,不许放任何实心方块 —— MC 规则:箱子头顶有实心方块就打不开(2026-09-18 17:13 起家里那口箱子被压住,三个人开箱全部失败)。 🔴 放方块硬约束(补充):④「在不在屋里 / 在不在盖房的位置」必须连高度一起算,站在屋顶上不算在屋里,不许从没封好的屋顶洞穿过;⑤ 门洞那一列永远空着,什么都不许放(包括会掉下来填进去的方块);⑥ 盖房材料排除会下落的方块(沙子、红沙、沙砾、各色混凝土粉末、铁砧等),没有别的材料就不盖;⑦ 服务器拒绝过的格子永久划掉,房子可以算「完成(跳过 N 格)」,否则脚本会一直把人派回去;⑧ 开工前先查目标格在不在别人的领地里,在就标「这里做不了」、不去试。麦家现在没有任何领地(Owner 定的),所以【任何领地都是别人的】—— 数据来源待定:服务器拒绝记录,或后台导出领地范围。 GP 在本服的设定是「新玩家放第一个箱子，自动圈一块半径 4 的地」。2026-09-18 已把两个 AI 账号的 griefprevention.createclaims 设成 false，按设计能挡住这条路，但没在游戏里实测过，麦豆的账号也不一定在那两个里面，所以只让麦娘放箱子，并且放完第一个就核对。箱子正上方要留空才能打开（放在半砖上的箱子，头顶还有 1 格空，够用）。Java 版里床和箱子都能放在半砖上，下面会空出半格，这是正常的。工作台顶面是完整方块，放在墙角、垫在半砖上以后，头顶只剩 1 格：僵尸、骷髅、苦力怕都太高；蜘蛛宽 1.4 格，被两面墙挡住，所以不会刷怪。</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="J94" s="7" t="inlineStr">
         <is>
-          <t>🔴 放方块硬约束(补充):④「在不在屋里 / 在不在盖房的位置」必须连高度一起算,站在屋顶上不算在屋里,不许从没封好的屋顶洞穿过;⑤ 门洞那一列永远空着,什么都不许放(包括会掉下来填进去的方块);⑥ 盖房材料排除会下落的方块(沙子、红沙、沙砾、各色混凝土粉末、铁砧等),没有别的材料就不盖;⑦ 服务器拒绝过的格子永久划掉,房子可以算「完成(跳过 N 格)」,否则脚本会一直把人派回去;⑧ 开工前先查目标格在不在别人的领地里,在就标「这里做不了」、不去试。麦家现在没有任何领地(Owner 定的),所以【任何领地都是别人的】—— 数据来源待定:服务器拒绝记录,或后台导出领地范围。 初稿用「房子盖好了 = 1 且 缺口 ≥ 1」：如果「盖好了」是现算的，有缺口时它就是 0，两条永远不能同时成立；所以改用只记一次、永不清除的「新房完工过」，旧判据「房子盖好了」的意思不动。初稿的「离家距离 ≤ 32」在搬家之前量的是旧家，改成「离新家址」，这样也顺带保证区块已加载、扫描是实时的。苦力怕爆炸会在墙上开洞；「困难」难度下僵尸会破木门，要查服务器难度。</t>
+          <t>⑨ 自家箱子正上方那一格永远空着,不许放任何实心方块 —— MC 规则:箱子头顶有实心方块就打不开(2026-09-18 17:13 起家里那口箱子被压住,三个人开箱全部失败)。 🔴 放方块硬约束(补充):④「在不在屋里 / 在不在盖房的位置」必须连高度一起算,站在屋顶上不算在屋里,不许从没封好的屋顶洞穿过;⑤ 门洞那一列永远空着,什么都不许放(包括会掉下来填进去的方块);⑥ 盖房材料排除会下落的方块(沙子、红沙、沙砾、各色混凝土粉末、铁砧等),没有别的材料就不盖;⑦ 服务器拒绝过的格子永久划掉,房子可以算「完成(跳过 N 格)」,否则脚本会一直把人派回去;⑧ 开工前先查目标格在不在别人的领地里,在就标「这里做不了」、不去试。麦家现在没有任何领地(Owner 定的),所以【任何领地都是别人的】—— 数据来源待定:服务器拒绝记录,或后台导出领地范围。 初稿用「房子盖好了 = 1 且 缺口 ≥ 1」：如果「盖好了」是现算的，有缺口时它就是 0，两条永远不能同时成立；所以改用只记一次、永不清除的「新房完工过」，旧判据「房子盖好了」的意思不动。初稿的「离家距离 ≤ 32」在搬家之前量的是旧家，改成「离新家址」，这样也顺带保证区块已加载、扫描是实时的。苦力怕爆炸会在墙上开洞；「困难」难度下僵尸会破木门，要查服务器难度。</t>
         </is>
       </c>
     </row>
@@ -5555,7 +5555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G160"/>
+  <dimension ref="A1:G161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6234,17 +6234,17 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>wife_make_hoe</t>
+          <t>wife_logs_to_planks</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>自己做一把锄头</t>
+          <t>从箱子拿原木做成木板</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>M1-1</t>
+          <t>M1-1, M1-3</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr"/>
@@ -6267,17 +6267,17 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>wife_planks</t>
+          <t>wife_make_hoe</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>把原木做成木板</t>
+          <t>自己做一把锄头</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>M3-2</t>
+          <t>M1-1</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
@@ -6300,17 +6300,17 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>wife_plant</t>
+          <t>wife_planks</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>把种子种下去</t>
+          <t>把原木做成木板</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>M1-2, M1-4, M1-8</t>
+          <t>M3-2</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr"/>
@@ -6333,17 +6333,17 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>wife_store</t>
+          <t>wife_plant</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>把家当收进箱子</t>
+          <t>把种子种下去</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>A12, A19, J-A12-2, M6-1</t>
+          <t>M1-2, M1-4, M1-8</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr"/>
@@ -6366,17 +6366,17 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>wife_store_crop</t>
+          <t>wife_store</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>把粮食收进粮箱</t>
+          <t>把家当收进箱子</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>A14, M1-3, M1-9, M8-7</t>
+          <t>A12, A19, J-A12-2, M6-1</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr"/>
@@ -6399,17 +6399,17 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>wife_take_planks</t>
+          <t>wife_store_crop</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>从箱子里拿木板</t>
+          <t>把粮食收进粮箱</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>M1-1</t>
+          <t>A14, M1-3, M1-9, M8-7</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr"/>
@@ -6432,17 +6432,17 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>wife_till</t>
+          <t>wife_take_planks</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>在家门口耕一块地</t>
+          <t>从箱子里拿木板</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>M1-2</t>
+          <t>M1-1</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr"/>
@@ -6465,49 +6465,45 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>J-A1-1</t>
+          <t>wife_till</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>残血(≤6)又有危险:立刻传送脱险(人在家门口就去出生点)</t>
+          <t>在家门口耕一块地</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>全家</t>
-        </is>
-      </c>
+          <t>M1-2</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr"/>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>escape_tp</t>
+          <t>(已写好,在 scripts.json 里)</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>新写</t>
+          <t>现有</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>现在就能做</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>J-A1-2</t>
+          <t>J-A1-1</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>血不到一半、还有危险(或传送在冷却):先跑开</t>
+          <t>残血(≤6)又有危险:立刻传送脱险(人在家门口就去出生点)</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -6522,7 +6518,7 @@
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>flee</t>
+          <t>escape_tp</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -6532,19 +6528,19 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>J-A1-3</t>
+          <t>J-A1-2</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>没危险了:吃到能回血,原地歇着,血涨回14点</t>
+          <t>血不到一半、还有危险(或传送在冷却):先跑开</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
@@ -6559,7 +6555,7 @@
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>eat(跳过条件: 饱食度 ≥ 18) → idle(秒=8; 跳过条件: 饱食度 ≤ 17)</t>
+          <t>flee</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -6576,17 +6572,17 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>J-A2-1</t>
+          <t>J-A1-3</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>按规矩把贴脸的普通怪打掉(三人共用)</t>
+          <t>没危险了:吃到能回血,原地歇着,血涨回14点</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -6596,7 +6592,7 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>fight</t>
+          <t>eat(跳过条件: 饱食度 ≥ 18) → idle(秒=8; 跳过条件: 饱食度 ≤ 17)</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -6613,12 +6609,12 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>J-A2-2</t>
+          <t>J-A2-1</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>麦娘手里有剑时才还手,其余条件同小麦</t>
+          <t>按规矩把贴脸的普通怪打掉(三人共用)</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
@@ -6628,7 +6624,7 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>麦娘</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
@@ -6643,19 +6639,19 @@
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>J-A2-3</t>
+          <t>J-A2-2</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>还在挨打,或刚复活就被怪贴脸:传送脱险(小麦、麦娘在家门口就去出生点;麦豆不去出生点,在家附近躲)</t>
+          <t>麦娘手里有剑时才还手,其余条件同小麦</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
@@ -6665,12 +6661,12 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>全家</t>
+          <t>麦娘</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>escape_tp</t>
+          <t>fight</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -6687,12 +6683,12 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>J-A2-4</t>
+          <t>J-A2-3</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>其余情况一律跑:没剑、血 &lt;14(已在打的 ≤10)、怪 &gt;2 只、有苦力怕、在水里、刚复活、不是普通怪、旁边有人或宠物</t>
+          <t>还在挨打,或刚复活就被怪贴脸:传送脱险(小麦、麦娘在家门口就去出生点;麦豆不去出生点,在家附近躲)</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
@@ -6707,7 +6703,7 @@
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>flee</t>
+          <t>escape_tp</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -6717,24 +6713,24 @@
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>J-A3-1</t>
+          <t>J-A2-4</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>身上有牛奶就喝掉,一次清掉所有坏效果</t>
+          <t>其余情况一律跑:没剑、血 &lt;14(已在打的 ≤10)、怪 &gt;2 只、有苦力怕、在水里、刚复活、不是普通怪、旁边有人或宠物</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
@@ -6744,7 +6740,7 @@
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>drink_milk</t>
+          <t>flee</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -6754,19 +6750,19 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>J-A3-2</t>
+          <t>J-A3-1</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>没有牛奶:吃饱、待在原地别冒险,等毒过去</t>
+          <t>身上有牛奶就喝掉,一次清掉所有坏效果</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
@@ -6781,7 +6777,7 @@
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>eat(跳过条件: 饱食度 ≥ 18) → idle(秒=10)</t>
+          <t>drink_milk</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -6791,24 +6787,24 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>J-A4-1</t>
+          <t>J-A3-2</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>背包里有吃的就直接吃</t>
+          <t>没有牛奶:吃饱、待在原地别冒险,等毒过去</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
@@ -6818,7 +6814,7 @@
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>eat</t>
+          <t>eat(跳过条件: 饱食度 ≥ 18) → idle(秒=10)</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -6835,12 +6831,12 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>J-A4-2</t>
+          <t>J-A4-1</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>身上没吃的:回家去粮箱拿面包来吃</t>
+          <t>背包里有吃的就直接吃</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
@@ -6855,7 +6851,7 @@
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件: 离家距离 ≤ 8) → take_from_chest(东西=bread|cooked_*; 地方=粮箱) → eat</t>
+          <t>eat</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -6865,19 +6861,19 @@
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>J-A4-3</t>
+          <t>J-A4-2</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>身上、粮箱都没吃的:小麦去打猎(夜里除非快饿死,否则不去),不打别人的动物</t>
+          <t>身上没吃的:回家去粮箱拿面包来吃</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
@@ -6887,12 +6883,12 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>hunt</t>
+          <t>go_home(跳过条件: 离家距离 ≤ 8) → take_from_chest(东西=bread|cooked_*; 地方=粮箱) → eat</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -6909,27 +6905,27 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>J-A5-1</t>
+          <t>J-A4-3</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>苦力怕已经贴到3格内:立刻传送走</t>
+          <t>身上、粮箱都没吃的:小麦去打猎(夜里除非快饿死,否则不去),不打别人的动物</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>全家</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>escape_tp</t>
+          <t>hunt</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
@@ -6946,12 +6942,12 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>J-A5-2</t>
+          <t>J-A5-1</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>其余情况:只躲苦力怕这一只,朝反方向跑到10格外</t>
+          <t>苦力怕已经贴到3格内:立刻传送走</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
@@ -6966,7 +6962,7 @@
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>flee(东西=creeper)</t>
+          <t>escape_tp</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -6983,27 +6979,27 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>J-A6-1</t>
+          <t>J-A5-2</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>骷髅/掠夺者贴到5格内、血&gt;10、手上有剑:冲上去打(它们近战很弱)</t>
+          <t>其余情况:只躲苦力怕这一只,朝反方向跑到10格外</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>fight</t>
+          <t>flee(东西=creeper)</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -7013,19 +7009,19 @@
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>J-A6-2</t>
+          <t>J-A6-1</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>血≤8还在被射:传送走</t>
+          <t>骷髅/掠夺者贴到5格内、血&gt;10、手上有剑:冲上去打(它们近战很弱)</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
@@ -7035,12 +7031,12 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>全家</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>escape_tp</t>
+          <t>fight</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -7050,19 +7046,19 @@
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>J-A6-3</t>
+          <t>J-A6-2</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>其余情况:先在身前放一块泥土或圆石挡箭,再跑出射程</t>
+          <t>血≤8还在被射:传送走</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
@@ -7077,7 +7073,7 @@
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>cover_arrows(东西=dirt|cobblestone) → flee</t>
+          <t>escape_tp</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -7094,17 +7090,17 @@
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>J-A7-1</t>
+          <t>J-A6-3</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>氧气剩不到五分之一,或脑袋卡进方块:立刻传送走</t>
+          <t>其余情况:先在身前放一块泥土或圆石挡箭,再跑出射程</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -7114,7 +7110,7 @@
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>escape_tp</t>
+          <t>cover_arrows(东西=dirt|cobblestone) → flee</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
@@ -7131,12 +7127,12 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>J-A7-2</t>
+          <t>J-A7-1</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>脑袋卡在方块里但传送用不了:原地挪开</t>
+          <t>氧气剩不到五分之一,或脑袋卡进方块:立刻传送走</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
@@ -7151,7 +7147,7 @@
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>wander(秒=2)</t>
+          <t>escape_tp</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
@@ -7161,19 +7157,19 @@
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>J-A7-3</t>
+          <t>J-A7-2</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>其余情况:往上浮、往岸边游</t>
+          <t>脑袋卡在方块里但传送用不了:原地挪开</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
@@ -7188,7 +7184,7 @@
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>surface</t>
+          <t>wander(秒=2)</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
@@ -7198,24 +7194,24 @@
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>J-A8-1</t>
+          <t>J-A7-3</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>在岩浆里:立刻传送走</t>
+          <t>其余情况:往上浮、往岸边游</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>A8</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
@@ -7225,7 +7221,7 @@
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>escape_tp</t>
+          <t>surface</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
@@ -7242,12 +7238,12 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>J-A8-2</t>
+          <t>J-A8-1</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>在岩浆里但传送用不了:往最近的实地爬出去</t>
+          <t>在岩浆里:立刻传送走</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
@@ -7262,7 +7258,7 @@
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>escape_lava</t>
+          <t>escape_tp</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -7279,12 +7275,12 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>J-A8-3</t>
+          <t>J-A8-2</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>身上着火、12格内记得有水:跳进水里灭火</t>
+          <t>在岩浆里但传送用不了:往最近的实地爬出去</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
@@ -7299,7 +7295,7 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方=水源)</t>
+          <t>escape_lava</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -7309,19 +7305,19 @@
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>J-A8-4</t>
+          <t>J-A8-3</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>着火但附近没水:挪开几步离开火源,吃饱顶住等火灭</t>
+          <t>身上着火、12格内记得有水:跳进水里灭火</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
@@ -7336,7 +7332,7 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>wander(秒=3) → eat(跳过条件: 饱食度 ≥ 18)</t>
+          <t>goto_place(地方=水源)</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -7353,17 +7349,17 @@
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>J-A9-1</t>
+          <t>J-A8-4</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>按血量切换走路时最多能往下跳几格(现有代码,不是动作)</t>
+          <t>着火但附近没水:挪开几步离开火源,吃饱顶住等火灭</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>A9</t>
+          <t>A8</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -7371,7 +7367,11 @@
           <t>全家</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr"/>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>wander(秒=3) → eat(跳过条件: 饱食度 ≥ 18)</t>
+        </is>
+      </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
           <t>新写</t>
@@ -7379,24 +7379,24 @@
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>现在就能做</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>J-A10-1</t>
+          <t>J-A9-1</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>卡住了:传送走(escape_tp 自己决定回家还是去出生点)</t>
+          <t>按血量切换走路时最多能往下跳几格(现有代码,不是动作)</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>A9</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
@@ -7404,11 +7404,7 @@
           <t>全家</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>escape_tp</t>
-        </is>
-      </c>
+      <c r="E53" s="7" t="inlineStr"/>
       <c r="F53" s="7" t="inlineStr">
         <is>
           <t>新写</t>
@@ -7416,24 +7412,24 @@
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>现在就能做</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>J-A11-1</t>
+          <t>J-A10-1</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>有自家的空床、周围没怪:去睡</t>
+          <t>卡住了:传送走(escape_tp 自己决定回家还是去出生点)</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>A11</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
@@ -7443,7 +7439,7 @@
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>sleep</t>
+          <t>escape_tp</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
@@ -7460,12 +7456,12 @@
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>J-A11-2</t>
+          <t>J-A11-1</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>没有空床但背包里材料够:先做一张床,放在家门口再睡</t>
+          <t>有自家的空床、周围没怪:去睡</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
@@ -7480,7 +7476,7 @@
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>craft(东西=bedIWouldCraft() 选出的颜色的床(如 white_bed)) → sleep</t>
+          <t>sleep</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
@@ -7497,12 +7493,12 @@
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>J-A11-3</t>
+          <t>J-A11-2</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>睡不了,但家里能安全过夜(有顶、有光、门洞堵上):回屋待到天亮</t>
+          <t>没有空床但背包里材料够:先做一张床,放在家门口再睡</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
@@ -7517,7 +7513,7 @@
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件: 在屋里 = 1) → idle(秒=30)</t>
+          <t>craft(东西=bedIWouldCraft() 选出的颜色的床(如 white_bed)) → sleep</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
@@ -7527,24 +7523,24 @@
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>J-A12-1</t>
+          <t>J-A11-3</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>每秒自动扔掉真正的杂物(现有代码,不是动作,不占身体)</t>
+          <t>睡不了,但家里能安全过夜(有顶、有光、门洞堵上):回屋待到天亮</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>A12</t>
+          <t>A11</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
@@ -7552,7 +7548,11 @@
           <t>全家</t>
         </is>
       </c>
-      <c r="E57" s="7" t="inlineStr"/>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>go_home(跳过条件: 在屋里 = 1) → idle(秒=30)</t>
+        </is>
+      </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
           <t>新写</t>
@@ -7560,19 +7560,19 @@
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>现在就能做</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>J-A12-2</t>
+          <t>J-A12-1</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>回家把能存的东西存进箱子</t>
+          <t>每秒自动扔掉真正的杂物(现有代码,不是动作,不占身体)</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
@@ -7585,11 +7585,7 @@
           <t>全家</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>go_home(跳过条件: 离家距离 ≤ 8) → store_items</t>
-        </is>
-      </c>
+      <c r="E58" s="7" t="inlineStr"/>
       <c r="F58" s="7" t="inlineStr">
         <is>
           <t>新写</t>
@@ -7597,19 +7593,19 @@
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>现在就能做</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>J-A12-3</t>
+          <t>J-A12-2</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>箱子满了、身上带着空箱子:贴着家里的箱子放下再存</t>
+          <t>回家把能存的东西存进箱子</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
@@ -7624,7 +7620,7 @@
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件: 离家距离 ≤ 8) → place_chest(地方=紧贴家里现有箱子) → store_items</t>
+          <t>go_home(跳过条件: 离家距离 ≤ 8) → store_items</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
@@ -7634,19 +7630,19 @@
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>J-A12-4</t>
+          <t>J-A12-3</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>箱子满了、身上没空箱子但有8块木板:先做一口箱子</t>
+          <t>箱子满了、身上带着空箱子:贴着家里的箱子放下再存</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
@@ -7661,7 +7657,7 @@
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>craft(东西=chest)</t>
+          <t>go_home(跳过条件: 离家距离 ≤ 8) → place_chest(地方=紧贴家里现有箱子) → store_items</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
@@ -7671,24 +7667,24 @@
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>J-A13-1</t>
+          <t>J-A12-4</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>白天、周围安全时,去把登记过的挡箭块一块块拆回来</t>
+          <t>箱子满了、身上没空箱子但有8块木板:先做一口箱子</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>A13</t>
+          <t>A12</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -7698,7 +7694,7 @@
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>pickup_cover</t>
+          <t>craft(东西=chest)</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
@@ -7708,24 +7704,24 @@
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>J-A14</t>
+          <t>J-A13-1</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>身上面包快吃完了，就回家从粮箱拿 3 个面包揣着。</t>
+          <t>白天、周围安全时,去把登记过的挡箭块一块块拆回来</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>A14</t>
+          <t>A13</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
@@ -7735,7 +7731,7 @@
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 24) → take_from_chest(东西：口粮（只拿面包、一次 3 个；要先加这个名字）)</t>
+          <t>pickup_cover</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
@@ -7752,27 +7748,27 @@
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>J-A15-1</t>
+          <t>J-A14</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>小麦睡前，床边只有一两只好打的怪（僵尸、蜘蛛之类），附近没有苦力怕、末影人、骷髅，自己血量足又有剑时，先打掉</t>
+          <t>身上面包快吃完了，就回家从粮箱拿 3 个面包揣着。</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>A15</t>
+          <t>A14</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>fight</t>
+          <t>go_home(跳过条件：离家距离 ≤ 24) → take_from_chest(东西：口粮（只拿面包、一次 3 个；要先加这个名字）)</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
@@ -7789,12 +7785,12 @@
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>J-A15-2</t>
+          <t>J-A15-1</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>床边有怪睡不成时，回家待在屋里，等床边没怪了再去睡（常常要等到天亮）</t>
+          <t>小麦睡前，床边只有一两只好打的怪（僵尸、蜘蛛之类），附近没有苦力怕、末影人、骷髅，自己血量足又有剑时，先打掉</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
@@ -7804,12 +7800,12 @@
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>全家</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离≤8) → idle</t>
+          <t>fight</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
@@ -7826,27 +7822,27 @@
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>J-A16</t>
+          <t>J-A15-2</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>新房破了洞、地板被炸或门没了，小麦就拿上木板、半砖和门回去，按原样补上。</t>
+          <t>床边有怪睡不成时，回家待在屋里，等床边没怪了再去睡（常常要等到天亮）</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>A16</t>
+          <t>A15</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>take_from_chest(东西=设计定的木板；数量=新房墙缺口数 + 新房屋顶缺口数 + 4；跳过条件：新房墙缺口数 = 0 且 新房屋顶缺口数 = 0) → take_from_chest(东西=半砖；数量=新房地面裸露格数；跳过条件：新房地面裸露格数 = 0) → take_from_chest(东西=门；数量=1；跳过条件：新房有门 = 1) → goto_place(地方=新家；直到 离新家址 ≤ 6；跳过条件：离新家址 ≤ 6) → build_house(阶段=补缺口；直到 新房缺口数 = 0)</t>
+          <t>go_home(跳过条件：离家距离≤8) → idle</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
@@ -7863,25 +7859,29 @@
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>J-A17</t>
+          <t>J-A16</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>右键把新房的门关上。</t>
+          <t>新房破了洞、地板被炸或门没了，小麦就拿上木板、半砖和门回去，按原样补上。</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>A17</t>
+          <t>A16</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>全家</t>
-        </is>
-      </c>
-      <c r="E66" s="7" t="inlineStr"/>
+          <t>小麦</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>take_from_chest(东西=设计定的木板；数量=新房墙缺口数 + 新房屋顶缺口数 + 4；跳过条件：新房墙缺口数 = 0 且 新房屋顶缺口数 = 0) → take_from_chest(东西=半砖；数量=新房地面裸露格数；跳过条件：新房地面裸露格数 = 0) → take_from_chest(东西=门；数量=1；跳过条件：新房有门 = 1) → goto_place(地方=新家；直到 离新家址 ≤ 6；跳过条件：离新家址 ≤ 6) → build_house(阶段=补缺口；直到 新房缺口数 = 0)</t>
+        </is>
+      </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
           <t>新写</t>
@@ -7896,25 +7896,25 @@
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>J-A20</t>
+          <t>J-A17</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>回家</t>
+          <t>右键把新房的门关上。</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>A20</t>
-        </is>
-      </c>
-      <c r="D67" s="7" t="inlineStr"/>
-      <c r="E67" s="7" t="inlineStr">
-        <is>
-          <t>go_home</t>
-        </is>
-      </c>
+          <t>A17</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>全家</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr"/>
       <c r="F67" s="7" t="inlineStr">
         <is>
           <t>新写</t>
@@ -7922,34 +7922,30 @@
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>现在就能做</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>J-A21-1</t>
+          <t>J-A20</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>离他近（32 格内，夜里 16 格内），或者他没家、白天、在 96 格内：走到他跟前，把吃的丢在他身边</t>
+          <t>回家</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>A21</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>全家</t>
-        </is>
-      </c>
+          <t>A20</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr"/>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>give_to_family(给=分给我的那个家人；东西=正经吃的（先熟肉、再面包；不送汤和煲、金苹果、腐肉；身上留≥2 个面包）；数量=这单能给的份数；地点=他身边)</t>
+          <t>go_home</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
@@ -7959,19 +7955,19 @@
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>现在就能做</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>J-A21-2</t>
+          <t>J-A21-1</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>离得远、两人的家都在粮箱旁：两人都传送回家，在粮箱旁交</t>
+          <t>离他近（32 格内，夜里 16 格内），或者他没家、白天、在 96 格内：走到他跟前，把吃的丢在他身边</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
@@ -7986,7 +7982,7 @@
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → goto_place(地方=粮箱（C-NAV-1 加的地名）) → give_to_family(给=分给我的那个家人；东西=正经吃的（先熟肉、再面包，身上留≥2 个面包）；数量=这单能给的份数；地点=粮箱旁 4 格内，他到了才丢)</t>
+          <t>give_to_family(给=分给我的那个家人；东西=正经吃的（先熟肉、再面包；不送汤和煲、金苹果、腐肉；身上留≥2 个面包）；数量=这单能给的份数；地点=他身边)</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
@@ -8003,12 +7999,12 @@
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>J-A21-3</t>
+          <t>J-A21-2</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>我身上没有能分的，但粮箱里有：替他回家从粮箱拿 3 份正经吃的（先面包、再熟肉），再送给他（主要是给不会开箱子、也没有家的麦豆）</t>
+          <t>离得远、两人的家都在粮箱旁：两人都传送回家，在粮箱旁交</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
@@ -8023,7 +8019,7 @@
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → goto_place(地方=粮箱) → take_from_chest(东西=正经吃的，一次 3 份（先面包、再熟肉）；拿之前记下身上份数，差值就是替他拿的份数) → give_to_family(给=分给我的那个家人；东西=刚替他拿的；数量=替他拿的份数（不受我的保底限制）；地点=按送吃的交接地点)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → goto_place(地方=粮箱（C-NAV-1 加的地名）) → give_to_family(给=分给我的那个家人；东西=正经吃的（先熟肉、再面包，身上留≥2 个面包）；数量=这单能给的份数；地点=粮箱旁 4 格内，他到了才丢)</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
@@ -8040,17 +8036,17 @@
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>J-A22-1</t>
+          <t>J-A21-3</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>他来我这儿交：原地站着、面朝他，东西落地就走上去捡</t>
+          <t>我身上没有能分的，但粮箱里有：替他回家从粮箱拿 3 份正经吃的（先面包、再熟肉），再送给他（主要是给不会开箱子、也没有家的麦豆）</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>A22</t>
+          <t>A21</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
@@ -8060,7 +8056,7 @@
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>idle(站着别动、面朝送东西的家人；直到：他丢出东西了=1；最多等到锁作废) → pick_up_drop(只捡这一单丢在我 6 格内、种类数量对得上的)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → goto_place(地方=粮箱) → take_from_chest(东西=正经吃的，一次 3 份（先面包、再熟肉）；拿之前记下身上份数，差值就是替他拿的份数) → give_to_family(给=分给我的那个家人；东西=刚替他拿的；数量=替他拿的份数（不受我的保底限制）；地点=按送吃的交接地点)</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
@@ -8077,12 +8073,12 @@
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>J-A22-2</t>
+          <t>J-A22-1</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>约好回家交：传送回家，走到粮箱旁站着等，东西落地就捡</t>
+          <t>他来我这儿交：原地站着、面朝他，东西落地就走上去捡</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
@@ -8097,7 +8093,7 @@
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → goto_place(地方=粮箱（C-NAV-1 加的地名）) → idle(直到：他丢出东西了=1；最多等到锁作废) → pick_up_drop(只捡这一单丢在我 6 格内、种类数量对得上的)</t>
+          <t>idle(站着别动、面朝送东西的家人；直到：他丢出东西了=1；最多等到锁作废) → pick_up_drop(只捡这一单丢在我 6 格内、种类数量对得上的)</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
@@ -8114,12 +8110,12 @@
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>J-A22-3</t>
+          <t>J-A22-2</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>家人来接我：原地等他走到跟前，然后跟着他走回家</t>
+          <t>约好回家交：传送回家，走到粮箱旁站着等，东西落地就捡</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
@@ -8134,7 +8130,7 @@
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>idle(直到：离来接我的家人 ≤ 6；最多等到锁作废) → follow_player(跟=来接我的家人（执行闸只许跟家人）；直到：离全家的家 ≤ 16)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → goto_place(地方=粮箱（C-NAV-1 加的地名）) → idle(直到：他丢出东西了=1；最多等到锁作废) → pick_up_drop(只捡这一单丢在我 6 格内、种类数量对得上的)</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
@@ -8151,12 +8147,12 @@
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>J-A22-4</t>
+          <t>J-A22-3</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>麦豆交给我、要我帮忙存的东西：收下后马上回家存进箱子</t>
+          <t>家人来接我：原地等他走到跟前，然后跟着他走回家</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
@@ -8166,12 +8162,12 @@
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>任意</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → store_items(存进大箱子；存完在锁里写「已存好」并删锁)</t>
+          <t>idle(直到：离来接我的家人 ≤ 6；最多等到锁作废) → follow_player(跟=来接我的家人（执行闸只许跟家人）；直到：离全家的家 ≤ 16)</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
@@ -8181,34 +8177,34 @@
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>J-A23-1</t>
+          <t>J-A22-4</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>走到他跟前，把那把工具丢在他身边</t>
+          <t>麦豆交给我、要我帮忙存的东西：收下后马上回家存进箱子</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>A23</t>
+          <t>A22</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>全家</t>
+          <t>任意</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>give_to_family(给=缺这件工具的家人；东西=多余的那种工具里耐久剩得最多的一把；数量=1；地点=他身边（两人都在家附近时就在家里）)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → store_items(存进大箱子；存完在锁里写「已存好」并删锁)</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
@@ -8218,34 +8214,34 @@
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>J-A24-1</t>
+          <t>J-A23-1</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>跑到他身边，只打围着他的那几只怪，打完就回去接着干原来的活</t>
+          <t>走到他跟前，把那把工具丢在他身边</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>A24</t>
+          <t>A23</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>fight(护着=被围攻的家人；只打他 6 格内主动攻击的普通近战怪；离他不超过 12 格；最多 60 秒)</t>
+          <t>give_to_family(给=缺这件工具的家人；东西=多余的那种工具里耐久剩得最多的一把；数量=1；地点=他身边（两人都在家附近时就在家里）)</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
@@ -8255,34 +8251,34 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>缺动作</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>J-A25-1</t>
+          <t>J-A24-1</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>往能护着我的大人那边跑，躲到他身后</t>
+          <t>跑到他身边，只打围着他的那几只怪，打完就回去接着干原来的活</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>A25</t>
+          <t>A24</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>麦豆</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>flee(往=能护着我的家人；到他身后 2 格（背对怪的那一侧）就站住)</t>
+          <t>fight(护着=被围攻的家人；只打他 6 格内主动攻击的普通近战怪；离他不超过 12 格；最多 60 秒)</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
@@ -8292,34 +8288,34 @@
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺动作</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>J-A26-1</t>
+          <t>J-A25-1</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>朝他走过去（看得见他以后，跟着他的实时位置走）</t>
+          <t>往能护着我的大人那边跑，躲到他身后</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>A26</t>
+          <t>A25</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>小麦 / 麦娘</t>
+          <t>麦豆</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>walk_to_family(目标=回不了家的家人；看不见时用状态板坐标，每 10 秒刷新；最多 300 秒)</t>
+          <t>flee(往=能护着我的家人；到他身后 2 格（背对怪的那一侧）就站住)</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
@@ -8336,12 +8332,12 @@
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>J-A26-2</t>
+          <t>J-A26-1</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>走到他身边后，领着他走回家，他跟丢了就停下等</t>
+          <t>朝他走过去（看得见他以后，跟着他的实时位置走）</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
@@ -8356,7 +8352,7 @@
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>lead_home(被接的人=回不了家的家人；他落后超过 12 格就停下等；直到：他离全家的家 ≤ 16；最多 600 秒；离天黑秒数 ≤ 60 时放弃)</t>
+          <t>walk_to_family(目标=回不了家的家人；看不见时用状态板坐标，每 10 秒刷新；最多 300 秒)</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
@@ -8373,27 +8369,27 @@
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>J-A27-1</t>
+          <t>J-A26-2</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>会存箱子的家人就在附近：走到她跟前，把能存的东西丢给她</t>
+          <t>走到他身边后，领着他走回家，他跟丢了就停下等</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>A27</t>
+          <t>A26</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>麦豆</t>
+          <t>小麦 / 麦娘</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>give_to_family(给=能接手的家人；东西=可存的东西（不含吃的、唯一的工具、贵重）；最多 5 格；地点=她身边)</t>
+          <t>lead_home(被接的人=回不了家的家人；他落后超过 12 格就停下等；直到：他离全家的家 ≤ 16；最多 600 秒；离天黑秒数 ≤ 60 时放弃)</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
@@ -8410,12 +8406,12 @@
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>J-A27-2</t>
+          <t>J-A27-1</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>离得远、两人都有家：回家，把能存的东西丢给回到家的麦娘（或小麦）</t>
+          <t>会存箱子的家人就在附近：走到她跟前，把能存的东西丢给她</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
@@ -8430,7 +8426,7 @@
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → give_to_family(给=能接手的家人；东西=可存的东西（不含吃的、唯一的工具、贵重）；最多 5 格；地点=家里大箱子旁 4 格内，她到了才丢)</t>
+          <t>give_to_family(给=能接手的家人；东西=可存的东西（不含吃的、唯一的工具、贵重）；最多 5 格；地点=她身边)</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
@@ -8447,27 +8443,27 @@
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>J-A28-1</t>
+          <t>J-A27-2</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>把多出来的吃的存进粮箱</t>
+          <t>离得远、两人都有家：回家，把能存的东西丢给回到家的麦娘（或小麦）</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>A28</t>
+          <t>A27</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>全家</t>
+          <t>麦豆</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>store_items(箱子=粮箱；东西=多出来的正经吃的（先熟肉、后面包；身上留 6 份、至少 2 个面包；粮箱最多补到 12 份）)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → give_to_family(给=能接手的家人；东西=可存的东西（不含吃的、唯一的工具、贵重）；最多 5 格；地点=家里大箱子旁 4 格内，她到了才丢)</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
@@ -8477,32 +8473,36 @@
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>缺动作</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>J-G3-0a</t>
+          <t>J-A28-1</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>如果库存只凑得出一种木头样式，就由代码直接定下来，不问模型。</t>
+          <t>把多出来的吃的存进粮箱</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>M3-2</t>
+          <t>A28</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
-        </is>
-      </c>
-      <c r="E83" s="7" t="inlineStr"/>
+          <t>全家</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>store_items(箱子=粮箱；东西=多出来的正经吃的（先熟肉、后面包；身上留 6 份、至少 2 个面包；粮箱最多补到 12 份）)</t>
+        </is>
+      </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
           <t>新写</t>
@@ -8510,29 +8510,29 @@
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺动作</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>J-G3-0b</t>
+          <t>J-G3-0a</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>如果新房里只有一种合法的家具摆法，就由代码直接定，不问模型。</t>
+          <t>如果库存只凑得出一种木头样式，就由代码直接定下来，不问模型。</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>M3-6</t>
+          <t>M3-2</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>麦娘</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr"/>
@@ -8550,29 +8550,25 @@
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>J-M1-0</t>
+          <t>J-G3-0b</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>小麦往离出生点远的方向转一圈，程序边走边给看到的空地打分，记下最适合种田的一块。</t>
+          <t>如果新房里只有一种合法的家具摆法，就由代码直接定，不问模型。</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>M1-0</t>
+          <t>M3-6</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
-        </is>
-      </c>
-      <c r="E85" s="7" t="inlineStr">
-        <is>
-          <t>explore(方向：离出生点更远的那一侧（东/南/西/北，由代码按出生点方位算，不问模型）)</t>
-        </is>
-      </c>
+          <t>麦娘</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr"/>
       <c r="F85" s="7" t="inlineStr">
         <is>
           <t>新写</t>
@@ -8587,27 +8583,27 @@
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>J-M1-2</t>
+          <t>J-M1-0</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>走到田里，锄完这一批地马上种上麦子，直到 9 格都种满。</t>
+          <t>小麦往离出生点远的方向转一圈，程序边走边给看到的空地打分，记下最适合种田的一块。</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>M1-2</t>
+          <t>M1-0</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>麦娘</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方：田；跳过条件：离田距离 ≤ 16) → till_soil(跳过条件：耕好的地 ≥ 9) → plant_seeds(跳过条件：有种子 = 0)</t>
+          <t>explore(方向：离出生点更远的那一侧（东/南/西/北，由代码按出生点方位算，不问模型）)</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
@@ -8624,17 +8620,17 @@
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>J-M1-4</t>
+          <t>J-M1-2</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>田里攒够几株熟麦子就去收，收完当场把空出来的格子补种上。</t>
+          <t>走到田里，锄完这一批地马上种上麦子，直到 9 格都种满。</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>M1-4</t>
+          <t>M1-2</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
@@ -8644,7 +8640,7 @@
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方：田；跳过条件：离田距离 ≤ 16) → harvest_crop → plant_seeds(跳过条件：有种子 = 0)</t>
+          <t>goto_place(地方：田；跳过条件：离田距离 ≤ 16) → till_soil(跳过条件：耕好的地 ≥ 9) → plant_seeds(跳过条件：有种子 = 0)</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
@@ -8661,27 +8657,27 @@
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>J-M1-6</t>
+          <t>J-M1-4</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>小麦从箱子拿 3 个铁锭做个铁桶，去最近的水边装一桶水，回来倒进田边挖好的一格坑里。</t>
+          <t>田里攒够几株熟麦子就去收，收完当场把空出来的格子补种上。</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>M1-6</t>
+          <t>M1-4</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>麦娘</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 24) → take_from_chest(东西：铁锭（要先加这个名字，一次拿 3 个）；跳过条件：身上有桶 ≥ 1) → craft(东西：bucket；跳过条件：身上有桶 ≥ 1) → goto_place(地方：田；跳过条件：离田距离 ≤ 16)</t>
+          <t>goto_place(地方：田；跳过条件：离田距离 ≤ 16) → harvest_crop → plant_seeds(跳过条件：有种子 = 0)</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
@@ -8698,27 +8694,27 @@
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>J-M1-7</t>
+          <t>J-M1-6</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>在水浇得到的地方把麦田一批批扩大，锄一批种一批，直到 64 格。</t>
+          <t>小麦从箱子拿 3 个铁锭做个铁桶，去最近的水边装一桶水，回来倒进田边挖好的一格坑里。</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>M1-7</t>
+          <t>M1-6</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>麦娘</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方：田；跳过条件：离田距离 ≤ 16) → till_soil(跳过条件：有水的自家田 ≥ 64) → plant_seeds(跳过条件：有种子 = 0)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 24) → take_from_chest(东西：铁锭（要先加这个名字，一次拿 3 个）；跳过条件：身上有桶 ≥ 1) → craft(东西：bucket；跳过条件：身上有桶 ≥ 1) → goto_place(地方：田；跳过条件：离田距离 ≤ 16)</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
@@ -8735,12 +8731,12 @@
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>J-M1-7b</t>
+          <t>J-M1-7</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>在水浇得到的地方把麦田一批批扩大，锄一批种一批，直到田的大小够全家吃（按实测吃掉的面包算，最少 64 格）。</t>
+          <t>在水浇得到的地方把麦田一批批扩大，锄一批种一批，直到 64 格。</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
@@ -8755,7 +8751,7 @@
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方=田；跳过条件：离田距离 ≤ 16) → till_soil(跳过条件：田格余量 ≥ 0) → plant_seeds(跳过条件：有种子 = 0)</t>
+          <t>goto_place(地方：田；跳过条件：离田距离 ≤ 16) → till_soil(跳过条件：有水的自家田 ≥ 64) → plant_seeds(跳过条件：有种子 = 0)</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
@@ -8772,27 +8768,27 @@
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>J-M1-8</t>
+          <t>J-M1-7b</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>麦豆白天去自家田里收熟麦子，当场种回去，再把小麦存进粮箱给妈妈做面包。</t>
+          <t>在水浇得到的地方把麦田一批批扩大，锄一批种一批，直到田的大小够全家吃（按实测吃掉的面包算，最少 64 格）。</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>M1-8</t>
+          <t>M1-7</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>麦豆</t>
+          <t>麦娘</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方=田；跳过条件：离田距离 ≤ 16) → harvest_crop(先拿田里收割锁，拿不到就跳过；只收自家田登记簿里的格子) → plant_seeds(收完的格子当场种回去；跳过条件：有种子 = 0) → go_home(跳过条件：离家距离 ≤ 8) → store_crop(麦豆身上只留 3 个面包、16 颗种子，小麦全部进粮箱)</t>
+          <t>goto_place(地方=田；跳过条件：离田距离 ≤ 16) → till_soil(跳过条件：田格余量 ≥ 0) → plant_seeds(跳过条件：有种子 = 0)</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
@@ -8809,12 +8805,12 @@
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>J-M1-8c</t>
+          <t>J-M1-8</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>麦豆收熟了的麦子(照抄麦娘的 wife_harvest,门槛换成麦豆的)</t>
+          <t>麦豆白天去自家田里收熟麦子，当场种回去，再把小麦存进粮箱给妈妈做面包。</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
@@ -8829,7 +8825,7 @@
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>go_home → harvest_crop</t>
+          <t>goto_place(地方=田；跳过条件：离田距离 ≤ 16) → harvest_crop(先拿田里收割锁，拿不到就跳过；只收自家田登记簿里的格子) → plant_seeds(收完的格子当场种回去；跳过条件：有种子 = 0) → go_home(跳过条件：离家距离 ≤ 8) → store_crop(麦豆身上只留 3 个面包、16 颗种子，小麦全部进粮箱)</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
@@ -8839,19 +8835,19 @@
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>卡在代码</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>J-M1-8d</t>
+          <t>J-M1-8c</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>麦豆把收空的地种回去(照抄 wife_plant,门槛换成麦豆的)</t>
+          <t>麦豆收熟了的麦子(照抄麦娘的 wife_harvest,门槛换成麦豆的)</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
@@ -8866,7 +8862,7 @@
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>go_home → plant_seeds</t>
+          <t>go_home → harvest_crop</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
@@ -8883,27 +8879,27 @@
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>J-M1-9</t>
+          <t>J-M1-8d</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>麦娘从粮箱拿出麦豆和自己存进去的小麦，做成面包再放回粮箱。</t>
+          <t>麦豆把收空的地种回去(照抄 wife_plant,门槛换成麦豆的)</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>M1-9</t>
+          <t>M1-8</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>麦娘</t>
+          <t>麦豆</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=小麦，从粮箱拿，拿 3 的倍数、最多 27 个) → craft(东西=bread) → store_crop(面包进粮箱（她身上照常留 3 个）)</t>
+          <t>go_home → plant_seeds</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
@@ -8913,24 +8909,24 @@
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>卡在代码</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>J-M2-1-1</t>
+          <t>J-M1-9</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>麦娘白天回家，从箱子拿线合成白羊毛，配同种木板，用家里现有的工作台做床；一轮做一张，做够 3 张为止</t>
+          <t>麦娘从粮箱拿出麦豆和自己存进去的小麦，做成面包再放回粮箱。</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>M2-1</t>
+          <t>M1-9</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
@@ -8940,7 +8936,7 @@
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离≤24) → take_from_chest(东西=线（别名待加）；跳过条件：背包线≥12 / 背包同色羊毛最多≥3) → craft(东西=white_wool；跳过条件：背包同色羊毛最多≥3) → craft(东西=white_wool；跳过条件：背包同色羊毛最多≥3) → craft(东西=white_wool；跳过条件：背包同色羊毛最多≥3) → take_from_chest(东西=原木；跳过条件：背包同种木板最多≥3 / 背包木头≥1) → craft(东西=planks；跳过条件：背包同种木板最多≥3) → craft(东西=bed)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=小麦，从粮箱拿，拿 3 的倍数、最多 27 个) → craft(东西=bread) → store_crop(面包进粮箱（她身上照常留 3 个）)</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
@@ -8957,12 +8953,12 @@
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>J-M2-1-2</t>
+          <t>J-M2-1-1</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>兜底：箱子里的线不够做下一张床时，小麦白天看见能打的羊就去打，凑够 3 块同色羊毛就回家做床</t>
+          <t>麦娘白天回家，从箱子拿线合成白羊毛，配同种木板，用家里现有的工作台做床；一轮做一张，做够 3 张为止</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
@@ -8972,12 +8968,12 @@
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>麦娘</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>hunt(跳过条件：背包同色羊毛最多≥3 / 附近能打的羊=0) → go_home(跳过条件：背包同色羊毛最多≤2 / 离家距离≤24) → take_from_chest(东西=原木；跳过条件：背包同种木板最多≥3 / 背包木头≥1 / 背包同色羊毛最多≤2) → craft(东西=planks；跳过条件：背包同种木板最多≥3 / 背包同色羊毛最多≤2) → craft(东西=bed；跳过条件：背包同色羊毛最多≤2)</t>
+          <t>go_home(跳过条件：离家距离≤24) → take_from_chest(东西=线（别名待加）；跳过条件：背包线≥12 / 背包同色羊毛最多≥3) → craft(东西=white_wool；跳过条件：背包同色羊毛最多≥3) → craft(东西=white_wool；跳过条件：背包同色羊毛最多≥3) → craft(东西=white_wool；跳过条件：背包同色羊毛最多≥3) → take_from_chest(东西=原木；跳过条件：背包同种木板最多≥3 / 背包木头≥1) → craft(东西=planks；跳过条件：背包同种木板最多≥3) → craft(东西=bed)</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
@@ -8994,27 +8990,27 @@
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>J-M2-3-1</t>
+          <t>J-M2-1-2</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>身上有床、家里又有人没床时，白天回家把床摆进屋里，记到下一个该有床的人名下</t>
+          <t>兜底：箱子里的线不够做下一张床时，小麦白天看见能打的羊就去打，凑够 3 块同色羊毛就回家做床</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>M2-3</t>
+          <t>M2-1</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>麦娘, 小麦</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离≤8)</t>
+          <t>hunt(跳过条件：背包同色羊毛最多≥3 / 附近能打的羊=0) → go_home(跳过条件：背包同色羊毛最多≤2 / 离家距离≤24) → take_from_chest(东西=原木；跳过条件：背包同种木板最多≥3 / 背包木头≥1 / 背包同色羊毛最多≤2) → craft(东西=planks；跳过条件：背包同种木板最多≥3 / 背包同色羊毛最多≤2) → craft(东西=bed；跳过条件：背包同色羊毛最多≤2)</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
@@ -9031,27 +9027,27 @@
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>J-M3-1</t>
+          <t>J-M2-3-1</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>小麦出门找地：先让服务器导出一份「别人在哪儿放过东西」的名单，再朝别人最少的方向一段一段走。每走完一段，代码就检查一次附近有没有合格的地；找到一块就记下，找到好几块就问一次模型挑哪块，然后传送回家。</t>
+          <t>身上有床、家里又有人没床时，白天回家把床摆进屋里，记到下一个该有床的人名下</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>M3-1</t>
+          <t>M2-3</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>麦娘, 小麦</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1。在这一步之前缺 request_footprint（跳过条件：足迹数据已就绪 = 1）) → explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1) → explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1) → explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1) → explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1) → explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1) → explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1) → explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1) → go_home(传送回旧家（/home base）。在它之前缺 mark_site：「合格的地址门朝向组合数」= 1 时代码直接记；≥ 2 时等 T-G3-2 选完再记)</t>
+          <t>go_home(跳过条件：离家距离≤8)</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
@@ -9068,27 +9064,27 @@
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>J-M3-2</t>
+          <t>J-M3-1</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>麦娘从共用箱子拿原木，劈成木板，做好半砖和门，再全部放回共用箱子。</t>
+          <t>小麦出门找地：先让服务器导出一份「别人在哪儿放过东西」的名单，再朝别人最少的方向一段一段走。每走完一段，代码就检查一次附近有没有合格的地；找到一块就记下，找到好几块就问一次模型挑哪块，然后传送回家。</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>M3-2</t>
+          <t>M3-1</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>麦娘</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>take_from_chest(东西=设计定的墙/屋顶木种的原木；数量按木板、半砖、门三个缺口现算（全缺时 49 根）；跳过条件：新房木板缺口 = 0 且 新房半砖缺口 = 0 且 新房门缺口 = 0) → craft(东西=对应木种的木板；次数=上一步拿到的原木数；跳过条件：同上) → craft(东西=对应木种的半砖；次数=9（27 木板出 54 块）；跳过条件：新房半砖缺口 = 0) → craft(东西=对应木种的门；次数=1（6 木板出 3 扇）；跳过条件：新房门缺口 = 0) → store_items(东西=木板、半砖、门 → 共用箱子（必须存，别的家人看不见你的背包）)</t>
+          <t>explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1。在这一步之前缺 request_footprint（跳过条件：足迹数据已就绪 = 1）) → explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1) → explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1) → explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1) → explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1) → explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1) → explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1) → explore(方向=找地方向；跳过条件：合格候选新家址数 ≥ 1) → go_home(传送回旧家（/home base）。在它之前缺 mark_site：「合格的地址门朝向组合数」= 1 时代码直接记；≥ 2 时等 T-G3-2 选完再记)</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
@@ -9105,27 +9101,27 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>J-M3-3</t>
+          <t>J-M3-2</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>小麦从共用箱子拿墙用的木板、柱子原木和门，走到新家址，补平地面、砌墙、装门，然后传送回家。</t>
+          <t>麦娘从共用箱子拿原木，劈成木板，做好半砖和门，再全部放回共用箱子。</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>M3-3</t>
+          <t>M3-2</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>麦娘</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>take_from_chest(东西=设计定的墙木板；数量=新房墙缺口数（最多 82）；跳过条件：背包木板 ≥ 该数) → take_from_chest(东西=柱子原木；数量=12 + ceil(地基补平格数/4)；跳过条件：背包木头 ≥ 该数) → craft(东西=补平用的木板；次数=ceil(地基补平格数/4)；跳过条件：地基补平缺口 = 0) → take_from_chest(东西=门；数量=1；跳过条件：新房有门 = 1) → goto_place(地方=新家；直到 离新家址 ≤ 6（没有「直到」时，连写 4 个相同步骤，每步跳过条件：离新家址 ≤ 6）) → build_house(阶段=补平；直到 地基补平缺口 = 0；跳过条件：地基补平缺口 = 0) → build_house(阶段=墙柱门；直到 新房墙缺口数 = 0 且 新房有门 = 1) → go_home(传送回旧家)</t>
+          <t>take_from_chest(东西=设计定的墙/屋顶木种的原木；数量按木板、半砖、门三个缺口现算（全缺时 49 根）；跳过条件：新房木板缺口 = 0 且 新房半砖缺口 = 0 且 新房门缺口 = 0) → craft(东西=对应木种的木板；次数=上一步拿到的原木数；跳过条件：同上) → craft(东西=对应木种的半砖；次数=9（27 木板出 54 块）；跳过条件：新房半砖缺口 = 0) → craft(东西=对应木种的门；次数=1（6 木板出 3 扇）；跳过条件：新房门缺口 = 0) → store_items(东西=木板、半砖、门 → 共用箱子（必须存，别的家人看不见你的背包）)</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
@@ -9142,17 +9138,17 @@
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>J-M3-4</t>
+          <t>J-M3-3</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>小麦带上半砖和屋顶木板去新房，先铺地板再封顶，然后传送回家。</t>
+          <t>小麦从共用箱子拿墙用的木板、柱子原木和门，走到新家址，补平地面、砌墙、装门，然后传送回家。</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>M3-4</t>
+          <t>M3-3</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
@@ -9162,7 +9158,7 @@
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>take_from_chest(东西=半砖；数量=新房地面裸露格数；跳过条件：新房地面裸露格数 = 0) → take_from_chest(东西=设计定的屋顶木板；数量=新房屋顶缺口数；跳过条件：新房屋顶缺口数 = 0) → goto_place(地方=新家；直到 离新家址 ≤ 6) → build_house(阶段=地板；直到 新房地面裸露格数 = 0；跳过条件：新房地面裸露格数 = 0) → build_house(阶段=屋顶；直到 新房屋顶缺口数 = 0) → go_home(传送回旧家)</t>
+          <t>take_from_chest(东西=设计定的墙木板；数量=新房墙缺口数（最多 82）；跳过条件：背包木板 ≥ 该数) → take_from_chest(东西=柱子原木；数量=12 + ceil(地基补平格数/4)；跳过条件：背包木头 ≥ 该数) → craft(东西=补平用的木板；次数=ceil(地基补平格数/4)；跳过条件：地基补平缺口 = 0) → take_from_chest(东西=门；数量=1；跳过条件：新房有门 = 1) → goto_place(地方=新家；直到 离新家址 ≤ 6（没有「直到」时，连写 4 个相同步骤，每步跳过条件：离新家址 ≤ 6）) → build_house(阶段=补平；直到 地基补平缺口 = 0；跳过条件：地基补平缺口 = 0) → build_house(阶段=墙柱门；直到 新房墙缺口数 = 0 且 新房有门 = 1) → go_home(传送回旧家)</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
@@ -9179,27 +9175,27 @@
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>J-M3-5a</t>
+          <t>J-M3-4</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>麦娘用箱子里的线合成白羊毛，再做白床，做够 3 张。</t>
+          <t>小麦带上半砖和屋顶木板去新房，先铺地板再封顶，然后传送回家。</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>M3-5</t>
+          <t>M3-4</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>麦娘</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>take_from_chest(东西=string；数量=12×(3 − 麦家的床数)（箱子里不够就拿全部）) → take_from_chest(东西=非设计木种的木板；数量=3×(3 − 麦家的床数)；跳过条件：背包木板 ≥ 该数) → craft(东西=white_wool；次数=拿到的线 ÷ 4（每次 4 根线）) → craft(东西=white_bed；次数=白羊毛数 ÷ 3（每次 3 羊毛 + 3 木板）)</t>
+          <t>take_from_chest(东西=半砖；数量=新房地面裸露格数；跳过条件：新房地面裸露格数 = 0) → take_from_chest(东西=设计定的屋顶木板；数量=新房屋顶缺口数；跳过条件：新房屋顶缺口数 = 0) → goto_place(地方=新家；直到 离新家址 ≤ 6) → build_house(阶段=地板；直到 新房地面裸露格数 = 0；跳过条件：新房地面裸露格数 = 0) → build_house(阶段=屋顶；直到 新房屋顶缺口数 = 0) → go_home(传送回旧家)</t>
         </is>
       </c>
       <c r="F102" s="7" t="inlineStr">
@@ -9216,12 +9212,12 @@
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>J-M3-5b</t>
+          <t>J-M3-5a</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>麦娘用木板做 6 个箱子和 1 个工作台，带在身上等着摆。</t>
+          <t>麦娘用箱子里的线合成白羊毛，再做白床，做够 3 张。</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
@@ -9236,7 +9232,7 @@
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>take_from_chest(东西=非设计木种的木板；数量=8×(6 − 麦家的箱子数) + 4×(1 − 麦家的工作台数)；跳过条件：背包木板 ≥ 该数) → craft(东西=crafting_table；次数=1；跳过条件：麦家的工作台数 ≥ 1) → craft(东西=chest；次数=6 − 麦家的箱子数；跳过条件：麦家的箱子数 ≥ 6)</t>
+          <t>take_from_chest(东西=string；数量=12×(3 − 麦家的床数)（箱子里不够就拿全部）) → take_from_chest(东西=非设计木种的木板；数量=3×(3 − 麦家的床数)；跳过条件：背包木板 ≥ 该数) → craft(东西=white_wool；次数=拿到的线 ÷ 4（每次 4 根线）) → craft(东西=white_bed；次数=白羊毛数 ÷ 3（每次 3 羊毛 + 3 木板）)</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
@@ -9246,24 +9242,24 @@
       </c>
       <c r="G103" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>J-M3-6</t>
+          <t>J-M3-5b</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>麦娘带着床、箱子、工作台走到新房，按定好的摆法放进去，然后传送回家。</t>
+          <t>麦娘用木板做 6 个箱子和 1 个工作台，带在身上等着摆。</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>M3-6</t>
+          <t>M3-5</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
@@ -9273,7 +9269,7 @@
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方=新家；直到 离新家址 ≤ 3) → go_home(传送回旧家。在它之前缺 place_furniture（摆家具，放完第一个箱子先核对领地）)</t>
+          <t>take_from_chest(东西=非设计木种的木板；数量=8×(6 − 麦家的箱子数) + 4×(1 − 麦家的工作台数)；跳过条件：背包木板 ≥ 该数) → craft(东西=crafting_table；次数=1；跳过条件：麦家的工作台数 ≥ 1) → craft(东西=chest；次数=6 − 麦家的箱子数；跳过条件：麦家的箱子数 ≥ 6)</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr">
@@ -9283,34 +9279,34 @@
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>J-M3-7a</t>
+          <t>J-M3-6</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>小麦传送回旧家，从旧箱子里把东西装满一背包，走到新房存进新箱子；来回搬，直到旧箱子空了。</t>
+          <t>麦娘带着床、箱子、工作台走到新房，按定好的摆法放进去，然后传送回家。</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>M3-7</t>
+          <t>M3-6</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>麦娘</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>go_home(传送回旧家（旧箱子就在旁边）；跳过条件：离家距离 ≤ 8) → take_from_chest(箱子=旧箱子；东西=全部；背包只剩 2 格就停) → goto_place(地方=新家；直到 离新家址 ≤ 3) → store_items(箱子=新房箱子；东西=刚从旧箱子拿的全部)</t>
+          <t>goto_place(地方=新家；直到 离新家址 ≤ 3) → go_home(传送回旧家。在它之前缺 place_furniture（摆家具，放完第一个箱子先核对领地）)</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr">
@@ -9327,12 +9323,12 @@
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>J-M3-7b</t>
+          <t>J-M3-7a</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>旧箱子空了以后，小麦和麦娘各自走进新房，把家设在屋里，并在自己那张床上点一下。</t>
+          <t>小麦传送回旧家，从旧箱子里把东西装满一背包，走到新房存进新箱子；来回搬，直到旧箱子空了。</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
@@ -9342,12 +9338,12 @@
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>小麦 / 麦娘</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方=新家；直到 离新家址 ≤ 3) → set_home(新房屋内一格空地（不站在床或箱子上）；扩展：同时切共用箱子指针；跳过条件：我的家离新房距离 ≤ 4) → sleep(点自己那张新床设重生点（白天也点）；跳过条件：我的重生床在新房 = 1)</t>
+          <t>go_home(传送回旧家（旧箱子就在旁边）；跳过条件：离家距离 ≤ 8) → take_from_chest(箱子=旧箱子；东西=全部；背包只剩 2 格就停) → goto_place(地方=新家；直到 离新家址 ≤ 3) → store_items(箱子=新房箱子；东西=刚从旧箱子拿的全部)</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
@@ -9364,12 +9360,12 @@
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>J-M3-7c</t>
+          <t>J-M3-7b</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>麦豆跟着小麦走到新房，把家设在屋里，在自己那张床上点一下。</t>
+          <t>旧箱子空了以后，小麦和麦娘各自走进新房，把家设在屋里，并在自己那张床上点一下。</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
@@ -9379,12 +9375,12 @@
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>麦豆</t>
+          <t>小麦 / 麦娘</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
-          <t>follow_player(对象=XiaoMai；跳过条件：离新家址 ≤ 16) → goto_place(地方=新家；直到 离新家址 ≤ 3) → set_home(新房屋内一格空地；跳过条件：我的家离新房距离 ≤ 4) → sleep(点自己那张新床设重生点；跳过条件：我的重生床在新房 = 1)</t>
+          <t>goto_place(地方=新家；直到 离新家址 ≤ 3) → set_home(新房屋内一格空地（不站在床或箱子上）；扩展：同时切共用箱子指针；跳过条件：我的家离新房距离 ≤ 4) → sleep(点自己那张新床设重生点（白天也点）；跳过条件：我的重生床在新房 = 1)</t>
         </is>
       </c>
       <c r="F107" s="7" t="inlineStr">
@@ -9401,23 +9397,27 @@
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>J-M4-1</t>
+          <t>J-M3-7c</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>往离出生点远的方向探路</t>
+          <t>麦豆跟着小麦走到新房，把家设在屋里，在自己那张床上点一下。</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>M4-1</t>
-        </is>
-      </c>
-      <c r="D108" s="7" t="inlineStr"/>
+          <t>M3-7</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>麦豆</t>
+        </is>
+      </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>explore(背离出生点的方向)</t>
+          <t>follow_player(对象=XiaoMai；跳过条件：离新家址 ≤ 16) → goto_place(地方=新家；直到 离新家址 ≤ 3) → set_home(新房屋内一格空地；跳过条件：我的家离新房距离 ≤ 4) → sleep(点自己那张新床设重生点；跳过条件：我的重生床在新房 = 1)</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
@@ -9427,30 +9427,30 @@
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
-          <t>缺动作</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>J-M4-2</t>
+          <t>J-M4-1</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>去新址设家</t>
+          <t>往离出生点远的方向探路</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>M4-2</t>
+          <t>M4-1</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr"/>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>goto_place(新家址) → set_home</t>
+          <t>explore(背离出生点的方向)</t>
         </is>
       </c>
       <c r="F109" s="7" t="inlineStr">
@@ -9460,30 +9460,30 @@
       </c>
       <c r="G109" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>缺动作</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>J-M4-3</t>
+          <t>J-M4-2</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>一趟趟搬旧箱子</t>
+          <t>去新址设家</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>M4-3</t>
+          <t>M4-2</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr"/>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>goto_place(旧家) → take_from_chest(旧箱子,留 6 格空) → go_home → store_items</t>
+          <t>goto_place(新家址) → set_home</t>
         </is>
       </c>
       <c r="F110" s="7" t="inlineStr">
@@ -9493,30 +9493,30 @@
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>缺动作</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>J-M4-4</t>
+          <t>J-M4-3</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>只拆清单里自家放下的方块</t>
+          <t>一趟趟搬旧箱子</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>M4-4</t>
+          <t>M4-3</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr"/>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>goto_place(旧家)</t>
+          <t>goto_place(旧家) → take_from_chest(旧箱子,留 6 格空) → go_home → store_items</t>
         </is>
       </c>
       <c r="F111" s="7" t="inlineStr">
@@ -9533,23 +9533,23 @@
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>J-M5-2</t>
+          <t>J-M4-4</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>做木镐</t>
+          <t>只拆清单里自家放下的方块</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>M5-2</t>
+          <t>M4-4</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr"/>
       <c r="E112" s="7" t="inlineStr">
         <is>
-          <t>take_from_chest(oak_planks×3、stick×2) → craft(wooden_pickaxe)</t>
+          <t>goto_place(旧家)</t>
         </is>
       </c>
       <c r="F112" s="7" t="inlineStr">
@@ -9559,30 +9559,30 @@
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
-          <t>现在就能做</t>
+          <t>缺动作</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>J-M5-3</t>
+          <t>J-M5-2</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>进资源世界挖圆石</t>
+          <t>做木镐</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>M5-3</t>
+          <t>M5-2</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr"/>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>goto_place(资源世界入口) → go_home → store_items</t>
+          <t>take_from_chest(oak_planks×3、stick×2) → craft(wooden_pickaxe)</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
@@ -9592,19 +9592,19 @@
       </c>
       <c r="G113" s="7" t="inlineStr">
         <is>
-          <t>缺动作</t>
+          <t>现在就能做</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>J-M5-3b</t>
+          <t>J-M5-3</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>小麦带着镐去资源世界挖石头，挖够 64 块圆石带回家存进大箱子。</t>
+          <t>进资源世界挖圆石</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
@@ -9612,14 +9612,10 @@
           <t>M5-3</t>
         </is>
       </c>
-      <c r="D114" s="7" t="inlineStr">
-        <is>
-          <t>小麦</t>
-        </is>
-      </c>
+      <c r="D114" s="7" t="inlineStr"/>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=镐（最好的一把）；跳过条件：背包里最好的镐等级 ≥ 1) → take_from_chest(东西=口粮（留底 9）；跳过条件：身上吃的 ≥ 4) → goto_place(地方=资源世界（/res go）) → mine(方块=石头（深板岩也算）；直到 背包圆石 + 箱子里圆石 ≥ 64 或 15 分钟 或 该回主世界 = 1) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(圆石进大箱子)</t>
+          <t>goto_place(资源世界入口) → go_home → store_items</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr">
@@ -9629,30 +9625,34 @@
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺动作</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>J-M7-3</t>
+          <t>J-M5-3b</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>麦豆跟着爸爸砍树</t>
+          <t>小麦带着镐去资源世界挖石头，挖够 64 块圆石带回家存进大箱子。</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>M7-3</t>
-        </is>
-      </c>
-      <c r="D115" s="7" t="inlineStr"/>
+          <t>M5-3</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>小麦</t>
+        </is>
+      </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>follow_player(小麦) → gather_wood → store_items</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=镐（最好的一把）；跳过条件：背包里最好的镐等级 ≥ 1) → take_from_chest(东西=口粮（留底 9）；跳过条件：身上吃的 ≥ 4) → goto_place(地方=资源世界（/res go）) → mine(方块=石头（深板岩也算）；直到 背包圆石 + 箱子里圆石 ≥ 64 或 15 分钟 或 该回主世界 = 1) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(圆石进大箱子)</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr">
@@ -9662,19 +9662,19 @@
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>缺动作</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>J-M7-3c</t>
+          <t>J-M7-3</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>麦豆在家附近砍树(只砍看得见的树,不去远处林子;离家 40 格内,照抄 child_play 的范围)</t>
+          <t>麦豆跟着爸爸砍树</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
@@ -9682,14 +9682,10 @@
           <t>M7-3</t>
         </is>
       </c>
-      <c r="D116" s="7" t="inlineStr">
-        <is>
-          <t>麦豆</t>
-        </is>
-      </c>
+      <c r="D116" s="7" t="inlineStr"/>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>gather_wood</t>
+          <t>follow_player(小麦) → gather_wood → store_items</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr">
@@ -9699,19 +9695,19 @@
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>卡在代码</t>
+          <t>缺动作</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>J-M7-3d</t>
+          <t>J-M7-3c</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>麦豆身上有木头就回家存进箱子(照抄 wife_store;箱子满了被忘掉时「有箱子」变 0,不会反复空跑)</t>
+          <t>麦豆在家附近砍树(只砍看得见的树,不去远处林子;离家 40 格内,照抄 child_play 的范围)</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
@@ -9726,7 +9722,7 @@
       </c>
       <c r="E117" s="7" t="inlineStr">
         <is>
-          <t>go_home → store_items</t>
+          <t>gather_wood</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr">
@@ -9736,30 +9732,34 @@
       </c>
       <c r="G117" s="7" t="inlineStr">
         <is>
-          <t>要放行动作</t>
+          <t>卡在代码</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>J-M7-4</t>
+          <t>J-M7-3d</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t>没被点名时离真人太近就回家</t>
+          <t>麦豆身上有木头就回家存进箱子(照抄 wife_store;箱子满了被忘掉时「有箱子」变 0,不会反复空跑)</t>
         </is>
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>M7-4</t>
-        </is>
-      </c>
-      <c r="D118" s="7" t="inlineStr"/>
+          <t>M7-3</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>麦豆</t>
+        </is>
+      </c>
       <c r="E118" s="7" t="inlineStr">
         <is>
-          <t>go_home</t>
+          <t>go_home → store_items</t>
         </is>
       </c>
       <c r="F118" s="7" t="inlineStr">
@@ -9769,34 +9769,30 @@
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>要放行动作</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>J-M7-5</t>
+          <t>J-M7-4</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>走到正在干活的家人旁边 4~8 格处，待着看。</t>
+          <t>没被点名时离真人太近就回家</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>M7-5</t>
-        </is>
-      </c>
-      <c r="D119" s="7" t="inlineStr">
-        <is>
-          <t>麦豆</t>
-        </is>
-      </c>
+          <t>M7-4</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="inlineStr"/>
       <c r="E119" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方=家人身边（停在 4~8 格外，不进田里）) → idle(30 秒；跳过条件：离最近在干活的家人距离 ≥ 17)</t>
+          <t>go_home</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">
@@ -9806,34 +9802,34 @@
       </c>
       <c r="G119" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>J-M8-1a</t>
+          <t>J-M7-5</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t>用箱子里现成的铁锭做一把铁镐。</t>
+          <t>走到正在干活的家人旁边 4~8 格处，待着看。</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>M8-1</t>
+          <t>M7-5</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>麦豆</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=铁锭 3、木棍 2；跳过条件：背包铁锭 ≥ 3) → craft(东西=iron_pickaxe（要工作台）)</t>
+          <t>goto_place(地方=家人身边（停在 4~8 格外，不进田里）) → idle(30 秒；跳过条件：离最近在干活的家人距离 ≥ 17)</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
@@ -9850,12 +9846,12 @@
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>J-M8-1b</t>
+          <t>J-M8-1a</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
-          <t>箱子里的铁不够时：用圆石做石镐和熔炉，去资源世界挖 3 块铁矿、就地烧成铁锭，回家做铁镐。</t>
+          <t>用箱子里现成的铁锭做一把铁镐。</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
@@ -9870,7 +9866,7 @@
       </c>
       <c r="E121" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=圆石 11、木棍 4、原木 4（燃料）、口粮（留底 9；跳过条件：身上吃的 ≥ 6）) → take_from_chest(东西=镐（最好的一把）；跳过条件：背包里最好的镐等级 ≥ 2) → craft(东西=stone_pickaxe；跳过条件：背包里最好的镐等级 ≥ 2) → craft(东西=furnace；跳过条件：身上有熔炉 ≥ 1) → goto_place(地方=资源世界（/res go）) → mine(矿=铁矿，下到 y≈16 开巷道；直到 背包粗铁 ≥ 3 或 25 分钟 或 该回主世界 = 1) → smelt(随身熔炉；粗铁全部，燃料原木；烧完挖回熔炉) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → craft(东西=iron_pickaxe)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=铁锭 3、木棍 2；跳过条件：背包铁锭 ≥ 3) → craft(东西=iron_pickaxe（要工作台）)</t>
         </is>
       </c>
       <c r="F121" s="7" t="inlineStr">
@@ -9887,17 +9883,17 @@
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>J-M8-2</t>
+          <t>J-M8-1b</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t>小麦带着熔炉和燃料去资源世界挖铁，挖完就地烧成铁锭，带回家存进大箱子。</t>
+          <t>箱子里的铁不够时：用圆石做石镐和熔炉，去资源世界挖 3 块铁矿、就地烧成铁锭，回家做铁镐。</t>
         </is>
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>M8-2</t>
+          <t>M8-1</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
@@ -9907,7 +9903,7 @@
       </c>
       <c r="E122" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=镐（拿最好的一把）；跳过条件：背包里最好的镐等级 ≥ 2) → take_from_chest(东西=口粮（留底 9）；跳过条件：身上吃的 ≥ 6) → take_from_chest(东西=粗铁（全部）；跳过条件：箱子里没有粗铁) → take_from_chest(东西=圆石 8；跳过条件：身上有熔炉 ≥ 1) → craft(东西=furnace；跳过条件：身上有熔炉 ≥ 1) → take_from_chest(东西=原木（当燃料），数量 = 还差的铁锭 ÷ 1.5 向上取整，最多 24 根；跳过条件：身上的原木已经够) → goto_place(地方=资源世界（/res go）) → mine(矿=铁矿，下到 y≈16 开 1×2 巷道；顺手挖煤，看见沙砾就挖到背包燧石 ≥ 1；直到 背包粗铁 ≥ 出发时的还差铁锭 或 背包空格 ≤ 2 或 这一趟 ≥ 25 分钟 或 该回主世界 = 1) → smelt(放下随身熔炉，粗铁全部，燃料先煤后原木；烧完用镐把熔炉挖回来) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(铁锭、煤、燧石进大箱子（镐和熔炉留在身上）)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=圆石 11、木棍 4、原木 4（燃料）、口粮（留底 9；跳过条件：身上吃的 ≥ 6）) → take_from_chest(东西=镐（最好的一把）；跳过条件：背包里最好的镐等级 ≥ 2) → craft(东西=stone_pickaxe；跳过条件：背包里最好的镐等级 ≥ 2) → craft(东西=furnace；跳过条件：身上有熔炉 ≥ 1) → goto_place(地方=资源世界（/res go）) → mine(矿=铁矿，下到 y≈16 开巷道；直到 背包粗铁 ≥ 3 或 25 分钟 或 该回主世界 = 1) → smelt(随身熔炉；粗铁全部，燃料原木；烧完挖回熔炉) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → craft(东西=iron_pickaxe)</t>
         </is>
       </c>
       <c r="F122" s="7" t="inlineStr">
@@ -9924,17 +9920,17 @@
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>J-M8-3a</t>
+          <t>J-M8-2</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>回家把铁锭做成还缺的铁甲、铁剑、盾、桶和打火石，然后穿好。</t>
+          <t>小麦带着熔炉和燃料去资源世界挖铁，挖完就地烧成铁锭，带回家存进大箱子。</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>M8-3</t>
+          <t>M8-2</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
@@ -9944,7 +9940,7 @@
       </c>
       <c r="E123" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=铁锭（按能做的件现算）、木棍（按件现算）、木板 6（跳过条件：有盾牌 ≥ 1）、燧石 1（跳过条件：有打火石 ≥ 1 或 能拿到的燧石 = 0）) → craft(按缺的做，先 iron_sword、shield，再 iron_chestplate、iron_leggings、iron_helmet、iron_boots、bucket、flint_and_steel；已有的、料不够的跳过) → wear_armor(平时穿法：四件最好的护甲 + 副手盾)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=镐（拿最好的一把）；跳过条件：背包里最好的镐等级 ≥ 2) → take_from_chest(东西=口粮（留底 9）；跳过条件：身上吃的 ≥ 6) → take_from_chest(东西=粗铁（全部）；跳过条件：箱子里没有粗铁) → take_from_chest(东西=圆石 8；跳过条件：身上有熔炉 ≥ 1) → craft(东西=furnace；跳过条件：身上有熔炉 ≥ 1) → take_from_chest(东西=原木（当燃料），数量 = 还差的铁锭 ÷ 1.5 向上取整，最多 24 根；跳过条件：身上的原木已经够) → goto_place(地方=资源世界（/res go）) → mine(矿=铁矿，下到 y≈16 开 1×2 巷道；顺手挖煤，看见沙砾就挖到背包燧石 ≥ 1；直到 背包粗铁 ≥ 出发时的还差铁锭 或 背包空格 ≤ 2 或 这一趟 ≥ 25 分钟 或 该回主世界 = 1) → smelt(放下随身熔炉，粗铁全部，燃料先煤后原木；烧完用镐把熔炉挖回来) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(铁锭、煤、燧石进大箱子（镐和熔炉留在身上）)</t>
         </is>
       </c>
       <c r="F123" s="7" t="inlineStr">
@@ -9961,12 +9957,12 @@
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>J-M8-3b</t>
+          <t>J-M8-3a</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t>缺燧石做打火石时，去资源世界挖沙砾拿燧石。</t>
+          <t>回家把铁锭做成还缺的铁甲、铁剑、盾、桶和打火石，然后穿好。</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
@@ -9981,7 +9977,7 @@
       </c>
       <c r="E124" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方=资源世界（/res go）) → mine(方块=沙砾；直到 背包燧石 ≥ 2 或 15 分钟 或 该回主世界 = 1) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(燧石进大箱子)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=铁锭（按能做的件现算）、木棍（按件现算）、木板 6（跳过条件：有盾牌 ≥ 1）、燧石 1（跳过条件：有打火石 ≥ 1 或 能拿到的燧石 = 0）) → craft(按缺的做，先 iron_sword、shield，再 iron_chestplate、iron_leggings、iron_helmet、iron_boots、bucket、flint_and_steel；已有的、料不够的跳过) → wear_armor(平时穿法：四件最好的护甲 + 副手盾)</t>
         </is>
       </c>
       <c r="F124" s="7" t="inlineStr">
@@ -9998,12 +9994,12 @@
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>J-M8-3c</t>
+          <t>J-M8-3b</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>拿个空桶，去附近天然的河或湖装一桶水带在身上。</t>
+          <t>缺燧石做打火石时，去资源世界挖沙砾拿燧石。</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
@@ -10018,7 +10014,7 @@
       </c>
       <c r="E125" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8 或 身上空桶 ≥ 1) → take_from_chest(东西=桶；跳过条件：身上空桶 ≥ 1) → goto_place(地方=水源（只认 C-FRM-25 认可的天然水）) → fill_bucket</t>
+          <t>goto_place(地方=资源世界（/res go）) → mine(方块=沙砾；直到 背包燧石 ≥ 2 或 15 分钟 或 该回主世界 = 1) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(燧石进大箱子)</t>
         </is>
       </c>
       <c r="F125" s="7" t="inlineStr">
@@ -10035,17 +10031,17 @@
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>J-M8-4a</t>
+          <t>J-M8-3c</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>您同意的话，用箱子里的 3 颗钻石直接做钻石镐。</t>
+          <t>拿个空桶，去附近天然的河或湖装一桶水带在身上。</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>M8-4</t>
+          <t>M8-3</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
@@ -10055,7 +10051,7 @@
       </c>
       <c r="E126" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=钻石 3、木棍 2) → craft(东西=diamond_pickaxe（要工作台）)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8 或 身上空桶 ≥ 1) → take_from_chest(东西=桶；跳过条件：身上空桶 ≥ 1) → goto_place(地方=水源（只认 C-FRM-25 认可的天然水）) → fill_bucket</t>
         </is>
       </c>
       <c r="F126" s="7" t="inlineStr">
@@ -10072,12 +10068,12 @@
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>J-M8-4b</t>
+          <t>J-M8-4a</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>不用箱子里的钻石时，穿上铁甲、带上水桶，去资源世界最深处挖 3 颗钻石回来做钻石镐。</t>
+          <t>您同意的话，用箱子里的 3 颗钻石直接做钻石镐。</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
@@ -10092,7 +10088,7 @@
       </c>
       <c r="E127" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=铁镐；跳过条件：背包里最好的镐等级 ≥ 3) → take_from_chest(东西=口粮（留底 9）；跳过条件：身上吃的 ≥ 8) → wear_armor(平时穿法) → goto_place(地方=资源世界（/res go）) → mine(矿=钻石，y≈−58 开巷道，岩浆安全规则按 C-CRF-22；直到 背包钻石 ≥ 3 或 25 分钟 或 该回主世界 = 1) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → craft(东西=diamond_pickaxe；跳过条件：背包钻石 ≤ 2)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=钻石 3、木棍 2) → craft(东西=diamond_pickaxe（要工作台）)</t>
         </is>
       </c>
       <c r="F127" s="7" t="inlineStr">
@@ -10109,17 +10105,17 @@
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>J-M8-5</t>
+          <t>J-M8-4b</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
         <is>
-          <t>带着钻石镐和水桶去资源世界找岩浆，浇上水变成黑曜石，挖够 10 块带回家。</t>
+          <t>不用箱子里的钻石时，穿上铁甲、带上水桶，去资源世界最深处挖 3 颗钻石回来做钻石镐。</t>
         </is>
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>M8-5</t>
+          <t>M8-4</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
@@ -10129,7 +10125,7 @@
       </c>
       <c r="E128" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=钻石镐；跳过条件：背包里最好的镐等级 ≥ 4) → take_from_chest(东西=口粮（留底 9）；跳过条件：身上吃的 ≥ 8) → goto_place(地方=资源世界（/res go）) → explore(找岩浆：先看落点附近地表的岩浆湖，没有就下到 y≈−54 以下的洞穴；跳过条件：看得见岩浆源；最多 10 分钟) → cast_obsidian(直到 黑曜石的家底 ≥ 10（背包里的也算） 或 该回主世界 = 1) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(黑曜石进大箱子)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=铁镐；跳过条件：背包里最好的镐等级 ≥ 3) → take_from_chest(东西=口粮（留底 9）；跳过条件：身上吃的 ≥ 8) → wear_armor(平时穿法) → goto_place(地方=资源世界（/res go）) → mine(矿=钻石，y≈−58 开巷道，岩浆安全规则按 C-CRF-22；直到 背包钻石 ≥ 3 或 25 分钟 或 该回主世界 = 1) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → craft(东西=diamond_pickaxe；跳过条件：背包钻石 ≤ 2)</t>
         </is>
       </c>
       <c r="F128" s="7" t="inlineStr">
@@ -10146,17 +10142,17 @@
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>J-M8-6</t>
+          <t>J-M8-5</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
         <is>
-          <t>拿上 10 块黑曜石，走到您批准的位置，砌好传送门框并点着。</t>
+          <t>带着钻石镐和水桶去资源世界找岩浆，浇上水变成黑曜石，挖够 10 块带回家。</t>
         </is>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>M8-6</t>
+          <t>M8-5</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
@@ -10166,7 +10162,7 @@
       </c>
       <c r="E129" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=黑曜石（缺几块拿几块）、打火石（跳过条件：身上有）) → goto_place(地方=传送门位置) → build_portal(只补缺的格子，每块记进自家方块登记；用打火石点着，回读有紫色的门方块才算成)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=钻石镐；跳过条件：背包里最好的镐等级 ≥ 4) → take_from_chest(东西=口粮（留底 9）；跳过条件：身上吃的 ≥ 8) → goto_place(地方=资源世界（/res go）) → explore(找岩浆：先看落点附近地表的岩浆湖，没有就下到 y≈−54 以下的洞穴；跳过条件：看得见岩浆源；最多 10 分钟) → cast_obsidian(直到 黑曜石的家底 ≥ 10（背包里的也算） 或 该回主世界 = 1) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(黑曜石进大箱子)</t>
         </is>
       </c>
       <c r="F129" s="7" t="inlineStr">
@@ -10183,17 +10179,17 @@
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>J-M8-8a</t>
+          <t>J-M8-6</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
         <is>
-          <t>去资源世界挖金矿、烧成 5 个金锭，给金头盔备料。</t>
+          <t>拿上 10 块黑曜石，走到您批准的位置，砌好传送门框并点着。</t>
         </is>
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>M8-8</t>
+          <t>M8-6</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
@@ -10203,7 +10199,7 @@
       </c>
       <c r="E130" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=铁镐或更好；跳过条件：背包里最好的镐等级 ≥ 3) → take_from_chest(东西=口粮（留底 9）；跳过条件：身上吃的 ≥ 6) → take_from_chest(东西=圆石 8；跳过条件：身上有熔炉 ≥ 1) → craft(东西=furnace；跳过条件：身上有熔炉 ≥ 1) → take_from_chest(东西=原木 4（燃料）；跳过条件：身上的原木 ≥ 4) → goto_place(地方=资源世界（/res go）) → mine(矿=金矿，y≈−16 开巷道（恶地地表也行）；直到 背包粗金 + 金的家底 ≥ 5 或 25 分钟 或 该回主世界 = 1) → smelt(随身熔炉，粗金全部；烧完把熔炉挖回来) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(金锭进大箱子)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=黑曜石（缺几块拿几块）、打火石（跳过条件：身上有）) → goto_place(地方=传送门位置) → build_portal(只补缺的格子，每块记进自家方块登记；用打火石点着，回读有紫色的门方块才算成)</t>
         </is>
       </c>
       <c r="F130" s="7" t="inlineStr">
@@ -10220,12 +10216,12 @@
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>J-M8-8b</t>
+          <t>J-M8-8a</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
         <is>
-          <t>出发去下界前在家收拾行李：做好金头盔戴上，从粮箱拿够口粮、从大箱子拿 64 块圆石，用不上的东西存掉。</t>
+          <t>去资源世界挖金矿、烧成 5 个金锭，给金头盔备料。</t>
         </is>
       </c>
       <c r="C131" s="7" t="inlineStr">
@@ -10240,7 +10236,7 @@
       </c>
       <c r="E131" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=金锭 5；跳过条件：穿着金护甲件数 ≥ 1 或 背包金头盔 ≥ 1) → craft(东西=golden_helmet；跳过条件：同上) → wear_armor(下界穿法：金头盔 + 另外三件最好的护甲 + 副手盾) → take_from_chest(东西=口粮，从粮箱拿，留底 9（打开箱子按真数重算）；直到 身上吃的 ≥ 16) → take_from_chest(东西=圆石；直到 身上的圆石 ≥ 64) → store_items(用不上的存掉，行李清单上的留着；直到 背包空格 ≥ 8)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=铁镐或更好；跳过条件：背包里最好的镐等级 ≥ 3) → take_from_chest(东西=口粮（留底 9）；跳过条件：身上吃的 ≥ 6) → take_from_chest(东西=圆石 8；跳过条件：身上有熔炉 ≥ 1) → craft(东西=furnace；跳过条件：身上有熔炉 ≥ 1) → take_from_chest(东西=原木 4（燃料）；跳过条件：身上的原木 ≥ 4) → goto_place(地方=资源世界（/res go）) → mine(矿=金矿，y≈−16 开巷道（恶地地表也行）；直到 背包粗金 + 金的家底 ≥ 5 或 25 分钟 或 该回主世界 = 1) → smelt(随身熔炉，粗金全部；烧完把熔炉挖回来) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(金锭进大箱子)</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr">
@@ -10257,17 +10253,17 @@
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>J-M8-9</t>
+          <t>J-M8-8b</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
-          <t>穿过传送门进下界，朝一个方向一段段找，看到地狱砖城堡就记下位置，然后原路回家。</t>
+          <t>出发去下界前在家收拾行李：做好金头盔戴上，从粮箱拿够口粮、从大箱子拿 64 块圆石，用不上的东西存掉。</t>
         </is>
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>M8-9</t>
+          <t>M8-8</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
@@ -10277,7 +10273,7 @@
       </c>
       <c r="E132" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方=传送门（主世界那一头）；跳过条件：当前维度 = 2（下界）) → wear_armor(下界穿法；跳过条件：穿着金护甲件数 ≥ 1) → use_portal(进下界；跳过条件：当前维度 = 2；第一次过去先核对落点周围 32 格有没有别人的方块，有就原路回来、作废位置、写进后台) → explore(在下界：沿一个方向一段 64 格，离门 ≤ 600 格，避开玄武岩三角洲和堡垒遗迹；直到 记得下界要塞 = 1 或 该返航 = 1) → goto_place(地方=下界那一头的门；跳过条件：当前维度 = 0) → use_portal(回主世界；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → store_items(只存可存的，行李留着)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=金锭 5；跳过条件：穿着金护甲件数 ≥ 1 或 背包金头盔 ≥ 1) → craft(东西=golden_helmet；跳过条件：同上) → wear_armor(下界穿法：金头盔 + 另外三件最好的护甲 + 副手盾) → take_from_chest(东西=口粮，从粮箱拿，留底 9（打开箱子按真数重算）；直到 身上吃的 ≥ 16) → take_from_chest(东西=圆石；直到 身上的圆石 ≥ 64) → store_items(用不上的存掉，行李清单上的留着；直到 背包空格 ≥ 8)</t>
         </is>
       </c>
       <c r="F132" s="7" t="inlineStr">
@@ -10294,17 +10290,17 @@
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>J-M8-10</t>
+          <t>J-M8-9</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
         <is>
-          <t>去下界要塞的烈焰人刷怪笼旁边，举着盾一只只打烈焰人，攒烈焰棒，带回家存进箱子。</t>
+          <t>穿过传送门进下界，朝一个方向一段段找，看到地狱砖城堡就记下位置，然后原路回家。</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>M8-10</t>
+          <t>M8-9</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
@@ -10314,7 +10310,7 @@
       </c>
       <c r="E133" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方=传送门（主世界那一头）；跳过条件：当前维度 = 2) → wear_armor(下界穿法；跳过条件：穿着金护甲件数 ≥ 1) → use_portal(进下界；跳过条件：当前维度 = 2) → goto_place(地方=烈焰人刷怪笼，停在 6~8 格外的走廊) → fight(目标=烈焰人，举盾挡火球，打死后走过去捡；直到 做眼还缺的烈焰棒 = 0（背包里的也算） 或 该返航 = 1) → goto_place(地方=下界那一头的门；跳过条件：当前维度 = 0) → use_portal(回主世界；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → store_items(烈焰棒进大箱子)</t>
+          <t>goto_place(地方=传送门（主世界那一头）；跳过条件：当前维度 = 2（下界）) → wear_armor(下界穿法；跳过条件：穿着金护甲件数 ≥ 1) → use_portal(进下界；跳过条件：当前维度 = 2；第一次过去先核对落点周围 32 格有没有别人的方块，有就原路回来、作废位置、写进后台) → explore(在下界：沿一个方向一段 64 格，离门 ≤ 600 格，避开玄武岩三角洲和堡垒遗迹；直到 记得下界要塞 = 1 或 该返航 = 1) → goto_place(地方=下界那一头的门；跳过条件：当前维度 = 0) → use_portal(回主世界；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → store_items(只存可存的，行李留着)</t>
         </is>
       </c>
       <c r="F133" s="7" t="inlineStr">
@@ -10331,17 +10327,17 @@
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>J-M8-11</t>
+          <t>J-M8-10</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t>去下界的诡异森林，躲在自己搭的两格高小棚口，一只只打末影人，攒末影珍珠带回家。</t>
+          <t>去下界要塞的烈焰人刷怪笼旁边，举着盾一只只打烈焰人，攒烈焰棒，带回家存进箱子。</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>M8-11</t>
+          <t>M8-10</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
@@ -10351,7 +10347,7 @@
       </c>
       <c r="E134" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方=传送门（主世界那一头）；跳过条件：当前维度 = 2) → wear_armor(下界穿法；跳过条件：穿着金护甲件数 ≥ 1) → use_portal(进下界；跳过条件：当前维度 = 2) → goto_place(地方=诡异森林；还不记得就在下界 explore 找青绿色的地面，最多 10 分钟) → hunt_enderman(先搭两格高小棚，一次惹一只；直到 做眼还缺的末影珍珠 = 0（背包里的也算） 或 该返航 = 1；走前拆回小棚) → goto_place(地方=下界那一头的门；跳过条件：当前维度 = 0) → use_portal(回主世界；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → store_items(末影珍珠进大箱子)</t>
+          <t>goto_place(地方=传送门（主世界那一头）；跳过条件：当前维度 = 2) → wear_armor(下界穿法；跳过条件：穿着金护甲件数 ≥ 1) → use_portal(进下界；跳过条件：当前维度 = 2) → goto_place(地方=烈焰人刷怪笼，停在 6~8 格外的走廊) → fight(目标=烈焰人，举盾挡火球，打死后走过去捡；直到 做眼还缺的烈焰棒 = 0（背包里的也算） 或 该返航 = 1) → goto_place(地方=下界那一头的门；跳过条件：当前维度 = 0) → use_portal(回主世界；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → store_items(烈焰棒进大箱子)</t>
         </is>
       </c>
       <c r="F134" s="7" t="inlineStr">
@@ -10368,27 +10364,27 @@
     <row r="135">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>J-M8-12</t>
+          <t>J-M8-11</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
         <is>
-          <t>麦娘从大箱子拿烈焰棒和末影珍珠，合成末影之眼，再存回箱子。</t>
+          <t>去下界的诡异森林，躲在自己搭的两格高小棚口，一只只打末影人，攒末影珍珠带回家。</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>M8-12</t>
+          <t>M8-11</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>麦娘</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="E135" s="7" t="inlineStr">
         <is>
-          <t>take_from_chest(东西=烈焰棒、末影珍珠；数量按 min(能做的末影之眼数, 末影之眼缺口) 现算) → craft(东西=blaze_powder) → craft(东西=ender_eye) → store_items(末影之眼和多的烈焰粉进大箱子)</t>
+          <t>goto_place(地方=传送门（主世界那一头）；跳过条件：当前维度 = 2) → wear_armor(下界穿法；跳过条件：穿着金护甲件数 ≥ 1) → use_portal(进下界；跳过条件：当前维度 = 2) → goto_place(地方=诡异森林；还不记得就在下界 explore 找青绿色的地面，最多 10 分钟) → hunt_enderman(先搭两格高小棚，一次惹一只；直到 做眼还缺的末影珍珠 = 0（背包里的也算） 或 该返航 = 1；走前拆回小棚) → goto_place(地方=下界那一头的门；跳过条件：当前维度 = 0) → use_portal(回主世界；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → store_items(末影珍珠进大箱子)</t>
         </is>
       </c>
       <c r="F135" s="7" t="inlineStr">
@@ -10405,27 +10401,27 @@
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>J-M8-13a</t>
+          <t>J-M8-12</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t>带几个末影之眼出门，在两个地方各扔一次、捡回来，算出要塞大概在哪，然后传送回家。</t>
+          <t>麦娘从大箱子拿烈焰棒和末影珍珠，合成末影之眼，再存回箱子。</t>
         </is>
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>M8-13</t>
+          <t>M8-12</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>小麦</t>
+          <t>麦娘</t>
         </is>
       </c>
       <c r="E136" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=末影之眼 4、口粮（留底 9，直到 身上吃的 ≥ 8）) → throw_eye(在新家门口扔，记下方向，落地走过去捡) → goto_place(沿和第一次方向垂直的方向走 200 格（长距离，寻路不许挖）) → throw_eye(再扔一次、捡回；代码算两条线的交点，估计位置不在离原点 1280~2816 格内就作废重扔) → go_home(用 /home base 传送回家) → store_items(末影之眼放回大箱子)</t>
+          <t>take_from_chest(东西=烈焰棒、末影珍珠；数量按 min(能做的末影之眼数, 末影之眼缺口) 现算) → craft(东西=blaze_powder) → craft(东西=ender_eye) → store_items(末影之眼和多的烈焰粉进大箱子)</t>
         </is>
       </c>
       <c r="F136" s="7" t="inlineStr">
@@ -10442,12 +10438,12 @@
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>J-M8-13b</t>
+          <t>J-M8-13a</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
         <is>
-          <t>走到算出的要塞位置，近处再扔一次眼确认，从地面斜着挖下去，找到末地传送门框，记下位置后传送回家。</t>
+          <t>带几个末影之眼出门，在两个地方各扔一次、捡回来，算出要塞大概在哪，然后传送回家。</t>
         </is>
       </c>
       <c r="C137" s="7" t="inlineStr">
@@ -10462,7 +10458,7 @@
       </c>
       <c r="E137" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=末影之眼 3、口粮（留底 9，直到 身上吃的 ≥ 12）、圆石 64、镐（跳过条件：背包里最好的镐等级 ≥ 2）) → goto_place(地方=要塞估计位置（长距离，寻路不许挖）) → throw_eye(近处核对，眼往下钻 = 就在脚下；捡回) → dig_to_stronghold(先查 32 格内没有别人的东西和领地；楼梯形斜井往下，只挖天然方块；找到末地门框就记坐标和空门框数) → go_home(用 /home base 传送回家)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=末影之眼 4、口粮（留底 9，直到 身上吃的 ≥ 8）) → throw_eye(在新家门口扔，记下方向，落地走过去捡) → goto_place(沿和第一次方向垂直的方向走 200 格（长距离，寻路不许挖）) → throw_eye(再扔一次、捡回；代码算两条线的交点，估计位置不在离原点 1280~2816 格内就作废重扔) → go_home(用 /home base 传送回家) → store_items(末影之眼放回大箱子)</t>
         </is>
       </c>
       <c r="F137" s="7" t="inlineStr">
@@ -10479,17 +10475,17 @@
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>J-M8-14</t>
+          <t>J-M8-13b</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
         <is>
-          <t>带着末影之眼走到要塞，把空门框一个个嵌满，点亮末地传送门，然后传送回家。</t>
+          <t>走到算出的要塞位置，近处再扔一次眼确认，从地面斜着挖下去，找到末地传送门框，记下位置后传送回家。</t>
         </is>
       </c>
       <c r="C138" s="7" t="inlineStr">
         <is>
-          <t>M8-14</t>
+          <t>M8-13</t>
         </is>
       </c>
       <c r="D138" s="7" t="inlineStr">
@@ -10499,7 +10495,7 @@
       </c>
       <c r="E138" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=末影之眼，数量=空门框数；口粮（留底 9，直到 身上吃的 ≥ 8）) → goto_place(地方=要塞末地门（长距离，寻路不许挖）) → fill_portal_frame(每个空门框嵌一颗眼，回读中间是不是末地门) → go_home(用 /home base 传送回家)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=末影之眼 3、口粮（留底 9，直到 身上吃的 ≥ 12）、圆石 64、镐（跳过条件：背包里最好的镐等级 ≥ 2）) → goto_place(地方=要塞估计位置（长距离，寻路不许挖）) → throw_eye(近处核对，眼往下钻 = 就在脚下；捡回) → dig_to_stronghold(先查 32 格内没有别人的东西和领地；楼梯形斜井往下，只挖天然方块；找到末地门框就记坐标和空门框数) → go_home(用 /home base 传送回家)</t>
         </is>
       </c>
       <c r="F138" s="7" t="inlineStr">
@@ -10516,17 +10512,17 @@
     <row r="139">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>J-M8-15a</t>
+          <t>J-M8-14</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
         <is>
-          <t>在家用线和木棍做弓，用燧石、木棍、羽毛做箭，做好存进大箱子。</t>
+          <t>带着末影之眼走到要塞，把空门框一个个嵌满，点亮末地传送门，然后传送回家。</t>
         </is>
       </c>
       <c r="C139" s="7" t="inlineStr">
         <is>
-          <t>M8-15</t>
+          <t>M8-14</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
@@ -10536,7 +10532,7 @@
       </c>
       <c r="E139" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=线 3（跳过条件：有弓 ≥ 1）、木棍、燧石、羽毛（按缺的现算）) → craft(东西=bow；跳过条件：有弓 ≥ 1) → craft(东西=arrow；直到 箭的家底 ≥ 64，材料用完就停) → store_items(东西=弓、箭，进大箱子)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=末影之眼，数量=空门框数；口粮（留底 9，直到 身上吃的 ≥ 8）) → goto_place(地方=要塞末地门（长距离，寻路不许挖）) → fill_portal_frame(每个空门框嵌一颗眼，回读中间是不是末地门) → go_home(用 /home base 传送回家)</t>
         </is>
       </c>
       <c r="F139" s="7" t="inlineStr">
@@ -10553,12 +10549,12 @@
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>J-M8-15b</t>
+          <t>J-M8-15a</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
-          <t>去资源世界打鸡拿羽毛、挖沙砾拿燧石，给做箭备料。</t>
+          <t>在家用线和木棍做弓，用燧石、木棍、羽毛做箭，做好存进大箱子。</t>
         </is>
       </c>
       <c r="C140" s="7" t="inlineStr">
@@ -10573,7 +10569,7 @@
       </c>
       <c r="E140" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方=资源世界（/res go）) → hunt(目标=鸡，打死后捡羽毛；跳过条件：做箭还缺的羽毛 = 0；直到 做箭还缺的羽毛 = 0 或 15 分钟) → mine(方块=沙砾；跳过条件：做箭还缺的燧石 = 0；直到 做箭还缺的燧石 = 0 或 10 分钟) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(羽毛、燧石进大箱子)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=线 3（跳过条件：有弓 ≥ 1）、木棍、燧石、羽毛（按缺的现算）) → craft(东西=bow；跳过条件：有弓 ≥ 1) → craft(东西=arrow；直到 箭的家底 ≥ 64，材料用完就停) → store_items(东西=弓、箭，进大箱子)</t>
         </is>
       </c>
       <c r="F140" s="7" t="inlineStr">
@@ -10590,17 +10586,17 @@
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>J-M8-16</t>
+          <t>J-M8-15b</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
-          <t>（等您批）带着 4 个末地水晶进末地，放在中间返回门的四边，把龙叫回来。</t>
+          <t>去资源世界打鸡拿羽毛、挖沙砾拿燧石，给做箭备料。</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>M8-16</t>
+          <t>M8-15</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
@@ -10610,7 +10606,7 @@
       </c>
       <c r="E141" s="7" t="inlineStr">
         <is>
-          <t>take_from_chest(东西=末地水晶 4) → goto_place(地方=要塞末地门；跳过条件：当前维度 = 3（末地）) → use_portal(进末地；跳过条件：当前维度 = 3) → respawn_dragon(4 个水晶放在中间返回门的四边)</t>
+          <t>goto_place(地方=资源世界（/res go）) → hunt(目标=鸡，打死后捡羽毛；跳过条件：做箭还缺的羽毛 = 0；直到 做箭还缺的羽毛 = 0 或 15 分钟) → mine(方块=沙砾；跳过条件：做箭还缺的燧石 = 0；直到 做箭还缺的燧石 = 0 或 10 分钟) → goto_place(地方=羊羊主世界（/home base，被拦就 /spawn）；跳过条件：当前维度 = 0) → store_items(羽毛、燧石进大箱子)</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr">
@@ -10627,17 +10623,17 @@
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>J-M8-17a</t>
+          <t>J-M8-16</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr">
         <is>
-          <t>进末地前在家收拾：拿上弓和 64 支箭、128 块圆石和 24 个吃的，换回四件铁甲。</t>
+          <t>（等您批）带着 4 个末地水晶进末地，放在中间返回门的四边，把龙叫回来。</t>
         </is>
       </c>
       <c r="C142" s="7" t="inlineStr">
         <is>
-          <t>M8-17</t>
+          <t>M8-16</t>
         </is>
       </c>
       <c r="D142" s="7" t="inlineStr">
@@ -10647,7 +10643,7 @@
       </c>
       <c r="E142" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=弓（跳过条件：身上有弓）、箭（直到 身上的箭 ≥ 64）) → take_from_chest(东西=圆石；直到 身上的圆石 ≥ 128) → take_from_chest(东西=口粮，从粮箱拿，留底 9（打开箱子按真数重算）；直到 身上吃的 ≥ 24) → wear_armor(末地穿法：四件最好的护甲 + 副手盾) → store_items(用不上的存掉，行李清单上的留着；直到 背包空格 ≥ 6)</t>
+          <t>take_from_chest(东西=末地水晶 4) → goto_place(地方=要塞末地门；跳过条件：当前维度 = 3（末地）) → use_portal(进末地；跳过条件：当前维度 = 3) → respawn_dragon(4 个水晶放在中间返回门的四边)</t>
         </is>
       </c>
       <c r="F142" s="7" t="inlineStr">
@@ -10664,12 +10660,12 @@
     <row r="143">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>J-M8-17b</t>
+          <t>J-M8-17a</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
         <is>
-          <t>走到要塞，穿门进末地，先射掉柱子上的末地水晶，再趁龙落到中间时打它，打完从中间的门回家。</t>
+          <t>进末地前在家收拾：拿上弓和 64 支箭、128 块圆石和 24 个吃的，换回四件铁甲。</t>
         </is>
       </c>
       <c r="C143" s="7" t="inlineStr">
@@ -10684,7 +10680,7 @@
       </c>
       <c r="E143" s="7" t="inlineStr">
         <is>
-          <t>goto_place(地方=要塞末地门（长距离，寻路不许挖）；跳过条件：当前维度 = 3) → use_portal(进末地；跳过条件：当前维度 = 3) → dragon_fight(先看平台要不要搭路；射水晶，笼子里的垫高去打；趁龙落地近身打；不看末影人；血 ≤ 8 先吃，≤ 6 传送回家) → use_portal(龙死后走中间的返回门回主世界，回应结束字幕；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → store_items</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → take_from_chest(东西=弓（跳过条件：身上有弓）、箭（直到 身上的箭 ≥ 64）) → take_from_chest(东西=圆石；直到 身上的圆石 ≥ 128) → take_from_chest(东西=口粮，从粮箱拿，留底 9（打开箱子按真数重算）；直到 身上吃的 ≥ 24) → wear_armor(末地穿法：四件最好的护甲 + 副手盾) → store_items(用不上的存掉，行李清单上的留着；直到 背包空格 ≥ 6)</t>
         </is>
       </c>
       <c r="F143" s="7" t="inlineStr">
@@ -10701,17 +10697,17 @@
     <row r="144">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>J-T0-1</t>
+          <t>J-M8-17b</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
         <is>
-          <t>小麦零候选时的兜底：回家核对箱子、把东西存好，在家等 1 分钟再重算。</t>
+          <t>走到要塞，穿门进末地，先射掉柱子上的末地水晶，再趁龙落到中间时打它，打完从中间的门回家。</t>
         </is>
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
-          <t>T0</t>
+          <t>M8-17</t>
         </is>
       </c>
       <c r="D144" s="7" t="inlineStr">
@@ -10721,7 +10717,7 @@
       </c>
       <c r="E144" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → check_chest(只打开看、不拿；核对完先重算一次候选，有了就结束兜底；跳过条件：开箱快照距今秒数 ≤ 600) → store_items(跳过条件：可存的东西 = 0) → idle(60 秒，然后重算候选)</t>
+          <t>goto_place(地方=要塞末地门（长距离，寻路不许挖）；跳过条件：当前维度 = 3) → use_portal(进末地；跳过条件：当前维度 = 3) → dragon_fight(先看平台要不要搭路；射水晶，笼子里的垫高去打；趁龙落地近身打；不看末影人；血 ≤ 8 先吃，≤ 6 传送回家) → use_portal(龙死后走中间的返回门回主世界，回应结束字幕；跳过条件：当前维度 = 0) → go_home(跳过条件：离家距离 ≤ 8) → store_items</t>
         </is>
       </c>
       <c r="F144" s="7" t="inlineStr">
@@ -10738,12 +10734,12 @@
     <row r="145">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t>J-T0-2</t>
+          <t>J-T0-1</t>
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr">
         <is>
-          <t>麦娘零候选时的兜底：回家核对两口箱子，把身上的小麦做成面包、东西存好，在家等 1 分钟再重算。</t>
+          <t>小麦零候选时的兜底：回家核对箱子、把东西存好，在家等 1 分钟再重算。</t>
         </is>
       </c>
       <c r="C145" s="7" t="inlineStr">
@@ -10753,12 +10749,12 @@
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>麦娘</t>
+          <t>小麦</t>
         </is>
       </c>
       <c r="E145" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 8) → check_chest(大箱子和粮箱只看不拿；跳过条件：开箱快照距今秒数 ≤ 600) → craft(东西=bread；跳过条件：有小麦 ≤ 2) → store_crop(跳过条件：能存粮 = 0) → store_items(跳过条件：可存的东西 = 0) → idle(60 秒，然后重算候选)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → check_chest(只打开看、不拿；核对完先重算一次候选，有了就结束兜底；跳过条件：开箱快照距今秒数 ≤ 600) → store_items(跳过条件：可存的东西 = 0) → idle(60 秒，然后重算候选)</t>
         </is>
       </c>
       <c r="F145" s="7" t="inlineStr">
@@ -10775,12 +10771,12 @@
     <row r="146">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>J-T0-3</t>
+          <t>J-T0-2</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
         <is>
-          <t>麦豆零候选时的兜底：回家门口、离真人远的地方玩一会儿（天黑就待在屋里），30 秒后重算。</t>
+          <t>麦娘零候选时的兜底：回家核对两口箱子，把身上的小麦做成面包、东西存好，在家等 1 分钟再重算。</t>
         </is>
       </c>
       <c r="C146" s="7" t="inlineStr">
@@ -10790,12 +10786,12 @@
       </c>
       <c r="D146" s="7" t="inlineStr">
         <is>
-          <t>麦豆</t>
+          <t>麦娘</t>
         </is>
       </c>
       <c r="E146" s="7" t="inlineStr">
         <is>
-          <t>go_home(跳过条件：离家距离 ≤ 16) → wander(家门口 16 格内；跳过条件：天黑了 = 1 或 血量 ≤ 15 或 离最近真人玩家距离 ≤ 24) → idle(30 秒，然后重算候选)</t>
+          <t>go_home(跳过条件：离家距离 ≤ 8) → check_chest(大箱子和粮箱只看不拿；跳过条件：开箱快照距今秒数 ≤ 600) → craft(东西=bread；跳过条件：有小麦 ≤ 2) → store_crop(跳过条件：能存粮 = 0) → store_items(跳过条件：可存的东西 = 0) → idle(60 秒，然后重算候选)</t>
         </is>
       </c>
       <c r="F146" s="7" t="inlineStr">
@@ -10805,32 +10801,36 @@
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
-          <t>缺判据</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>J-T1-1</t>
+          <t>J-T0-3</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
         <is>
-          <t>把这一档能做的几件活连同全家现状交给模型，让它排个先后，然后照这个顺序一件件开工。</t>
+          <t>麦豆零候选时的兜底：回家门口、离真人远的地方玩一会儿（天黑就待在屋里），30 秒后重算。</t>
         </is>
       </c>
       <c r="C147" s="7" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T0</t>
         </is>
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>全家</t>
-        </is>
-      </c>
-      <c r="E147" s="7" t="inlineStr"/>
+          <t>麦豆</t>
+        </is>
+      </c>
+      <c r="E147" s="7" t="inlineStr">
+        <is>
+          <t>go_home(跳过条件：离家距离 ≤ 16) → wander(家门口 16 格内；跳过条件：天黑了 = 1 或 血量 ≤ 15 或 离最近真人玩家距离 ≤ 24) → idle(30 秒，然后重算候选)</t>
+        </is>
+      </c>
       <c r="F147" s="7" t="inlineStr">
         <is>
           <t>新写</t>
@@ -10838,24 +10838,24 @@
       </c>
       <c r="G147" s="7" t="inlineStr">
         <is>
-          <t>判据动作都缺</t>
+          <t>缺判据</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>J-T1-2</t>
+          <t>J-T1-1</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
         <is>
-          <t>把连败的那件活、失败原话和这个小目标剩下的办法交给模型，让它只回一个编号，然后换那条做。</t>
+          <t>把这一档能做的几件活连同全家现状交给模型，让它排个先后，然后照这个顺序一件件开工。</t>
         </is>
       </c>
       <c r="C148" s="7" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D148" s="7" t="inlineStr">
@@ -10878,17 +10878,17 @@
     <row r="149">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>J-T8</t>
+          <t>J-T1-2</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
         <is>
-          <t>「做同一件小目标时、30 分钟内因为同一种原因死了两次：饿死、…」这条触发的脚本</t>
+          <t>把连败的那件活、失败原话和这个小目标剩下的办法交给模型，让它只回一个编号，然后换那条做。</t>
         </is>
       </c>
       <c r="C149" s="7" t="inlineStr">
         <is>
-          <t>T8</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D149" s="7" t="inlineStr">
@@ -10896,11 +10896,7 @@
           <t>全家</t>
         </is>
       </c>
-      <c r="E149" s="7" t="inlineStr">
-        <is>
-          <t>(代码)收集候选(按这条触发的规则算出所有可选项) → (代码)只有 0 或 1 个候选(直接由代码决定,不问模型) → ask_model(≥2 个候选时问一次,只许回候选编号) → (代码)执行选中的那一项(问不到或超时:代码按固定规则兜底,不卡住)</t>
-        </is>
-      </c>
+      <c r="E149" s="7" t="inlineStr"/>
       <c r="F149" s="7" t="inlineStr">
         <is>
           <t>新写</t>
@@ -10908,24 +10904,24 @@
       </c>
       <c r="G149" s="7" t="inlineStr">
         <is>
-          <t>缺动作</t>
+          <t>判据动作都缺</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>J-T10</t>
+          <t>J-T8</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr">
         <is>
-          <t>「您（Owner）在游戏里点名叫它做某件事时，代码…」这条触发的脚本</t>
+          <t>「做同一件小目标时、30 分钟内因为同一种原因死了两次：饿死、…」这条触发的脚本</t>
         </is>
       </c>
       <c r="C150" s="7" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T8</t>
         </is>
       </c>
       <c r="D150" s="7" t="inlineStr">
@@ -10952,17 +10948,17 @@
     <row r="151">
       <c r="A151" s="7" t="inlineStr">
         <is>
-          <t>J-T11</t>
+          <t>J-T10</t>
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr">
         <is>
-          <t>「房子盖好以后，如果有两种以上合法的家具摆法（比如床靠北墙还是…」这条触发的脚本</t>
+          <t>「您（Owner）在游戏里点名叫它做某件事时，代码…」这条触发的脚本</t>
         </is>
       </c>
       <c r="C151" s="7" t="inlineStr">
         <is>
-          <t>T11</t>
+          <t>T10</t>
         </is>
       </c>
       <c r="D151" s="7" t="inlineStr">
@@ -10989,27 +10985,27 @@
     <row r="152">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t>child_make_leather_tunic</t>
+          <t>J-T11</t>
         </is>
       </c>
       <c r="B152" s="7" t="inlineStr">
         <is>
-          <t>麦豆用箱子里 8 张皮革给自己做一件皮衣</t>
+          <t>「房子盖好以后，如果有两种以上合法的家具摆法（比如床靠北墙还是…」这条触发的脚本</t>
         </is>
       </c>
       <c r="C152" s="7" t="inlineStr">
         <is>
-          <t>M5-7</t>
+          <t>T11</t>
         </is>
       </c>
       <c r="D152" s="7" t="inlineStr">
         <is>
-          <t>麦豆</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="E152" s="7" t="inlineStr">
         <is>
-          <t>go_home → take_from_chest(皮革) → craft(leather_chestplate)</t>
+          <t>(代码)收集候选(按这条触发的规则算出所有可选项) → (代码)只有 0 或 1 个候选(直接由代码决定,不问模型) → ask_model(≥2 个候选时问一次,只许回候选编号) → (代码)执行选中的那一项(问不到或超时:代码按固定规则兜底,不卡住)</t>
         </is>
       </c>
       <c r="F152" s="7" t="inlineStr">
@@ -11019,34 +11015,34 @@
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
-          <t>缺判据/动作(代码刀)</t>
+          <t>缺动作</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t>make_diamond_sword</t>
+          <t>child_make_leather_tunic</t>
         </is>
       </c>
       <c r="B153" s="7" t="inlineStr">
         <is>
-          <t>用家里箱子的 2 颗钻石给自己做一把钻石剑</t>
+          <t>麦豆用箱子里 8 张皮革给自己做一件皮衣</t>
         </is>
       </c>
       <c r="C153" s="7" t="inlineStr">
         <is>
-          <t>M5-6</t>
+          <t>M5-7</t>
         </is>
       </c>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>全家</t>
+          <t>麦豆</t>
         </is>
       </c>
       <c r="E153" s="7" t="inlineStr">
         <is>
-          <t>go_home → take_from_chest(钻石) → take_from_chest(木棍) → craft(diamond_sword)</t>
+          <t>go_home → take_from_chest(皮革) → craft(leather_chestplate)</t>
         </is>
       </c>
       <c r="F153" s="7" t="inlineStr">
@@ -11063,23 +11059,27 @@
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t>think_goal_order</t>
+          <t>make_diamond_sword</t>
         </is>
       </c>
       <c r="B154" s="7" t="inlineStr">
         <is>
-          <t>问模型给同档大目标排先后或并行</t>
+          <t>用家里箱子的 2 颗钻石给自己做一把钻石剑</t>
         </is>
       </c>
       <c r="C154" s="7" t="inlineStr">
         <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="D154" s="7" t="inlineStr"/>
+          <t>M5-6</t>
+        </is>
+      </c>
+      <c r="D154" s="7" t="inlineStr">
+        <is>
+          <t>全家</t>
+        </is>
+      </c>
       <c r="E154" s="7" t="inlineStr">
         <is>
-          <t>ask_model(同档可开工的 G 编号)</t>
+          <t>go_home → take_from_chest(钻石) → take_from_chest(木棍) → craft(diamond_sword)</t>
         </is>
       </c>
       <c r="F154" s="7" t="inlineStr">
@@ -11089,30 +11089,30 @@
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
-          <t>缺动作</t>
+          <t>缺判据/动作(代码刀)</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
         <is>
-          <t>think_home_site</t>
+          <t>think_goal_order</t>
         </is>
       </c>
       <c r="B155" s="7" t="inlineStr">
         <is>
-          <t>问模型选新家址</t>
+          <t>问模型给同档大目标排先后或并行</t>
         </is>
       </c>
       <c r="C155" s="7" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D155" s="7" t="inlineStr"/>
       <c r="E155" s="7" t="inlineStr">
         <is>
-          <t>ask_model(候选家址编号 + 打分明细)</t>
+          <t>ask_model(同档可开工的 G 编号)</t>
         </is>
       </c>
       <c r="F155" s="7" t="inlineStr">
@@ -11129,23 +11129,23 @@
     <row r="156">
       <c r="A156" s="7" t="inlineStr">
         <is>
-          <t>think_house_design</t>
+          <t>think_home_site</t>
         </is>
       </c>
       <c r="B156" s="7" t="inlineStr">
         <is>
-          <t>问模型选房子方案</t>
+          <t>问模型选新家址</t>
         </is>
       </c>
       <c r="C156" s="7" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D156" s="7" t="inlineStr"/>
       <c r="E156" s="7" t="inlineStr">
         <is>
-          <t>ask_model(代码列出的方案编号)</t>
+          <t>ask_model(候选家址编号 + 打分明细)</t>
         </is>
       </c>
       <c r="F156" s="7" t="inlineStr">
@@ -11162,23 +11162,23 @@
     <row r="157">
       <c r="A157" s="7" t="inlineStr">
         <is>
-          <t>think_pick_task</t>
+          <t>think_house_design</t>
         </is>
       </c>
       <c r="B157" s="7" t="inlineStr">
         <is>
-          <t>(已并入 J-T1-1)问模型给同档小目标排先后</t>
+          <t>问模型选房子方案</t>
         </is>
       </c>
       <c r="C157" s="7" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D157" s="7" t="inlineStr"/>
       <c r="E157" s="7" t="inlineStr">
         <is>
-          <t>ask_model(同档候选编号;默认=最久没做的)</t>
+          <t>ask_model(代码列出的方案编号)</t>
         </is>
       </c>
       <c r="F157" s="7" t="inlineStr">
@@ -11195,23 +11195,23 @@
     <row r="158">
       <c r="A158" s="7" t="inlineStr">
         <is>
-          <t>think_reply</t>
+          <t>think_pick_task</t>
         </is>
       </c>
       <c r="B158" s="7" t="inlineStr">
         <is>
-          <t>被点名时写一句回话,并从 3 个选项里挑一个</t>
+          <t>(已并入 J-T1-1)问模型给同档小目标排先后</t>
         </is>
       </c>
       <c r="C158" s="7" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D158" s="7" t="inlineStr"/>
       <c r="E158" s="7" t="inlineStr">
         <is>
-          <t>ask_model(回话 + 选项:只回话/跟他走/不理) → say(模型写的那句) → follow_player(只在选了「跟他走」时;最多 120 秒)</t>
+          <t>ask_model(同档候选编号;默认=最久没做的)</t>
         </is>
       </c>
       <c r="F158" s="7" t="inlineStr">
@@ -11228,27 +11228,23 @@
     <row r="159">
       <c r="A159" s="7" t="inlineStr">
         <is>
-          <t>wife_logs_to_planks</t>
+          <t>think_reply</t>
         </is>
       </c>
       <c r="B159" s="7" t="inlineStr">
         <is>
-          <t>麦娘从箱子拿原木做成 8 块同种木板(缺锄头或没地方存粮时)</t>
+          <t>被点名时写一句回话,并从 3 个选项里挑一个</t>
         </is>
       </c>
       <c r="C159" s="7" t="inlineStr">
         <is>
-          <t>M1-1</t>
-        </is>
-      </c>
-      <c r="D159" s="7" t="inlineStr">
-        <is>
-          <t>麦娘</t>
-        </is>
-      </c>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="D159" s="7" t="inlineStr"/>
       <c r="E159" s="7" t="inlineStr">
         <is>
-          <t>go_home → store_items → take_from_chest(原木) → craft(planks) → craft(planks)</t>
+          <t>ask_model(回话 + 选项:只回话/跟他走/不理) → say(模型写的那句) → follow_player(只在选了「跟他走」时;最多 120 秒)</t>
         </is>
       </c>
       <c r="F159" s="7" t="inlineStr">
@@ -11258,42 +11254,79 @@
       </c>
       <c r="G159" s="7" t="inlineStr">
         <is>
-          <t>缺判据/动作(代码刀)</t>
+          <t>缺动作</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="7" t="inlineStr">
         <is>
+          <t>wife_logs_to_planks</t>
+        </is>
+      </c>
+      <c r="B160" s="7" t="inlineStr">
+        <is>
+          <t>麦娘从箱子拿原木做成 8 块同种木板(缺锄头或没地方存粮时)</t>
+        </is>
+      </c>
+      <c r="C160" s="7" t="inlineStr">
+        <is>
+          <t>M1-1</t>
+        </is>
+      </c>
+      <c r="D160" s="7" t="inlineStr">
+        <is>
+          <t>麦娘</t>
+        </is>
+      </c>
+      <c r="E160" s="7" t="inlineStr">
+        <is>
+          <t>go_home → store_items → take_from_chest(原木) → craft(planks) → craft(planks)</t>
+        </is>
+      </c>
+      <c r="F160" s="7" t="inlineStr">
+        <is>
+          <t>新写</t>
+        </is>
+      </c>
+      <c r="G160" s="7" t="inlineStr">
+        <is>
+          <t>缺判据/动作(代码刀)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="7" t="inlineStr">
+        <is>
           <t>wife_make_iron_helmet</t>
         </is>
       </c>
-      <c r="B160" s="7" t="inlineStr">
+      <c r="B161" s="7" t="inlineStr">
         <is>
           <t>麦娘用箱子里 5 个铁锭给自己做一个铁头盔</t>
         </is>
       </c>
-      <c r="C160" s="7" t="inlineStr">
+      <c r="C161" s="7" t="inlineStr">
         <is>
           <t>M5-7</t>
         </is>
       </c>
-      <c r="D160" s="7" t="inlineStr">
+      <c r="D161" s="7" t="inlineStr">
         <is>
           <t>麦娘</t>
         </is>
       </c>
-      <c r="E160" s="7" t="inlineStr">
+      <c r="E161" s="7" t="inlineStr">
         <is>
           <t>go_home → take_from_chest(铁锭) → craft(iron_helmet)</t>
         </is>
       </c>
-      <c r="F160" s="7" t="inlineStr">
+      <c r="F161" s="7" t="inlineStr">
         <is>
           <t>新写</t>
         </is>
       </c>
-      <c r="G160" s="7" t="inlineStr">
+      <c r="G161" s="7" t="inlineStr">
         <is>
           <t>缺判据/动作(代码刀)</t>
         </is>
@@ -21405,7 +21438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E554"/>
+  <dimension ref="A1:E564"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -36350,6 +36383,276 @@
       <c r="E554" s="7" t="inlineStr">
         <is>
           <t>fork 1 查实(2026-09-18):小麦从没封好的屋顶洞掉进屋里(「在不在屋里」只看平面);洞那一列在孩子的领地里,服务器拒了 379 次,程序从不划掉</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B555" s="7" t="inlineStr">
+        <is>
+          <t>M1-2</t>
+        </is>
+      </c>
+      <c r="C555" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D555" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 开田要留走道(每格离能站的地方 ≤3 格)</t>
+        </is>
+      </c>
+      <c r="E555" s="7" t="inlineStr">
+        <is>
+          <t>平级会话 RCON 实测麦娘两格耕地被围、够不着</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B556" s="7" t="inlineStr">
+        <is>
+          <t>M1-7</t>
+        </is>
+      </c>
+      <c r="C556" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D556" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 开田要留走道(每格离能站的地方 ≤3 格)</t>
+        </is>
+      </c>
+      <c r="E556" s="7" t="inlineStr">
+        <is>
+          <t>平级会话 RCON 实测麦娘两格耕地被围、够不着</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B557" s="7" t="inlineStr">
+        <is>
+          <t>J-M1-7</t>
+        </is>
+      </c>
+      <c r="C557" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D557" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 开田要留走道(每格离能站的地方 ≤3 格)</t>
+        </is>
+      </c>
+      <c r="E557" s="7" t="inlineStr">
+        <is>
+          <t>平级会话 RCON 实测麦娘两格耕地被围、够不着</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B558" s="7" t="inlineStr">
+        <is>
+          <t>J-M1-7b</t>
+        </is>
+      </c>
+      <c r="C558" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D558" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 开田要留走道(每格离能站的地方 ≤3 格)</t>
+        </is>
+      </c>
+      <c r="E558" s="7" t="inlineStr">
+        <is>
+          <t>平级会话 RCON 实测麦娘两格耕地被围、够不着</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B559" s="7" t="inlineStr">
+        <is>
+          <t>M3-3</t>
+        </is>
+      </c>
+      <c r="C559" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D559" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 加放方块硬约束 ⑨:自家箱子正上方永远空着</t>
+        </is>
+      </c>
+      <c r="E559" s="7" t="inlineStr">
+        <is>
+          <t>CoreProtect 实测箱子头顶被压住后全家开箱失败</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B560" s="7" t="inlineStr">
+        <is>
+          <t>M3-4</t>
+        </is>
+      </c>
+      <c r="C560" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D560" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 加放方块硬约束 ⑨:自家箱子正上方永远空着</t>
+        </is>
+      </c>
+      <c r="E560" s="7" t="inlineStr">
+        <is>
+          <t>CoreProtect 实测箱子头顶被压住后全家开箱失败</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B561" s="7" t="inlineStr">
+        <is>
+          <t>M3-6</t>
+        </is>
+      </c>
+      <c r="C561" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D561" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 加放方块硬约束 ⑨:自家箱子正上方永远空着</t>
+        </is>
+      </c>
+      <c r="E561" s="7" t="inlineStr">
+        <is>
+          <t>CoreProtect 实测箱子头顶被压住后全家开箱失败</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B562" s="7" t="inlineStr">
+        <is>
+          <t>M2-3</t>
+        </is>
+      </c>
+      <c r="C562" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D562" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 加放方块硬约束 ⑨:自家箱子正上方永远空着</t>
+        </is>
+      </c>
+      <c r="E562" s="7" t="inlineStr">
+        <is>
+          <t>CoreProtect 实测箱子头顶被压住后全家开箱失败</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B563" s="7" t="inlineStr">
+        <is>
+          <t>A16</t>
+        </is>
+      </c>
+      <c r="C563" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D563" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 加放方块硬约束 ⑨:自家箱子正上方永远空着</t>
+        </is>
+      </c>
+      <c r="E563" s="7" t="inlineStr">
+        <is>
+          <t>CoreProtect 实测箱子头顶被压住后全家开箱失败</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B564" s="7" t="inlineStr">
+        <is>
+          <t>M4-3</t>
+        </is>
+      </c>
+      <c r="C564" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D564" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] 加放方块硬约束 ⑨:自家箱子正上方永远空着</t>
+        </is>
+      </c>
+      <c r="E564" s="7" t="inlineStr">
+        <is>
+          <t>CoreProtect 实测箱子头顶被压住后全家开箱失败</t>
         </is>
       </c>
     </row>

--- a/ai-player/goal-table/小麦家族工作分解-填写版.xlsx
+++ b/ai-player/goal-table/小麦家族工作分解-填写版.xlsx
@@ -1644,7 +1644,7 @@
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>⑨ 自家箱子正上方那一格永远空着,不许放任何实心方块 —— MC 规则:箱子头顶有实心方块就打不开(2026-09-18 17:13 起家里那口箱子被压住,三个人开箱全部失败)。 🔴 放方块硬约束(补充):④「在不在屋里 / 在不在盖房的位置」必须连高度一起算,站在屋顶上不算在屋里,不许从没封好的屋顶洞穿过;⑤ 门洞那一列永远空着,什么都不许放(包括会掉下来填进去的方块);⑥ 盖房材料排除会下落的方块(沙子、红沙、沙砾、各色混凝土粉末、铁砧等),没有别的材料就不盖;⑦ 服务器拒绝过的格子永久划掉,房子可以算「完成(跳过 N 格)」,否则脚本会一直把人派回去;⑧ 开工前先查目标格在不在别人的领地里,在就标「这里做不了」、不去试。麦家现在没有任何领地(Owner 定的),所以【任何领地都是别人的】—— 数据来源待定:服务器拒绝记录,或后台导出领地范围。 🔴 盖房硬约束(2026-09-18 实测小麦被自己的房子关住,20 分钟失败 110 次):① 任何一步都不许把方块放进盖房人正站的格子、头顶那格和门洞;② 每放一块之前,代码先算「放完以后我还走得出去吗」(站的格子到屋外有通路),走不出去就先走出去再放;③ 同一块连着被服务器拒绝 3 次,就换下一块或收工,不原地重试。这三条由代码判断,不问模型。 ⏳ 过渡:搬家(拍板第 1 件)定之前,挂在这里的 build_house / get_build_mats / son_take_mats 仍在现在的家把房子盖完(线上老行为,不倒退);定了搬以后改成在新家址盖。 门是 2 格高的物品，要点门洞下面那块地面的顶面放，朝向跟人的朝向走。墙的判定只看实心不实心，不看方块名（泥土长成草那次的教训）。站位必须站在墙格以外的格子上，不能用「离中心多远」来判断。僵尸自己开不了木门。</t>
+          <t>✅ Owner 定(2026-09-18 傍晚):现在这间房「就这样算盖完了」—— 选项原文「屋顶留一个小洞。小麦不再去补那一块,也不会再掉进去卡住。完全不碰 某个孩子 的地,也不用跟孩子打招呼。」屋顶 (-17,65,161)/(-17,65,162) 两格整块在孩子的领地里 → 算「完成(跳过 2 格)」。这只定了「不补最后两格」,搬不搬家(拍板 1)、旧房和地上的木头怎么办(拍板 2、M3-9)仍然待定。 ⑨ 自家箱子正上方那一格永远空着,不许放任何实心方块 —— MC 规则:箱子头顶有实心方块就打不开(2026-09-18 17:13 起家里那口箱子被压住,三个人开箱全部失败)。 🔴 放方块硬约束(补充):④「在不在屋里 / 在不在盖房的位置」必须连高度一起算,站在屋顶上不算在屋里,不许从没封好的屋顶洞穿过;⑤ 门洞那一列永远空着,什么都不许放(包括会掉下来填进去的方块);⑥ 盖房材料排除会下落的方块(沙子、红沙、沙砾、各色混凝土粉末、铁砧等),没有别的材料就不盖;⑦ 服务器拒绝过的格子永久划掉,房子可以算「完成(跳过 N 格)」,否则脚本会一直把人派回去;⑧ 开工前先查目标格在不在别人的领地里,在就标「这里做不了」、不去试。麦家现在没有任何领地(Owner 定的),所以【任何领地都是别人的】—— 数据来源待定:服务器拒绝记录,或后台导出领地范围。 🔴 盖房硬约束(2026-09-18 实测小麦被自己的房子关住,20 分钟失败 110 次):① 任何一步都不许把方块放进盖房人正站的格子、头顶那格和门洞;② 每放一块之前,代码先算「放完以后我还走得出去吗」(站的格子到屋外有通路),走不出去就先走出去再放;③ 同一块连着被服务器拒绝 3 次,就换下一块或收工,不原地重试。这三条由代码判断,不问模型。 ⏳ 过渡:搬家(拍板第 1 件)定之前,挂在这里的 build_house / get_build_mats / son_take_mats 仍在现在的家把房子盖完(线上老行为,不倒退);定了搬以后改成在新家址盖。 门是 2 格高的物品，要点门洞下面那块地面的顶面放，朝向跟人的朝向走。墙的判定只看实心不实心，不看方块名（泥土长成草那次的教训）。站位必须站在墙格以外的格子上，不能用「离中心多远」来判断。僵尸自己开不了木门。</t>
         </is>
       </c>
     </row>
@@ -4208,7 +4208,7 @@
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>实测:这条自救以前 40 次成功 35 次(61~164 秒内拉出来);05:17 JST 零候选兜底上线后,兜底每一拍都把「卡住计时」清零,40 分钟里 0 次触发,小麦被自己的房子关住出不来。fork 1 查实(2026-09-18):小麦从没封好的屋顶洞掉进屋里(「在不在屋里」只看平面);洞那一列在孩子的领地里,服务器拒了 379 次,程序从不划掉被拒的格子;门口一列疑被下落的沙堵住;零候选兜底每拍清零「卡住计时」,75 秒自救从 05:17 起再没触发(之前 40 次成 35 次);睡觉挑最近的床,挑中了孩子领地里孩子的床。</t>
+          <t>实测:这条自救以前 40 次成功 35 次(61~164 秒内拉出来);05:17 JST 零候选兜底上线后,兜底每一拍都把「卡住计时」清零,40 分钟里 0 次触发,小麦被自己的房子关住出不来。fork 1 查实(2026-09-18):小麦从没封好的屋顶洞掉进屋里(「在不在屋里」只看平面);洞那一列在孩子的领地里,服务器拒了 379 次,程序从不划掉被拒的格子;下落的沙子落在他站的 (-17,63,161)(RCON 查过门口一列是空的,原先「门口被沙堵住」的推断是错的),寻路为什么走不出去还没查清;零候选兜底每拍清零「卡住计时」,75 秒自救从 05:17 起再没触发(之前 40 次成 35 次);睡觉挑最近的床,挑中了孩子领地里孩子的床。</t>
         </is>
       </c>
     </row>
@@ -20775,7 +20775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -21427,6 +21427,27 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>小麦现在那间房,屋顶最后 2 格在一个孩子的领地里,补不上,怎么办?</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr"/>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>已定(2026-09-18 傍晚):「就这样算盖完了」—— 屋顶留一个小洞,小麦不再去补,完全不碰孩子的地,也不用跟孩子打招呼。搬家和旧房仍待定。</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>第三轮·小麦被困(fork 1 会话问的)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21438,7 +21459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E564"/>
+  <dimension ref="A1:E565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -36653,6 +36674,33 @@
       <c r="E564" s="7" t="inlineStr">
         <is>
           <t>CoreProtect 实测箱子头顶被压住后全家开箱失败</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="7" t="inlineStr">
+        <is>
+          <t>第三轮修表</t>
+        </is>
+      </c>
+      <c r="B565" s="7" t="inlineStr">
+        <is>
+          <t>M3-3</t>
+        </is>
+      </c>
+      <c r="C565" s="7" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="D565" s="7" t="inlineStr">
+        <is>
+          <t>[第三轮] Owner 定:现在的房子就这样算盖完了(跳过孩子领地里的 2 格屋顶)</t>
+        </is>
+      </c>
+      <c r="E565" s="7" t="inlineStr">
+        <is>
+          <t>搬家、旧房仍待定</t>
         </is>
       </c>
     </row>
